--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 37.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 37.xlsx
@@ -526,8 +526,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -570,7 +568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -674,8 +672,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -705,6 +701,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-135.9400000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.1836e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-70.553</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.02930056710776019</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.6405990016638455</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.589749702026103</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.824793388429707</v>
+      </c>
+      <c r="J2" t="n">
+        <v>9.432026888864842</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.45957009787902</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 12.593x + -27042.640</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>7.82174430945274e-08</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2455.265262115215</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000002501e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8185226366895402</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-106.1700000000001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.2176e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-71.649</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.480022701475612</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.048488372092987</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.747043701799433</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.381683168316887</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.63132537760877</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 13.090x + -26524.848</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>5.421866676084226e-08</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2339.950276312656</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000000162e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8186999632410487</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-105.2900000000002</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.22401e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-72</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.09793814432989037</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.7197236180904809</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.607972027971993</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.164204923486249</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>85.4876478688723</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 12.671x + -25166.402</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.089600563549254e-09</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2300.817529950784</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000000091e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8187320914830568</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-92.4699999999998</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.22896e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-72.30200000000001</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.4296296296296545</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.187945670628036</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.814352941176516</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.303811659192842</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>84.84286460311084</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 11.080x + -21632.250</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>3.547081525494212e-12</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2274.467984741103</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8187874920412548</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-100.3099999999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.23227e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-72.473</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1950216702447615</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.7518172918802845</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.914725219686896</v>
+      </c>
+      <c r="I6" t="n">
+        <v>198.3639554685594</v>
+      </c>
+      <c r="J6" t="n">
+        <v>10.22460720698108</v>
+      </c>
+      <c r="K6" t="n">
+        <v>84.7323776488215</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 10.846x + -20927.315</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.519006579676908e-10</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2250.89898729645</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000003463e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8189090153561743</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-90.6099999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.23436e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-72.694</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.06501597444090429</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.9289377289377438</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.194461228600265</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>84.59105134495663</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 10.561x + -20154.181</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>7.422382637472134e-09</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2227.315017743516</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.00000000000006e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8190829829546588</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-83.95000000000005</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.23665e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-72.852</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.7691810344827577</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.4347941567064756</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.845958986731119</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.497112462006142</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>84.90403921391294</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 11.214x + -21251.371</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>5.054772902839284e-11</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2204.953974872117</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8192748780869882</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-82.73000000000002</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.2409e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-73.06100000000001</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1756676557863458</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.9686885245901828</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.019999999999881</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.240888382687974</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>84.33061355650793</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 10.073x + -18808.393</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>6.426184467443721e-10</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2182.927240455587</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000000414e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8195096820379845</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-75.68999999999983</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.24155e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-73.24299999999999</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.3970967741935599</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.8061988304093648</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.824253285543583</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.315241057542936</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>84.13571377470832</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 9.736x + -17977.213</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.505208771916953e-08</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2161.994632413858</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8197443557903424</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-78.76999999999998</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.24609e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-73.43300000000001</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1106759985996982</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.8184413038333375</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.833500934192491</v>
+      </c>
+      <c r="I11" t="n">
+        <v>144.9482804417476</v>
+      </c>
+      <c r="J11" t="n">
+        <v>12.15869700766287</v>
+      </c>
+      <c r="K11" t="n">
+        <v>83.62693198340274</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 8.953x + -16308.549</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>4.609727969716513e-08</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2141.491163647627</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000000093e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8199968971700398</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-72.99000000000001</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.24895e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-73.559</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.3702647657840789</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.143052837573473</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.8790804597700728</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.021743486973854</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>83.83798892062528</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 9.262x + -16752.711</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.97940369360391e-10</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2122.427144644078</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.000000000018457e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8202403327258045</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-68.1400000000001</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.25169e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-73.732</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.2877232142856614</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.405994550408705</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.50575539568316</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.936387434555119</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>83.20322023117525</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 8.390x + -14960.873</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.452407163255564e-10</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2103.396953553567</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8205032402107246</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-70.96000000000004</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.25313e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-73.881</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.3714269366830515</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.8503673459096406</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.043658230434645</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>12.98579330606225</v>
+      </c>
+      <c r="K14" t="n">
+        <v>83.31039133485693</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 8.526x + -15087.396</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>5.31530856367991e-08</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2084.708174013747</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.000000000003199e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8207675303493057</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-63.87000000000012</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.25514e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-74.036</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.6510152284263235</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.9631118881119339</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.31041666666649</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.234974358974374</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>82.77205570185487</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 7.885x + -13762.451</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.631295866833511e-08</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2066.81775251792</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.000000000000053e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8210534225163004</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-57.23000000000002</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.25865e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-74.211</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.5440170940171065</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.936247334754709</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.6707732634339</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.454852780806948</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>81.37261339886355</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 6.591x + -11265.956</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>7.345875151367063e-08</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2048.792832840928</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.000000000000946e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8213242656865217</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-55.64999999999986</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.25957e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-74.35599999999999</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.5098619329389125</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.7420062695924973</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.044923504867866</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.340714285714211</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>81.0653623008742</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 6.361x + -10747.536</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>225.4520561701192</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2039.051996498125</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.510715789863713e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8103600764440296</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-57.11999999999989</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.26299e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-74.477</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.4613285426200271</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.7398772601394012</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.99555212535027</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>13.81502638564219</v>
+      </c>
+      <c r="K18" t="n">
+        <v>81.44626384795927</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 6.648x + -11194.779</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.014639549571414e-08</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2013.7784627959</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8218891946936643</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-55.14999999999986</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.26416e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-74.639</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.2898748790101046</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.269621472933257</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.244571369077356</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>14.74319502199522</v>
+      </c>
+      <c r="K19" t="n">
+        <v>80.34224241284748</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 5.876x + -9714.786</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>9.581678617117404e-09</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1996.461483575034</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8221769445101934</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-50.51999999999998</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.26689e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-74.783</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.3332374905675237</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.107963636104315</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.289249762274023</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>14.88771675382138</v>
+      </c>
+      <c r="K20" t="n">
+        <v>79.69222702606045</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 5.498x + -8955.315</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>5.375682099186868e-08</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1978.463301056841</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.000000000000274e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8224584116270415</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-38.57999999999993</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.27011e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-74.971</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.2976653696498407</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.6623397435897345</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.763428571428488</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1867.049700598666</v>
+      </c>
+      <c r="J21" t="n">
+        <v>8.292286702259029</v>
+      </c>
+      <c r="K21" t="n">
+        <v>68.33184752971762</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 2.517x + -3596.283</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>2.294079101179809e-09</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1960.980244700381</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8227435059190626</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-46.54999999999995</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.27231e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-75.081</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.1556142395020361</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.9158969469020262</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.535521410276816</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>12.02037272647894</v>
+      </c>
+      <c r="K22" t="n">
+        <v>77.64371908125486</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 4.565x + -7184.518</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>3.962954813716136e-08</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1943.195022111756</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8230417856069404</v>
       </c>
     </row>
   </sheetData>
@@ -822,8 +1910,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -866,7 +1952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -970,8 +2056,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1001,6 +2085,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-350.1300000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.20003e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-63.839</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.431894484412487</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.8811166875783988</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.08922184630251</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.365713647531854</v>
+      </c>
+      <c r="J2" t="n">
+        <v>38.2566300129368</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.58749317576543</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 12.959x + -32878.982</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>3.552265266815576e-11</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2810.028019172369</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8185291862628377</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-205.3099999999999</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.29222e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-68.29300000000001</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.339083557951492</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.6986625514402766</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.613246753246833</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.484845005740534</v>
+      </c>
+      <c r="J3" t="n">
+        <v>40.84944473000199</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.33254120178223</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 15.601x + -34271.244</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>5.019998634059318e-10</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2503.763417908455</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000000003e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8193886405504134</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-140.0799999999999</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.2907e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-69.758</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.8489827856024568</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.134729981378031</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.030195258019581</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.372504302926083</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.52383344429219</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 16.462x + -34902.952</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>5.139725053026806e-08</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2425.264105437148</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.00000000000232e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8195412157595431</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-128.3699999999999</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.28409e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-70.52500000000001</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.477319587628826</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.2870216306156402</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.4399999999999719</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.570635559131069</v>
+      </c>
+      <c r="J5" t="n">
+        <v>14.57725431040487</v>
+      </c>
+      <c r="K5" t="n">
+        <v>85.47269265229681</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 12.629x + -25986.696</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.124254504031348e-09</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2384.578961884988</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000727e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.819626022323808</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-109.6400000000001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.27914e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-71.063</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.2379770992366461</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.2167682926829192</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.8632281553398714</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.256623931624028</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4.71765885319662</v>
+      </c>
+      <c r="K6" t="n">
+        <v>84.95719505833407</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 11.333x + -22901.437</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>3.18119233942094e-10</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2352.222820883977</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000000004e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.81971850671945</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-90.52999999999997</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.27454e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-71.434</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.3137404580153053</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.7694181326116535</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.798919891989181</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.65327210103329</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>85.06989948091764</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 11.593x + -23161.361</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>5.845755677649939e-09</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2321.25284060976</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000004895e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8198646601700366</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-86.07000000000016</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.27441e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-71.786</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1881212121211997</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.5490413723511688</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.054942233632748</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.331086773378218</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>84.44551878995303</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 10.283x + -20177.810</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.546946160616957e-08</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2292.428652930454</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000006078e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.820011424146474</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-83.73000000000002</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.27318e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-72.102</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.05238938053096634</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.301152737752157</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.8725058004639754</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.831724137930979</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>84.07635978635334</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 9.638x + -18618.632</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.181426989628064e-08</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2263.067685503016</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000000695e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8202095243714427</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-72.48999999999978</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.27401e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-72.398</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.532818532818521</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.265392781316305</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.261915367483245</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.32924382716062</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>83.30282229920091</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 8.516x + -16138.773</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>3.118462694968798e-11</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2235.436961411101</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8204178339387</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-63.79999999999995</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.27702e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-72.669</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.08376511226253135</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.8553914327916869</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.568986568986848</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.368965517241506</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>82.24184420943112</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 7.340x + -13616.678</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.693786795954945e-08</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2208.050817214159</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000005911e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8206528904194995</v>
       </c>
     </row>
   </sheetData>
@@ -1014,7 +2618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1118,8 +2722,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1149,6 +2751,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-335.8899999999999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.26992e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-67.372</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.4869999999999874</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.6737344794651208</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.575963718820805</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.951912811387893</v>
+      </c>
+      <c r="J2" t="n">
+        <v>26.20274229909328</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.54930609885143</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 12.848x + -27994.550</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>3.356916661256501e-10</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2452.906615047635</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8206739496801244</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-233.6299999999999</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.25966e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-69.82299999999999</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1497304582210163</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.3503177966101514</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.9553706505295381</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.72708453133978</v>
+      </c>
+      <c r="J3" t="n">
+        <v>31.23666636032365</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.93282605545672</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 14.064x + -29049.093</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>6.253085997257166e-10</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2351.907718848481</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000000007e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8208200367631943</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-192.3799999999999</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.25437e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-70.57599999999999</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.6931880108992096</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.970169851380163</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.738701923076884</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.363570391872275</v>
+      </c>
+      <c r="J4" t="n">
+        <v>40.65357220003479</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.13302842758512</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 14.794x + -30116.335</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>6.813337324920056e-08</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2315.725769299457</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000033246e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8207715042735004</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-186.5699999999997</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.24967e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-71.001</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.3458024691357947</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9166007905138214</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.182299421009067</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.658766066838045</v>
+      </c>
+      <c r="J5" t="n">
+        <v>29.38923148774891</v>
+      </c>
+      <c r="K5" t="n">
+        <v>85.87537354245515</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 13.867x + -27784.857</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>3.638750338927884e-08</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2287.05661856295</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000018e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8208208106397976</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-178.6199999999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.24991e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-71.354</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.2321518987341711</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1113342898134799</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.8645858343336816</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.8121238177128</v>
+      </c>
+      <c r="J6" t="n">
+        <v>24.71394861051551</v>
+      </c>
+      <c r="K6" t="n">
+        <v>85.63761957366458</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 13.109x + -25865.796</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.514072843960937e-09</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2258.473193636406</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000000945e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8209682809751588</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-177.7199999999998</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.25294e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-71.629</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.05934227885786165</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.6005761402328612</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.532840450276582</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.954573601903386</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>85.45919496875602</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 12.592x + -24467.612</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.041207795952953e-08</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2229.732318649618</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000000314e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8211768908728423</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-160.52</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.25734e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-71.94199999999999</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.4915335463258502</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.4865558912386746</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.185519801980111</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.924806201550274</v>
+      </c>
+      <c r="J8" t="n">
+        <v>21.18783918556908</v>
+      </c>
+      <c r="K8" t="n">
+        <v>85.56021029924068</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 12.879x + -24766.201</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>7.794897760382419e-08</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2201.885953625297</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000010577e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8214197738283352</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-156.0999999999999</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.26031e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-72.199</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.231912442396321</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.6570913461537948</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.081048867699593</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.711094674556141</v>
+      </c>
+      <c r="J9" t="n">
+        <v>20.32712017379618</v>
+      </c>
+      <c r="K9" t="n">
+        <v>85.55940687519681</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 12.877x + -24464.530</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>6.677412408832826e-10</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2174.902578029177</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000000308e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8216921411896099</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-143.6799999999998</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.26428e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-72.48699999999999</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.2057101024890352</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.271705822267619</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.8030549898166958</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.396064139941646</v>
+      </c>
+      <c r="J10" t="n">
+        <v>16.92010723924846</v>
+      </c>
+      <c r="K10" t="n">
+        <v>85.40422513712912</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 12.440x + -23321.493</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>3.005876595717843e-12</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2148.837317518531</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8219811738025582</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-128.5999999999999</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.26693e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-72.73</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.7619289340101655</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.5406703910614478</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.105078124999963</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.987357052096633</v>
+      </c>
+      <c r="J11" t="n">
+        <v>8.762145353953002</v>
+      </c>
+      <c r="K11" t="n">
+        <v>85.59276080069311</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 12.975x + -24113.264</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.088261798567025e-10</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2123.711437636119</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8222926092268291</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-127.3299999999999</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.27112e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-72.97499999999999</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.4365217391304382</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.5882830626450249</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.7748936170212753</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.905228136882119</v>
+      </c>
+      <c r="J12" t="n">
+        <v>10.9254735318043</v>
+      </c>
+      <c r="K12" t="n">
+        <v>85.24697785761123</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 12.027x + -22010.598</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.782017767900564e-08</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2100.123766861156</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.000000000013372e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8226092188268457</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-126.3199999999999</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.27351e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-73.182</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.0712492986465626</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.9195057918310804</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.733921613928859</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.02995129294358</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>85.05790523896528</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 11.565x + -20890.697</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.532804041585183e-08</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2077.061366627192</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.00000000000013e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8229320424686237</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-125.8</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.27644e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-73.383</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.1312300785086742</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.8418000460879128</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.613647221346541</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.285827468284071</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>84.97882892517599</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 11.382x + -20325.473</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.609562704242201e-08</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2053.947534549518</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8232660060759044</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-115.4299999999998</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.27914e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-73.56100000000001</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.3695086705202783</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.8465543644716442</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.138181818181774</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.667074164629117</v>
+      </c>
+      <c r="J15" t="n">
+        <v>6.151229337767465</v>
+      </c>
+      <c r="K15" t="n">
+        <v>85.18898742923123</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 11.881x + -21060.042</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>7.348741095256063e-08</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2032.367258601469</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8235950722342219</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-111.25</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.28279e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-73.82899999999999</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.09827574830586402</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.8198447735687885</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.534216757741388</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.599138654126015</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>84.35561416766511</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 10.118x + -17601.011</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.073449630468893e-09</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2010.869800452661</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.000000000002504e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8239336936761154</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-108.8799999999999</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.28588e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-73.968</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.230741238383157</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.6820397306422959</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.955199415995926</v>
+      </c>
+      <c r="I17" t="n">
+        <v>169.2793659631687</v>
+      </c>
+      <c r="J17" t="n">
+        <v>11.09197632594297</v>
+      </c>
+      <c r="K17" t="n">
+        <v>84.71072808275181</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 10.802x + -18658.892</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>194.9128416968672</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1997.956112222552</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.497888028501448e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8114528996329761</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-103.99</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.28858e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-74.142</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.2812007158236932</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.9821551153021205</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.651257533095767</v>
+      </c>
+      <c r="I18" t="n">
+        <v>204.796077482548</v>
+      </c>
+      <c r="J18" t="n">
+        <v>11.76774026077038</v>
+      </c>
+      <c r="K18" t="n">
+        <v>84.69030337307916</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 10.760x + -18399.176</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>3.269855886123153e-08</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1968.709742936593</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.000000000000175e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8246302099443671</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-94.97000000000003</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.28997e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-74.34099999999999</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.1469578783151231</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.088868613138731</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.590184049079822</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.314400805639467</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>84.62588928958161</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 10.630x + -17983.916</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>3.499427388928672e-08</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1948.006773315955</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.000000000000046e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8249848233707414</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-84.99000000000001</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.29365e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-74.547</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.295652173913164</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.522453703703692</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.168284789644061</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.098214285714322</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>84.1942210862541</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 9.835x + -16398.235</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>4.17880658220823e-08</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1926.945451865624</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.000000000000007e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8253519265853584</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-87.92000000000007</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.29598e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-74.712</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.3445262079741157</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.8480375779889433</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.836434238680506</v>
+      </c>
+      <c r="I21" t="n">
+        <v>240.1895114834599</v>
+      </c>
+      <c r="J21" t="n">
+        <v>12.94118715152236</v>
+      </c>
+      <c r="K21" t="n">
+        <v>84.19667320161133</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 9.839x + -16234.775</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.937766268094148e-08</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1906.448848261884</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.000000000000126e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8257241235007452</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-84.24000000000001</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.30063e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-74.887</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.1578404731347258</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.027030476449264</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.948484209243774</v>
+      </c>
+      <c r="I22" t="n">
+        <v>152.3408541231487</v>
+      </c>
+      <c r="J22" t="n">
+        <v>13.92238537179344</v>
+      </c>
+      <c r="K22" t="n">
+        <v>83.85151603775746</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 9.283x + -15107.811</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>4.752329891567776e-08</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1885.524683424949</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8260891804618763</v>
       </c>
     </row>
   </sheetData>
@@ -1162,7 +3856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1266,8 +3960,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1297,6 +3989,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-441.52</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.17084e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-63.712</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.008526011560703359</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.2356905158069797</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.223657289002546</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.937210319195471</v>
+      </c>
+      <c r="J2" t="n">
+        <v>18.31781065589669</v>
+      </c>
+      <c r="K2" t="n">
+        <v>84.65983800603161</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 10.698x + -26706.686</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>7.883427900413313e-10</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2774.566121206715</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8184418196520336</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-246.0999999999999</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.26824e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-68.53400000000001</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.4063169164882285</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.209662716499547</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.865051903114133</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.524650349650324</v>
+      </c>
+      <c r="J3" t="n">
+        <v>48.98266741622771</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.5720619659517</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 16.694x + -36140.694</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>5.593093609899253e-10</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2449.195621436328</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000056022e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8193364042068423</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-201.6700000000001</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.27197e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-69.932</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1388724035608282</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.5539375928677206</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.224352331606205</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.011111111111056</v>
+      </c>
+      <c r="J4" t="n">
+        <v>35.24388342079883</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.49428931529927</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 16.323x + -33815.253</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>8.915161895167579e-09</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2369.31096873786</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000000004e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8194467387990272</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-174.0499999999997</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.26753e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-70.63800000000001</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.3527233115468388</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.135159010600653</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.750452781371344</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.545211038961076</v>
+      </c>
+      <c r="J5" t="n">
+        <v>35.66630946901088</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.54633220578661</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 16.570x + -33711.183</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>7.923251920167434e-10</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2330.488411175554</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8194650980331833</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-166.7799999999997</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.26422e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-71.063</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.568979591837334</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.5918367346938418</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.246266829865426</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.630878438331771</v>
+      </c>
+      <c r="J6" t="n">
+        <v>30.54955838724893</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.40523466484903</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 15.918x + -31866.979</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.687712108181191e-10</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2298.737464489892</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8195465745926814</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-146.3100000000002</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.26397e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-71.49299999999999</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.5385826771653189</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.7513513513512898</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.773292682926698</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.62443181818189</v>
+      </c>
+      <c r="J7" t="n">
+        <v>31.14868334330851</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.50628571425651</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 16.379x + -32424.365</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>3.244383013434563e-09</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2268.743891509471</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000000671e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8196794514236461</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-134.9800000000002</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.26568e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-71.81</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1458715596330224</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.7686084142394567</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.9082830025884414</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.406709265175569</v>
+      </c>
+      <c r="J8" t="n">
+        <v>26.86433710735612</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.46587755173864</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 16.192x + -31643.771</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.644520601076616e-09</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2239.643704997689</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000001247e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8198512129396183</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-129</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.26951e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-72.119</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.5334164588528282</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.3569690265486528</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.486222910216602</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.998251028806719</v>
+      </c>
+      <c r="J9" t="n">
+        <v>21.72706834716728</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.13663104753107</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 14.808x + -28471.886</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>6.680290477220372e-10</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2211.694723348148</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8200324788438826</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-125.6400000000001</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.27133e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-72.371</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.08562231759656634</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.6327305605786776</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.179915433403778</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.367962308598139</v>
+      </c>
+      <c r="J10" t="n">
+        <v>20.68473178421213</v>
+      </c>
+      <c r="K10" t="n">
+        <v>86.14507632132964</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 14.841x + -28195.277</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.566576168441471e-09</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2184.9101920838</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8202582125603227</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-119.72</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.27413e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-72.613</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.5690839694655903</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.789198036006593</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.06653491436098</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.093353783231048</v>
+      </c>
+      <c r="J11" t="n">
+        <v>18.90079930798803</v>
+      </c>
+      <c r="K11" t="n">
+        <v>86.14517076772654</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 14.841x + -27865.281</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>4.576929854027643e-08</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2158.5683705583</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000002358e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8204968058166173</v>
       </c>
     </row>
   </sheetData>
@@ -1310,7 +4522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1414,8 +4626,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1445,6 +4655,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-280.1100000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.26531e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-68.236</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.09621212121211134</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.579910213243531</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.198611111111068</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.84922663080031</v>
+      </c>
+      <c r="J2" t="n">
+        <v>27.28134498970658</v>
+      </c>
+      <c r="K2" t="n">
+        <v>86.07779278082386</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 14.585x + -31510.790</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>7.59263497276218e-08</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2448.172831186998</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000001174e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8190425443742186</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-178.1899999999998</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.26623e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-70.407</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.127974276527387</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.592886456908658</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.572594303310357</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.902889150943452</v>
+      </c>
+      <c r="J3" t="n">
+        <v>45.80276428893944</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.71101429127195</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 17.401x + -35754.912</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>4.882485990923643e-08</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2344.058287504316</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000000328e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8192389671136557</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-162.51</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.26515e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-71.047</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1330097087378676</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.6944256756757132</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.8076222980659673</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.705754276827385</v>
+      </c>
+      <c r="J4" t="n">
+        <v>28.99724198031014</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.33261709878029</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 15.602x + -31305.693</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.391710035901277e-09</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2307.414050921421</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000033528e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8192374788991174</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-142.2400000000002</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.26581e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-71.413</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2635772357723764</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.639449541284046</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.681267605633818</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.196181556195921</v>
+      </c>
+      <c r="J5" t="n">
+        <v>28.72366326198399</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.40287891827006</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 15.907x + -31604.158</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>3.907241226290765e-09</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2281.789598885403</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000001366e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8192612212629248</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-140.45</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.26773e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-71.712</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.01210788447567915</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.5447299884820154</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.856184190534649</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.58000024195704</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>85.9769002109458</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 14.218x + -27814.628</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>8.138654619019943e-08</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2258.501092430848</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000017002e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8193622015874842</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-122.1899999999998</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.27016e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-71.94</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.7445880452343256</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.140589569160918</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.937861635220054</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.553503709810368</v>
+      </c>
+      <c r="J7" t="n">
+        <v>17.43443059815125</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.27982389567983</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 15.380x + -29923.521</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>5.396713625197265e-10</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2236.416516125864</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000000053e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8195187763847008</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-116.1500000000001</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.27357e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-72.148</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.6744597249507919</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.7736263736263697</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.406268958543911</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.199042709867385</v>
+      </c>
+      <c r="J8" t="n">
+        <v>13.06027197575831</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.20941217304882</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 15.093x + -29072.233</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.660286056378543e-09</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2214.540011872067</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000000018e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8197320493551178</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-113.6600000000001</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.27833e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-72.38200000000001</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.2073002754820919</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.3582966226137943</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.345641025641084</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.738850771869655</v>
+      </c>
+      <c r="J9" t="n">
+        <v>12.15643809338188</v>
+      </c>
+      <c r="K9" t="n">
+        <v>85.79513385908204</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 13.602x + -25834.003</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>4.33698953844215e-09</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2193.210525266819</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000003773e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8199704015880463</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-114.0699999999999</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.28047e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-72.521</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.2298837209302214</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.9225694444444078</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.323400936037491</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.832970027247847</v>
+      </c>
+      <c r="J10" t="n">
+        <v>14.5048227156996</v>
+      </c>
+      <c r="K10" t="n">
+        <v>85.96567808557072</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 14.179x + -26722.421</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.41124281947301e-08</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2172.325156704148</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000000008e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8202329282049027</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-99.66000000000008</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.2845e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-72.786</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.02760055478501769</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.9089694656488944</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.319334186939821</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.337323177366693</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4.717625830787687</v>
+      </c>
+      <c r="K11" t="n">
+        <v>85.5172088672479</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 12.755x + -23727.640</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>9.229985201283662e-08</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2151.965347585302</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000004753e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8205133468811094</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-101.25</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.28776e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-72.90900000000001</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.3793418647166591</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.425649350649342</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.9542828685259375</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.321040723981803</v>
+      </c>
+      <c r="J12" t="n">
+        <v>5.567578232998313</v>
+      </c>
+      <c r="K12" t="n">
+        <v>85.56542189687642</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 12.894x + -23785.300</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>3.164702529728533e-08</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2132.172169751793</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.000000000003629e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8208002111185573</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-101.8700000000001</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.2912e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-73.08199999999999</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.08666779644603255</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.080168917990076</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.01014971772294</v>
+      </c>
+      <c r="I13" t="n">
+        <v>170.0653319377327</v>
+      </c>
+      <c r="J13" t="n">
+        <v>10.83969555292598</v>
+      </c>
+      <c r="K13" t="n">
+        <v>85.31747505331563</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 12.209x + -22260.508</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.113454508951787e-08</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2112.461221515814</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.000000000000326e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8210845874163852</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-86.27999999999997</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.29467e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-73.259</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.3842712842713084</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.290158730158643</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.528615071282966</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.242210682492571</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>85.38524211641437</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 12.389x + -22421.764</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>6.866990322863331e-10</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2093.589109911672</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8213822948186666</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-85.08999999999992</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.29705e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-73.426</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.027234042553295</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.465553602811938</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.289686684072999</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.77490542244616</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>85.24034746041217</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 12.010x + -21513.078</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>9.524684903577736e-11</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2074.379845100409</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8216872463320141</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-88.47000000000003</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.30137e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-73.56999999999999</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.21411040280697</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.9528213977307621</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.161891702725772</v>
+      </c>
+      <c r="I16" t="n">
+        <v>234.9250182913892</v>
+      </c>
+      <c r="J16" t="n">
+        <v>11.46800660480105</v>
+      </c>
+      <c r="K16" t="n">
+        <v>85.06827953940441</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 11.589x + -20537.699</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>4.791237062375483e-08</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2055.375363242407</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.000000000005102e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8219848548655849</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-80.54999999999995</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.3027e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-73.717</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.05991820040898529</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.007889908256965</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.046840148698868</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.801273344651929</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>85.19625531608348</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 11.899x + -20938.394</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>6.15130475819423e-09</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2036.978913403617</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.000000000000003e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8222921132524216</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-75.55000000000018</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.30766e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-73.904</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.06120996441281047</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.350961538461419</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.141958041958062</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.245559400230678</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>84.56143802201298</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 10.503x + -18212.152</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>215.439725150856</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1995.954777419473</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.421089080265279e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8148377086709585</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-77.00999999999999</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.3117e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-74.04000000000001</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.2368739386270691</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.8097902213669905</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.287953337953273</v>
+      </c>
+      <c r="I19" t="n">
+        <v>281.5521706328904</v>
+      </c>
+      <c r="J19" t="n">
+        <v>12.28759359951612</v>
+      </c>
+      <c r="K19" t="n">
+        <v>84.47851608554285</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 10.345x + -17767.175</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>6.232654591143145e-09</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1999.304523283349</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.000000000000246e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8229108495188741</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-73.75</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.3163e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-74.197</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.2904118554497644</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.8952887230360997</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.303426508968609</v>
+      </c>
+      <c r="I20" t="n">
+        <v>142.7397743217941</v>
+      </c>
+      <c r="J20" t="n">
+        <v>12.79435262426438</v>
+      </c>
+      <c r="K20" t="n">
+        <v>84.09420207595871</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 9.667x + -16398.479</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>7.571974585333299e-10</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1980.823354486376</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8232226342904261</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-69.75</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.31836e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-74.351</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.4227656391380519</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.191995461282282</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.003856027382683</v>
+      </c>
+      <c r="I21" t="n">
+        <v>88.54771123134913</v>
+      </c>
+      <c r="J21" t="n">
+        <v>13.13137324208033</v>
+      </c>
+      <c r="K21" t="n">
+        <v>84.01084049015429</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 9.532x + -16013.677</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>3.945118807396416e-09</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1962.866129307823</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8235257258343727</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-66.95000000000005</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.3223e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-74.499</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.1574391531351618</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.136325712258059</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.154501364622637</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>13.3394274310729</v>
+      </c>
+      <c r="K22" t="n">
+        <v>83.67584587017204</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 9.023x + -14976.139</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>7.424481533400172e-08</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1944.151827818589</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.000000000000027e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.823832716983225</v>
       </c>
     </row>
   </sheetData>
@@ -1458,7 +5760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1562,8 +5864,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1593,6 +5893,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-471.4099999999999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.21568e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-63.826</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.03717826501429401</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.9036512667661331</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.304858934169242</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.398347880299212</v>
+      </c>
+      <c r="J2" t="n">
+        <v>17.52773798041081</v>
+      </c>
+      <c r="K2" t="n">
+        <v>84.5764744127804</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 10.533x + -25213.210</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.178533343438866e-12</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2658.812629016438</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8203803972618613</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-272.96</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.28968e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-68.801</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.00114942528747</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.6365644171779661</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.211347517730546</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.979069767441867</v>
+      </c>
+      <c r="J3" t="n">
+        <v>27.86887657473744</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.17563969181897</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 14.960x + -31277.199</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>5.321018380837263e-08</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2379.381414814334</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.00000000001412e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8210765106441527</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-204.6400000000001</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.28597e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-70.30200000000001</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.5792358803986944</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.198348623853214</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.345126353790681</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.879833546735038</v>
+      </c>
+      <c r="J4" t="n">
+        <v>35.09740516751448</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.54124499778651</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 16.545x + -33442.277</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>4.426657910376211e-08</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2308.640491278848</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.00000000000008e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8211563763242047</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-179.4899999999998</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.282e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-70.964</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.3695299837924907</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.7317617866004271</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.520353982300912</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.36239316239313</v>
+      </c>
+      <c r="J5" t="n">
+        <v>35.85785008889203</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.6233617917888</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 16.949x + -33669.094</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>4.07323689996329e-09</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2271.301881635975</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000654e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8211863162311187</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-161.8299999999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.28012e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-71.467</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.6836193447738098</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.718024263431579</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.299609374999871</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.596841230257761</v>
+      </c>
+      <c r="J6" t="n">
+        <v>29.36174383510147</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.46440893826606</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 16.185x + -31612.390</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>7.073228953434104e-12</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2239.342588407337</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8212713417327091</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-141.1600000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.28215e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-71.85899999999999</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.7341463414634198</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.9037707390648045</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.778440366972658</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.20272058823532</v>
+      </c>
+      <c r="J7" t="n">
+        <v>30.23905992524642</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.55211011509773</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 16.598x + -32029.383</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>6.116323499204814e-08</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2208.626226218052</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000004567e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8213975431315231</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-141.29</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.28493e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-72.2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.04825505694218435</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.7287996416597156</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.006861744505672</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.725666318463911</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.11491787455944</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 14.725x + -27888.574</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>5.751298632844075e-10</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2179.723996827127</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000000048e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8215651857466469</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-119.6900000000001</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.28725e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-72.48699999999999</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.6702495201535517</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.5075872534143083</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.728731762065069</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.178120617110777</v>
+      </c>
+      <c r="J9" t="n">
+        <v>19.4337680401639</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.42202768193623</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 15.993x + -30042.783</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>7.808436692014853e-12</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2152.038528362595</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8217690172635903</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-128.28</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.29008e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-72.72199999999999</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1961976532433493</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.7466548932889133</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.104446850700857</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.662353940939166</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>86.05687071797711</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 14.508x + -26793.564</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.31055830514826e-10</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2124.659760987732</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000000012e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8220058724131702</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-109.3800000000001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.29427e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-73.03100000000001</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1088129496402817</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.6109788359787877</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.662652439024532</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.515861214374207</v>
+      </c>
+      <c r="J11" t="n">
+        <v>13.48776047587132</v>
+      </c>
+      <c r="K11" t="n">
+        <v>85.98428394516897</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 14.245x + -25988.778</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>4.568867439192769e-08</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2098.5094102756</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000003242e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.822262789375012</v>
       </c>
     </row>
   </sheetData>
@@ -1606,7 +6426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1710,8 +6530,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1741,6 +6559,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-268.8200000000002</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.27208e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-68.58199999999999</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.3268547544409184</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.3639620653319273</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.135317460317502</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.999566294919434</v>
+      </c>
+      <c r="J2" t="n">
+        <v>28.58171116857689</v>
+      </c>
+      <c r="K2" t="n">
+        <v>86.16137949357943</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 14.904x + -31824.086</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>7.799273845483685e-09</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2416.473483771344</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000000672e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8204761022178662</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-172.8399999999999</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.27506e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-70.69199999999999</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.010450819672298</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.36998556998567</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.023262548262392</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.37401614530768</v>
+      </c>
+      <c r="J3" t="n">
+        <v>45.61712262839713</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.79263340993062</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 17.845x + -36113.653</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.548953750599256e-08</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2306.410461792562</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000000465e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8206982435186609</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-154.3299999999999</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.27772e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-71.28700000000001</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.3337711069418418</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8616384915474086</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.456127703398524</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.735040431266991</v>
+      </c>
+      <c r="J4" t="n">
+        <v>32.91758066093285</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.54811692382954</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 16.578x + -32806.276</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>6.348775983279524e-09</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2268.352087800372</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000006328e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8206928436905053</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-140.46</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.28344e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-71.64</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.5822335025379765</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.3393034825870915</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.083526011560681</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.682924693520053</v>
+      </c>
+      <c r="J5" t="n">
+        <v>24.54508164125475</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.23674973217966</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 15.203x + -29618.191</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>4.366292432417547e-08</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2241.71034169518</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000001511e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8207304499822511</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-134.0800000000002</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.28373e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-71.904</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.3136904761904776</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.8953033268100781</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3.26761658031052</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.034717314487501</v>
+      </c>
+      <c r="J6" t="n">
+        <v>23.60173868367039</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.24736211313162</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 15.246x + -29391.403</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.040892421831557e-12</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2217.495790347891</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8208330205522311</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-123.21</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.28826e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-72.15600000000001</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.04291044776119547</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.2950581395348822</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.8731196054253997</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.806311111111066</v>
+      </c>
+      <c r="J7" t="n">
+        <v>19.59912046677297</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.11350596708473</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 14.720x + -28051.952</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.163827076607538e-08</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2194.09778788681</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000043812e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8209980295427457</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-122.52</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.29134e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-72.348</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.3281818181817898</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.816512059369262</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.297667185069858</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.330802603036872</v>
+      </c>
+      <c r="J8" t="n">
+        <v>18.64732543072838</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.07504764752811</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 14.575x + -27492.437</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>5.421282168708254e-11</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2171.718961287622</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8211956966675322</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-109.8399999999999</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.29688e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-72.587</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.178793774319074</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.6773684210526116</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.001771653543291</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.098723792160551</v>
+      </c>
+      <c r="J9" t="n">
+        <v>11.7583777222668</v>
+      </c>
+      <c r="K9" t="n">
+        <v>85.79693583129814</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 13.607x + -25366.283</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>5.800470212966129e-09</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2150.271644099466</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000005795e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8214275415280712</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-113.6699999999998</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.299e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-72.749</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.03059747805387442</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.8862654114972607</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.168101995779776</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.881818023094851</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>85.73588205690906</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 13.412x + -24737.567</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>4.209818556764471e-08</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2129.886604784695</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000000114e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8216658026258539</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-95.74000000000001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.306e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-72.967</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.151244813278019</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.8328335832083608</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.831975867269925</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.216684961580693</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.923065558429141</v>
+      </c>
+      <c r="K11" t="n">
+        <v>85.48070060833098</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 12.652x + -23091.471</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>3.282787595306996e-08</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2109.777906018549</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000000349e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8219279195950848</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-94.34999999999991</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.30583e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-73.09099999999999</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.684496124031096</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.8995283018868317</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.265756097560942</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.158956276445599</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>85.81920739517349</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 13.680x + -24835.845</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.596273875510573e-10</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2091.004586416669</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.00000000000047e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8221969564938763</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-95.12999999999988</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.30816e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-73.26600000000001</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.1842735042735007</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.152362204724511</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.9858313817329802</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.084994640943294</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4.612823787080787</v>
+      </c>
+      <c r="K13" t="n">
+        <v>85.62399170057979</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 13.068x + -23470.116</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.424799153077533e-08</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2072.679106968035</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.000000000005907e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8224741148930019</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-92.51999999999998</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.31275e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-73.401</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.2252941176470674</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.097491638796096</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.846596858638824</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.909555984556186</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.754370899840299</v>
+      </c>
+      <c r="K14" t="n">
+        <v>85.55071496161554</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 12.852x + -22874.387</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>3.63933232433278e-08</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2054.57121273991</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.000000000000386e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8227540448103694</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-96</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.31459e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-73.57599999999999</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.303173811325937</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.7327051583199683</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.53760208464232</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.833069515023729</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>85.14591459323887</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 11.775x + -20697.785</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>8.284350392887859e-08</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2036.907459823528</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.00000000000012e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8230354745270387</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-84.94000000000005</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.31756e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-73.727</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.1888888888888683</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.8676007005253411</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.319271948608185</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.096476964769652</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>85.20306171179796</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 11.916x + -20792.965</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>3.120711221992213e-08</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2019.117536474495</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.000000000001246e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8233366675585391</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-80.84999999999991</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.32158e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-73.876</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.086604361370562</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.6737421383647707</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.201222222222253</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.373281596452195</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>85.0082594806691</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 11.449x + -19771.984</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>3.16789655310853e-09</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2001.861790416041</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.000000000000738e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8236274810406217</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-83.72000000000003</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.32559e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-73.995</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.422398723147652</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.239309165363264</v>
+      </c>
+      <c r="I18" t="n">
+        <v>220.5790203217626</v>
+      </c>
+      <c r="J18" t="n">
+        <v>11.88215658211635</v>
+      </c>
+      <c r="K18" t="n">
+        <v>84.95622239657972</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 11.330x + -19394.370</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>213.0517617979157</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1982.412671349128</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.464092348456783e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8143536509127001</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-68.64999999999986</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.32865e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-74.193</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.7847533632288599</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.6963358778626619</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.605189340813335</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.53189655172417</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>84.37381452768477</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 10.151x + -17141.683</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.566822510386609e-08</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1967.190607268022</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.000000000000009e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8242196422748366</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-69.83999999999992</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.3326e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-74.32899999999999</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.2832935560859366</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.7404326123127918</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.631699846860639</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.36012658227846</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>84.05341940455079</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 9.600x + -16025.173</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.245367317068335e-07</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1949.403625562016</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.000000000001419e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8245234996489053</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-71.32000000000016</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.33434e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-74.482</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.365206615101939</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.7872225741210328</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.225948247459714</v>
+      </c>
+      <c r="I21" t="n">
+        <v>101.6304037336233</v>
+      </c>
+      <c r="J21" t="n">
+        <v>12.64917044087986</v>
+      </c>
+      <c r="K21" t="n">
+        <v>83.89363160979561</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 9.347x + -15454.234</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.185533263051768e-09</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1932.263815453651</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.000000000000485e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8248405806765271</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-67.11000000000013</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.33696e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-74.619</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.1865732385879416</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.9332594066054982</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.111439809826614</v>
+      </c>
+      <c r="I22" t="n">
+        <v>36.49932329440752</v>
+      </c>
+      <c r="J22" t="n">
+        <v>12.64331534003451</v>
+      </c>
+      <c r="K22" t="n">
+        <v>83.86981723841019</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 9.311x + -15254.374</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>5.341544813221286e-08</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1915.068446222447</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.000000000000105e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.825137287977138</v>
       </c>
     </row>
   </sheetData>
@@ -1754,7 +7664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1858,8 +7768,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1889,6 +7797,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-327.9499999999998</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.41289e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-69.84699999999999</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.652969502407674</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.9714918759231738</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.823969631236549</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.324081920903947</v>
+      </c>
+      <c r="J2" t="n">
+        <v>22.82423733684878</v>
+      </c>
+      <c r="K2" t="n">
+        <v>86.06649056588259</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 14.543x + -26607.760</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.561212350355966e-08</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2002.081351190302</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000025406e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8208152587456541</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-187.1799999999998</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.40085e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-73.486</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.06595552634264876</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.6095211640488656</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.38003883746137</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.621239424175997</v>
+      </c>
+      <c r="J3" t="n">
+        <v>50.85254216498522</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.76546241648256</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 17.695x + -28977.903</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>7.958536421594163e-08</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1845.078878028542</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000000006e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8213138079844127</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-136.4099999999999</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.38173e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-74.542</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.5132828438434337</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8908917102314814</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.187218099859213</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.203137382955591</v>
+      </c>
+      <c r="J4" t="n">
+        <v>85.39575238121419</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.96343756573788</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 18.851x + -30029.175</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>6.629517581915167e-08</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1799.075986342032</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8214426527690188</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-117.6000000000001</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.3722e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-75.048</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.6363350520922247</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.8934421014780461</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.023616360547382</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.470953803303345</v>
+      </c>
+      <c r="J5" t="n">
+        <v>53.99923398529888</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.90504759300956</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 18.495x + -28940.059</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>9.655467005359109e-08</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1769.28253467059</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000139312e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8215546323192502</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-102.1800000000001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.36688e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-75.452</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.5206253863312862</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.090066845998116</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.098067154008203</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.38313973714139</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.7663765867857</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 17.700x + -27231.773</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.037721765307055e-11</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1741.065750781662</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8217464343880716</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-95.42000000000007</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.36447e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-75.76900000000001</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.3189518553430451</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.133811248587095</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.10164667200612</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.65644972942968</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.62685619091015</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 16.966x + -25668.738</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.544063932410871e-11</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1713.29247573609</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8219930186703909</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-92.87000000000012</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.36518e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-76.04900000000001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.2281633311814284</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.7282481621591466</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.153065842138447</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.769971558902065</v>
+      </c>
+      <c r="J8" t="n">
+        <v>11.11147487416984</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.30373212081655</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 15.479x + -22966.881</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>4.502247663862155e-08</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1686.289858227703</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000000003e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8222803212474934</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-78.04999999999995</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.36683e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-76.327</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.5797690245411441</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.362247955967011</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.576389246777412</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.870754713704029</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.36723549598375</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 15.751x + -23053.042</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>5.548853834689077e-08</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1659.747023603323</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8226145878480111</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-86.12999999999988</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.36865e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-76.54000000000001</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1421666842083509</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.8353907198479037</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.646223373422676</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.379534458877418</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>85.86676725399651</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 13.838x + -19835.018</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>7.439743487959913e-08</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1634.862859063115</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000025642e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8229475306037469</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-68.58999999999992</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.37054e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-76.782</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.199133148405159</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.511615056773624</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.428066822575181</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.70935048165387</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>85.99200204422762</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 14.272x + -20223.121</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>3.277321864779594e-09</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1611.30018337099</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000005047e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8232909354589683</v>
       </c>
     </row>
   </sheetData>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 37.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 37.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -528,12 +528,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -555,6 +555,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-218.6599999999999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.24383e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-68.199</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1088709677419345</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.1169354838709749</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.9373467112596927</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.710906862745058</v>
+      </c>
+      <c r="J2" t="n">
+        <v>31.95090078484899</v>
+      </c>
+      <c r="K2" t="n">
+        <v>86.213808969772</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>y = 15.111x + -33884.433</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-33884.43280066451</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.893447249540654e-11</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>218.6599999999999</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000000053e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8176282665165663</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-171.4899999999998</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.23962e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-69.407</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.08882803943045019</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.9273712737127594</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.439593908629462</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.762434782608725</v>
+      </c>
+      <c r="J3" t="n">
+        <v>40.37003936828826</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.51638124513785</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>y = 16.427x + -35829.666</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-35829.66572203031</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.361102179100492e-09</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>179.6999999999998</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000000198e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8178140973748232</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-151.29</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.24379e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-70.164</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.07149390243902387</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.3456483126110175</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.578769230769201</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.231582733812893</v>
+      </c>
+      <c r="J4" t="n">
+        <v>25.6634660535035</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.16211128698326</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>y = 14.907x + -31582.833</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-31582.83307428906</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>3.012713234428511e-09</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>178.5599999999999</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000000014e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8180347104926591</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-136.4100000000003</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.24522e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-70.727</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2601889338731617</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.3443361753958819</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.664341085271118</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.992842251563519</v>
+      </c>
+      <c r="J5" t="n">
+        <v>18.72734141500719</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.04141363964973</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>y = 14.451x + -29997.910</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-29997.91033496923</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>3.92679535815329e-08</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>174.04</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000019e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8182294985083717</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-117.3899999999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.24955e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-71.139</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.4259552042160158</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.543716814159225</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.797009674582347</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.920082449941083</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.12432079972868</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>y = 14.761x + -30169.335</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-30169.33452599037</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.027390056868385e-08</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>160.9699999999998</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000000624e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8184496117607183</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-113.2399999999998</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.25363e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-71.512</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.2482710926694099</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.9458868894601636</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.786717752235247</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.007663782447485</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4.51110953705539</v>
+      </c>
+      <c r="K7" t="n">
+        <v>85.77123499468352</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>y = 13.524x + -27115.043</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-27115.04254575271</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>9.673578386447352e-08</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>162.6900000000001</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000015006e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8186431331679291</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-107.6599999999999</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.25547e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-71.86</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.2365289256198387</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.6462519936204337</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.0199999999999</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.985517241379309</v>
+      </c>
+      <c r="J8" t="n">
+        <v>6.489044029537423</v>
+      </c>
+      <c r="K8" t="n">
+        <v>85.37825944008871</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>y = 12.370x + -24374.263</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-24374.26331696161</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>6.597009395349453e-08</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>163.1500000000001</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000000718e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8188787031310908</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-96.08999999999992</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.26042e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-72.11799999999999</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.4756152125279234</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.8560157790926779</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.147137404580147</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.4176935229068</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>85.27434755980602</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>y = 12.097x + -23530.521</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-23530.52061652963</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.954969134266329e-09</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>156.0999999999997</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000000055e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8190792212900569</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-84.73000000000002</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.26303e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-72.42</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.3281318681318835</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.3952885747938589</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.473522458628804</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.484276729559794</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>84.74055280911873</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>y = 10.863x + -20787.562</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-20787.56162940363</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>9.333546903233828e-08</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>151.1499999999999</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000005741e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8193053057181314</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-81.46000000000004</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.26613e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-72.63200000000001</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.5958997722096797</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.9006720430106904</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.382040229884739</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.840613382899512</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>84.58879417662122</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>y = 10.557x + -19951.747</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-19951.74725563313</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.680971884019061e-09</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>148.2199999999998</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8195905642347411</v>
       </c>
     </row>
   </sheetData>
@@ -674,12 +1194,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -689,7 +1209,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -734,19 +1254,19 @@
       <c r="K2" t="n">
         <v>85.45957009787902</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 12.593x + -27042.640</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-27042.63991557862</v>
       </c>
       <c r="Y2" t="n">
         <v>7.82174430945274e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>2455.265262115215</v>
+        <v>187.77</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000002501e-08</v>
@@ -786,19 +1306,19 @@
       <c r="K3" t="n">
         <v>85.63132537760877</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 13.090x + -26524.848</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-26524.84820753023</v>
       </c>
       <c r="Y3" t="n">
         <v>5.421866676084226e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>2339.950276312656</v>
+        <v>162.3600000000001</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000162e-08</v>
@@ -838,19 +1358,19 @@
       <c r="K4" t="n">
         <v>85.4876478688723</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 12.671x + -25166.402</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-25166.40150012512</v>
       </c>
       <c r="Y4" t="n">
         <v>1.089600563549254e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>2300.817529950784</v>
+        <v>162.1600000000001</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000091e-08</v>
@@ -890,19 +1410,19 @@
       <c r="K5" t="n">
         <v>84.84286460311084</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 11.080x + -21632.250</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-21632.2498408126</v>
       </c>
       <c r="Y5" t="n">
         <v>3.547081525494212e-12</v>
       </c>
       <c r="Z5" t="n">
-        <v>2274.467984741103</v>
+        <v>159.1199999999999</v>
       </c>
       <c r="AA5" t="n">
         <v>1e-08</v>
@@ -942,19 +1462,19 @@
       <c r="K6" t="n">
         <v>84.7323776488215</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 10.846x + -20927.315</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-20927.31508191576</v>
       </c>
       <c r="Y6" t="n">
         <v>1.519006579676908e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>2250.89898729645</v>
+        <v>165</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000003463e-08</v>
@@ -994,19 +1514,19 @@
       <c r="K7" t="n">
         <v>84.59105134495663</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 10.561x + -20154.181</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-20154.1812093094</v>
       </c>
       <c r="Y7" t="n">
         <v>7.422382637472134e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>2227.315017743516</v>
+        <v>157.8499999999999</v>
       </c>
       <c r="AA7" t="n">
         <v>1.00000000000006e-08</v>
@@ -1046,19 +1566,19 @@
       <c r="K8" t="n">
         <v>84.90403921391294</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 11.214x + -21251.371</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-21251.371166875</v>
       </c>
       <c r="Y8" t="n">
         <v>5.054772902839284e-11</v>
       </c>
       <c r="Z8" t="n">
-        <v>2204.953974872117</v>
+        <v>147.28</v>
       </c>
       <c r="AA8" t="n">
         <v>1e-08</v>
@@ -1098,19 +1618,19 @@
       <c r="K9" t="n">
         <v>84.33061355650793</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 10.073x + -18808.393</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-18808.39280830049</v>
       </c>
       <c r="Y9" t="n">
         <v>6.426184467443721e-10</v>
       </c>
       <c r="Z9" t="n">
-        <v>2182.927240455587</v>
+        <v>152.4399999999998</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000414e-08</v>
@@ -1150,19 +1670,19 @@
       <c r="K10" t="n">
         <v>84.13571377470832</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 9.736x + -17977.213</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-17977.21283307825</v>
       </c>
       <c r="Y10" t="n">
         <v>1.505208771916953e-08</v>
       </c>
       <c r="Z10" t="n">
-        <v>2161.994632413858</v>
+        <v>144.74</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000001e-08</v>
@@ -1202,19 +1722,19 @@
       <c r="K11" t="n">
         <v>83.62693198340274</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 8.953x + -16308.549</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-16308.54884706572</v>
       </c>
       <c r="Y11" t="n">
         <v>4.609727969716513e-08</v>
       </c>
       <c r="Z11" t="n">
-        <v>2141.491163647627</v>
+        <v>152.3099999999999</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000093e-08</v>
@@ -1254,19 +1774,19 @@
       <c r="K12" t="n">
         <v>83.83798892062528</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 9.262x + -16752.711</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-16752.71122741924</v>
       </c>
       <c r="Y12" t="n">
         <v>2.97940369360391e-10</v>
       </c>
       <c r="Z12" t="n">
-        <v>2122.427144644078</v>
+        <v>144.76</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000018457e-08</v>
@@ -1306,19 +1826,19 @@
       <c r="K13" t="n">
         <v>83.20322023117525</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 8.390x + -14960.873</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-14960.87306688871</v>
       </c>
       <c r="Y13" t="n">
         <v>2.452407163255564e-10</v>
       </c>
       <c r="Z13" t="n">
-        <v>2103.396953553567</v>
+        <v>142.1400000000001</v>
       </c>
       <c r="AA13" t="n">
         <v>1e-08</v>
@@ -1358,19 +1878,19 @@
       <c r="K14" t="n">
         <v>83.31039133485693</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 8.526x + -15087.396</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-15087.39618723035</v>
       </c>
       <c r="Y14" t="n">
         <v>5.31530856367991e-08</v>
       </c>
       <c r="Z14" t="n">
-        <v>2084.708174013747</v>
+        <v>144.71</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000003199e-08</v>
@@ -1410,19 +1930,19 @@
       <c r="K15" t="n">
         <v>82.77205570185487</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 7.885x + -13762.451</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-13762.45113829071</v>
       </c>
       <c r="Y15" t="n">
         <v>2.631295866833511e-08</v>
       </c>
       <c r="Z15" t="n">
-        <v>2066.81775251792</v>
+        <v>138.53</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000000053e-08</v>
@@ -1462,19 +1982,19 @@
       <c r="K16" t="n">
         <v>81.37261339886355</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 6.591x + -11265.956</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-11265.9556534322</v>
       </c>
       <c r="Y16" t="n">
         <v>7.345875151367063e-08</v>
       </c>
       <c r="Z16" t="n">
-        <v>2048.792832840928</v>
+        <v>136.3899999999999</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000000946e-08</v>
@@ -1514,19 +2034,19 @@
       <c r="K17" t="n">
         <v>81.0653623008742</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 6.361x + -10747.536</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-10747.53572476451</v>
       </c>
       <c r="Y17" t="n">
         <v>225.4520561701192</v>
       </c>
       <c r="Z17" t="n">
-        <v>2039.051996498125</v>
+        <v>134.0699999999999</v>
       </c>
       <c r="AA17" t="n">
         <v>1.510715789863713e-08</v>
@@ -1566,19 +2086,19 @@
       <c r="K18" t="n">
         <v>81.44626384795927</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 6.648x + -11194.779</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-11194.77942225678</v>
       </c>
       <c r="Y18" t="n">
         <v>1.014639549571414e-08</v>
       </c>
       <c r="Z18" t="n">
-        <v>2013.7784627959</v>
+        <v>135.8099999999999</v>
       </c>
       <c r="AA18" t="n">
         <v>1e-08</v>
@@ -1618,19 +2138,19 @@
       <c r="K19" t="n">
         <v>80.34224241284748</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 5.876x + -9714.786</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-9714.786155060667</v>
       </c>
       <c r="Y19" t="n">
         <v>9.581678617117404e-09</v>
       </c>
       <c r="Z19" t="n">
-        <v>1996.461483575034</v>
+        <v>135.3399999999999</v>
       </c>
       <c r="AA19" t="n">
         <v>1e-08</v>
@@ -1670,19 +2190,19 @@
       <c r="K20" t="n">
         <v>79.69222702606045</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 5.498x + -8955.315</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-8955.315205019604</v>
       </c>
       <c r="Y20" t="n">
         <v>5.375682099186868e-08</v>
       </c>
       <c r="Z20" t="n">
-        <v>1978.463301056841</v>
+        <v>131.54</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000274e-08</v>
@@ -1722,19 +2242,19 @@
       <c r="K21" t="n">
         <v>68.33184752971762</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 2.517x + -3596.283</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-3596.283406158472</v>
       </c>
       <c r="Y21" t="n">
         <v>2.294079101179809e-09</v>
       </c>
       <c r="Z21" t="n">
-        <v>1960.980244700381</v>
+        <v>126.05</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000000001e-08</v>
@@ -1774,19 +2294,19 @@
       <c r="K22" t="n">
         <v>77.64371908125486</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 4.565x + -7184.518</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-7184.517534263151</v>
       </c>
       <c r="Y22" t="n">
         <v>3.962954813716136e-08</v>
       </c>
       <c r="Z22" t="n">
-        <v>1943.195022111756</v>
+        <v>130.9099999999999</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000001e-08</v>
@@ -1806,7 +2326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1912,12 +2432,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -1927,7 +2447,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -1939,6 +2459,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-149</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.27294e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-70.212</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1377253814147054</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.5629430719656501</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.065820312499969</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.631500572737585</v>
+      </c>
+      <c r="J2" t="n">
+        <v>26.52221769991947</v>
+      </c>
+      <c r="K2" t="n">
+        <v>86.30453737813669</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>y = 15.483x + -32328.171</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-32328.17147043583</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>6.759203652615179e-12</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>173.98</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8191011171213556</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-128.7300000000002</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.26925e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-70.964</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1207894736842202</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.2109480812641009</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.727401129943493</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.058928571428568</v>
+      </c>
+      <c r="J3" t="n">
+        <v>14.96426361016274</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.93608381357207</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>y = 14.075x + -28618.126</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-28618.12641874233</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>6.420144283658278e-09</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>170.9100000000001</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.00000000000424e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.819158854778375</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-112.25</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.26783e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-71.386</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1295652173913009</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.457097791798051</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9557506584723289</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.273717948717932</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.681735239928523</v>
+      </c>
+      <c r="K4" t="n">
+        <v>85.67170262351074</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>y = 13.212x + -26459.303</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-26459.30299960887</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>6.911585327235647e-10</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>164.04</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000001963e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8192077658626172</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-111.22</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.2684e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-71.68600000000001</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.1426403641881793</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.2949778434268754</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.002176165803086</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.853786407767103</v>
+      </c>
+      <c r="J5" t="n">
+        <v>7.637224899724427</v>
+      </c>
+      <c r="K5" t="n">
+        <v>85.33004455851005</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>y = 12.242x + -24151.196</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-24151.1958163995</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>3.081182921806102e-10</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>167.2700000000002</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000001058e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8193358946850418</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-100.5400000000002</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.26993e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-71.97499999999999</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.283169934640523</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1156387665198062</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.384948096885778</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.163495346432306</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.688692417291086</v>
+      </c>
+      <c r="K6" t="n">
+        <v>85.03478076531864</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>y = 11.511x + -22407.568</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-22407.56782625177</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.83114843799154e-11</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>162.74</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8195168089212844</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-83.66999999999985</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.27219e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-72.274</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.01135225375626116</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.6962580645160908</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.831591173054323</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.493097781429663</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>84.2400002662892</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>y = 9.914x + -18982.498</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-18982.49840342342</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.495115508536951e-09</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>157.27</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000000559e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8197447445237518</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-91.66000000000008</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.27296e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-72.444</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.07807486631016659</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.3324637681159458</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.307331378298916</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.695432692307555</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>84.43062595896234</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>y = 10.255x + -19465.724</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-19465.72351907413</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>7.737159419216305e-10</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>160.6300000000001</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000000122e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8200057803792258</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-86.48000000000002</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.27522e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-72.636</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1341750841750771</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.011721611721508</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.8588805166846648</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.063777372262793</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>84.45046240258837</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>y = 10.292x + -19339.904</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-19339.90430714014</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>3.828090437360283e-09</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>156.0900000000001</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000000009e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8202771340231321</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-77.75999999999999</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.27726e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-72.879</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.07529411764707157</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.8552980132449808</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.133294255568543</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.676223776223773</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>83.6422461829779</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>y = 8.975x + -16594.348</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-16594.34793244085</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>3.230477346280985e-09</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>154.1000000000001</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000000039e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8205441858580831</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-79.19000000000005</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.27978e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-73.063</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.002571593300138852</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.6903123642057366</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.962285863326118</v>
+      </c>
+      <c r="I11" t="n">
+        <v>99.74616749257568</v>
+      </c>
+      <c r="J11" t="n">
+        <v>11.05691453182798</v>
+      </c>
+      <c r="K11" t="n">
+        <v>83.31773182951167</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>y = 8.535x + -15596.079</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-15596.07931553804</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>3.684517039775811e-10</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>156.9100000000001</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000000403e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8208021342611612</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-70.65000000000009</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.28017e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-73.253</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.6487940630797658</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.5527454242927992</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.7203931203931289</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.232245681381968</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>83.03145397549866</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>y = 8.181x + -14769.675</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-14769.67481251643</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>7.446918971046903e-09</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>149.9400000000001</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.000000000002036e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8210655469749927</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-71.86999999999989</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.28219e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-73.373</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.2305605786618494</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.6732049036777501</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.6869158878504688</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.599117174959912</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>83.58078884250946</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>y = 8.888x + -15975.074</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-15975.07404308421</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>7.181384087052383e-08</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>145.6099999999999</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.821347552752409</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-67.41000000000008</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.28395e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-73.58</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.1053719008264366</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.9346760070052187</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.660254083484704</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.463922518159819</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>82.47404990565391</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>y = 7.569x + -13355.789</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-13355.78921682381</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>6.494330681542102e-08</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>148.23</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.000000000000028e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8216530084900049</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-59.77999999999997</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.28736e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-73.764</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.6781186094069789</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.7646058732611916</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.249132321041141</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.762386831275659</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>81.1654071925622</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>y = 6.434x + -11123.339</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-11123.3390118636</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.078887734892475e-09</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>144.48</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8219399487869644</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-60.40000000000009</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.28791e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-73.91200000000001</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.05174050632911318</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.7378446115288498</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.821863799283468</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.478697571743799</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>81.25011141979748</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>y = 6.497x + -11142.644</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-11142.64404687529</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.597180696414356e-08</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>142.9100000000001</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.000000000000017e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8221908137552887</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-62.96000000000004</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.28949e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-74.04000000000001</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.1077569267046579</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.8628880939403321</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.076976556772219</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>12.62484052896874</v>
+      </c>
+      <c r="K17" t="n">
+        <v>82.04382341130896</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>y = 7.155x + -12259.449</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-12259.44871055042</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>6.987006061311345e-10</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>143.23</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.000000000000009e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8224715805486366</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-56.23000000000002</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.29168e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-74.23099999999999</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.176780744818429</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.9103422243583772</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.143715902524771</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>12.49799451256502</v>
+      </c>
+      <c r="K18" t="n">
+        <v>80.54836204260863</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>y = 6.007x + -10070.587</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-10070.58681058115</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>2.220542885308264e-08</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>141.1900000000001</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.000000000000029e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8227723225802002</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-53.95000000000005</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.29517e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-74.402</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.1010356071492755</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.6008663326674747</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.382839315726722</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>10.18982465148447</v>
+      </c>
+      <c r="K19" t="n">
+        <v>79.32418504194004</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>y = 5.305x + -8737.158</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-8737.157956490941</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.769899736642806e-08</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>143</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.00000000000004e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8230382867241879</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-46.00999999999999</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.29603e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-74.532</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.4139037433154948</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.5054739652870959</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.297139451728147</v>
+      </c>
+      <c r="I20" t="n">
+        <v>597.5635477582638</v>
+      </c>
+      <c r="J20" t="n">
+        <v>7.925446018006033</v>
+      </c>
+      <c r="K20" t="n">
+        <v>76.44555650575067</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>y = 4.148x + -6563.056</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-6563.055618966206</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.050267230992006e-07</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>133.5</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.000000000008203e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8233282147880248</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-35.8900000000001</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.29874e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-74.678</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.079816513760966</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.162073669850004</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.324105621805775</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>9.00388309997849</v>
+      </c>
+      <c r="K21" t="n">
+        <v>66.39545723699418</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>y = 2.288x + -3177.936</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-3177.935540046626</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>4.423441237068347e-12</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>124.8700000000001</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8236014468632761</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-44.6099999999999</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.29975e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-74.821</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.2988756647136587</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.387271293560417</v>
+      </c>
+      <c r="H22" t="n">
+        <v>420.3744437853853</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.12848237024448</v>
+      </c>
+      <c r="J22" t="n">
+        <v>14.88860810910578</v>
+      </c>
+      <c r="K22" t="n">
+        <v>75.40248657078702</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>y = 3.840x + -5931.217</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-5931.216647222574</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>8.14539827550597e-08</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>133.3299999999999</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8238986609882004</v>
       </c>
     </row>
   </sheetData>
@@ -2058,12 +3670,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -2073,7 +3685,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -2118,19 +3730,19 @@
       <c r="K2" t="n">
         <v>85.58749317576543</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 12.959x + -32878.982</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-32878.98200338369</v>
       </c>
       <c r="Y2" t="n">
         <v>3.552265266815576e-11</v>
       </c>
       <c r="Z2" t="n">
-        <v>2810.028019172369</v>
+        <v>350.1300000000001</v>
       </c>
       <c r="AA2" t="n">
         <v>1e-08</v>
@@ -2170,19 +3782,19 @@
       <c r="K3" t="n">
         <v>86.33254120178223</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 15.601x + -34271.244</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-34271.2444060718</v>
       </c>
       <c r="Y3" t="n">
         <v>5.019998634059318e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>2503.763417908455</v>
+        <v>205.3099999999999</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000003e-08</v>
@@ -2222,19 +3834,19 @@
       <c r="K4" t="n">
         <v>86.52383344429219</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 16.462x + -34902.952</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-34902.95157167217</v>
       </c>
       <c r="Y4" t="n">
         <v>5.139725053026806e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>2425.264105437148</v>
+        <v>164.1799999999998</v>
       </c>
       <c r="AA4" t="n">
         <v>1.00000000000232e-08</v>
@@ -2274,19 +3886,19 @@
       <c r="K5" t="n">
         <v>85.47269265229681</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 12.629x + -25986.696</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-25986.6960195928</v>
       </c>
       <c r="Y5" t="n">
         <v>1.124254504031348e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>2384.578961884988</v>
+        <v>176.2399999999998</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000727e-08</v>
@@ -2326,19 +3938,19 @@
       <c r="K6" t="n">
         <v>84.95719505833407</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 11.333x + -22901.437</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-22901.43711584846</v>
       </c>
       <c r="Y6" t="n">
         <v>3.18119233942094e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>2352.222820883977</v>
+        <v>171.6299999999999</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000004e-08</v>
@@ -2378,19 +3990,19 @@
       <c r="K7" t="n">
         <v>85.06989948091764</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 11.593x + -23161.361</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-23161.36054999249</v>
       </c>
       <c r="Y7" t="n">
         <v>5.845755677649939e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>2321.25284060976</v>
+        <v>154.01</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000004895e-08</v>
@@ -2430,19 +4042,19 @@
       <c r="K8" t="n">
         <v>84.44551878995303</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 10.283x + -20177.810</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-20177.81004093328</v>
       </c>
       <c r="Y8" t="n">
         <v>1.546946160616957e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>2292.428652930454</v>
+        <v>156.1399999999999</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000006078e-08</v>
@@ -2482,19 +4094,19 @@
       <c r="K9" t="n">
         <v>84.07635978635334</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 9.638x + -18618.632</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-18618.63192384122</v>
       </c>
       <c r="Y9" t="n">
         <v>2.181426989628064e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>2263.067685503016</v>
+        <v>156.8499999999999</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000695e-08</v>
@@ -2534,19 +4146,19 @@
       <c r="K10" t="n">
         <v>83.30282229920091</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 8.516x + -16138.773</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-16138.77255993648</v>
       </c>
       <c r="Y10" t="n">
         <v>3.118462694968798e-11</v>
       </c>
       <c r="Z10" t="n">
-        <v>2235.436961411101</v>
+        <v>149.4200000000001</v>
       </c>
       <c r="AA10" t="n">
         <v>1e-08</v>
@@ -2586,19 +4198,19 @@
       <c r="K11" t="n">
         <v>82.24184420943112</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 7.340x + -13616.678</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-13616.67804076343</v>
       </c>
       <c r="Y11" t="n">
         <v>1.693786795954945e-08</v>
       </c>
       <c r="Z11" t="n">
-        <v>2208.050817214159</v>
+        <v>144.5700000000002</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000005911e-08</v>
@@ -2724,12 +4336,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -2739,7 +4351,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -2784,19 +4396,19 @@
       <c r="K2" t="n">
         <v>85.54930609885143</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 12.848x + -27994.550</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-27994.55023666909</v>
       </c>
       <c r="Y2" t="n">
         <v>3.356916661256501e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>2452.906615047635</v>
+        <v>335.8899999999999</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000002e-08</v>
@@ -2836,19 +4448,19 @@
       <c r="K3" t="n">
         <v>85.93282605545672</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 14.064x + -29049.093</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-29049.09257838171</v>
       </c>
       <c r="Y3" t="n">
         <v>6.253085997257166e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>2351.907718848481</v>
+        <v>233.6299999999999</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000007e-08</v>
@@ -2888,19 +4500,19 @@
       <c r="K4" t="n">
         <v>86.13302842758512</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 14.794x + -30116.335</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-30116.33539777904</v>
       </c>
       <c r="Y4" t="n">
         <v>6.813337324920056e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>2315.725769299457</v>
+        <v>197.1400000000001</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000033246e-08</v>
@@ -2940,19 +4552,19 @@
       <c r="K5" t="n">
         <v>85.87537354245515</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 13.867x + -27784.857</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-27784.85662755503</v>
       </c>
       <c r="Y5" t="n">
         <v>3.638750338927884e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>2287.05661856295</v>
+        <v>201.3899999999999</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000018e-08</v>
@@ -2992,19 +4604,19 @@
       <c r="K6" t="n">
         <v>85.63761957366458</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 13.109x + -25865.796</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-25865.7963457353</v>
       </c>
       <c r="Y6" t="n">
         <v>1.514072843960937e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>2258.473193636406</v>
+        <v>200.7600000000002</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000945e-08</v>
@@ -3044,19 +4656,19 @@
       <c r="K7" t="n">
         <v>85.45919496875602</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 12.592x + -24467.612</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-24467.6119776858</v>
       </c>
       <c r="Y7" t="n">
         <v>1.041207795952953e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>2229.732318649618</v>
+        <v>202.1500000000001</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000314e-08</v>
@@ -3096,19 +4708,19 @@
       <c r="K8" t="n">
         <v>85.56021029924068</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 12.879x + -24766.201</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-24766.20096783365</v>
       </c>
       <c r="Y8" t="n">
         <v>7.794897760382419e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>2201.885953625297</v>
+        <v>193.9899999999998</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000010577e-08</v>
@@ -3148,19 +4760,19 @@
       <c r="K9" t="n">
         <v>85.55940687519681</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 12.877x + -24464.530</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-24464.5295775602</v>
       </c>
       <c r="Y9" t="n">
         <v>6.677412408832826e-10</v>
       </c>
       <c r="Z9" t="n">
-        <v>2174.902578029177</v>
+        <v>191.02</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000308e-08</v>
@@ -3200,19 +4812,19 @@
       <c r="K10" t="n">
         <v>85.40422513712912</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 12.440x + -23321.493</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-23321.49282712353</v>
       </c>
       <c r="Y10" t="n">
         <v>3.005876595717843e-12</v>
       </c>
       <c r="Z10" t="n">
-        <v>2148.837317518531</v>
+        <v>185.9299999999998</v>
       </c>
       <c r="AA10" t="n">
         <v>1e-08</v>
@@ -3252,19 +4864,19 @@
       <c r="K11" t="n">
         <v>85.59276080069311</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 12.975x + -24113.264</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-24113.26421218426</v>
       </c>
       <c r="Y11" t="n">
         <v>2.088261798567025e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>2123.711437636119</v>
+        <v>173.3599999999999</v>
       </c>
       <c r="AA11" t="n">
         <v>1e-08</v>
@@ -3304,19 +4916,19 @@
       <c r="K12" t="n">
         <v>85.24697785761123</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 12.027x + -22010.598</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-22010.59773809439</v>
       </c>
       <c r="Y12" t="n">
         <v>1.782017767900564e-08</v>
       </c>
       <c r="Z12" t="n">
-        <v>2100.123766861156</v>
+        <v>177.8</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000013372e-08</v>
@@ -3356,19 +4968,19 @@
       <c r="K13" t="n">
         <v>85.05790523896528</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 11.565x + -20890.697</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-20890.69694865254</v>
       </c>
       <c r="Y13" t="n">
         <v>1.532804041585183e-08</v>
       </c>
       <c r="Z13" t="n">
-        <v>2077.061366627192</v>
+        <v>176.76</v>
       </c>
       <c r="AA13" t="n">
         <v>1.00000000000013e-08</v>
@@ -3408,19 +5020,19 @@
       <c r="K14" t="n">
         <v>84.97882892517599</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 11.382x + -20325.473</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-20325.47257140532</v>
       </c>
       <c r="Y14" t="n">
         <v>1.609562704242201e-08</v>
       </c>
       <c r="Z14" t="n">
-        <v>2053.947534549518</v>
+        <v>178.6100000000001</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000001e-08</v>
@@ -3460,19 +5072,19 @@
       <c r="K15" t="n">
         <v>85.18898742923123</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 11.881x + -21060.042</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-21060.04159968036</v>
       </c>
       <c r="Y15" t="n">
         <v>7.348741095256063e-08</v>
       </c>
       <c r="Z15" t="n">
-        <v>2032.367258601469</v>
+        <v>167.29</v>
       </c>
       <c r="AA15" t="n">
         <v>1e-08</v>
@@ -3512,19 +5124,19 @@
       <c r="K16" t="n">
         <v>84.35561416766511</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 10.118x + -17601.011</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-17601.01131604091</v>
       </c>
       <c r="Y16" t="n">
         <v>2.073449630468893e-09</v>
       </c>
       <c r="Z16" t="n">
-        <v>2010.869800452661</v>
+        <v>173.3599999999999</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000002504e-08</v>
@@ -3564,19 +5176,19 @@
       <c r="K17" t="n">
         <v>84.71072808275181</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 10.802x + -18658.892</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-18658.89170008088</v>
       </c>
       <c r="Y17" t="n">
         <v>194.9128416968672</v>
       </c>
       <c r="Z17" t="n">
-        <v>1997.956112222552</v>
+        <v>167.27</v>
       </c>
       <c r="AA17" t="n">
         <v>1.497888028501448e-08</v>
@@ -3616,19 +5228,19 @@
       <c r="K18" t="n">
         <v>84.69030337307916</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 10.760x + -18399.176</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-18399.17593732727</v>
       </c>
       <c r="Y18" t="n">
         <v>3.269855886123153e-08</v>
       </c>
       <c r="Z18" t="n">
-        <v>1968.709742936593</v>
+        <v>162.5899999999999</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000000175e-08</v>
@@ -3668,19 +5280,19 @@
       <c r="K19" t="n">
         <v>84.62588928958161</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 10.630x + -17983.916</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-17983.91603330377</v>
       </c>
       <c r="Y19" t="n">
         <v>3.499427388928672e-08</v>
       </c>
       <c r="Z19" t="n">
-        <v>1948.006773315955</v>
+        <v>155.6700000000001</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000000046e-08</v>
@@ -3720,19 +5332,19 @@
       <c r="K20" t="n">
         <v>84.1942210862541</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 9.835x + -16398.235</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-16398.23479152647</v>
       </c>
       <c r="Y20" t="n">
         <v>4.17880658220823e-08</v>
       </c>
       <c r="Z20" t="n">
-        <v>1926.945451865624</v>
+        <v>150.01</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000007e-08</v>
@@ -3772,19 +5384,19 @@
       <c r="K21" t="n">
         <v>84.19667320161133</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 9.839x + -16234.775</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-16234.77503383726</v>
       </c>
       <c r="Y21" t="n">
         <v>1.937766268094148e-08</v>
       </c>
       <c r="Z21" t="n">
-        <v>1906.448848261884</v>
+        <v>151.6700000000001</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000000126e-08</v>
@@ -3824,19 +5436,19 @@
       <c r="K22" t="n">
         <v>83.85151603775746</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 9.283x + -15107.811</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-15107.81057219486</v>
       </c>
       <c r="Y22" t="n">
         <v>4.752329891567776e-08</v>
       </c>
       <c r="Z22" t="n">
-        <v>1885.524683424949</v>
+        <v>150.71</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000001e-08</v>
@@ -3962,12 +5574,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -3977,7 +5589,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -4022,19 +5634,19 @@
       <c r="K2" t="n">
         <v>84.65983800603161</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 10.698x + -26706.686</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-26706.68584874164</v>
       </c>
       <c r="Y2" t="n">
         <v>7.883427900413313e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>2774.566121206715</v>
+        <v>441.52</v>
       </c>
       <c r="AA2" t="n">
         <v>1e-08</v>
@@ -4074,19 +5686,19 @@
       <c r="K3" t="n">
         <v>86.5720619659517</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 16.694x + -36140.694</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-36140.69431407058</v>
       </c>
       <c r="Y3" t="n">
         <v>5.593093609899253e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>2449.195621436328</v>
+        <v>246.0999999999999</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000056022e-08</v>
@@ -4126,19 +5738,19 @@
       <c r="K4" t="n">
         <v>86.49428931529927</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 16.323x + -33815.253</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-33815.25327228026</v>
       </c>
       <c r="Y4" t="n">
         <v>8.915161895167579e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>2369.31096873786</v>
+        <v>201.6700000000001</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000004e-08</v>
@@ -4178,19 +5790,19 @@
       <c r="K5" t="n">
         <v>86.54633220578661</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 16.570x + -33711.183</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-33711.18331039534</v>
       </c>
       <c r="Y5" t="n">
         <v>7.923251920167434e-10</v>
       </c>
       <c r="Z5" t="n">
-        <v>2330.488411175554</v>
+        <v>175.2399999999998</v>
       </c>
       <c r="AA5" t="n">
         <v>1e-08</v>
@@ -4230,19 +5842,19 @@
       <c r="K6" t="n">
         <v>86.40523466484903</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 15.918x + -31866.979</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-31866.97935458959</v>
       </c>
       <c r="Y6" t="n">
         <v>1.687712108181191e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>2298.737464489892</v>
+        <v>173.6199999999999</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000001e-08</v>
@@ -4282,19 +5894,19 @@
       <c r="K7" t="n">
         <v>86.50628571425651</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 16.379x + -32424.365</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-32424.3647979683</v>
       </c>
       <c r="Y7" t="n">
         <v>3.244383013434563e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>2268.743891509471</v>
+        <v>167.26</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000671e-08</v>
@@ -4334,19 +5946,19 @@
       <c r="K8" t="n">
         <v>86.46587755173864</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 16.192x + -31643.771</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-31643.77130862837</v>
       </c>
       <c r="Y8" t="n">
         <v>2.644520601076616e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>2239.643704997689</v>
+        <v>161.8799999999999</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000001247e-08</v>
@@ -4386,19 +5998,19 @@
       <c r="K9" t="n">
         <v>86.13663104753107</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 14.808x + -28471.886</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-28471.88613184045</v>
       </c>
       <c r="Y9" t="n">
         <v>6.680290477220372e-10</v>
       </c>
       <c r="Z9" t="n">
-        <v>2211.694723348148</v>
+        <v>163.8299999999999</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000001e-08</v>
@@ -4438,19 +6050,19 @@
       <c r="K10" t="n">
         <v>86.14507632132964</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 14.841x + -28195.277</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-28195.27725672555</v>
       </c>
       <c r="Y10" t="n">
         <v>2.566576168441471e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>2184.9101920838</v>
+        <v>161.55</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000002e-08</v>
@@ -4490,19 +6102,19 @@
       <c r="K11" t="n">
         <v>86.14517076772654</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 14.841x + -27865.281</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-27865.28103089625</v>
       </c>
       <c r="Y11" t="n">
         <v>4.576929854027643e-08</v>
       </c>
       <c r="Z11" t="n">
-        <v>2158.5683705583</v>
+        <v>158.3399999999999</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000002358e-08</v>
@@ -4628,12 +6240,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -4643,7 +6255,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -4688,19 +6300,19 @@
       <c r="K2" t="n">
         <v>86.07779278082386</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 14.585x + -31510.790</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-31510.78978625819</v>
       </c>
       <c r="Y2" t="n">
         <v>7.59263497276218e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>2448.172831186998</v>
+        <v>280.1100000000001</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000001174e-08</v>
@@ -4740,19 +6352,19 @@
       <c r="K3" t="n">
         <v>86.71101429127195</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 17.401x + -35754.912</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-35754.91170814761</v>
       </c>
       <c r="Y3" t="n">
         <v>4.882485990923643e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>2344.058287504316</v>
+        <v>178.1899999999998</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000328e-08</v>
@@ -4792,19 +6404,19 @@
       <c r="K4" t="n">
         <v>86.33261709878029</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 15.602x + -31305.693</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-31305.69343450797</v>
       </c>
       <c r="Y4" t="n">
         <v>1.391710035901277e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>2307.414050921421</v>
+        <v>175.9400000000003</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000033528e-08</v>
@@ -4844,19 +6456,19 @@
       <c r="K5" t="n">
         <v>86.40287891827006</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 15.907x + -31604.158</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-31604.15765627037</v>
       </c>
       <c r="Y5" t="n">
         <v>3.907241226290765e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>2281.789598885403</v>
+        <v>166.96</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000001366e-08</v>
@@ -4896,19 +6508,19 @@
       <c r="K6" t="n">
         <v>85.9769002109458</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 14.218x + -27814.628</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-27814.62822560456</v>
       </c>
       <c r="Y6" t="n">
         <v>8.138654619019943e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>2258.501092430848</v>
+        <v>173.8300000000002</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000017002e-08</v>
@@ -4948,19 +6560,19 @@
       <c r="K7" t="n">
         <v>86.27982389567983</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 15.380x + -29923.521</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-29923.52076585288</v>
       </c>
       <c r="Y7" t="n">
         <v>5.396713625197265e-10</v>
       </c>
       <c r="Z7" t="n">
-        <v>2236.416516125864</v>
+        <v>158.8900000000001</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000053e-08</v>
@@ -5000,19 +6612,19 @@
       <c r="K8" t="n">
         <v>86.20941217304882</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 15.093x + -29072.233</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-29072.23275389842</v>
       </c>
       <c r="Y8" t="n">
         <v>2.660286056378543e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>2214.540011872067</v>
+        <v>156.2399999999998</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000018e-08</v>
@@ -5052,19 +6664,19 @@
       <c r="K9" t="n">
         <v>85.79513385908204</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 13.602x + -25834.003</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-25834.00251372231</v>
       </c>
       <c r="Y9" t="n">
         <v>4.33698953844215e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>2193.210525266819</v>
+        <v>161.52</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000003773e-08</v>
@@ -5104,19 +6716,19 @@
       <c r="K10" t="n">
         <v>85.96567808557072</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 14.179x + -26722.421</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-26722.42094626218</v>
       </c>
       <c r="Y10" t="n">
         <v>1.41124281947301e-08</v>
       </c>
       <c r="Z10" t="n">
-        <v>2172.325156704148</v>
+        <v>158.6700000000001</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000008e-08</v>
@@ -5156,19 +6768,19 @@
       <c r="K11" t="n">
         <v>85.5172088672479</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 12.755x + -23727.640</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-23727.63986318794</v>
       </c>
       <c r="Y11" t="n">
         <v>9.229985201283662e-08</v>
       </c>
       <c r="Z11" t="n">
-        <v>2151.965347585302</v>
+        <v>154.72</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000004753e-08</v>
@@ -5208,19 +6820,19 @@
       <c r="K12" t="n">
         <v>85.56542189687642</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 12.894x + -23785.300</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-23785.29957196176</v>
       </c>
       <c r="Y12" t="n">
         <v>3.164702529728533e-08</v>
       </c>
       <c r="Z12" t="n">
-        <v>2132.172169751793</v>
+        <v>153.8299999999999</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000003629e-08</v>
@@ -5260,19 +6872,19 @@
       <c r="K13" t="n">
         <v>85.31747505331563</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 12.209x + -22260.508</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-22260.50799699948</v>
       </c>
       <c r="Y13" t="n">
         <v>1.113454508951787e-08</v>
       </c>
       <c r="Z13" t="n">
-        <v>2112.461221515814</v>
+        <v>156.6700000000001</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000326e-08</v>
@@ -5312,19 +6924,19 @@
       <c r="K14" t="n">
         <v>85.38524211641437</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 12.389x + -22421.764</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-22421.76430748341</v>
       </c>
       <c r="Y14" t="n">
         <v>6.866990322863331e-10</v>
       </c>
       <c r="Z14" t="n">
-        <v>2093.589109911672</v>
+        <v>144.05</v>
       </c>
       <c r="AA14" t="n">
         <v>1e-08</v>
@@ -5364,19 +6976,19 @@
       <c r="K15" t="n">
         <v>85.24034746041217</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 12.010x + -21513.078</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-21513.07805774334</v>
       </c>
       <c r="Y15" t="n">
         <v>9.524684903577736e-11</v>
       </c>
       <c r="Z15" t="n">
-        <v>2074.379845100409</v>
+        <v>144.22</v>
       </c>
       <c r="AA15" t="n">
         <v>1e-08</v>
@@ -5416,19 +7028,19 @@
       <c r="K16" t="n">
         <v>85.06827953940441</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 11.589x + -20537.699</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-20537.69861342705</v>
       </c>
       <c r="Y16" t="n">
         <v>4.791237062375483e-08</v>
       </c>
       <c r="Z16" t="n">
-        <v>2055.375363242407</v>
+        <v>148.51</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000005102e-08</v>
@@ -5468,19 +7080,19 @@
       <c r="K17" t="n">
         <v>85.19625531608348</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 11.899x + -20938.394</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-20938.39357372569</v>
       </c>
       <c r="Y17" t="n">
         <v>6.15130475819423e-09</v>
       </c>
       <c r="Z17" t="n">
-        <v>2036.978913403617</v>
+        <v>139.6499999999999</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000000003e-08</v>
@@ -5520,19 +7132,19 @@
       <c r="K18" t="n">
         <v>84.56143802201298</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 10.503x + -18212.152</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-18212.15246948718</v>
       </c>
       <c r="Y18" t="n">
         <v>215.439725150856</v>
       </c>
       <c r="Z18" t="n">
-        <v>1995.954777419473</v>
+        <v>140.5400000000002</v>
       </c>
       <c r="AA18" t="n">
         <v>1.421089080265279e-08</v>
@@ -5572,19 +7184,19 @@
       <c r="K19" t="n">
         <v>84.47851608554285</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 10.345x + -17767.175</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-17767.17453717029</v>
       </c>
       <c r="Y19" t="n">
         <v>6.232654591143145e-09</v>
       </c>
       <c r="Z19" t="n">
-        <v>1999.304523283349</v>
+        <v>141.52</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000000246e-08</v>
@@ -5624,19 +7236,19 @@
       <c r="K20" t="n">
         <v>84.09420207595871</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 9.667x + -16398.479</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-16398.47873422297</v>
       </c>
       <c r="Y20" t="n">
         <v>7.571974585333299e-10</v>
       </c>
       <c r="Z20" t="n">
-        <v>1980.823354486376</v>
+        <v>141.0899999999999</v>
       </c>
       <c r="AA20" t="n">
         <v>1e-08</v>
@@ -5676,19 +7288,19 @@
       <c r="K21" t="n">
         <v>84.01084049015429</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 9.532x + -16013.677</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-16013.67661334544</v>
       </c>
       <c r="Y21" t="n">
         <v>3.945118807396416e-09</v>
       </c>
       <c r="Z21" t="n">
-        <v>1962.866129307823</v>
+        <v>137.3699999999999</v>
       </c>
       <c r="AA21" t="n">
         <v>1e-08</v>
@@ -5728,19 +7340,19 @@
       <c r="K22" t="n">
         <v>83.67584587017204</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 9.023x + -14976.139</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-14976.13898527562</v>
       </c>
       <c r="Y22" t="n">
         <v>7.424481533400172e-08</v>
       </c>
       <c r="Z22" t="n">
-        <v>1944.151827818589</v>
+        <v>136.28</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000027e-08</v>
@@ -5866,12 +7478,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -5881,7 +7493,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -5926,19 +7538,19 @@
       <c r="K2" t="n">
         <v>84.5764744127804</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 10.533x + -25213.210</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-25213.20964593093</v>
       </c>
       <c r="Y2" t="n">
         <v>1.178533343438866e-12</v>
       </c>
       <c r="Z2" t="n">
-        <v>2658.812629016438</v>
+        <v>471.4099999999999</v>
       </c>
       <c r="AA2" t="n">
         <v>1e-08</v>
@@ -5978,19 +7590,19 @@
       <c r="K3" t="n">
         <v>86.17563969181897</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 14.960x + -31277.199</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-31277.19949447679</v>
       </c>
       <c r="Y3" t="n">
         <v>5.321018380837263e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>2379.381414814334</v>
+        <v>272.96</v>
       </c>
       <c r="AA3" t="n">
         <v>1.00000000001412e-08</v>
@@ -6030,19 +7642,19 @@
       <c r="K4" t="n">
         <v>86.54124499778651</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 16.545x + -33442.277</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-33442.27658870722</v>
       </c>
       <c r="Y4" t="n">
         <v>4.426657910376211e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>2308.640491278848</v>
+        <v>204.6400000000001</v>
       </c>
       <c r="AA4" t="n">
         <v>1.00000000000008e-08</v>
@@ -6082,19 +7694,19 @@
       <c r="K5" t="n">
         <v>86.6233617917888</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 16.949x + -33669.094</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-33669.09441678843</v>
       </c>
       <c r="Y5" t="n">
         <v>4.07323689996329e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>2271.301881635975</v>
+        <v>179.4899999999998</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000654e-08</v>
@@ -6134,19 +7746,19 @@
       <c r="K6" t="n">
         <v>86.46440893826606</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 16.185x + -31612.390</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-31612.38967299644</v>
       </c>
       <c r="Y6" t="n">
         <v>7.073228953434104e-12</v>
       </c>
       <c r="Z6" t="n">
-        <v>2239.342588407337</v>
+        <v>172.96</v>
       </c>
       <c r="AA6" t="n">
         <v>1e-08</v>
@@ -6186,19 +7798,19 @@
       <c r="K7" t="n">
         <v>86.55211011509773</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 16.598x + -32029.383</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-32029.38294373039</v>
       </c>
       <c r="Y7" t="n">
         <v>6.116323499204814e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>2208.626226218052</v>
+        <v>163.0899999999999</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000004567e-08</v>
@@ -6238,19 +7850,19 @@
       <c r="K8" t="n">
         <v>86.11491787455944</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 14.725x + -27888.574</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-27888.57401359933</v>
       </c>
       <c r="Y8" t="n">
         <v>5.751298632844075e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>2179.723996827127</v>
+        <v>172.02</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000048e-08</v>
@@ -6290,19 +7902,19 @@
       <c r="K9" t="n">
         <v>86.42202768193623</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 15.993x + -30042.783</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-30042.78279684855</v>
       </c>
       <c r="Y9" t="n">
         <v>7.808436692014853e-12</v>
       </c>
       <c r="Z9" t="n">
-        <v>2152.038528362595</v>
+        <v>154.3899999999999</v>
       </c>
       <c r="AA9" t="n">
         <v>1e-08</v>
@@ -6342,19 +7954,19 @@
       <c r="K10" t="n">
         <v>86.05687071797711</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 14.508x + -26793.564</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-26793.56365285002</v>
       </c>
       <c r="Y10" t="n">
         <v>1.31055830514826e-10</v>
       </c>
       <c r="Z10" t="n">
-        <v>2124.659760987732</v>
+        <v>164.21</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000012e-08</v>
@@ -6394,19 +8006,19 @@
       <c r="K11" t="n">
         <v>85.98428394516897</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 14.245x + -25988.778</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-25988.77844201832</v>
       </c>
       <c r="Y11" t="n">
         <v>4.568867439192769e-08</v>
       </c>
       <c r="Z11" t="n">
-        <v>2098.5094102756</v>
+        <v>154.51</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000003242e-08</v>
@@ -6532,12 +8144,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -6547,7 +8159,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -6592,19 +8204,19 @@
       <c r="K2" t="n">
         <v>86.16137949357943</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 14.904x + -31824.086</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-31824.08555246776</v>
       </c>
       <c r="Y2" t="n">
         <v>7.799273845483685e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>2416.473483771344</v>
+        <v>268.8200000000002</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000672e-08</v>
@@ -6644,19 +8256,19 @@
       <c r="K3" t="n">
         <v>86.79263340993062</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 17.845x + -36113.653</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-36113.65276631213</v>
       </c>
       <c r="Y3" t="n">
         <v>2.548953750599256e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>2306.410461792562</v>
+        <v>172.8399999999999</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000465e-08</v>
@@ -6696,19 +8308,19 @@
       <c r="K4" t="n">
         <v>86.54811692382954</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 16.578x + -32806.276</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-32806.27562153985</v>
       </c>
       <c r="Y4" t="n">
         <v>6.348775983279524e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>2268.352087800372</v>
+        <v>169.2199999999998</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000006328e-08</v>
@@ -6748,19 +8360,19 @@
       <c r="K5" t="n">
         <v>86.23674973217966</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 15.203x + -29618.191</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-29618.19054009091</v>
       </c>
       <c r="Y5" t="n">
         <v>4.366292432417547e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>2241.71034169518</v>
+        <v>169.1199999999999</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000001511e-08</v>
@@ -6800,19 +8412,19 @@
       <c r="K6" t="n">
         <v>86.24736211313162</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 15.246x + -29391.403</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-29391.40258984867</v>
       </c>
       <c r="Y6" t="n">
         <v>2.040892421831557e-12</v>
       </c>
       <c r="Z6" t="n">
-        <v>2217.495790347891</v>
+        <v>165.5200000000002</v>
       </c>
       <c r="AA6" t="n">
         <v>1e-08</v>
@@ -6852,19 +8464,19 @@
       <c r="K7" t="n">
         <v>86.11350596708473</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 14.720x + -28051.952</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-28051.95150293668</v>
       </c>
       <c r="Y7" t="n">
         <v>1.163827076607538e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>2194.09778788681</v>
+        <v>162.0000000000002</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000043812e-08</v>
@@ -6904,19 +8516,19 @@
       <c r="K8" t="n">
         <v>86.07504764752811</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 14.575x + -27492.437</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-27492.4371183081</v>
       </c>
       <c r="Y8" t="n">
         <v>5.421282168708254e-11</v>
       </c>
       <c r="Z8" t="n">
-        <v>2171.718961287622</v>
+        <v>161.76</v>
       </c>
       <c r="AA8" t="n">
         <v>1e-08</v>
@@ -6956,19 +8568,19 @@
       <c r="K9" t="n">
         <v>85.79693583129814</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 13.607x + -25366.283</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-25366.28310645062</v>
       </c>
       <c r="Y9" t="n">
         <v>5.800470212966129e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>2150.271644099466</v>
+        <v>158.45</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000005795e-08</v>
@@ -7008,19 +8620,19 @@
       <c r="K10" t="n">
         <v>85.73588205690906</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 13.412x + -24737.567</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-24737.56724248871</v>
       </c>
       <c r="Y10" t="n">
         <v>4.209818556764471e-08</v>
       </c>
       <c r="Z10" t="n">
-        <v>2129.886604784695</v>
+        <v>161.3199999999999</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000114e-08</v>
@@ -7060,19 +8672,19 @@
       <c r="K11" t="n">
         <v>85.48070060833098</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 12.652x + -23091.471</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-23091.47112830595</v>
       </c>
       <c r="Y11" t="n">
         <v>3.282787595306996e-08</v>
       </c>
       <c r="Z11" t="n">
-        <v>2109.777906018549</v>
+        <v>152.3800000000001</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000349e-08</v>
@@ -7112,19 +8724,19 @@
       <c r="K12" t="n">
         <v>85.81920739517349</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 13.680x + -24835.845</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-24835.84474048759</v>
       </c>
       <c r="Y12" t="n">
         <v>1.596273875510573e-10</v>
       </c>
       <c r="Z12" t="n">
-        <v>2091.004586416669</v>
+        <v>145.77</v>
       </c>
       <c r="AA12" t="n">
         <v>1.00000000000047e-08</v>
@@ -7164,19 +8776,19 @@
       <c r="K13" t="n">
         <v>85.62399170057979</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 13.068x + -23470.116</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-23470.11550650002</v>
       </c>
       <c r="Y13" t="n">
         <v>1.424799153077533e-08</v>
       </c>
       <c r="Z13" t="n">
-        <v>2072.679106968035</v>
+        <v>148.5999999999999</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000005907e-08</v>
@@ -7216,19 +8828,19 @@
       <c r="K14" t="n">
         <v>85.55071496161554</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 12.852x + -22874.387</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-22874.38725960436</v>
       </c>
       <c r="Y14" t="n">
         <v>3.63933232433278e-08</v>
       </c>
       <c r="Z14" t="n">
-        <v>2054.57121273991</v>
+        <v>147.95</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000386e-08</v>
@@ -7268,19 +8880,19 @@
       <c r="K15" t="n">
         <v>85.14591459323887</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 11.775x + -20697.785</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-20697.7849186613</v>
       </c>
       <c r="Y15" t="n">
         <v>8.284350392887859e-08</v>
       </c>
       <c r="Z15" t="n">
-        <v>2036.907459823528</v>
+        <v>154.4200000000001</v>
       </c>
       <c r="AA15" t="n">
         <v>1.00000000000012e-08</v>
@@ -7320,19 +8932,19 @@
       <c r="K16" t="n">
         <v>85.20306171179796</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 11.916x + -20792.965</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-20792.96495376527</v>
       </c>
       <c r="Y16" t="n">
         <v>3.120711221992213e-08</v>
       </c>
       <c r="Z16" t="n">
-        <v>2019.117536474495</v>
+        <v>144.3700000000001</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000001246e-08</v>
@@ -7372,19 +8984,19 @@
       <c r="K17" t="n">
         <v>85.0082594806691</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 11.449x + -19771.984</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-19771.9837905243</v>
       </c>
       <c r="Y17" t="n">
         <v>3.16789655310853e-09</v>
       </c>
       <c r="Z17" t="n">
-        <v>2001.861790416041</v>
+        <v>142.6499999999999</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000000738e-08</v>
@@ -7424,19 +9036,19 @@
       <c r="K18" t="n">
         <v>84.95622239657972</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 11.330x + -19394.370</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-19394.36958960264</v>
       </c>
       <c r="Y18" t="n">
         <v>213.0517617979157</v>
       </c>
       <c r="Z18" t="n">
-        <v>1982.412671349128</v>
+        <v>144.3300000000002</v>
       </c>
       <c r="AA18" t="n">
         <v>1.464092348456783e-08</v>
@@ -7476,19 +9088,19 @@
       <c r="K19" t="n">
         <v>84.37381452768477</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 10.151x + -17141.683</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-17141.6828876498</v>
       </c>
       <c r="Y19" t="n">
         <v>1.566822510386609e-08</v>
       </c>
       <c r="Z19" t="n">
-        <v>1967.190607268022</v>
+        <v>135.5</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000000009e-08</v>
@@ -7528,19 +9140,19 @@
       <c r="K20" t="n">
         <v>84.05341940455079</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 9.600x + -16025.173</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-16025.17259570055</v>
       </c>
       <c r="Y20" t="n">
         <v>1.245367317068335e-07</v>
       </c>
       <c r="Z20" t="n">
-        <v>1949.403625562016</v>
+        <v>138.52</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000001419e-08</v>
@@ -7580,19 +9192,19 @@
       <c r="K21" t="n">
         <v>83.89363160979561</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 9.347x + -15454.234</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-15454.23373669312</v>
       </c>
       <c r="Y21" t="n">
         <v>1.185533263051768e-09</v>
       </c>
       <c r="Z21" t="n">
-        <v>1932.263815453651</v>
+        <v>140.25</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000000485e-08</v>
@@ -7632,19 +9244,19 @@
       <c r="K22" t="n">
         <v>83.86981723841019</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 9.311x + -15254.374</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-15254.3744343405</v>
       </c>
       <c r="Y22" t="n">
         <v>5.341544813221286e-08</v>
       </c>
       <c r="Z22" t="n">
-        <v>1915.068446222447</v>
+        <v>135.3700000000001</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000105e-08</v>
@@ -7770,12 +9382,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -7785,7 +9397,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -7830,19 +9442,19 @@
       <c r="K2" t="n">
         <v>86.06649056588259</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 14.543x + -26607.760</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-26607.76010804871</v>
       </c>
       <c r="Y2" t="n">
         <v>2.561212350355966e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>2002.081351190302</v>
+        <v>327.9499999999998</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000025406e-08</v>
@@ -7882,19 +9494,19 @@
       <c r="K3" t="n">
         <v>86.76546241648256</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 17.695x + -28977.903</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-28977.90291191796</v>
       </c>
       <c r="Y3" t="n">
         <v>7.958536421594163e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>1845.078878028542</v>
+        <v>187.1799999999998</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000006e-08</v>
@@ -7934,19 +9546,19 @@
       <c r="K4" t="n">
         <v>86.96343756573788</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 18.851x + -30029.175</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-30029.17494132651</v>
       </c>
       <c r="Y4" t="n">
         <v>6.629517581915167e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>1799.075986342032</v>
+        <v>136.4099999999999</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000002e-08</v>
@@ -7986,19 +9598,19 @@
       <c r="K5" t="n">
         <v>86.90504759300956</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 18.495x + -28940.059</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-28940.05921438317</v>
       </c>
       <c r="Y5" t="n">
         <v>9.655467005359109e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>1769.28253467059</v>
+        <v>128.22</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000139312e-08</v>
@@ -8038,19 +9650,19 @@
       <c r="K6" t="n">
         <v>86.7663765867857</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 17.700x + -27231.773</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-27231.77261128127</v>
       </c>
       <c r="Y6" t="n">
         <v>2.037721765307055e-11</v>
       </c>
       <c r="Z6" t="n">
-        <v>1741.065750781662</v>
+        <v>121.96</v>
       </c>
       <c r="AA6" t="n">
         <v>1e-08</v>
@@ -8090,19 +9702,19 @@
       <c r="K7" t="n">
         <v>86.62685619091015</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 16.966x + -25668.738</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-25668.73843584974</v>
       </c>
       <c r="Y7" t="n">
         <v>1.544063932410871e-11</v>
       </c>
       <c r="Z7" t="n">
-        <v>1713.29247573609</v>
+        <v>119.9400000000001</v>
       </c>
       <c r="AA7" t="n">
         <v>1e-08</v>
@@ -8142,19 +9754,19 @@
       <c r="K8" t="n">
         <v>86.30373212081655</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 15.479x + -22966.881</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-22966.88120499742</v>
       </c>
       <c r="Y8" t="n">
         <v>4.502247663862155e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>1686.289858227703</v>
+        <v>120.27</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000003e-08</v>
@@ -8194,19 +9806,19 @@
       <c r="K9" t="n">
         <v>86.36723549598375</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 15.751x + -23053.042</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-23053.0418001188</v>
       </c>
       <c r="Y9" t="n">
         <v>5.548853834689077e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>1659.747023603323</v>
+        <v>109.6899999999998</v>
       </c>
       <c r="AA9" t="n">
         <v>1e-08</v>
@@ -8246,19 +9858,19 @@
       <c r="K10" t="n">
         <v>85.86676725399651</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 13.838x + -19835.018</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-19835.01773981188</v>
       </c>
       <c r="Y10" t="n">
         <v>7.439743487959913e-08</v>
       </c>
       <c r="Z10" t="n">
-        <v>1634.862859063115</v>
+        <v>117.3099999999999</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000025642e-08</v>
@@ -8298,19 +9910,19 @@
       <c r="K11" t="n">
         <v>85.99200204422762</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 14.272x + -20223.121</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-20223.12058336674</v>
       </c>
       <c r="Y11" t="n">
         <v>3.277321864779594e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>1611.30018337099</v>
+        <v>103.52</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000005047e-08</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 37.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 37.xlsx
@@ -528,12 +528,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -588,10 +588,8 @@
       <c r="K2" t="n">
         <v>86.213808969772</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 15.111x + -33884.433</t>
-        </is>
+      <c r="W2" t="n">
+        <v>15.11079491418703</v>
       </c>
       <c r="X2" t="n">
         <v>-33884.43280066451</v>
@@ -600,7 +598,7 @@
         <v>1.893447249540654e-11</v>
       </c>
       <c r="Z2" t="n">
-        <v>218.6599999999999</v>
+        <v>2578.408537518617</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000053e-08</v>
@@ -640,10 +638,8 @@
       <c r="K3" t="n">
         <v>86.51638124513785</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 16.427x + -35829.666</t>
-        </is>
+      <c r="W3" t="n">
+        <v>16.42692960319695</v>
       </c>
       <c r="X3" t="n">
         <v>-35829.66572203031</v>
@@ -652,7 +648,7 @@
         <v>1.361102179100492e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>179.6999999999998</v>
+        <v>2497.589322194382</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000198e-08</v>
@@ -692,10 +688,8 @@
       <c r="K4" t="n">
         <v>86.16211128698326</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 14.907x + -31582.833</t>
-        </is>
+      <c r="W4" t="n">
+        <v>14.90664947099158</v>
       </c>
       <c r="X4" t="n">
         <v>-31582.83307428906</v>
@@ -704,7 +698,7 @@
         <v>3.012713234428511e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>178.5599999999999</v>
+        <v>2438.852105202525</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000014e-08</v>
@@ -744,10 +738,8 @@
       <c r="K5" t="n">
         <v>86.04141363964973</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 14.451x + -29997.910</t>
-        </is>
+      <c r="W5" t="n">
+        <v>14.45076058823592</v>
       </c>
       <c r="X5" t="n">
         <v>-29997.91033496923</v>
@@ -756,7 +748,7 @@
         <v>3.92679535815329e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>174.04</v>
+        <v>2391.33213503281</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000019e-08</v>
@@ -796,10 +788,8 @@
       <c r="K6" t="n">
         <v>86.12432079972868</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 14.761x + -30169.335</t>
-        </is>
+      <c r="W6" t="n">
+        <v>14.76086174755428</v>
       </c>
       <c r="X6" t="n">
         <v>-30169.33452599037</v>
@@ -808,7 +798,7 @@
         <v>1.027390056868385e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>160.9699999999998</v>
+        <v>2350.327227582303</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000624e-08</v>
@@ -848,10 +838,8 @@
       <c r="K7" t="n">
         <v>85.77123499468352</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 13.524x + -27115.043</t>
-        </is>
+      <c r="W7" t="n">
+        <v>13.52444643847756</v>
       </c>
       <c r="X7" t="n">
         <v>-27115.04254575271</v>
@@ -860,7 +848,7 @@
         <v>9.673578386447352e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>162.6900000000001</v>
+        <v>2314.549376081962</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000015006e-08</v>
@@ -900,10 +888,8 @@
       <c r="K8" t="n">
         <v>85.37825944008871</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 12.370x + -24374.263</t>
-        </is>
+      <c r="W8" t="n">
+        <v>12.37011350224619</v>
       </c>
       <c r="X8" t="n">
         <v>-24374.26331696161</v>
@@ -912,7 +898,7 @@
         <v>6.597009395349453e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>163.1500000000001</v>
+        <v>2282.704001911986</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000718e-08</v>
@@ -952,10 +938,8 @@
       <c r="K9" t="n">
         <v>85.27434755980602</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 12.097x + -23530.521</t>
-        </is>
+      <c r="W9" t="n">
+        <v>12.09691152370871</v>
       </c>
       <c r="X9" t="n">
         <v>-23530.52061652963</v>
@@ -964,7 +948,7 @@
         <v>1.954969134266329e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>156.0999999999997</v>
+        <v>2254.143282146671</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000055e-08</v>
@@ -1004,10 +988,8 @@
       <c r="K10" t="n">
         <v>84.74055280911873</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 10.863x + -20787.562</t>
-        </is>
+      <c r="W10" t="n">
+        <v>10.86326323359942</v>
       </c>
       <c r="X10" t="n">
         <v>-20787.56162940363</v>
@@ -1016,7 +998,7 @@
         <v>9.333546903233828e-08</v>
       </c>
       <c r="Z10" t="n">
-        <v>151.1499999999999</v>
+        <v>2227.503790509776</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000005741e-08</v>
@@ -1056,10 +1038,8 @@
       <c r="K11" t="n">
         <v>84.58879417662122</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 10.557x + -19951.747</t>
-        </is>
+      <c r="W11" t="n">
+        <v>10.5568572289101</v>
       </c>
       <c r="X11" t="n">
         <v>-19951.74725563313</v>
@@ -1068,7 +1048,7 @@
         <v>2.680971884019061e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>148.2199999999998</v>
+        <v>2201.678702542886</v>
       </c>
       <c r="AA11" t="n">
         <v>1e-08</v>
@@ -1194,12 +1174,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -1254,10 +1234,8 @@
       <c r="K2" t="n">
         <v>85.45957009787902</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 12.593x + -27042.640</t>
-        </is>
+      <c r="W2" t="n">
+        <v>12.59259461433588</v>
       </c>
       <c r="X2" t="n">
         <v>-27042.63991557862</v>
@@ -1266,7 +1244,7 @@
         <v>7.82174430945274e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>187.77</v>
+        <v>2455.265262115215</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000002501e-08</v>
@@ -1306,10 +1284,8 @@
       <c r="K3" t="n">
         <v>85.63132537760877</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 13.090x + -26524.848</t>
-        </is>
+      <c r="W3" t="n">
+        <v>13.08971427682943</v>
       </c>
       <c r="X3" t="n">
         <v>-26524.84820753023</v>
@@ -1318,7 +1294,7 @@
         <v>5.421866676084226e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>162.3600000000001</v>
+        <v>2339.950276312656</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000162e-08</v>
@@ -1358,10 +1334,8 @@
       <c r="K4" t="n">
         <v>85.4876478688723</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 12.671x + -25166.402</t>
-        </is>
+      <c r="W4" t="n">
+        <v>12.67127907417432</v>
       </c>
       <c r="X4" t="n">
         <v>-25166.40150012512</v>
@@ -1370,7 +1344,7 @@
         <v>1.089600563549254e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>162.1600000000001</v>
+        <v>2300.817529950784</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000091e-08</v>
@@ -1410,10 +1384,8 @@
       <c r="K5" t="n">
         <v>84.84286460311084</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 11.080x + -21632.250</t>
-        </is>
+      <c r="W5" t="n">
+        <v>11.07998180379455</v>
       </c>
       <c r="X5" t="n">
         <v>-21632.2498408126</v>
@@ -1422,7 +1394,7 @@
         <v>3.547081525494212e-12</v>
       </c>
       <c r="Z5" t="n">
-        <v>159.1199999999999</v>
+        <v>2274.467984741103</v>
       </c>
       <c r="AA5" t="n">
         <v>1e-08</v>
@@ -1462,10 +1434,8 @@
       <c r="K6" t="n">
         <v>84.7323776488215</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 10.846x + -20927.315</t>
-        </is>
+      <c r="W6" t="n">
+        <v>10.84630868447197</v>
       </c>
       <c r="X6" t="n">
         <v>-20927.31508191576</v>
@@ -1474,7 +1444,7 @@
         <v>1.519006579676908e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>165</v>
+        <v>2250.89898729645</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000003463e-08</v>
@@ -1514,10 +1484,8 @@
       <c r="K7" t="n">
         <v>84.59105134495663</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 10.561x + -20154.181</t>
-        </is>
+      <c r="W7" t="n">
+        <v>10.56128893297003</v>
       </c>
       <c r="X7" t="n">
         <v>-20154.1812093094</v>
@@ -1526,7 +1494,7 @@
         <v>7.422382637472134e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>157.8499999999999</v>
+        <v>2227.315017743516</v>
       </c>
       <c r="AA7" t="n">
         <v>1.00000000000006e-08</v>
@@ -1566,10 +1534,8 @@
       <c r="K8" t="n">
         <v>84.90403921391294</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 11.214x + -21251.371</t>
-        </is>
+      <c r="W8" t="n">
+        <v>11.21370860709948</v>
       </c>
       <c r="X8" t="n">
         <v>-21251.371166875</v>
@@ -1578,7 +1544,7 @@
         <v>5.054772902839284e-11</v>
       </c>
       <c r="Z8" t="n">
-        <v>147.28</v>
+        <v>2204.953974872117</v>
       </c>
       <c r="AA8" t="n">
         <v>1e-08</v>
@@ -1618,10 +1584,8 @@
       <c r="K9" t="n">
         <v>84.33061355650793</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 10.073x + -18808.393</t>
-        </is>
+      <c r="W9" t="n">
+        <v>10.07316464817905</v>
       </c>
       <c r="X9" t="n">
         <v>-18808.39280830049</v>
@@ -1630,7 +1594,7 @@
         <v>6.426184467443721e-10</v>
       </c>
       <c r="Z9" t="n">
-        <v>152.4399999999998</v>
+        <v>2182.927240455587</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000414e-08</v>
@@ -1670,10 +1634,8 @@
       <c r="K10" t="n">
         <v>84.13571377470832</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 9.736x + -17977.213</t>
-        </is>
+      <c r="W10" t="n">
+        <v>9.736149532744328</v>
       </c>
       <c r="X10" t="n">
         <v>-17977.21283307825</v>
@@ -1682,7 +1644,7 @@
         <v>1.505208771916953e-08</v>
       </c>
       <c r="Z10" t="n">
-        <v>144.74</v>
+        <v>2161.994632413858</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000001e-08</v>
@@ -1722,10 +1684,8 @@
       <c r="K11" t="n">
         <v>83.62693198340274</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 8.953x + -16308.549</t>
-        </is>
+      <c r="W11" t="n">
+        <v>8.953190197812932</v>
       </c>
       <c r="X11" t="n">
         <v>-16308.54884706572</v>
@@ -1734,7 +1694,7 @@
         <v>4.609727969716513e-08</v>
       </c>
       <c r="Z11" t="n">
-        <v>152.3099999999999</v>
+        <v>2141.491163647627</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000093e-08</v>
@@ -1774,10 +1734,8 @@
       <c r="K12" t="n">
         <v>83.83798892062528</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 9.262x + -16752.711</t>
-        </is>
+      <c r="W12" t="n">
+        <v>9.262350478321244</v>
       </c>
       <c r="X12" t="n">
         <v>-16752.71122741924</v>
@@ -1786,7 +1744,7 @@
         <v>2.97940369360391e-10</v>
       </c>
       <c r="Z12" t="n">
-        <v>144.76</v>
+        <v>2122.427144644078</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000018457e-08</v>
@@ -1826,10 +1784,8 @@
       <c r="K13" t="n">
         <v>83.20322023117525</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 8.390x + -14960.873</t>
-        </is>
+      <c r="W13" t="n">
+        <v>8.390262785299676</v>
       </c>
       <c r="X13" t="n">
         <v>-14960.87306688871</v>
@@ -1838,7 +1794,7 @@
         <v>2.452407163255564e-10</v>
       </c>
       <c r="Z13" t="n">
-        <v>142.1400000000001</v>
+        <v>2103.396953553567</v>
       </c>
       <c r="AA13" t="n">
         <v>1e-08</v>
@@ -1878,10 +1834,8 @@
       <c r="K14" t="n">
         <v>83.31039133485693</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 8.526x + -15087.396</t>
-        </is>
+      <c r="W14" t="n">
+        <v>8.525938583617762</v>
       </c>
       <c r="X14" t="n">
         <v>-15087.39618723035</v>
@@ -1890,7 +1844,7 @@
         <v>5.31530856367991e-08</v>
       </c>
       <c r="Z14" t="n">
-        <v>144.71</v>
+        <v>2084.708174013747</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000003199e-08</v>
@@ -1930,10 +1884,8 @@
       <c r="K15" t="n">
         <v>82.77205570185487</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 7.885x + -13762.451</t>
-        </is>
+      <c r="W15" t="n">
+        <v>7.884886174652769</v>
       </c>
       <c r="X15" t="n">
         <v>-13762.45113829071</v>
@@ -1942,7 +1894,7 @@
         <v>2.631295866833511e-08</v>
       </c>
       <c r="Z15" t="n">
-        <v>138.53</v>
+        <v>2066.81775251792</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000000053e-08</v>
@@ -1982,10 +1934,8 @@
       <c r="K16" t="n">
         <v>81.37261339886355</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 6.591x + -11265.956</t>
-        </is>
+      <c r="W16" t="n">
+        <v>6.590883140842604</v>
       </c>
       <c r="X16" t="n">
         <v>-11265.9556534322</v>
@@ -1994,7 +1944,7 @@
         <v>7.345875151367063e-08</v>
       </c>
       <c r="Z16" t="n">
-        <v>136.3899999999999</v>
+        <v>2048.792832840928</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000000946e-08</v>
@@ -2034,10 +1984,8 @@
       <c r="K17" t="n">
         <v>81.0653623008742</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 6.361x + -10747.536</t>
-        </is>
+      <c r="W17" t="n">
+        <v>6.360706249932048</v>
       </c>
       <c r="X17" t="n">
         <v>-10747.53572476451</v>
@@ -2046,7 +1994,7 @@
         <v>225.4520561701192</v>
       </c>
       <c r="Z17" t="n">
-        <v>134.0699999999999</v>
+        <v>2039.051996498125</v>
       </c>
       <c r="AA17" t="n">
         <v>1.510715789863713e-08</v>
@@ -2086,10 +2034,8 @@
       <c r="K18" t="n">
         <v>81.44626384795927</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 6.648x + -11194.779</t>
-        </is>
+      <c r="W18" t="n">
+        <v>6.648496026660166</v>
       </c>
       <c r="X18" t="n">
         <v>-11194.77942225678</v>
@@ -2098,7 +2044,7 @@
         <v>1.014639549571414e-08</v>
       </c>
       <c r="Z18" t="n">
-        <v>135.8099999999999</v>
+        <v>2013.7784627959</v>
       </c>
       <c r="AA18" t="n">
         <v>1e-08</v>
@@ -2138,10 +2084,8 @@
       <c r="K19" t="n">
         <v>80.34224241284748</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 5.876x + -9714.786</t>
-        </is>
+      <c r="W19" t="n">
+        <v>5.876324005354421</v>
       </c>
       <c r="X19" t="n">
         <v>-9714.786155060667</v>
@@ -2150,7 +2094,7 @@
         <v>9.581678617117404e-09</v>
       </c>
       <c r="Z19" t="n">
-        <v>135.3399999999999</v>
+        <v>1996.461483575034</v>
       </c>
       <c r="AA19" t="n">
         <v>1e-08</v>
@@ -2190,10 +2134,8 @@
       <c r="K20" t="n">
         <v>79.69222702606045</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 5.498x + -8955.315</t>
-        </is>
+      <c r="W20" t="n">
+        <v>5.49840428730893</v>
       </c>
       <c r="X20" t="n">
         <v>-8955.315205019604</v>
@@ -2202,7 +2144,7 @@
         <v>5.375682099186868e-08</v>
       </c>
       <c r="Z20" t="n">
-        <v>131.54</v>
+        <v>1978.463301056841</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000274e-08</v>
@@ -2242,10 +2184,8 @@
       <c r="K21" t="n">
         <v>68.33184752971762</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 2.517x + -3596.283</t>
-        </is>
+      <c r="W21" t="n">
+        <v>2.516960505517481</v>
       </c>
       <c r="X21" t="n">
         <v>-3596.283406158472</v>
@@ -2254,7 +2194,7 @@
         <v>2.294079101179809e-09</v>
       </c>
       <c r="Z21" t="n">
-        <v>126.05</v>
+        <v>1960.980244700381</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000000001e-08</v>
@@ -2294,10 +2234,8 @@
       <c r="K22" t="n">
         <v>77.64371908125486</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 4.565x + -7184.518</t>
-        </is>
+      <c r="W22" t="n">
+        <v>4.564866310470252</v>
       </c>
       <c r="X22" t="n">
         <v>-7184.517534263151</v>
@@ -2306,7 +2244,7 @@
         <v>3.962954813716136e-08</v>
       </c>
       <c r="Z22" t="n">
-        <v>130.9099999999999</v>
+        <v>1943.195022111756</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000001e-08</v>
@@ -2432,12 +2370,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -2492,10 +2430,8 @@
       <c r="K2" t="n">
         <v>86.30453737813669</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 15.483x + -32328.171</t>
-        </is>
+      <c r="W2" t="n">
+        <v>15.4828538005469</v>
       </c>
       <c r="X2" t="n">
         <v>-32328.17147043583</v>
@@ -2504,7 +2440,7 @@
         <v>6.759203652615179e-12</v>
       </c>
       <c r="Z2" t="n">
-        <v>173.98</v>
+        <v>2390.816269073804</v>
       </c>
       <c r="AA2" t="n">
         <v>1e-08</v>
@@ -2544,10 +2480,8 @@
       <c r="K3" t="n">
         <v>85.93608381357207</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 14.075x + -28618.126</t>
-        </is>
+      <c r="W3" t="n">
+        <v>14.07501086633753</v>
       </c>
       <c r="X3" t="n">
         <v>-28618.12641874233</v>
@@ -2556,7 +2490,7 @@
         <v>6.420144283658278e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>170.9100000000001</v>
+        <v>2343.605233010768</v>
       </c>
       <c r="AA3" t="n">
         <v>1.00000000000424e-08</v>
@@ -2596,10 +2530,8 @@
       <c r="K4" t="n">
         <v>85.67170262351074</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 13.212x + -26459.303</t>
-        </is>
+      <c r="W4" t="n">
+        <v>13.21229623021994</v>
       </c>
       <c r="X4" t="n">
         <v>-26459.30299960887</v>
@@ -2608,7 +2540,7 @@
         <v>6.911585327235647e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>164.04</v>
+        <v>2314.315309352774</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000001963e-08</v>
@@ -2648,10 +2580,8 @@
       <c r="K5" t="n">
         <v>85.33004455851005</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 12.242x + -24151.196</t>
-        </is>
+      <c r="W5" t="n">
+        <v>12.24183986044723</v>
       </c>
       <c r="X5" t="n">
         <v>-24151.1958163995</v>
@@ -2660,7 +2590,7 @@
         <v>3.081182921806102e-10</v>
       </c>
       <c r="Z5" t="n">
-        <v>167.2700000000002</v>
+        <v>2287.834550709267</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000001058e-08</v>
@@ -2700,10 +2630,8 @@
       <c r="K6" t="n">
         <v>85.03478076531864</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 11.511x + -22407.568</t>
-        </is>
+      <c r="W6" t="n">
+        <v>11.51052496840783</v>
       </c>
       <c r="X6" t="n">
         <v>-22407.56782625177</v>
@@ -2712,7 +2640,7 @@
         <v>2.83114843799154e-11</v>
       </c>
       <c r="Z6" t="n">
-        <v>162.74</v>
+        <v>2262.839999367438</v>
       </c>
       <c r="AA6" t="n">
         <v>1e-08</v>
@@ -2752,10 +2680,8 @@
       <c r="K7" t="n">
         <v>84.2400002662892</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 9.914x + -18982.498</t>
-        </is>
+      <c r="W7" t="n">
+        <v>9.913651483187909</v>
       </c>
       <c r="X7" t="n">
         <v>-18982.49840342342</v>
@@ -2764,7 +2690,7 @@
         <v>1.495115508536951e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>157.27</v>
+        <v>2238.890647832516</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000559e-08</v>
@@ -2804,10 +2730,8 @@
       <c r="K8" t="n">
         <v>84.43062595896234</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 10.255x + -19465.724</t>
-        </is>
+      <c r="W8" t="n">
+        <v>10.25522982194955</v>
       </c>
       <c r="X8" t="n">
         <v>-19465.72351907413</v>
@@ -2816,7 +2740,7 @@
         <v>7.737159419216305e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>160.6300000000001</v>
+        <v>2215.767698232795</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000122e-08</v>
@@ -2856,10 +2780,8 @@
       <c r="K9" t="n">
         <v>84.45046240258837</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 10.292x + -19339.904</t>
-        </is>
+      <c r="W9" t="n">
+        <v>10.29211795212646</v>
       </c>
       <c r="X9" t="n">
         <v>-19339.90430714014</v>
@@ -2868,7 +2790,7 @@
         <v>3.828090437360283e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>156.0900000000001</v>
+        <v>2193.053516771275</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000009e-08</v>
@@ -2908,10 +2830,8 @@
       <c r="K10" t="n">
         <v>83.6422461829779</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 8.975x + -16594.348</t>
-        </is>
+      <c r="W10" t="n">
+        <v>8.974934835992356</v>
       </c>
       <c r="X10" t="n">
         <v>-16594.34793244085</v>
@@ -2920,7 +2840,7 @@
         <v>3.230477346280985e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>154.1000000000001</v>
+        <v>2171.461490941084</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000039e-08</v>
@@ -2960,10 +2880,8 @@
       <c r="K11" t="n">
         <v>83.31773182951167</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 8.535x + -15596.079</t>
-        </is>
+      <c r="W11" t="n">
+        <v>8.535389969490076</v>
       </c>
       <c r="X11" t="n">
         <v>-15596.07931553804</v>
@@ -2972,7 +2890,7 @@
         <v>3.684517039775811e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>156.9100000000001</v>
+        <v>2151.274158037089</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000403e-08</v>
@@ -3012,10 +2930,8 @@
       <c r="K12" t="n">
         <v>83.03145397549866</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 8.181x + -14769.675</t>
-        </is>
+      <c r="W12" t="n">
+        <v>8.18147515995436</v>
       </c>
       <c r="X12" t="n">
         <v>-14769.67481251643</v>
@@ -3024,7 +2940,7 @@
         <v>7.446918971046903e-09</v>
       </c>
       <c r="Z12" t="n">
-        <v>149.9400000000001</v>
+        <v>2131.326899902479</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000002036e-08</v>
@@ -3064,10 +2980,8 @@
       <c r="K13" t="n">
         <v>83.58078884250946</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 8.888x + -15975.074</t>
-        </is>
+      <c r="W13" t="n">
+        <v>8.888296224222582</v>
       </c>
       <c r="X13" t="n">
         <v>-15975.07404308421</v>
@@ -3076,7 +2990,7 @@
         <v>7.181384087052383e-08</v>
       </c>
       <c r="Z13" t="n">
-        <v>145.6099999999999</v>
+        <v>2111.343376094178</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000002e-08</v>
@@ -3116,10 +3030,8 @@
       <c r="K14" t="n">
         <v>82.47404990565391</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 7.569x + -13355.789</t>
-        </is>
+      <c r="W14" t="n">
+        <v>7.569261213164475</v>
       </c>
       <c r="X14" t="n">
         <v>-13355.78921682381</v>
@@ -3128,7 +3040,7 @@
         <v>6.494330681542102e-08</v>
       </c>
       <c r="Z14" t="n">
-        <v>148.23</v>
+        <v>2091.041853246386</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000028e-08</v>
@@ -3168,10 +3080,8 @@
       <c r="K15" t="n">
         <v>81.1654071925622</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 6.434x + -11123.339</t>
-        </is>
+      <c r="W15" t="n">
+        <v>6.4339107332009</v>
       </c>
       <c r="X15" t="n">
         <v>-11123.3390118636</v>
@@ -3180,7 +3090,7 @@
         <v>1.078887734892475e-09</v>
       </c>
       <c r="Z15" t="n">
-        <v>144.48</v>
+        <v>2072.09304580414</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000000002e-08</v>
@@ -3220,10 +3130,8 @@
       <c r="K16" t="n">
         <v>81.25011141979748</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 6.497x + -11142.644</t>
-        </is>
+      <c r="W16" t="n">
+        <v>6.49718835944087</v>
       </c>
       <c r="X16" t="n">
         <v>-11142.64404687529</v>
@@ -3232,7 +3140,7 @@
         <v>2.597180696414356e-08</v>
       </c>
       <c r="Z16" t="n">
-        <v>142.9100000000001</v>
+        <v>2054.277041036133</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000000017e-08</v>
@@ -3272,10 +3180,8 @@
       <c r="K17" t="n">
         <v>82.04382341130896</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 7.155x + -12259.449</t>
-        </is>
+      <c r="W17" t="n">
+        <v>7.155074524292647</v>
       </c>
       <c r="X17" t="n">
         <v>-12259.44871055042</v>
@@ -3284,7 +3190,7 @@
         <v>6.987006061311345e-10</v>
       </c>
       <c r="Z17" t="n">
-        <v>143.23</v>
+        <v>2035.878660396785</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000000009e-08</v>
@@ -3324,10 +3230,8 @@
       <c r="K18" t="n">
         <v>80.54836204260863</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 6.007x + -10070.587</t>
-        </is>
+      <c r="W18" t="n">
+        <v>6.006907316357553</v>
       </c>
       <c r="X18" t="n">
         <v>-10070.58681058115</v>
@@ -3336,7 +3240,7 @@
         <v>2.220542885308264e-08</v>
       </c>
       <c r="Z18" t="n">
-        <v>141.1900000000001</v>
+        <v>2018.006363133932</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000000029e-08</v>
@@ -3376,10 +3280,8 @@
       <c r="K19" t="n">
         <v>79.32418504194004</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 5.305x + -8737.158</t>
-        </is>
+      <c r="W19" t="n">
+        <v>5.304622809673369</v>
       </c>
       <c r="X19" t="n">
         <v>-8737.157956490941</v>
@@ -3388,7 +3290,7 @@
         <v>1.769899736642806e-08</v>
       </c>
       <c r="Z19" t="n">
-        <v>143</v>
+        <v>2000.627236910612</v>
       </c>
       <c r="AA19" t="n">
         <v>1.00000000000004e-08</v>
@@ -3428,10 +3330,8 @@
       <c r="K20" t="n">
         <v>76.44555650575067</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 4.148x + -6563.056</t>
-        </is>
+      <c r="W20" t="n">
+        <v>4.147932263933119</v>
       </c>
       <c r="X20" t="n">
         <v>-6563.055618966206</v>
@@ -3440,7 +3340,7 @@
         <v>1.050267230992006e-07</v>
       </c>
       <c r="Z20" t="n">
-        <v>133.5</v>
+        <v>1983.373668669812</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000008203e-08</v>
@@ -3480,10 +3380,8 @@
       <c r="K21" t="n">
         <v>66.39545723699418</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 2.288x + -3177.936</t>
-        </is>
+      <c r="W21" t="n">
+        <v>2.288414978859699</v>
       </c>
       <c r="X21" t="n">
         <v>-3177.935540046626</v>
@@ -3492,7 +3390,7 @@
         <v>4.423441237068347e-12</v>
       </c>
       <c r="Z21" t="n">
-        <v>124.8700000000001</v>
+        <v>1966.909809023754</v>
       </c>
       <c r="AA21" t="n">
         <v>1e-08</v>
@@ -3532,10 +3430,8 @@
       <c r="K22" t="n">
         <v>75.40248657078702</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 3.840x + -5931.217</t>
-        </is>
+      <c r="W22" t="n">
+        <v>3.839742268476164</v>
       </c>
       <c r="X22" t="n">
         <v>-5931.216647222574</v>
@@ -3544,7 +3440,7 @@
         <v>8.14539827550597e-08</v>
       </c>
       <c r="Z22" t="n">
-        <v>133.3299999999999</v>
+        <v>1949.736583056744</v>
       </c>
       <c r="AA22" t="n">
         <v>1e-08</v>
@@ -3670,12 +3566,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -3730,10 +3626,8 @@
       <c r="K2" t="n">
         <v>85.58749317576543</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 12.959x + -32878.982</t>
-        </is>
+      <c r="W2" t="n">
+        <v>12.95917804770604</v>
       </c>
       <c r="X2" t="n">
         <v>-32878.98200338369</v>
@@ -3742,7 +3636,7 @@
         <v>3.552265266815576e-11</v>
       </c>
       <c r="Z2" t="n">
-        <v>350.1300000000001</v>
+        <v>2810.028019172369</v>
       </c>
       <c r="AA2" t="n">
         <v>1e-08</v>
@@ -3782,10 +3676,8 @@
       <c r="K3" t="n">
         <v>86.33254120178223</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 15.601x + -34271.244</t>
-        </is>
+      <c r="W3" t="n">
+        <v>15.60140437099001</v>
       </c>
       <c r="X3" t="n">
         <v>-34271.2444060718</v>
@@ -3794,7 +3686,7 @@
         <v>5.019998634059318e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>205.3099999999999</v>
+        <v>2503.763417908455</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000003e-08</v>
@@ -3834,10 +3726,8 @@
       <c r="K4" t="n">
         <v>86.52383344429219</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 16.462x + -34902.952</t>
-        </is>
+      <c r="W4" t="n">
+        <v>16.46223246911723</v>
       </c>
       <c r="X4" t="n">
         <v>-34902.95157167217</v>
@@ -3846,7 +3736,7 @@
         <v>5.139725053026806e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>164.1799999999998</v>
+        <v>2425.264105437148</v>
       </c>
       <c r="AA4" t="n">
         <v>1.00000000000232e-08</v>
@@ -3886,10 +3776,8 @@
       <c r="K5" t="n">
         <v>85.47269265229681</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 12.629x + -25986.696</t>
-        </is>
+      <c r="W5" t="n">
+        <v>12.62924771528568</v>
       </c>
       <c r="X5" t="n">
         <v>-25986.6960195928</v>
@@ -3898,7 +3786,7 @@
         <v>1.124254504031348e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>176.2399999999998</v>
+        <v>2384.578961884988</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000727e-08</v>
@@ -3938,10 +3826,8 @@
       <c r="K6" t="n">
         <v>84.95719505833407</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 11.333x + -22901.437</t>
-        </is>
+      <c r="W6" t="n">
+        <v>11.33253390931329</v>
       </c>
       <c r="X6" t="n">
         <v>-22901.43711584846</v>
@@ -3950,7 +3836,7 @@
         <v>3.18119233942094e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>171.6299999999999</v>
+        <v>2352.222820883977</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000004e-08</v>
@@ -3990,10 +3876,8 @@
       <c r="K7" t="n">
         <v>85.06989948091764</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 11.593x + -23161.361</t>
-        </is>
+      <c r="W7" t="n">
+        <v>11.59292868412084</v>
       </c>
       <c r="X7" t="n">
         <v>-23161.36054999249</v>
@@ -4002,7 +3886,7 @@
         <v>5.845755677649939e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>154.01</v>
+        <v>2321.25284060976</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000004895e-08</v>
@@ -4042,10 +3926,8 @@
       <c r="K8" t="n">
         <v>84.44551878995303</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 10.283x + -20177.810</t>
-        </is>
+      <c r="W8" t="n">
+        <v>10.28290016869336</v>
       </c>
       <c r="X8" t="n">
         <v>-20177.81004093328</v>
@@ -4054,7 +3936,7 @@
         <v>1.546946160616957e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>156.1399999999999</v>
+        <v>2292.428652930454</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000006078e-08</v>
@@ -4094,10 +3976,8 @@
       <c r="K9" t="n">
         <v>84.07635978635334</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 9.638x + -18618.632</t>
-        </is>
+      <c r="W9" t="n">
+        <v>9.637906645515752</v>
       </c>
       <c r="X9" t="n">
         <v>-18618.63192384122</v>
@@ -4106,7 +3986,7 @@
         <v>2.181426989628064e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>156.8499999999999</v>
+        <v>2263.067685503016</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000695e-08</v>
@@ -4146,10 +4026,8 @@
       <c r="K10" t="n">
         <v>83.30282229920091</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 8.516x + -16138.773</t>
-        </is>
+      <c r="W10" t="n">
+        <v>8.516214533260847</v>
       </c>
       <c r="X10" t="n">
         <v>-16138.77255993648</v>
@@ -4158,7 +4036,7 @@
         <v>3.118462694968798e-11</v>
       </c>
       <c r="Z10" t="n">
-        <v>149.4200000000001</v>
+        <v>2235.436961411101</v>
       </c>
       <c r="AA10" t="n">
         <v>1e-08</v>
@@ -4198,10 +4076,8 @@
       <c r="K11" t="n">
         <v>82.24184420943112</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 7.340x + -13616.678</t>
-        </is>
+      <c r="W11" t="n">
+        <v>7.340041498655531</v>
       </c>
       <c r="X11" t="n">
         <v>-13616.67804076343</v>
@@ -4210,7 +4086,7 @@
         <v>1.693786795954945e-08</v>
       </c>
       <c r="Z11" t="n">
-        <v>144.5700000000002</v>
+        <v>2208.050817214159</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000005911e-08</v>
@@ -4336,12 +4212,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -4396,10 +4272,8 @@
       <c r="K2" t="n">
         <v>85.54930609885143</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 12.848x + -27994.550</t>
-        </is>
+      <c r="W2" t="n">
+        <v>12.8475451673552</v>
       </c>
       <c r="X2" t="n">
         <v>-27994.55023666909</v>
@@ -4408,7 +4282,7 @@
         <v>3.356916661256501e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>335.8899999999999</v>
+        <v>2452.906615047635</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000002e-08</v>
@@ -4448,10 +4322,8 @@
       <c r="K3" t="n">
         <v>85.93282605545672</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 14.064x + -29049.093</t>
-        </is>
+      <c r="W3" t="n">
+        <v>14.06369903347455</v>
       </c>
       <c r="X3" t="n">
         <v>-29049.09257838171</v>
@@ -4460,7 +4332,7 @@
         <v>6.253085997257166e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>233.6299999999999</v>
+        <v>2351.907718848481</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000007e-08</v>
@@ -4500,10 +4372,8 @@
       <c r="K4" t="n">
         <v>86.13302842758512</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 14.794x + -30116.335</t>
-        </is>
+      <c r="W4" t="n">
+        <v>14.79420167824835</v>
       </c>
       <c r="X4" t="n">
         <v>-30116.33539777904</v>
@@ -4512,7 +4382,7 @@
         <v>6.813337324920056e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>197.1400000000001</v>
+        <v>2315.725769299457</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000033246e-08</v>
@@ -4552,10 +4422,8 @@
       <c r="K5" t="n">
         <v>85.87537354245515</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 13.867x + -27784.857</t>
-        </is>
+      <c r="W5" t="n">
+        <v>13.86713946698253</v>
       </c>
       <c r="X5" t="n">
         <v>-27784.85662755503</v>
@@ -4564,7 +4432,7 @@
         <v>3.638750338927884e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>201.3899999999999</v>
+        <v>2287.05661856295</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000018e-08</v>
@@ -4604,10 +4472,8 @@
       <c r="K6" t="n">
         <v>85.63761957366458</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 13.109x + -25865.796</t>
-        </is>
+      <c r="W6" t="n">
+        <v>13.10867392331554</v>
       </c>
       <c r="X6" t="n">
         <v>-25865.7963457353</v>
@@ -4616,7 +4482,7 @@
         <v>1.514072843960937e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>200.7600000000002</v>
+        <v>2258.473193636406</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000945e-08</v>
@@ -4656,10 +4522,8 @@
       <c r="K7" t="n">
         <v>85.45919496875602</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 12.592x + -24467.612</t>
-        </is>
+      <c r="W7" t="n">
+        <v>12.59154993513136</v>
       </c>
       <c r="X7" t="n">
         <v>-24467.6119776858</v>
@@ -4668,7 +4532,7 @@
         <v>1.041207795952953e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>202.1500000000001</v>
+        <v>2229.732318649618</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000314e-08</v>
@@ -4708,10 +4572,8 @@
       <c r="K8" t="n">
         <v>85.56021029924068</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 12.879x + -24766.201</t>
-        </is>
+      <c r="W8" t="n">
+        <v>12.8792260947461</v>
       </c>
       <c r="X8" t="n">
         <v>-24766.20096783365</v>
@@ -4720,7 +4582,7 @@
         <v>7.794897760382419e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>193.9899999999998</v>
+        <v>2201.885953625297</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000010577e-08</v>
@@ -4760,10 +4622,8 @@
       <c r="K9" t="n">
         <v>85.55940687519681</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 12.877x + -24464.530</t>
-        </is>
+      <c r="W9" t="n">
+        <v>12.87688653762767</v>
       </c>
       <c r="X9" t="n">
         <v>-24464.5295775602</v>
@@ -4772,7 +4632,7 @@
         <v>6.677412408832826e-10</v>
       </c>
       <c r="Z9" t="n">
-        <v>191.02</v>
+        <v>2174.902578029177</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000308e-08</v>
@@ -4812,10 +4672,8 @@
       <c r="K10" t="n">
         <v>85.40422513712912</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 12.440x + -23321.493</t>
-        </is>
+      <c r="W10" t="n">
+        <v>12.44030672333366</v>
       </c>
       <c r="X10" t="n">
         <v>-23321.49282712353</v>
@@ -4824,7 +4682,7 @@
         <v>3.005876595717843e-12</v>
       </c>
       <c r="Z10" t="n">
-        <v>185.9299999999998</v>
+        <v>2148.837317518531</v>
       </c>
       <c r="AA10" t="n">
         <v>1e-08</v>
@@ -4864,10 +4722,8 @@
       <c r="K11" t="n">
         <v>85.59276080069311</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 12.975x + -24113.264</t>
-        </is>
+      <c r="W11" t="n">
+        <v>12.97472850640924</v>
       </c>
       <c r="X11" t="n">
         <v>-24113.26421218426</v>
@@ -4876,7 +4732,7 @@
         <v>2.088261798567025e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>173.3599999999999</v>
+        <v>2123.711437636119</v>
       </c>
       <c r="AA11" t="n">
         <v>1e-08</v>
@@ -4916,10 +4772,8 @@
       <c r="K12" t="n">
         <v>85.24697785761123</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 12.027x + -22010.598</t>
-        </is>
+      <c r="W12" t="n">
+        <v>12.02693509018668</v>
       </c>
       <c r="X12" t="n">
         <v>-22010.59773809439</v>
@@ -4928,7 +4782,7 @@
         <v>1.782017767900564e-08</v>
       </c>
       <c r="Z12" t="n">
-        <v>177.8</v>
+        <v>2100.123766861156</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000013372e-08</v>
@@ -4968,10 +4822,8 @@
       <c r="K13" t="n">
         <v>85.05790523896528</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 11.565x + -20890.697</t>
-        </is>
+      <c r="W13" t="n">
+        <v>11.56465363896059</v>
       </c>
       <c r="X13" t="n">
         <v>-20890.69694865254</v>
@@ -4980,7 +4832,7 @@
         <v>1.532804041585183e-08</v>
       </c>
       <c r="Z13" t="n">
-        <v>176.76</v>
+        <v>2077.061366627192</v>
       </c>
       <c r="AA13" t="n">
         <v>1.00000000000013e-08</v>
@@ -5020,10 +4872,8 @@
       <c r="K14" t="n">
         <v>84.97882892517599</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 11.382x + -20325.473</t>
-        </is>
+      <c r="W14" t="n">
+        <v>11.38161299652891</v>
       </c>
       <c r="X14" t="n">
         <v>-20325.47257140532</v>
@@ -5032,7 +4882,7 @@
         <v>1.609562704242201e-08</v>
       </c>
       <c r="Z14" t="n">
-        <v>178.6100000000001</v>
+        <v>2053.947534549518</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000001e-08</v>
@@ -5072,10 +4922,8 @@
       <c r="K15" t="n">
         <v>85.18898742923123</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 11.881x + -21060.042</t>
-        </is>
+      <c r="W15" t="n">
+        <v>11.88129490106161</v>
       </c>
       <c r="X15" t="n">
         <v>-21060.04159968036</v>
@@ -5084,7 +4932,7 @@
         <v>7.348741095256063e-08</v>
       </c>
       <c r="Z15" t="n">
-        <v>167.29</v>
+        <v>2032.367258601469</v>
       </c>
       <c r="AA15" t="n">
         <v>1e-08</v>
@@ -5124,10 +4972,8 @@
       <c r="K16" t="n">
         <v>84.35561416766511</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 10.118x + -17601.011</t>
-        </is>
+      <c r="W16" t="n">
+        <v>10.11807351576503</v>
       </c>
       <c r="X16" t="n">
         <v>-17601.01131604091</v>
@@ -5136,7 +4982,7 @@
         <v>2.073449630468893e-09</v>
       </c>
       <c r="Z16" t="n">
-        <v>173.3599999999999</v>
+        <v>2010.869800452661</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000002504e-08</v>
@@ -5176,10 +5022,8 @@
       <c r="K17" t="n">
         <v>84.71072808275181</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 10.802x + -18658.892</t>
-        </is>
+      <c r="W17" t="n">
+        <v>10.80166188820601</v>
       </c>
       <c r="X17" t="n">
         <v>-18658.89170008088</v>
@@ -5188,7 +5032,7 @@
         <v>194.9128416968672</v>
       </c>
       <c r="Z17" t="n">
-        <v>167.27</v>
+        <v>1997.956112222552</v>
       </c>
       <c r="AA17" t="n">
         <v>1.497888028501448e-08</v>
@@ -5228,10 +5072,8 @@
       <c r="K18" t="n">
         <v>84.69030337307916</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 10.760x + -18399.176</t>
-        </is>
+      <c r="W18" t="n">
+        <v>10.75987387345335</v>
       </c>
       <c r="X18" t="n">
         <v>-18399.17593732727</v>
@@ -5240,7 +5082,7 @@
         <v>3.269855886123153e-08</v>
       </c>
       <c r="Z18" t="n">
-        <v>162.5899999999999</v>
+        <v>1968.709742936593</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000000175e-08</v>
@@ -5280,10 +5122,8 @@
       <c r="K19" t="n">
         <v>84.62588928958161</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 10.630x + -17983.916</t>
-        </is>
+      <c r="W19" t="n">
+        <v>10.63016017542289</v>
       </c>
       <c r="X19" t="n">
         <v>-17983.91603330377</v>
@@ -5292,7 +5132,7 @@
         <v>3.499427388928672e-08</v>
       </c>
       <c r="Z19" t="n">
-        <v>155.6700000000001</v>
+        <v>1948.006773315955</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000000046e-08</v>
@@ -5332,10 +5172,8 @@
       <c r="K20" t="n">
         <v>84.1942210862541</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 9.835x + -16398.235</t>
-        </is>
+      <c r="W20" t="n">
+        <v>9.834950007408469</v>
       </c>
       <c r="X20" t="n">
         <v>-16398.23479152647</v>
@@ -5344,7 +5182,7 @@
         <v>4.17880658220823e-08</v>
       </c>
       <c r="Z20" t="n">
-        <v>150.01</v>
+        <v>1926.945451865624</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000007e-08</v>
@@ -5384,10 +5222,8 @@
       <c r="K21" t="n">
         <v>84.19667320161133</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 9.839x + -16234.775</t>
-        </is>
+      <c r="W21" t="n">
+        <v>9.839134206106463</v>
       </c>
       <c r="X21" t="n">
         <v>-16234.77503383726</v>
@@ -5396,7 +5232,7 @@
         <v>1.937766268094148e-08</v>
       </c>
       <c r="Z21" t="n">
-        <v>151.6700000000001</v>
+        <v>1906.448848261884</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000000126e-08</v>
@@ -5436,10 +5272,8 @@
       <c r="K22" t="n">
         <v>83.85151603775746</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 9.283x + -15107.811</t>
-        </is>
+      <c r="W22" t="n">
+        <v>9.282886142075425</v>
       </c>
       <c r="X22" t="n">
         <v>-15107.81057219486</v>
@@ -5448,7 +5282,7 @@
         <v>4.752329891567776e-08</v>
       </c>
       <c r="Z22" t="n">
-        <v>150.71</v>
+        <v>1885.524683424949</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000001e-08</v>
@@ -5574,12 +5408,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -5634,10 +5468,8 @@
       <c r="K2" t="n">
         <v>84.65983800603161</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 10.698x + -26706.686</t>
-        </is>
+      <c r="W2" t="n">
+        <v>10.69813543401735</v>
       </c>
       <c r="X2" t="n">
         <v>-26706.68584874164</v>
@@ -5646,7 +5478,7 @@
         <v>7.883427900413313e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>441.52</v>
+        <v>2774.566121206715</v>
       </c>
       <c r="AA2" t="n">
         <v>1e-08</v>
@@ -5686,10 +5518,8 @@
       <c r="K3" t="n">
         <v>86.5720619659517</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 16.694x + -36140.694</t>
-        </is>
+      <c r="W3" t="n">
+        <v>16.69440914035216</v>
       </c>
       <c r="X3" t="n">
         <v>-36140.69431407058</v>
@@ -5698,7 +5528,7 @@
         <v>5.593093609899253e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>246.0999999999999</v>
+        <v>2449.195621436328</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000056022e-08</v>
@@ -5738,10 +5568,8 @@
       <c r="K4" t="n">
         <v>86.49428931529927</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 16.323x + -33815.253</t>
-        </is>
+      <c r="W4" t="n">
+        <v>16.32315568605788</v>
       </c>
       <c r="X4" t="n">
         <v>-33815.25327228026</v>
@@ -5750,7 +5578,7 @@
         <v>8.915161895167579e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>201.6700000000001</v>
+        <v>2369.31096873786</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000004e-08</v>
@@ -5790,10 +5618,8 @@
       <c r="K5" t="n">
         <v>86.54633220578661</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 16.570x + -33711.183</t>
-        </is>
+      <c r="W5" t="n">
+        <v>16.56973769831434</v>
       </c>
       <c r="X5" t="n">
         <v>-33711.18331039534</v>
@@ -5802,7 +5628,7 @@
         <v>7.923251920167434e-10</v>
       </c>
       <c r="Z5" t="n">
-        <v>175.2399999999998</v>
+        <v>2330.488411175554</v>
       </c>
       <c r="AA5" t="n">
         <v>1e-08</v>
@@ -5842,10 +5668,8 @@
       <c r="K6" t="n">
         <v>86.40523466484903</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 15.918x + -31866.979</t>
-        </is>
+      <c r="W6" t="n">
+        <v>15.91775132115982</v>
       </c>
       <c r="X6" t="n">
         <v>-31866.97935458959</v>
@@ -5854,7 +5678,7 @@
         <v>1.687712108181191e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>173.6199999999999</v>
+        <v>2298.737464489892</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000001e-08</v>
@@ -5894,10 +5718,8 @@
       <c r="K7" t="n">
         <v>86.50628571425651</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 16.379x + -32424.365</t>
-        </is>
+      <c r="W7" t="n">
+        <v>16.37934454992757</v>
       </c>
       <c r="X7" t="n">
         <v>-32424.3647979683</v>
@@ -5906,7 +5728,7 @@
         <v>3.244383013434563e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>167.26</v>
+        <v>2268.743891509471</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000671e-08</v>
@@ -5946,10 +5768,8 @@
       <c r="K8" t="n">
         <v>86.46587755173864</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 16.192x + -31643.771</t>
-        </is>
+      <c r="W8" t="n">
+        <v>16.19160001210235</v>
       </c>
       <c r="X8" t="n">
         <v>-31643.77130862837</v>
@@ -5958,7 +5778,7 @@
         <v>2.644520601076616e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>161.8799999999999</v>
+        <v>2239.643704997689</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000001247e-08</v>
@@ -5998,10 +5818,8 @@
       <c r="K9" t="n">
         <v>86.13663104753107</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 14.808x + -28471.886</t>
-        </is>
+      <c r="W9" t="n">
+        <v>14.80803934345315</v>
       </c>
       <c r="X9" t="n">
         <v>-28471.88613184045</v>
@@ -6010,7 +5828,7 @@
         <v>6.680290477220372e-10</v>
       </c>
       <c r="Z9" t="n">
-        <v>163.8299999999999</v>
+        <v>2211.694723348148</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000001e-08</v>
@@ -6050,10 +5868,8 @@
       <c r="K10" t="n">
         <v>86.14507632132964</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 14.841x + -28195.277</t>
-        </is>
+      <c r="W10" t="n">
+        <v>14.84057887122033</v>
       </c>
       <c r="X10" t="n">
         <v>-28195.27725672555</v>
@@ -6062,7 +5878,7 @@
         <v>2.566576168441471e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>161.55</v>
+        <v>2184.9101920838</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000002e-08</v>
@@ -6102,10 +5918,8 @@
       <c r="K11" t="n">
         <v>86.14517076772654</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 14.841x + -27865.281</t>
-        </is>
+      <c r="W11" t="n">
+        <v>14.84094357687393</v>
       </c>
       <c r="X11" t="n">
         <v>-27865.28103089625</v>
@@ -6114,7 +5928,7 @@
         <v>4.576929854027643e-08</v>
       </c>
       <c r="Z11" t="n">
-        <v>158.3399999999999</v>
+        <v>2158.5683705583</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000002358e-08</v>
@@ -6240,12 +6054,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -6300,10 +6114,8 @@
       <c r="K2" t="n">
         <v>86.07779278082386</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 14.585x + -31510.790</t>
-        </is>
+      <c r="W2" t="n">
+        <v>14.58521938025298</v>
       </c>
       <c r="X2" t="n">
         <v>-31510.78978625819</v>
@@ -6312,7 +6124,7 @@
         <v>7.59263497276218e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>280.1100000000001</v>
+        <v>2448.172831186998</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000001174e-08</v>
@@ -6352,10 +6164,8 @@
       <c r="K3" t="n">
         <v>86.71101429127195</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 17.401x + -35754.912</t>
-        </is>
+      <c r="W3" t="n">
+        <v>17.40136246034252</v>
       </c>
       <c r="X3" t="n">
         <v>-35754.91170814761</v>
@@ -6364,7 +6174,7 @@
         <v>4.882485990923643e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>178.1899999999998</v>
+        <v>2344.058287504316</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000328e-08</v>
@@ -6404,10 +6214,8 @@
       <c r="K4" t="n">
         <v>86.33261709878029</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 15.602x + -31305.693</t>
-        </is>
+      <c r="W4" t="n">
+        <v>15.60172812781192</v>
       </c>
       <c r="X4" t="n">
         <v>-31305.69343450797</v>
@@ -6416,7 +6224,7 @@
         <v>1.391710035901277e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>175.9400000000003</v>
+        <v>2307.414050921421</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000033528e-08</v>
@@ -6456,10 +6264,8 @@
       <c r="K5" t="n">
         <v>86.40287891827006</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 15.907x + -31604.158</t>
-        </is>
+      <c r="W5" t="n">
+        <v>15.90729940551821</v>
       </c>
       <c r="X5" t="n">
         <v>-31604.15765627037</v>
@@ -6468,7 +6274,7 @@
         <v>3.907241226290765e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>166.96</v>
+        <v>2281.789598885403</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000001366e-08</v>
@@ -6508,10 +6314,8 @@
       <c r="K6" t="n">
         <v>85.9769002109458</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 14.218x + -27814.628</t>
-        </is>
+      <c r="W6" t="n">
+        <v>14.21828667036405</v>
       </c>
       <c r="X6" t="n">
         <v>-27814.62822560456</v>
@@ -6520,7 +6324,7 @@
         <v>8.138654619019943e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>173.8300000000002</v>
+        <v>2258.501092430848</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000017002e-08</v>
@@ -6560,10 +6364,8 @@
       <c r="K7" t="n">
         <v>86.27982389567983</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 15.380x + -29923.521</t>
-        </is>
+      <c r="W7" t="n">
+        <v>15.37971297586586</v>
       </c>
       <c r="X7" t="n">
         <v>-29923.52076585288</v>
@@ -6572,7 +6374,7 @@
         <v>5.396713625197265e-10</v>
       </c>
       <c r="Z7" t="n">
-        <v>158.8900000000001</v>
+        <v>2236.416516125864</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000053e-08</v>
@@ -6612,10 +6414,8 @@
       <c r="K8" t="n">
         <v>86.20941217304882</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 15.093x + -29072.233</t>
-        </is>
+      <c r="W8" t="n">
+        <v>15.09321636962727</v>
       </c>
       <c r="X8" t="n">
         <v>-29072.23275389842</v>
@@ -6624,7 +6424,7 @@
         <v>2.660286056378543e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>156.2399999999998</v>
+        <v>2214.540011872067</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000018e-08</v>
@@ -6664,10 +6464,8 @@
       <c r="K9" t="n">
         <v>85.79513385908204</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 13.602x + -25834.003</t>
-        </is>
+      <c r="W9" t="n">
+        <v>13.6015933304339</v>
       </c>
       <c r="X9" t="n">
         <v>-25834.00251372231</v>
@@ -6676,7 +6474,7 @@
         <v>4.33698953844215e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>161.52</v>
+        <v>2193.210525266819</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000003773e-08</v>
@@ -6716,10 +6514,8 @@
       <c r="K10" t="n">
         <v>85.96567808557072</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 14.179x + -26722.421</t>
-        </is>
+      <c r="W10" t="n">
+        <v>14.17860570379382</v>
       </c>
       <c r="X10" t="n">
         <v>-26722.42094626218</v>
@@ -6728,7 +6524,7 @@
         <v>1.41124281947301e-08</v>
       </c>
       <c r="Z10" t="n">
-        <v>158.6700000000001</v>
+        <v>2172.325156704148</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000008e-08</v>
@@ -6768,10 +6564,8 @@
       <c r="K11" t="n">
         <v>85.5172088672479</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 12.755x + -23727.640</t>
-        </is>
+      <c r="W11" t="n">
+        <v>12.75518302956416</v>
       </c>
       <c r="X11" t="n">
         <v>-23727.63986318794</v>
@@ -6780,7 +6574,7 @@
         <v>9.229985201283662e-08</v>
       </c>
       <c r="Z11" t="n">
-        <v>154.72</v>
+        <v>2151.965347585302</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000004753e-08</v>
@@ -6820,10 +6614,8 @@
       <c r="K12" t="n">
         <v>85.56542189687642</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 12.894x + -23785.300</t>
-        </is>
+      <c r="W12" t="n">
+        <v>12.89442272168864</v>
       </c>
       <c r="X12" t="n">
         <v>-23785.29957196176</v>
@@ -6832,7 +6624,7 @@
         <v>3.164702529728533e-08</v>
       </c>
       <c r="Z12" t="n">
-        <v>153.8299999999999</v>
+        <v>2132.172169751793</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000003629e-08</v>
@@ -6872,10 +6664,8 @@
       <c r="K13" t="n">
         <v>85.31747505331563</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 12.209x + -22260.508</t>
-        </is>
+      <c r="W13" t="n">
+        <v>12.20883237135663</v>
       </c>
       <c r="X13" t="n">
         <v>-22260.50799699948</v>
@@ -6884,7 +6674,7 @@
         <v>1.113454508951787e-08</v>
       </c>
       <c r="Z13" t="n">
-        <v>156.6700000000001</v>
+        <v>2112.461221515814</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000326e-08</v>
@@ -6924,10 +6714,8 @@
       <c r="K14" t="n">
         <v>85.38524211641437</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 12.389x + -22421.764</t>
-        </is>
+      <c r="W14" t="n">
+        <v>12.38891233107171</v>
       </c>
       <c r="X14" t="n">
         <v>-22421.76430748341</v>
@@ -6936,7 +6724,7 @@
         <v>6.866990322863331e-10</v>
       </c>
       <c r="Z14" t="n">
-        <v>144.05</v>
+        <v>2093.589109911672</v>
       </c>
       <c r="AA14" t="n">
         <v>1e-08</v>
@@ -6976,10 +6764,8 @@
       <c r="K15" t="n">
         <v>85.24034746041217</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 12.010x + -21513.078</t>
-        </is>
+      <c r="W15" t="n">
+        <v>12.0101038958284</v>
       </c>
       <c r="X15" t="n">
         <v>-21513.07805774334</v>
@@ -6988,7 +6774,7 @@
         <v>9.524684903577736e-11</v>
       </c>
       <c r="Z15" t="n">
-        <v>144.22</v>
+        <v>2074.379845100409</v>
       </c>
       <c r="AA15" t="n">
         <v>1e-08</v>
@@ -7028,10 +6814,8 @@
       <c r="K16" t="n">
         <v>85.06827953940441</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 11.589x + -20537.699</t>
-        </is>
+      <c r="W16" t="n">
+        <v>11.58910184507283</v>
       </c>
       <c r="X16" t="n">
         <v>-20537.69861342705</v>
@@ -7040,7 +6824,7 @@
         <v>4.791237062375483e-08</v>
       </c>
       <c r="Z16" t="n">
-        <v>148.51</v>
+        <v>2055.375363242407</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000005102e-08</v>
@@ -7080,10 +6864,8 @@
       <c r="K17" t="n">
         <v>85.19625531608348</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 11.899x + -20938.394</t>
-        </is>
+      <c r="W17" t="n">
+        <v>11.89935556707356</v>
       </c>
       <c r="X17" t="n">
         <v>-20938.39357372569</v>
@@ -7092,7 +6874,7 @@
         <v>6.15130475819423e-09</v>
       </c>
       <c r="Z17" t="n">
-        <v>139.6499999999999</v>
+        <v>2036.978913403617</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000000003e-08</v>
@@ -7132,10 +6914,8 @@
       <c r="K18" t="n">
         <v>84.56143802201298</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 10.503x + -18212.152</t>
-        </is>
+      <c r="W18" t="n">
+        <v>10.50343798962148</v>
       </c>
       <c r="X18" t="n">
         <v>-18212.15246948718</v>
@@ -7144,7 +6924,7 @@
         <v>215.439725150856</v>
       </c>
       <c r="Z18" t="n">
-        <v>140.5400000000002</v>
+        <v>1995.954777419473</v>
       </c>
       <c r="AA18" t="n">
         <v>1.421089080265279e-08</v>
@@ -7184,10 +6964,8 @@
       <c r="K19" t="n">
         <v>84.47851608554285</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 10.345x + -17767.175</t>
-        </is>
+      <c r="W19" t="n">
+        <v>10.34473803912889</v>
       </c>
       <c r="X19" t="n">
         <v>-17767.17453717029</v>
@@ -7196,7 +6974,7 @@
         <v>6.232654591143145e-09</v>
       </c>
       <c r="Z19" t="n">
-        <v>141.52</v>
+        <v>1999.304523283349</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000000246e-08</v>
@@ -7236,10 +7014,8 @@
       <c r="K20" t="n">
         <v>84.09420207595871</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 9.667x + -16398.479</t>
-        </is>
+      <c r="W20" t="n">
+        <v>9.667232401881646</v>
       </c>
       <c r="X20" t="n">
         <v>-16398.47873422297</v>
@@ -7248,7 +7024,7 @@
         <v>7.571974585333299e-10</v>
       </c>
       <c r="Z20" t="n">
-        <v>141.0899999999999</v>
+        <v>1980.823354486376</v>
       </c>
       <c r="AA20" t="n">
         <v>1e-08</v>
@@ -7288,10 +7064,8 @@
       <c r="K21" t="n">
         <v>84.01084049015429</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 9.532x + -16013.677</t>
-        </is>
+      <c r="W21" t="n">
+        <v>9.531712064456077</v>
       </c>
       <c r="X21" t="n">
         <v>-16013.67661334544</v>
@@ -7300,7 +7074,7 @@
         <v>3.945118807396416e-09</v>
       </c>
       <c r="Z21" t="n">
-        <v>137.3699999999999</v>
+        <v>1962.866129307823</v>
       </c>
       <c r="AA21" t="n">
         <v>1e-08</v>
@@ -7340,10 +7114,8 @@
       <c r="K22" t="n">
         <v>83.67584587017204</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 9.023x + -14976.139</t>
-        </is>
+      <c r="W22" t="n">
+        <v>9.023010523109644</v>
       </c>
       <c r="X22" t="n">
         <v>-14976.13898527562</v>
@@ -7352,7 +7124,7 @@
         <v>7.424481533400172e-08</v>
       </c>
       <c r="Z22" t="n">
-        <v>136.28</v>
+        <v>1944.151827818589</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000027e-08</v>
@@ -7478,12 +7250,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -7538,10 +7310,8 @@
       <c r="K2" t="n">
         <v>84.5764744127804</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 10.533x + -25213.210</t>
-        </is>
+      <c r="W2" t="n">
+        <v>10.53273353379627</v>
       </c>
       <c r="X2" t="n">
         <v>-25213.20964593093</v>
@@ -7550,7 +7320,7 @@
         <v>1.178533343438866e-12</v>
       </c>
       <c r="Z2" t="n">
-        <v>471.4099999999999</v>
+        <v>2658.812629016438</v>
       </c>
       <c r="AA2" t="n">
         <v>1e-08</v>
@@ -7590,10 +7360,8 @@
       <c r="K3" t="n">
         <v>86.17563969181897</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 14.960x + -31277.199</t>
-        </is>
+      <c r="W3" t="n">
+        <v>14.95953847465796</v>
       </c>
       <c r="X3" t="n">
         <v>-31277.19949447679</v>
@@ -7602,7 +7370,7 @@
         <v>5.321018380837263e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>272.96</v>
+        <v>2379.381414814334</v>
       </c>
       <c r="AA3" t="n">
         <v>1.00000000001412e-08</v>
@@ -7642,10 +7410,8 @@
       <c r="K4" t="n">
         <v>86.54124499778651</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 16.545x + -33442.277</t>
-        </is>
+      <c r="W4" t="n">
+        <v>16.54530740975163</v>
       </c>
       <c r="X4" t="n">
         <v>-33442.27658870722</v>
@@ -7654,7 +7420,7 @@
         <v>4.426657910376211e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>204.6400000000001</v>
+        <v>2308.640491278848</v>
       </c>
       <c r="AA4" t="n">
         <v>1.00000000000008e-08</v>
@@ -7694,10 +7460,8 @@
       <c r="K5" t="n">
         <v>86.6233617917888</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 16.949x + -33669.094</t>
-        </is>
+      <c r="W5" t="n">
+        <v>16.94864190427047</v>
       </c>
       <c r="X5" t="n">
         <v>-33669.09441678843</v>
@@ -7706,7 +7470,7 @@
         <v>4.07323689996329e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>179.4899999999998</v>
+        <v>2271.301881635975</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000654e-08</v>
@@ -7746,10 +7510,8 @@
       <c r="K6" t="n">
         <v>86.46440893826606</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 16.185x + -31612.390</t>
-        </is>
+      <c r="W6" t="n">
+        <v>16.18485725363871</v>
       </c>
       <c r="X6" t="n">
         <v>-31612.38967299644</v>
@@ -7758,7 +7520,7 @@
         <v>7.073228953434104e-12</v>
       </c>
       <c r="Z6" t="n">
-        <v>172.96</v>
+        <v>2239.342588407337</v>
       </c>
       <c r="AA6" t="n">
         <v>1e-08</v>
@@ -7798,10 +7560,8 @@
       <c r="K7" t="n">
         <v>86.55211011509773</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 16.598x + -32029.383</t>
-        </is>
+      <c r="W7" t="n">
+        <v>16.59757227241609</v>
       </c>
       <c r="X7" t="n">
         <v>-32029.38294373039</v>
@@ -7810,7 +7570,7 @@
         <v>6.116323499204814e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>163.0899999999999</v>
+        <v>2208.626226218052</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000004567e-08</v>
@@ -7850,10 +7610,8 @@
       <c r="K8" t="n">
         <v>86.11491787455944</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 14.725x + -27888.574</t>
-        </is>
+      <c r="W8" t="n">
+        <v>14.72502721987783</v>
       </c>
       <c r="X8" t="n">
         <v>-27888.57401359933</v>
@@ -7862,7 +7620,7 @@
         <v>5.751298632844075e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>172.02</v>
+        <v>2179.723996827127</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000048e-08</v>
@@ -7902,10 +7660,8 @@
       <c r="K9" t="n">
         <v>86.42202768193623</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 15.993x + -30042.783</t>
-        </is>
+      <c r="W9" t="n">
+        <v>15.99265637160989</v>
       </c>
       <c r="X9" t="n">
         <v>-30042.78279684855</v>
@@ -7914,7 +7670,7 @@
         <v>7.808436692014853e-12</v>
       </c>
       <c r="Z9" t="n">
-        <v>154.3899999999999</v>
+        <v>2152.038528362595</v>
       </c>
       <c r="AA9" t="n">
         <v>1e-08</v>
@@ -7954,10 +7710,8 @@
       <c r="K10" t="n">
         <v>86.05687071797711</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 14.508x + -26793.564</t>
-        </is>
+      <c r="W10" t="n">
+        <v>14.50758793014598</v>
       </c>
       <c r="X10" t="n">
         <v>-26793.56365285002</v>
@@ -7966,7 +7720,7 @@
         <v>1.31055830514826e-10</v>
       </c>
       <c r="Z10" t="n">
-        <v>164.21</v>
+        <v>2124.659760987732</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000012e-08</v>
@@ -8006,10 +7760,8 @@
       <c r="K11" t="n">
         <v>85.98428394516897</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 14.245x + -25988.778</t>
-        </is>
+      <c r="W11" t="n">
+        <v>14.24451601456959</v>
       </c>
       <c r="X11" t="n">
         <v>-25988.77844201832</v>
@@ -8018,7 +7770,7 @@
         <v>4.568867439192769e-08</v>
       </c>
       <c r="Z11" t="n">
-        <v>154.51</v>
+        <v>2098.5094102756</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000003242e-08</v>
@@ -8144,12 +7896,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -8204,10 +7956,8 @@
       <c r="K2" t="n">
         <v>86.16137949357943</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 14.904x + -31824.086</t>
-        </is>
+      <c r="W2" t="n">
+        <v>14.90379915294437</v>
       </c>
       <c r="X2" t="n">
         <v>-31824.08555246776</v>
@@ -8216,7 +7966,7 @@
         <v>7.799273845483685e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>268.8200000000002</v>
+        <v>2416.473483771344</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000672e-08</v>
@@ -8256,10 +8006,8 @@
       <c r="K3" t="n">
         <v>86.79263340993062</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 17.845x + -36113.653</t>
-        </is>
+      <c r="W3" t="n">
+        <v>17.8451439499894</v>
       </c>
       <c r="X3" t="n">
         <v>-36113.65276631213</v>
@@ -8268,7 +8016,7 @@
         <v>2.548953750599256e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>172.8399999999999</v>
+        <v>2306.410461792562</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000465e-08</v>
@@ -8308,10 +8056,8 @@
       <c r="K4" t="n">
         <v>86.54811692382954</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 16.578x + -32806.276</t>
-        </is>
+      <c r="W4" t="n">
+        <v>16.57832548785629</v>
       </c>
       <c r="X4" t="n">
         <v>-32806.27562153985</v>
@@ -8320,7 +8066,7 @@
         <v>6.348775983279524e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>169.2199999999998</v>
+        <v>2268.352087800372</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000006328e-08</v>
@@ -8360,10 +8106,8 @@
       <c r="K5" t="n">
         <v>86.23674973217966</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 15.203x + -29618.191</t>
-        </is>
+      <c r="W5" t="n">
+        <v>15.20317817144176</v>
       </c>
       <c r="X5" t="n">
         <v>-29618.19054009091</v>
@@ -8372,7 +8116,7 @@
         <v>4.366292432417547e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>169.1199999999999</v>
+        <v>2241.71034169518</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000001511e-08</v>
@@ -8412,10 +8156,8 @@
       <c r="K6" t="n">
         <v>86.24736211313162</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 15.246x + -29391.403</t>
-        </is>
+      <c r="W6" t="n">
+        <v>15.24629616551704</v>
       </c>
       <c r="X6" t="n">
         <v>-29391.40258984867</v>
@@ -8424,7 +8166,7 @@
         <v>2.040892421831557e-12</v>
       </c>
       <c r="Z6" t="n">
-        <v>165.5200000000002</v>
+        <v>2217.495790347891</v>
       </c>
       <c r="AA6" t="n">
         <v>1e-08</v>
@@ -8464,10 +8206,8 @@
       <c r="K7" t="n">
         <v>86.11350596708473</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 14.720x + -28051.952</t>
-        </is>
+      <c r="W7" t="n">
+        <v>14.71966139354527</v>
       </c>
       <c r="X7" t="n">
         <v>-28051.95150293668</v>
@@ -8476,7 +8216,7 @@
         <v>1.163827076607538e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>162.0000000000002</v>
+        <v>2194.09778788681</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000043812e-08</v>
@@ -8516,10 +8256,8 @@
       <c r="K8" t="n">
         <v>86.07504764752811</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 14.575x + -27492.437</t>
-        </is>
+      <c r="W8" t="n">
+        <v>14.57498644759217</v>
       </c>
       <c r="X8" t="n">
         <v>-27492.4371183081</v>
@@ -8528,7 +8266,7 @@
         <v>5.421282168708254e-11</v>
       </c>
       <c r="Z8" t="n">
-        <v>161.76</v>
+        <v>2171.718961287622</v>
       </c>
       <c r="AA8" t="n">
         <v>1e-08</v>
@@ -8568,10 +8306,8 @@
       <c r="K9" t="n">
         <v>85.79693583129814</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 13.607x + -25366.283</t>
-        </is>
+      <c r="W9" t="n">
+        <v>13.60744570377883</v>
       </c>
       <c r="X9" t="n">
         <v>-25366.28310645062</v>
@@ -8580,7 +8316,7 @@
         <v>5.800470212966129e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>158.45</v>
+        <v>2150.271644099466</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000005795e-08</v>
@@ -8620,10 +8356,8 @@
       <c r="K10" t="n">
         <v>85.73588205690906</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 13.412x + -24737.567</t>
-        </is>
+      <c r="W10" t="n">
+        <v>13.41190804852343</v>
       </c>
       <c r="X10" t="n">
         <v>-24737.56724248871</v>
@@ -8632,7 +8366,7 @@
         <v>4.209818556764471e-08</v>
       </c>
       <c r="Z10" t="n">
-        <v>161.3199999999999</v>
+        <v>2129.886604784695</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000114e-08</v>
@@ -8672,10 +8406,8 @@
       <c r="K11" t="n">
         <v>85.48070060833098</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 12.652x + -23091.471</t>
-        </is>
+      <c r="W11" t="n">
+        <v>12.65171940152116</v>
       </c>
       <c r="X11" t="n">
         <v>-23091.47112830595</v>
@@ -8684,7 +8416,7 @@
         <v>3.282787595306996e-08</v>
       </c>
       <c r="Z11" t="n">
-        <v>152.3800000000001</v>
+        <v>2109.777906018549</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000349e-08</v>
@@ -8724,10 +8456,8 @@
       <c r="K12" t="n">
         <v>85.81920739517349</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 13.680x + -24835.845</t>
-        </is>
+      <c r="W12" t="n">
+        <v>13.68019415199602</v>
       </c>
       <c r="X12" t="n">
         <v>-24835.84474048759</v>
@@ -8736,7 +8466,7 @@
         <v>1.596273875510573e-10</v>
       </c>
       <c r="Z12" t="n">
-        <v>145.77</v>
+        <v>2091.004586416669</v>
       </c>
       <c r="AA12" t="n">
         <v>1.00000000000047e-08</v>
@@ -8776,10 +8506,8 @@
       <c r="K13" t="n">
         <v>85.62399170057979</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 13.068x + -23470.116</t>
-        </is>
+      <c r="W13" t="n">
+        <v>13.0676921238932</v>
       </c>
       <c r="X13" t="n">
         <v>-23470.11550650002</v>
@@ -8788,7 +8516,7 @@
         <v>1.424799153077533e-08</v>
       </c>
       <c r="Z13" t="n">
-        <v>148.5999999999999</v>
+        <v>2072.679106968035</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000005907e-08</v>
@@ -8828,10 +8556,8 @@
       <c r="K14" t="n">
         <v>85.55071496161554</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 12.852x + -22874.387</t>
-        </is>
+      <c r="W14" t="n">
+        <v>12.85162974153452</v>
       </c>
       <c r="X14" t="n">
         <v>-22874.38725960436</v>
@@ -8840,7 +8566,7 @@
         <v>3.63933232433278e-08</v>
       </c>
       <c r="Z14" t="n">
-        <v>147.95</v>
+        <v>2054.57121273991</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000386e-08</v>
@@ -8880,10 +8606,8 @@
       <c r="K15" t="n">
         <v>85.14591459323887</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 11.775x + -20697.785</t>
-        </is>
+      <c r="W15" t="n">
+        <v>11.77536653826197</v>
       </c>
       <c r="X15" t="n">
         <v>-20697.7849186613</v>
@@ -8892,7 +8616,7 @@
         <v>8.284350392887859e-08</v>
       </c>
       <c r="Z15" t="n">
-        <v>154.4200000000001</v>
+        <v>2036.907459823528</v>
       </c>
       <c r="AA15" t="n">
         <v>1.00000000000012e-08</v>
@@ -8932,10 +8656,8 @@
       <c r="K16" t="n">
         <v>85.20306171179796</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 11.916x + -20792.965</t>
-        </is>
+      <c r="W16" t="n">
+        <v>11.91631893868786</v>
       </c>
       <c r="X16" t="n">
         <v>-20792.96495376527</v>
@@ -8944,7 +8666,7 @@
         <v>3.120711221992213e-08</v>
       </c>
       <c r="Z16" t="n">
-        <v>144.3700000000001</v>
+        <v>2019.117536474495</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000001246e-08</v>
@@ -8984,10 +8706,8 @@
       <c r="K17" t="n">
         <v>85.0082594806691</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 11.449x + -19771.984</t>
-        </is>
+      <c r="W17" t="n">
+        <v>11.44906108399377</v>
       </c>
       <c r="X17" t="n">
         <v>-19771.9837905243</v>
@@ -8996,7 +8716,7 @@
         <v>3.16789655310853e-09</v>
       </c>
       <c r="Z17" t="n">
-        <v>142.6499999999999</v>
+        <v>2001.861790416041</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000000738e-08</v>
@@ -9036,10 +8756,8 @@
       <c r="K18" t="n">
         <v>84.95622239657972</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 11.330x + -19394.370</t>
-        </is>
+      <c r="W18" t="n">
+        <v>11.33033717120812</v>
       </c>
       <c r="X18" t="n">
         <v>-19394.36958960264</v>
@@ -9048,7 +8766,7 @@
         <v>213.0517617979157</v>
       </c>
       <c r="Z18" t="n">
-        <v>144.3300000000002</v>
+        <v>1982.412671349128</v>
       </c>
       <c r="AA18" t="n">
         <v>1.464092348456783e-08</v>
@@ -9088,10 +8806,8 @@
       <c r="K19" t="n">
         <v>84.37381452768477</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 10.151x + -17141.683</t>
-        </is>
+      <c r="W19" t="n">
+        <v>10.15101724148481</v>
       </c>
       <c r="X19" t="n">
         <v>-17141.6828876498</v>
@@ -9100,7 +8816,7 @@
         <v>1.566822510386609e-08</v>
       </c>
       <c r="Z19" t="n">
-        <v>135.5</v>
+        <v>1967.190607268022</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000000009e-08</v>
@@ -9140,10 +8856,8 @@
       <c r="K20" t="n">
         <v>84.05341940455079</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 9.600x + -16025.173</t>
-        </is>
+      <c r="W20" t="n">
+        <v>9.600459284815479</v>
       </c>
       <c r="X20" t="n">
         <v>-16025.17259570055</v>
@@ -9152,7 +8866,7 @@
         <v>1.245367317068335e-07</v>
       </c>
       <c r="Z20" t="n">
-        <v>138.52</v>
+        <v>1949.403625562016</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000001419e-08</v>
@@ -9192,10 +8906,8 @@
       <c r="K21" t="n">
         <v>83.89363160979561</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 9.347x + -15454.234</t>
-        </is>
+      <c r="W21" t="n">
+        <v>9.347402608555718</v>
       </c>
       <c r="X21" t="n">
         <v>-15454.23373669312</v>
@@ -9204,7 +8916,7 @@
         <v>1.185533263051768e-09</v>
       </c>
       <c r="Z21" t="n">
-        <v>140.25</v>
+        <v>1932.263815453651</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000000485e-08</v>
@@ -9244,10 +8956,8 @@
       <c r="K22" t="n">
         <v>83.86981723841019</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 9.311x + -15254.374</t>
-        </is>
+      <c r="W22" t="n">
+        <v>9.310813091120549</v>
       </c>
       <c r="X22" t="n">
         <v>-15254.3744343405</v>
@@ -9256,7 +8966,7 @@
         <v>5.341544813221286e-08</v>
       </c>
       <c r="Z22" t="n">
-        <v>135.3700000000001</v>
+        <v>1915.068446222447</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000105e-08</v>
@@ -9382,12 +9092,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -9442,10 +9152,8 @@
       <c r="K2" t="n">
         <v>86.06649056588259</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 14.543x + -26607.760</t>
-        </is>
+      <c r="W2" t="n">
+        <v>14.54318003780779</v>
       </c>
       <c r="X2" t="n">
         <v>-26607.76010804871</v>
@@ -9454,7 +9162,7 @@
         <v>2.561212350355966e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>327.9499999999998</v>
+        <v>2002.081351190302</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000025406e-08</v>
@@ -9494,10 +9202,8 @@
       <c r="K3" t="n">
         <v>86.76546241648256</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 17.695x + -28977.903</t>
-        </is>
+      <c r="W3" t="n">
+        <v>17.69492494451351</v>
       </c>
       <c r="X3" t="n">
         <v>-28977.90291191796</v>
@@ -9506,7 +9212,7 @@
         <v>7.958536421594163e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>187.1799999999998</v>
+        <v>1845.078878028542</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000006e-08</v>
@@ -9546,10 +9252,8 @@
       <c r="K4" t="n">
         <v>86.96343756573788</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 18.851x + -30029.175</t>
-        </is>
+      <c r="W4" t="n">
+        <v>18.85096281736867</v>
       </c>
       <c r="X4" t="n">
         <v>-30029.17494132651</v>
@@ -9558,7 +9262,7 @@
         <v>6.629517581915167e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>136.4099999999999</v>
+        <v>1799.075986342032</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000002e-08</v>
@@ -9598,10 +9302,8 @@
       <c r="K5" t="n">
         <v>86.90504759300956</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 18.495x + -28940.059</t>
-        </is>
+      <c r="W5" t="n">
+        <v>18.49464364817777</v>
       </c>
       <c r="X5" t="n">
         <v>-28940.05921438317</v>
@@ -9610,7 +9312,7 @@
         <v>9.655467005359109e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>128.22</v>
+        <v>1769.28253467059</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000139312e-08</v>
@@ -9650,10 +9352,8 @@
       <c r="K6" t="n">
         <v>86.7663765867857</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 17.700x + -27231.773</t>
-        </is>
+      <c r="W6" t="n">
+        <v>17.69993807928302</v>
       </c>
       <c r="X6" t="n">
         <v>-27231.77261128127</v>
@@ -9662,7 +9362,7 @@
         <v>2.037721765307055e-11</v>
       </c>
       <c r="Z6" t="n">
-        <v>121.96</v>
+        <v>1741.065750781662</v>
       </c>
       <c r="AA6" t="n">
         <v>1e-08</v>
@@ -9702,10 +9402,8 @@
       <c r="K7" t="n">
         <v>86.62685619091015</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 16.966x + -25668.738</t>
-        </is>
+      <c r="W7" t="n">
+        <v>16.96624050265522</v>
       </c>
       <c r="X7" t="n">
         <v>-25668.73843584974</v>
@@ -9714,7 +9412,7 @@
         <v>1.544063932410871e-11</v>
       </c>
       <c r="Z7" t="n">
-        <v>119.9400000000001</v>
+        <v>1713.29247573609</v>
       </c>
       <c r="AA7" t="n">
         <v>1e-08</v>
@@ -9754,10 +9452,8 @@
       <c r="K8" t="n">
         <v>86.30373212081655</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 15.479x + -22966.881</t>
-        </is>
+      <c r="W8" t="n">
+        <v>15.47947138083346</v>
       </c>
       <c r="X8" t="n">
         <v>-22966.88120499742</v>
@@ -9766,7 +9462,7 @@
         <v>4.502247663862155e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>120.27</v>
+        <v>1686.289858227703</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000003e-08</v>
@@ -9806,10 +9502,8 @@
       <c r="K9" t="n">
         <v>86.36723549598375</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 15.751x + -23053.042</t>
-        </is>
+      <c r="W9" t="n">
+        <v>15.75080959971839</v>
       </c>
       <c r="X9" t="n">
         <v>-23053.0418001188</v>
@@ -9818,7 +9512,7 @@
         <v>5.548853834689077e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>109.6899999999998</v>
+        <v>1659.747023603323</v>
       </c>
       <c r="AA9" t="n">
         <v>1e-08</v>
@@ -9858,10 +9552,8 @@
       <c r="K10" t="n">
         <v>85.86676725399651</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 13.838x + -19835.018</t>
-        </is>
+      <c r="W10" t="n">
+        <v>13.83816496641358</v>
       </c>
       <c r="X10" t="n">
         <v>-19835.01773981188</v>
@@ -9870,7 +9562,7 @@
         <v>7.439743487959913e-08</v>
       </c>
       <c r="Z10" t="n">
-        <v>117.3099999999999</v>
+        <v>1634.862859063115</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000025642e-08</v>
@@ -9910,10 +9602,8 @@
       <c r="K11" t="n">
         <v>85.99200204422762</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 14.272x + -20223.121</t>
-        </is>
+      <c r="W11" t="n">
+        <v>14.27203626382984</v>
       </c>
       <c r="X11" t="n">
         <v>-20223.12058336674</v>
@@ -9922,7 +9612,7 @@
         <v>3.277321864779594e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>103.52</v>
+        <v>1611.30018337099</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000005047e-08</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 37.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 37.xlsx
@@ -428,7 +428,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -559,7 +559,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-218.6599999999999</v>
@@ -609,7 +609,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-171.4899999999998</v>
@@ -659,7 +659,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-151.29</v>
@@ -709,7 +709,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-136.4100000000003</v>
@@ -759,7 +759,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-117.3899999999999</v>
@@ -809,7 +809,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-113.2399999999998</v>
@@ -859,7 +859,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-107.6599999999999</v>
@@ -909,7 +909,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-96.08999999999992</v>
@@ -959,7 +959,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-84.73000000000002</v>
@@ -1009,7 +1009,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-81.46000000000004</v>
@@ -1074,7 +1074,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -2270,7 +2270,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -3466,7 +3466,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -3597,7 +3597,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-350.1300000000001</v>
@@ -3647,7 +3647,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-205.3099999999999</v>
@@ -3697,7 +3697,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-140.0799999999999</v>
@@ -3747,7 +3747,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-128.3699999999999</v>
@@ -3797,7 +3797,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-109.6400000000001</v>
@@ -3847,7 +3847,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-90.52999999999997</v>
@@ -3897,7 +3897,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-86.07000000000016</v>
@@ -3947,7 +3947,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-83.73000000000002</v>
@@ -3997,7 +3997,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-72.48999999999978</v>
@@ -4047,7 +4047,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-63.79999999999995</v>
@@ -4112,7 +4112,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -5308,7 +5308,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -5439,7 +5439,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-441.52</v>
@@ -5489,7 +5489,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-246.0999999999999</v>
@@ -5539,7 +5539,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-201.6700000000001</v>
@@ -5589,7 +5589,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-174.0499999999997</v>
@@ -5639,7 +5639,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-166.7799999999997</v>
@@ -5689,7 +5689,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-146.3100000000002</v>
@@ -5739,7 +5739,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-134.9800000000002</v>
@@ -5789,7 +5789,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-129</v>
@@ -5839,7 +5839,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-125.6400000000001</v>
@@ -5889,7 +5889,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-119.72</v>
@@ -5954,7 +5954,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -7150,7 +7150,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -7281,7 +7281,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-471.4099999999999</v>
@@ -7331,7 +7331,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-272.96</v>
@@ -7381,7 +7381,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-204.6400000000001</v>
@@ -7431,7 +7431,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-179.4899999999998</v>
@@ -7481,7 +7481,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-161.8299999999999</v>
@@ -7531,7 +7531,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-141.1600000000001</v>
@@ -7581,7 +7581,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-141.29</v>
@@ -7631,7 +7631,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-119.6900000000001</v>
@@ -7681,7 +7681,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-128.28</v>
@@ -7731,7 +7731,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-109.3800000000001</v>
@@ -7796,7 +7796,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -8992,7 +8992,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -9123,7 +9123,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-327.9499999999998</v>
@@ -9173,7 +9173,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-187.1799999999998</v>
@@ -9223,7 +9223,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-136.4099999999999</v>
@@ -9273,7 +9273,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-117.6000000000001</v>
@@ -9323,7 +9323,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-102.1800000000001</v>
@@ -9373,7 +9373,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-95.42000000000007</v>
@@ -9423,7 +9423,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-92.87000000000012</v>
@@ -9473,7 +9473,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-78.04999999999995</v>
@@ -9523,7 +9523,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-86.12999999999988</v>
@@ -9573,7 +9573,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-68.58999999999992</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 37.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 37.xlsx
@@ -562,7 +562,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-218.6599999999999</v>
+        <v>1814.005</v>
       </c>
       <c r="D2" t="n">
         <v>2.24383e-07</v>
@@ -612,7 +612,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-171.4899999999998</v>
+        <v>1751.481</v>
       </c>
       <c r="D3" t="n">
         <v>2.23962e-07</v>
@@ -662,7 +662,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-151.29</v>
+        <v>1693.408</v>
       </c>
       <c r="D4" t="n">
         <v>2.24379e-07</v>
@@ -712,7 +712,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-136.4100000000003</v>
+        <v>1652.642</v>
       </c>
       <c r="D5" t="n">
         <v>2.24522e-07</v>
@@ -762,7 +762,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-117.3899999999999</v>
+        <v>1625.187</v>
       </c>
       <c r="D6" t="n">
         <v>2.24955e-07</v>
@@ -812,7 +812,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-113.2399999999998</v>
+        <v>1587.675</v>
       </c>
       <c r="D7" t="n">
         <v>2.25363e-07</v>
@@ -862,7 +862,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-107.6599999999999</v>
+        <v>1555.746</v>
       </c>
       <c r="D8" t="n">
         <v>2.25547e-07</v>
@@ -912,7 +912,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-96.08999999999992</v>
+        <v>1536.202</v>
       </c>
       <c r="D9" t="n">
         <v>2.26042e-07</v>
@@ -962,7 +962,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-84.73000000000002</v>
+        <v>1515.169</v>
       </c>
       <c r="D10" t="n">
         <v>2.26303e-07</v>
@@ -1012,7 +1012,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-81.46000000000004</v>
+        <v>1494.237</v>
       </c>
       <c r="D11" t="n">
         <v>2.26613e-07</v>
@@ -1208,7 +1208,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-135.9400000000001</v>
+        <v>1734.173</v>
       </c>
       <c r="D2" t="n">
         <v>2.1836e-07</v>
@@ -1258,7 +1258,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-106.1700000000001</v>
+        <v>1616.769</v>
       </c>
       <c r="D3" t="n">
         <v>2.2176e-07</v>
@@ -1308,7 +1308,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-105.2900000000002</v>
+        <v>1574.053</v>
       </c>
       <c r="D4" t="n">
         <v>2.22401e-07</v>
@@ -1358,7 +1358,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-92.4699999999998</v>
+        <v>1550.28</v>
       </c>
       <c r="D5" t="n">
         <v>2.22896e-07</v>
@@ -1408,7 +1408,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-100.3099999999999</v>
+        <v>1520.239</v>
       </c>
       <c r="D6" t="n">
         <v>2.23227e-07</v>
@@ -1458,7 +1458,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-90.6099999999999</v>
+        <v>1506.123</v>
       </c>
       <c r="D7" t="n">
         <v>2.23436e-07</v>
@@ -1508,7 +1508,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-83.95000000000005</v>
+        <v>1493.475</v>
       </c>
       <c r="D8" t="n">
         <v>2.23665e-07</v>
@@ -1558,7 +1558,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-82.73000000000002</v>
+        <v>1469.502</v>
       </c>
       <c r="D9" t="n">
         <v>2.2409e-07</v>
@@ -1608,7 +1608,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-75.68999999999983</v>
+        <v>1457.948</v>
       </c>
       <c r="D10" t="n">
         <v>2.24155e-07</v>
@@ -1658,7 +1658,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-78.76999999999998</v>
+        <v>1431.258</v>
       </c>
       <c r="D11" t="n">
         <v>2.24609e-07</v>
@@ -1708,7 +1708,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-72.99000000000001</v>
+        <v>1422.243</v>
       </c>
       <c r="D12" t="n">
         <v>2.24895e-07</v>
@@ -1758,7 +1758,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-68.1400000000001</v>
+        <v>1406.964</v>
       </c>
       <c r="D13" t="n">
         <v>2.25169e-07</v>
@@ -1808,7 +1808,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-70.96000000000004</v>
+        <v>1387.754</v>
       </c>
       <c r="D14" t="n">
         <v>2.25313e-07</v>
@@ -1858,7 +1858,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-63.87000000000012</v>
+        <v>1377.823</v>
       </c>
       <c r="D15" t="n">
         <v>2.25514e-07</v>
@@ -1908,7 +1908,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-57.23000000000002</v>
+        <v>1363.499</v>
       </c>
       <c r="D16" t="n">
         <v>2.25865e-07</v>
@@ -1958,7 +1958,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-55.64999999999986</v>
+        <v>1350.148</v>
       </c>
       <c r="D17" t="n">
         <v>2.25957e-07</v>
@@ -2008,7 +2008,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-57.11999999999989</v>
+        <v>1333.816</v>
       </c>
       <c r="D18" t="n">
         <v>2.26299e-07</v>
@@ -2058,7 +2058,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-55.14999999999986</v>
+        <v>1318.449</v>
       </c>
       <c r="D19" t="n">
         <v>2.26416e-07</v>
@@ -2108,7 +2108,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-50.51999999999998</v>
+        <v>1309.593</v>
       </c>
       <c r="D20" t="n">
         <v>2.26689e-07</v>
@@ -2158,7 +2158,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-38.57999999999993</v>
+        <v>1300.287</v>
       </c>
       <c r="D21" t="n">
         <v>2.27011e-07</v>
@@ -2208,7 +2208,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-46.54999999999995</v>
+        <v>1279.247</v>
       </c>
       <c r="D22" t="n">
         <v>2.27231e-07</v>
@@ -2404,7 +2404,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-149</v>
+        <v>1666.632</v>
       </c>
       <c r="D2" t="n">
         <v>2.27294e-07</v>
@@ -2454,7 +2454,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-128.7300000000002</v>
+        <v>1616.93</v>
       </c>
       <c r="D3" t="n">
         <v>2.26925e-07</v>
@@ -2504,7 +2504,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-112.25</v>
+        <v>1592.246</v>
       </c>
       <c r="D4" t="n">
         <v>2.26783e-07</v>
@@ -2554,7 +2554,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-111.22</v>
+        <v>1562.477</v>
       </c>
       <c r="D5" t="n">
         <v>2.2684e-07</v>
@@ -2604,7 +2604,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-100.5400000000002</v>
+        <v>1542.867</v>
       </c>
       <c r="D6" t="n">
         <v>2.26993e-07</v>
@@ -2654,7 +2654,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-83.66999999999985</v>
+        <v>1527.195</v>
       </c>
       <c r="D7" t="n">
         <v>2.27219e-07</v>
@@ -2704,7 +2704,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-91.66000000000008</v>
+        <v>1501.91</v>
       </c>
       <c r="D8" t="n">
         <v>2.27296e-07</v>
@@ -2754,7 +2754,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-86.48000000000002</v>
+        <v>1486.43</v>
       </c>
       <c r="D9" t="n">
         <v>2.27522e-07</v>
@@ -2804,7 +2804,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-77.75999999999999</v>
+        <v>1469.84</v>
       </c>
       <c r="D10" t="n">
         <v>2.27726e-07</v>
@@ -2854,7 +2854,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-79.19000000000005</v>
+        <v>1447.476</v>
       </c>
       <c r="D11" t="n">
         <v>2.27978e-07</v>
@@ -2904,7 +2904,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-70.65000000000009</v>
+        <v>1436.798</v>
       </c>
       <c r="D12" t="n">
         <v>2.28017e-07</v>
@@ -2954,7 +2954,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-71.86999999999989</v>
+        <v>1422.429</v>
       </c>
       <c r="D13" t="n">
         <v>2.28219e-07</v>
@@ -3004,7 +3004,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-67.41000000000008</v>
+        <v>1403.969</v>
       </c>
       <c r="D14" t="n">
         <v>2.28395e-07</v>
@@ -3054,7 +3054,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-59.77999999999997</v>
+        <v>1390.713</v>
       </c>
       <c r="D15" t="n">
         <v>2.28736e-07</v>
@@ -3104,7 +3104,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-60.40000000000009</v>
+        <v>1375.576</v>
       </c>
       <c r="D16" t="n">
         <v>2.28791e-07</v>
@@ -3154,7 +3154,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-62.96000000000004</v>
+        <v>1358.484</v>
       </c>
       <c r="D17" t="n">
         <v>2.28949e-07</v>
@@ -3204,7 +3204,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-56.23000000000002</v>
+        <v>1344.776</v>
       </c>
       <c r="D18" t="n">
         <v>2.29168e-07</v>
@@ -3254,7 +3254,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-53.95000000000005</v>
+        <v>1331.007</v>
       </c>
       <c r="D19" t="n">
         <v>2.29517e-07</v>
@@ -3304,7 +3304,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-46.00999999999999</v>
+        <v>1325.802</v>
       </c>
       <c r="D20" t="n">
         <v>2.29603e-07</v>
@@ -3354,7 +3354,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-35.8900000000001</v>
+        <v>1319.285</v>
       </c>
       <c r="D21" t="n">
         <v>2.29874e-07</v>
@@ -3404,7 +3404,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-44.6099999999999</v>
+        <v>1295.816</v>
       </c>
       <c r="D22" t="n">
         <v>2.29975e-07</v>
@@ -3600,7 +3600,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-350.1300000000001</v>
+        <v>2114.352</v>
       </c>
       <c r="D2" t="n">
         <v>2.20003e-07</v>
@@ -3650,7 +3650,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-205.3099999999999</v>
+        <v>1776.086</v>
       </c>
       <c r="D3" t="n">
         <v>2.29222e-07</v>
@@ -3700,7 +3700,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-140.0799999999999</v>
+        <v>1707.509</v>
       </c>
       <c r="D4" t="n">
         <v>2.2907e-07</v>
@@ -3750,7 +3750,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-128.3699999999999</v>
+        <v>1651.816</v>
       </c>
       <c r="D5" t="n">
         <v>2.28409e-07</v>
@@ -3800,7 +3800,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-109.6400000000001</v>
+        <v>1622.346</v>
       </c>
       <c r="D6" t="n">
         <v>2.27914e-07</v>
@@ -3850,7 +3850,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-90.52999999999997</v>
+        <v>1609.309</v>
       </c>
       <c r="D7" t="n">
         <v>2.27454e-07</v>
@@ -3900,7 +3900,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-86.07000000000016</v>
+        <v>1577.922</v>
       </c>
       <c r="D8" t="n">
         <v>2.27441e-07</v>
@@ -3950,7 +3950,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-83.73000000000002</v>
+        <v>1549.557</v>
       </c>
       <c r="D9" t="n">
         <v>2.27318e-07</v>
@@ -4000,7 +4000,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-72.48999999999978</v>
+        <v>1529.537</v>
       </c>
       <c r="D10" t="n">
         <v>2.27401e-07</v>
@@ -4050,7 +4050,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-63.79999999999995</v>
+        <v>1508.141</v>
       </c>
       <c r="D11" t="n">
         <v>2.27702e-07</v>
@@ -4246,7 +4246,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-335.8899999999999</v>
+        <v>1752.188</v>
       </c>
       <c r="D2" t="n">
         <v>2.26992e-07</v>
@@ -4296,7 +4296,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-233.6299999999999</v>
+        <v>1641.5</v>
       </c>
       <c r="D3" t="n">
         <v>2.25966e-07</v>
@@ -4346,7 +4346,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-192.3799999999999</v>
+        <v>1613.235</v>
       </c>
       <c r="D4" t="n">
         <v>2.25437e-07</v>
@@ -4396,7 +4396,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-186.5699999999997</v>
+        <v>1580.094</v>
       </c>
       <c r="D5" t="n">
         <v>2.24967e-07</v>
@@ -4446,7 +4446,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-178.6199999999999</v>
+        <v>1552.763</v>
       </c>
       <c r="D6" t="n">
         <v>2.24991e-07</v>
@@ -4496,7 +4496,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-177.7199999999998</v>
+        <v>1523.405</v>
       </c>
       <c r="D7" t="n">
         <v>2.25294e-07</v>
@@ -4546,7 +4546,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-160.52</v>
+        <v>1504.731</v>
       </c>
       <c r="D8" t="n">
         <v>2.25734e-07</v>
@@ -4596,7 +4596,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-156.0999999999999</v>
+        <v>1481.167</v>
       </c>
       <c r="D9" t="n">
         <v>2.26031e-07</v>
@@ -4646,7 +4646,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-143.6799999999998</v>
+        <v>1460.938</v>
       </c>
       <c r="D10" t="n">
         <v>2.26428e-07</v>
@@ -4696,7 +4696,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-128.5999999999999</v>
+        <v>1449.985</v>
       </c>
       <c r="D11" t="n">
         <v>2.26693e-07</v>
@@ -4746,7 +4746,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-127.3299999999999</v>
+        <v>1422.934</v>
       </c>
       <c r="D12" t="n">
         <v>2.27112e-07</v>
@@ -4796,7 +4796,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-126.3199999999999</v>
+        <v>1401.637</v>
       </c>
       <c r="D13" t="n">
         <v>2.27351e-07</v>
@@ -4846,7 +4846,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-125.8</v>
+        <v>1386.363</v>
       </c>
       <c r="D14" t="n">
         <v>2.27644e-07</v>
@@ -4896,7 +4896,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-115.4299999999998</v>
+        <v>1374.024</v>
       </c>
       <c r="D15" t="n">
         <v>2.27914e-07</v>
@@ -4946,7 +4946,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-111.25</v>
+        <v>1348.227</v>
       </c>
       <c r="D16" t="n">
         <v>2.28279e-07</v>
@@ -4996,7 +4996,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-108.8799999999999</v>
+        <v>1335.891</v>
       </c>
       <c r="D17" t="n">
         <v>2.28588e-07</v>
@@ -5046,7 +5046,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-103.99</v>
+        <v>1319.195</v>
       </c>
       <c r="D18" t="n">
         <v>2.28858e-07</v>
@@ -5096,7 +5096,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-94.97000000000003</v>
+        <v>1309.05</v>
       </c>
       <c r="D19" t="n">
         <v>2.28997e-07</v>
@@ -5146,7 +5146,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-84.99000000000001</v>
+        <v>1295.642</v>
       </c>
       <c r="D20" t="n">
         <v>2.29365e-07</v>
@@ -5196,7 +5196,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-87.92000000000007</v>
+        <v>1274.321</v>
       </c>
       <c r="D21" t="n">
         <v>2.29598e-07</v>
@@ -5246,7 +5246,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-84.24000000000001</v>
+        <v>1257.798</v>
       </c>
       <c r="D22" t="n">
         <v>2.30063e-07</v>
@@ -5442,7 +5442,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-441.52</v>
+        <v>2065.626</v>
       </c>
       <c r="D2" t="n">
         <v>2.17084e-07</v>
@@ -5492,7 +5492,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-246.0999999999999</v>
+        <v>1734.047</v>
       </c>
       <c r="D3" t="n">
         <v>2.26824e-07</v>
@@ -5542,7 +5542,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-201.6700000000001</v>
+        <v>1642.096</v>
       </c>
       <c r="D4" t="n">
         <v>2.27197e-07</v>
@@ -5592,7 +5592,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-174.0499999999997</v>
+        <v>1605.516</v>
       </c>
       <c r="D5" t="n">
         <v>2.26753e-07</v>
@@ -5642,7 +5642,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-166.7799999999997</v>
+        <v>1573.433</v>
       </c>
       <c r="D6" t="n">
         <v>2.26422e-07</v>
@@ -5692,7 +5692,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-146.3100000000002</v>
+        <v>1551.094</v>
       </c>
       <c r="D7" t="n">
         <v>2.26397e-07</v>
@@ -5742,7 +5742,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-134.9800000000002</v>
+        <v>1529.057</v>
       </c>
       <c r="D8" t="n">
         <v>2.26568e-07</v>
@@ -5792,7 +5792,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-129</v>
+        <v>1500.209</v>
       </c>
       <c r="D9" t="n">
         <v>2.26951e-07</v>
@@ -5842,7 +5842,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-125.6400000000001</v>
+        <v>1476.013</v>
       </c>
       <c r="D10" t="n">
         <v>2.27133e-07</v>
@@ -5892,7 +5892,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-119.72</v>
+        <v>1454.721</v>
       </c>
       <c r="D11" t="n">
         <v>2.27413e-07</v>
@@ -6088,7 +6088,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-280.1100000000001</v>
+        <v>1725.394</v>
       </c>
       <c r="D2" t="n">
         <v>2.26531e-07</v>
@@ -6138,7 +6138,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-178.1899999999998</v>
+        <v>1623.539</v>
       </c>
       <c r="D3" t="n">
         <v>2.26623e-07</v>
@@ -6188,7 +6188,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-162.51</v>
+        <v>1576.376</v>
       </c>
       <c r="D4" t="n">
         <v>2.26515e-07</v>
@@ -6238,7 +6238,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-142.2400000000002</v>
+        <v>1559.103</v>
       </c>
       <c r="D5" t="n">
         <v>2.26581e-07</v>
@@ -6288,7 +6288,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-140.45</v>
+        <v>1528.372</v>
       </c>
       <c r="D6" t="n">
         <v>2.26773e-07</v>
@@ -6338,7 +6338,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-122.1899999999998</v>
+        <v>1522.61</v>
       </c>
       <c r="D7" t="n">
         <v>2.27016e-07</v>
@@ -6388,7 +6388,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-116.1500000000001</v>
+        <v>1504.563</v>
       </c>
       <c r="D8" t="n">
         <v>2.27357e-07</v>
@@ -6438,7 +6438,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-113.6600000000001</v>
+        <v>1479.745</v>
       </c>
       <c r="D9" t="n">
         <v>2.27833e-07</v>
@@ -6488,7 +6488,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-114.0699999999999</v>
+        <v>1463.767</v>
       </c>
       <c r="D10" t="n">
         <v>2.28047e-07</v>
@@ -6538,7 +6538,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-99.66000000000008</v>
+        <v>1448.391</v>
       </c>
       <c r="D11" t="n">
         <v>2.2845e-07</v>
@@ -6588,7 +6588,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-101.25</v>
+        <v>1432.515</v>
       </c>
       <c r="D12" t="n">
         <v>2.28776e-07</v>
@@ -6638,7 +6638,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-101.8700000000001</v>
+        <v>1412.245</v>
       </c>
       <c r="D13" t="n">
         <v>2.2912e-07</v>
@@ -6688,7 +6688,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-86.27999999999997</v>
+        <v>1407.569</v>
       </c>
       <c r="D14" t="n">
         <v>2.29467e-07</v>
@@ -6738,7 +6738,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-85.08999999999992</v>
+        <v>1390.912</v>
       </c>
       <c r="D15" t="n">
         <v>2.29705e-07</v>
@@ -6788,7 +6788,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-88.47000000000003</v>
+        <v>1369.928</v>
       </c>
       <c r="D16" t="n">
         <v>2.30137e-07</v>
@@ -6838,7 +6838,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-80.54999999999995</v>
+        <v>1362.544</v>
       </c>
       <c r="D17" t="n">
         <v>2.3027e-07</v>
@@ -6888,7 +6888,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-75.55000000000018</v>
+        <v>1345.587</v>
       </c>
       <c r="D18" t="n">
         <v>2.30766e-07</v>
@@ -6938,7 +6938,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-77.00999999999999</v>
+        <v>1331.909</v>
       </c>
       <c r="D19" t="n">
         <v>2.3117e-07</v>
@@ -6988,7 +6988,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-73.75</v>
+        <v>1316.11</v>
       </c>
       <c r="D20" t="n">
         <v>2.3163e-07</v>
@@ -7038,7 +7038,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-69.75</v>
+        <v>1301.998</v>
       </c>
       <c r="D21" t="n">
         <v>2.31836e-07</v>
@@ -7088,7 +7088,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-66.95000000000005</v>
+        <v>1289.785</v>
       </c>
       <c r="D22" t="n">
         <v>2.3223e-07</v>
@@ -7284,7 +7284,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-471.4099999999999</v>
+        <v>1976.583</v>
       </c>
       <c r="D2" t="n">
         <v>2.21568e-07</v>
@@ -7334,7 +7334,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-272.96</v>
+        <v>1669.171</v>
       </c>
       <c r="D3" t="n">
         <v>2.28968e-07</v>
@@ -7384,7 +7384,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-204.6400000000001</v>
+        <v>1600.702</v>
       </c>
       <c r="D4" t="n">
         <v>2.28597e-07</v>
@@ -7434,7 +7434,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-179.4899999999998</v>
+        <v>1563.355</v>
       </c>
       <c r="D5" t="n">
         <v>2.282e-07</v>
@@ -7484,7 +7484,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-161.8299999999999</v>
+        <v>1532.769</v>
       </c>
       <c r="D6" t="n">
         <v>2.28012e-07</v>
@@ -7534,7 +7534,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-141.1600000000001</v>
+        <v>1512.521</v>
       </c>
       <c r="D7" t="n">
         <v>2.28215e-07</v>
@@ -7584,7 +7584,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-141.29</v>
+        <v>1474.567</v>
       </c>
       <c r="D8" t="n">
         <v>2.28493e-07</v>
@@ -7634,7 +7634,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-119.6900000000001</v>
+        <v>1464.828</v>
       </c>
       <c r="D9" t="n">
         <v>2.28725e-07</v>
@@ -7684,7 +7684,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-128.28</v>
+        <v>1431.029</v>
       </c>
       <c r="D10" t="n">
         <v>2.29008e-07</v>
@@ -7734,7 +7734,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-109.3800000000001</v>
+        <v>1415.186</v>
       </c>
       <c r="D11" t="n">
         <v>2.29427e-07</v>
@@ -7930,7 +7930,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-268.8200000000002</v>
+        <v>1707.309</v>
       </c>
       <c r="D2" t="n">
         <v>2.27208e-07</v>
@@ -7980,7 +7980,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-172.8399999999999</v>
+        <v>1602.314</v>
       </c>
       <c r="D3" t="n">
         <v>2.27506e-07</v>
@@ -8030,7 +8030,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-154.3299999999999</v>
+        <v>1557.452</v>
       </c>
       <c r="D4" t="n">
         <v>2.27772e-07</v>
@@ -8080,7 +8080,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-140.46</v>
+        <v>1531.421</v>
       </c>
       <c r="D5" t="n">
         <v>2.28344e-07</v>
@@ -8130,7 +8130,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-134.0800000000002</v>
+        <v>1510.483</v>
       </c>
       <c r="D6" t="n">
         <v>2.28373e-07</v>
@@ -8180,7 +8180,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-123.21</v>
+        <v>1491.157</v>
       </c>
       <c r="D7" t="n">
         <v>2.28826e-07</v>
@@ -8230,7 +8230,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-122.52</v>
+        <v>1470.39</v>
       </c>
       <c r="D8" t="n">
         <v>2.29134e-07</v>
@@ -8280,7 +8280,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-109.8399999999999</v>
+        <v>1454.956</v>
       </c>
       <c r="D9" t="n">
         <v>2.29688e-07</v>
@@ -8330,7 +8330,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-113.6699999999998</v>
+        <v>1433.046</v>
       </c>
       <c r="D10" t="n">
         <v>2.299e-07</v>
@@ -8380,7 +8380,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-95.74000000000001</v>
+        <v>1423.702</v>
       </c>
       <c r="D11" t="n">
         <v>2.306e-07</v>
@@ -8430,7 +8430,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-94.34999999999991</v>
+        <v>1413.549</v>
       </c>
       <c r="D12" t="n">
         <v>2.30583e-07</v>
@@ -8480,7 +8480,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-95.12999999999988</v>
+        <v>1393.484</v>
       </c>
       <c r="D13" t="n">
         <v>2.30816e-07</v>
@@ -8530,7 +8530,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-92.51999999999998</v>
+        <v>1379.736</v>
       </c>
       <c r="D14" t="n">
         <v>2.31275e-07</v>
@@ -8580,7 +8580,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-96</v>
+        <v>1360.813</v>
       </c>
       <c r="D15" t="n">
         <v>2.31459e-07</v>
@@ -8630,7 +8630,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-84.94000000000005</v>
+        <v>1356.489</v>
       </c>
       <c r="D16" t="n">
         <v>2.31756e-07</v>
@@ -8680,7 +8680,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-80.84999999999991</v>
+        <v>1339.859</v>
       </c>
       <c r="D17" t="n">
         <v>2.32158e-07</v>
@@ -8730,7 +8730,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-83.72000000000003</v>
+        <v>1327.183</v>
       </c>
       <c r="D18" t="n">
         <v>2.32559e-07</v>
@@ -8780,7 +8780,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-68.64999999999986</v>
+        <v>1317.642</v>
       </c>
       <c r="D19" t="n">
         <v>2.32865e-07</v>
@@ -8830,7 +8830,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-69.83999999999992</v>
+        <v>1302.174</v>
       </c>
       <c r="D20" t="n">
         <v>2.3326e-07</v>
@@ -8880,7 +8880,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-71.32000000000016</v>
+        <v>1282.304</v>
       </c>
       <c r="D21" t="n">
         <v>2.33434e-07</v>
@@ -8930,7 +8930,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-67.11000000000013</v>
+        <v>1271.53</v>
       </c>
       <c r="D22" t="n">
         <v>2.33696e-07</v>
@@ -9126,7 +9126,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-327.9499999999998</v>
+        <v>1363.689</v>
       </c>
       <c r="D2" t="n">
         <v>2.41289e-07</v>
@@ -9176,7 +9176,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-187.1799999999998</v>
+        <v>1179.436</v>
       </c>
       <c r="D3" t="n">
         <v>2.40085e-07</v>
@@ -9226,7 +9226,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-136.4099999999999</v>
+        <v>1137.492</v>
       </c>
       <c r="D4" t="n">
         <v>2.38173e-07</v>
@@ -9276,7 +9276,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-117.6000000000001</v>
+        <v>1110.765</v>
       </c>
       <c r="D5" t="n">
         <v>2.3722e-07</v>
@@ -9326,7 +9326,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-102.1800000000001</v>
+        <v>1088.304</v>
       </c>
       <c r="D6" t="n">
         <v>2.36688e-07</v>
@@ -9376,7 +9376,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-95.42000000000007</v>
+        <v>1062.168</v>
       </c>
       <c r="D7" t="n">
         <v>2.36447e-07</v>
@@ -9426,7 +9426,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-92.87000000000012</v>
+        <v>1035.495</v>
       </c>
       <c r="D8" t="n">
         <v>2.36518e-07</v>
@@ -9476,7 +9476,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-78.04999999999995</v>
+        <v>1021.711</v>
       </c>
       <c r="D9" t="n">
         <v>2.36683e-07</v>
@@ -9526,7 +9526,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-86.12999999999988</v>
+        <v>989.984</v>
       </c>
       <c r="D10" t="n">
         <v>2.36865e-07</v>
@@ -9576,7 +9576,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-68.58999999999992</v>
+        <v>982.1680000000001</v>
       </c>
       <c r="D11" t="n">
         <v>2.37054e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 37.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 37.xlsx
@@ -438,7 +438,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -564,6 +564,9 @@
       <c r="B2" t="n">
         <v>1814.005</v>
       </c>
+      <c r="C2" t="n">
+        <v>2238.888957344104</v>
+      </c>
       <c r="D2" t="n">
         <v>2.24383e-07</v>
       </c>
@@ -614,6 +617,9 @@
       <c r="B3" t="n">
         <v>1751.481</v>
       </c>
+      <c r="C3" t="n">
+        <v>2181.764380934869</v>
+      </c>
       <c r="D3" t="n">
         <v>2.23962e-07</v>
       </c>
@@ -664,6 +670,9 @@
       <c r="B4" t="n">
         <v>1693.408</v>
       </c>
+      <c r="C4" t="n">
+        <v>2130.515606069677</v>
+      </c>
       <c r="D4" t="n">
         <v>2.24379e-07</v>
       </c>
@@ -714,6 +723,9 @@
       <c r="B5" t="n">
         <v>1652.642</v>
       </c>
+      <c r="C5" t="n">
+        <v>2090.770210489846</v>
+      </c>
       <c r="D5" t="n">
         <v>2.24522e-07</v>
       </c>
@@ -764,6 +776,9 @@
       <c r="B6" t="n">
         <v>1625.187</v>
       </c>
+      <c r="C6" t="n">
+        <v>2062.718267637992</v>
+      </c>
       <c r="D6" t="n">
         <v>2.24955e-07</v>
       </c>
@@ -814,6 +829,9 @@
       <c r="B7" t="n">
         <v>1587.675</v>
       </c>
+      <c r="C7" t="n">
+        <v>2027.83291869917</v>
+      </c>
       <c r="D7" t="n">
         <v>2.25363e-07</v>
       </c>
@@ -864,6 +882,9 @@
       <c r="B8" t="n">
         <v>1555.746</v>
       </c>
+      <c r="C8" t="n">
+        <v>2000.054977658849</v>
+      </c>
       <c r="D8" t="n">
         <v>2.25547e-07</v>
       </c>
@@ -914,6 +935,9 @@
       <c r="B9" t="n">
         <v>1536.202</v>
       </c>
+      <c r="C9" t="n">
+        <v>1981.311910774808</v>
+      </c>
       <c r="D9" t="n">
         <v>2.26042e-07</v>
       </c>
@@ -964,6 +988,9 @@
       <c r="B10" t="n">
         <v>1515.169</v>
       </c>
+      <c r="C10" t="n">
+        <v>1956.678038206551</v>
+      </c>
       <c r="D10" t="n">
         <v>2.26303e-07</v>
       </c>
@@ -1013,6 +1040,9 @@
       </c>
       <c r="B11" t="n">
         <v>1494.237</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1939.611393330302</v>
       </c>
       <c r="D11" t="n">
         <v>2.26613e-07</v>
@@ -1084,7 +1114,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -1210,6 +1240,9 @@
       <c r="B2" t="n">
         <v>1734.173</v>
       </c>
+      <c r="C2" t="n">
+        <v>2208.72236273694</v>
+      </c>
       <c r="D2" t="n">
         <v>2.1836e-07</v>
       </c>
@@ -1260,6 +1293,9 @@
       <c r="B3" t="n">
         <v>1616.769</v>
       </c>
+      <c r="C3" t="n">
+        <v>2055.701533927863</v>
+      </c>
       <c r="D3" t="n">
         <v>2.2176e-07</v>
       </c>
@@ -1310,6 +1346,9 @@
       <c r="B4" t="n">
         <v>1574.053</v>
       </c>
+      <c r="C4" t="n">
+        <v>2012.46008941781</v>
+      </c>
       <c r="D4" t="n">
         <v>2.22401e-07</v>
       </c>
@@ -1360,6 +1399,9 @@
       <c r="B5" t="n">
         <v>1550.28</v>
       </c>
+      <c r="C5" t="n">
+        <v>1988.530096823612</v>
+      </c>
       <c r="D5" t="n">
         <v>2.22896e-07</v>
       </c>
@@ -1410,6 +1452,9 @@
       <c r="B6" t="n">
         <v>1520.239</v>
       </c>
+      <c r="C6" t="n">
+        <v>1963.616743166558</v>
+      </c>
       <c r="D6" t="n">
         <v>2.23227e-07</v>
       </c>
@@ -1460,6 +1505,9 @@
       <c r="B7" t="n">
         <v>1506.123</v>
       </c>
+      <c r="C7" t="n">
+        <v>1948.409939626798</v>
+      </c>
       <c r="D7" t="n">
         <v>2.23436e-07</v>
       </c>
@@ -1510,6 +1558,9 @@
       <c r="B8" t="n">
         <v>1493.475</v>
       </c>
+      <c r="C8" t="n">
+        <v>1934.813295582696</v>
+      </c>
       <c r="D8" t="n">
         <v>2.23665e-07</v>
       </c>
@@ -1560,6 +1611,9 @@
       <c r="B9" t="n">
         <v>1469.502</v>
       </c>
+      <c r="C9" t="n">
+        <v>1913.11392593876</v>
+      </c>
       <c r="D9" t="n">
         <v>2.2409e-07</v>
       </c>
@@ -1610,6 +1664,9 @@
       <c r="B10" t="n">
         <v>1457.948</v>
       </c>
+      <c r="C10" t="n">
+        <v>1898.95463328362</v>
+      </c>
       <c r="D10" t="n">
         <v>2.24155e-07</v>
       </c>
@@ -1660,6 +1717,9 @@
       <c r="B11" t="n">
         <v>1431.258</v>
       </c>
+      <c r="C11" t="n">
+        <v>1875.748439083413</v>
+      </c>
       <c r="D11" t="n">
         <v>2.24609e-07</v>
       </c>
@@ -1710,6 +1770,9 @@
       <c r="B12" t="n">
         <v>1422.243</v>
       </c>
+      <c r="C12" t="n">
+        <v>1863.993734506017</v>
+      </c>
       <c r="D12" t="n">
         <v>2.24895e-07</v>
       </c>
@@ -1760,6 +1823,9 @@
       <c r="B13" t="n">
         <v>1406.964</v>
       </c>
+      <c r="C13" t="n">
+        <v>1848.549032655684</v>
+      </c>
       <c r="D13" t="n">
         <v>2.25169e-07</v>
       </c>
@@ -1810,6 +1876,9 @@
       <c r="B14" t="n">
         <v>1387.754</v>
       </c>
+      <c r="C14" t="n">
+        <v>1830.66822299377</v>
+      </c>
       <c r="D14" t="n">
         <v>2.25313e-07</v>
       </c>
@@ -1860,6 +1929,9 @@
       <c r="B15" t="n">
         <v>1377.823</v>
       </c>
+      <c r="C15" t="n">
+        <v>1819.529757053389</v>
+      </c>
       <c r="D15" t="n">
         <v>2.25514e-07</v>
       </c>
@@ -1910,6 +1982,9 @@
       <c r="B16" t="n">
         <v>1363.499</v>
       </c>
+      <c r="C16" t="n">
+        <v>1804.660160027916</v>
+      </c>
       <c r="D16" t="n">
         <v>2.25865e-07</v>
       </c>
@@ -1960,6 +2035,9 @@
       <c r="B17" t="n">
         <v>1350.148</v>
       </c>
+      <c r="C17" t="n">
+        <v>1790.298221364868</v>
+      </c>
       <c r="D17" t="n">
         <v>2.25957e-07</v>
       </c>
@@ -2010,6 +2088,9 @@
       <c r="B18" t="n">
         <v>1333.816</v>
       </c>
+      <c r="C18" t="n">
+        <v>1773.998488042879</v>
+      </c>
       <c r="D18" t="n">
         <v>2.26299e-07</v>
       </c>
@@ -2060,6 +2141,9 @@
       <c r="B19" t="n">
         <v>1318.449</v>
       </c>
+      <c r="C19" t="n">
+        <v>1758.454319681135</v>
+      </c>
       <c r="D19" t="n">
         <v>2.26416e-07</v>
       </c>
@@ -2110,6 +2194,9 @@
       <c r="B20" t="n">
         <v>1309.593</v>
       </c>
+      <c r="C20" t="n">
+        <v>1745.13548672248</v>
+      </c>
       <c r="D20" t="n">
         <v>2.26689e-07</v>
       </c>
@@ -2160,6 +2247,9 @@
       <c r="B21" t="n">
         <v>1300.287</v>
       </c>
+      <c r="C21" t="n">
+        <v>1736.888908032435</v>
+      </c>
       <c r="D21" t="n">
         <v>2.27011e-07</v>
       </c>
@@ -2209,6 +2299,9 @@
       </c>
       <c r="B22" t="n">
         <v>1279.247</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1715.756573114495</v>
       </c>
       <c r="D22" t="n">
         <v>2.27231e-07</v>
@@ -2280,7 +2373,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -2406,6 +2499,9 @@
       <c r="B2" t="n">
         <v>1666.632</v>
       </c>
+      <c r="C2" t="n">
+        <v>2100.773393507358</v>
+      </c>
       <c r="D2" t="n">
         <v>2.27294e-07</v>
       </c>
@@ -2456,6 +2552,9 @@
       <c r="B3" t="n">
         <v>1616.93</v>
       </c>
+      <c r="C3" t="n">
+        <v>2047.956735210037</v>
+      </c>
       <c r="D3" t="n">
         <v>2.26925e-07</v>
       </c>
@@ -2506,6 +2605,9 @@
       <c r="B4" t="n">
         <v>1592.246</v>
       </c>
+      <c r="C4" t="n">
+        <v>2019.972257365567</v>
+      </c>
       <c r="D4" t="n">
         <v>2.26783e-07</v>
       </c>
@@ -2556,6 +2658,9 @@
       <c r="B5" t="n">
         <v>1562.477</v>
       </c>
+      <c r="C5" t="n">
+        <v>1997.248667989006</v>
+      </c>
       <c r="D5" t="n">
         <v>2.2684e-07</v>
       </c>
@@ -2606,6 +2711,9 @@
       <c r="B6" t="n">
         <v>1542.867</v>
       </c>
+      <c r="C6" t="n">
+        <v>1977.839566544007</v>
+      </c>
       <c r="D6" t="n">
         <v>2.26993e-07</v>
       </c>
@@ -2656,6 +2764,9 @@
       <c r="B7" t="n">
         <v>1527.195</v>
       </c>
+      <c r="C7" t="n">
+        <v>1961.56163853549</v>
+      </c>
       <c r="D7" t="n">
         <v>2.27219e-07</v>
       </c>
@@ -2706,6 +2817,9 @@
       <c r="B8" t="n">
         <v>1501.91</v>
       </c>
+      <c r="C8" t="n">
+        <v>1938.764184336931</v>
+      </c>
       <c r="D8" t="n">
         <v>2.27296e-07</v>
       </c>
@@ -2756,6 +2870,9 @@
       <c r="B9" t="n">
         <v>1486.43</v>
       </c>
+      <c r="C9" t="n">
+        <v>1922.57095567159</v>
+      </c>
       <c r="D9" t="n">
         <v>2.27522e-07</v>
       </c>
@@ -2806,6 +2923,9 @@
       <c r="B10" t="n">
         <v>1469.84</v>
       </c>
+      <c r="C10" t="n">
+        <v>1904.025576292133</v>
+      </c>
       <c r="D10" t="n">
         <v>2.27726e-07</v>
       </c>
@@ -2856,6 +2976,9 @@
       <c r="B11" t="n">
         <v>1447.476</v>
       </c>
+      <c r="C11" t="n">
+        <v>1882.479883837841</v>
+      </c>
       <c r="D11" t="n">
         <v>2.27978e-07</v>
       </c>
@@ -2906,6 +3029,9 @@
       <c r="B12" t="n">
         <v>1436.798</v>
       </c>
+      <c r="C12" t="n">
+        <v>1868.952916125145</v>
+      </c>
       <c r="D12" t="n">
         <v>2.28017e-07</v>
       </c>
@@ -2956,6 +3082,9 @@
       <c r="B13" t="n">
         <v>1422.429</v>
       </c>
+      <c r="C13" t="n">
+        <v>1854.336474445235</v>
+      </c>
       <c r="D13" t="n">
         <v>2.28219e-07</v>
       </c>
@@ -3006,6 +3135,9 @@
       <c r="B14" t="n">
         <v>1403.969</v>
       </c>
+      <c r="C14" t="n">
+        <v>1843.085086708337</v>
+      </c>
       <c r="D14" t="n">
         <v>2.28395e-07</v>
       </c>
@@ -3056,6 +3188,9 @@
       <c r="B15" t="n">
         <v>1390.713</v>
       </c>
+      <c r="C15" t="n">
+        <v>1829.234555355921</v>
+      </c>
       <c r="D15" t="n">
         <v>2.28736e-07</v>
       </c>
@@ -3106,6 +3241,9 @@
       <c r="B16" t="n">
         <v>1375.576</v>
       </c>
+      <c r="C16" t="n">
+        <v>1810.60908098756</v>
+      </c>
       <c r="D16" t="n">
         <v>2.28791e-07</v>
       </c>
@@ -3156,6 +3294,9 @@
       <c r="B17" t="n">
         <v>1358.484</v>
       </c>
+      <c r="C17" t="n">
+        <v>1792.496740505121</v>
+      </c>
       <c r="D17" t="n">
         <v>2.28949e-07</v>
       </c>
@@ -3206,6 +3347,9 @@
       <c r="B18" t="n">
         <v>1344.776</v>
       </c>
+      <c r="C18" t="n">
+        <v>1779.565125889865</v>
+      </c>
       <c r="D18" t="n">
         <v>2.29168e-07</v>
       </c>
@@ -3256,6 +3400,9 @@
       <c r="B19" t="n">
         <v>1331.007</v>
       </c>
+      <c r="C19" t="n">
+        <v>1763.02073434414</v>
+      </c>
       <c r="D19" t="n">
         <v>2.29517e-07</v>
       </c>
@@ -3306,6 +3453,9 @@
       <c r="B20" t="n">
         <v>1325.802</v>
       </c>
+      <c r="C20" t="n">
+        <v>1755.921174867555</v>
+      </c>
       <c r="D20" t="n">
         <v>2.29603e-07</v>
       </c>
@@ -3356,6 +3506,9 @@
       <c r="B21" t="n">
         <v>1319.285</v>
       </c>
+      <c r="C21" t="n">
+        <v>1744.860761538582</v>
+      </c>
       <c r="D21" t="n">
         <v>2.29874e-07</v>
       </c>
@@ -3405,6 +3558,9 @@
       </c>
       <c r="B22" t="n">
         <v>1295.816</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1727.18301184386</v>
       </c>
       <c r="D22" t="n">
         <v>2.29975e-07</v>
@@ -3476,7 +3632,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -3602,6 +3758,9 @@
       <c r="B2" t="n">
         <v>2114.352</v>
       </c>
+      <c r="C2" t="n">
+        <v>2622.082681448851</v>
+      </c>
       <c r="D2" t="n">
         <v>2.20003e-07</v>
       </c>
@@ -3652,6 +3811,9 @@
       <c r="B3" t="n">
         <v>1776.086</v>
       </c>
+      <c r="C3" t="n">
+        <v>2204.325735835511</v>
+      </c>
       <c r="D3" t="n">
         <v>2.29222e-07</v>
       </c>
@@ -3702,6 +3864,9 @@
       <c r="B4" t="n">
         <v>1707.509</v>
       </c>
+      <c r="C4" t="n">
+        <v>2122.06145040809</v>
+      </c>
       <c r="D4" t="n">
         <v>2.2907e-07</v>
       </c>
@@ -3752,6 +3917,9 @@
       <c r="B5" t="n">
         <v>1651.816</v>
       </c>
+      <c r="C5" t="n">
+        <v>2074.321638043706</v>
+      </c>
       <c r="D5" t="n">
         <v>2.28409e-07</v>
       </c>
@@ -3802,6 +3970,9 @@
       <c r="B6" t="n">
         <v>1622.346</v>
       </c>
+      <c r="C6" t="n">
+        <v>2048.950869429521</v>
+      </c>
       <c r="D6" t="n">
         <v>2.27914e-07</v>
       </c>
@@ -3852,6 +4023,9 @@
       <c r="B7" t="n">
         <v>1609.309</v>
       </c>
+      <c r="C7" t="n">
+        <v>2031.244450190667</v>
+      </c>
       <c r="D7" t="n">
         <v>2.27454e-07</v>
       </c>
@@ -3902,6 +4076,9 @@
       <c r="B8" t="n">
         <v>1577.922</v>
       </c>
+      <c r="C8" t="n">
+        <v>2002.463466557829</v>
+      </c>
       <c r="D8" t="n">
         <v>2.27441e-07</v>
       </c>
@@ -3952,6 +4129,9 @@
       <c r="B9" t="n">
         <v>1549.557</v>
       </c>
+      <c r="C9" t="n">
+        <v>1974.576761178508</v>
+      </c>
       <c r="D9" t="n">
         <v>2.27318e-07</v>
       </c>
@@ -4002,6 +4182,9 @@
       <c r="B10" t="n">
         <v>1529.537</v>
       </c>
+      <c r="C10" t="n">
+        <v>1955.719537220519</v>
+      </c>
       <c r="D10" t="n">
         <v>2.27401e-07</v>
       </c>
@@ -4051,6 +4234,9 @@
       </c>
       <c r="B11" t="n">
         <v>1508.141</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1935.486029281826</v>
       </c>
       <c r="D11" t="n">
         <v>2.27702e-07</v>
@@ -4122,7 +4308,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -4248,6 +4434,9 @@
       <c r="B2" t="n">
         <v>1752.188</v>
       </c>
+      <c r="C2" t="n">
+        <v>2211.449038200349</v>
+      </c>
       <c r="D2" t="n">
         <v>2.26992e-07</v>
       </c>
@@ -4298,6 +4487,9 @@
       <c r="B3" t="n">
         <v>1641.5</v>
       </c>
+      <c r="C3" t="n">
+        <v>2076.397425720556</v>
+      </c>
       <c r="D3" t="n">
         <v>2.25966e-07</v>
       </c>
@@ -4348,6 +4540,9 @@
       <c r="B4" t="n">
         <v>1613.235</v>
       </c>
+      <c r="C4" t="n">
+        <v>2041.611685644711</v>
+      </c>
       <c r="D4" t="n">
         <v>2.25437e-07</v>
       </c>
@@ -4398,6 +4593,9 @@
       <c r="B5" t="n">
         <v>1580.094</v>
       </c>
+      <c r="C5" t="n">
+        <v>2015.357201216074</v>
+      </c>
       <c r="D5" t="n">
         <v>2.24967e-07</v>
       </c>
@@ -4448,6 +4646,9 @@
       <c r="B6" t="n">
         <v>1552.763</v>
       </c>
+      <c r="C6" t="n">
+        <v>1988.528617118454</v>
+      </c>
       <c r="D6" t="n">
         <v>2.24991e-07</v>
       </c>
@@ -4498,6 +4699,9 @@
       <c r="B7" t="n">
         <v>1523.405</v>
       </c>
+      <c r="C7" t="n">
+        <v>1963.199561538411</v>
+      </c>
       <c r="D7" t="n">
         <v>2.25294e-07</v>
       </c>
@@ -4548,6 +4752,9 @@
       <c r="B8" t="n">
         <v>1504.731</v>
       </c>
+      <c r="C8" t="n">
+        <v>1943.363577596999</v>
+      </c>
       <c r="D8" t="n">
         <v>2.25734e-07</v>
       </c>
@@ -4598,6 +4805,9 @@
       <c r="B9" t="n">
         <v>1481.167</v>
       </c>
+      <c r="C9" t="n">
+        <v>1921.024791025693</v>
+      </c>
       <c r="D9" t="n">
         <v>2.26031e-07</v>
       </c>
@@ -4648,6 +4858,9 @@
       <c r="B10" t="n">
         <v>1460.938</v>
       </c>
+      <c r="C10" t="n">
+        <v>1900.966858515827</v>
+      </c>
       <c r="D10" t="n">
         <v>2.26428e-07</v>
       </c>
@@ -4698,6 +4911,9 @@
       <c r="B11" t="n">
         <v>1449.985</v>
       </c>
+      <c r="C11" t="n">
+        <v>1886.941042762658</v>
+      </c>
       <c r="D11" t="n">
         <v>2.26693e-07</v>
       </c>
@@ -4748,6 +4964,9 @@
       <c r="B12" t="n">
         <v>1422.934</v>
       </c>
+      <c r="C12" t="n">
+        <v>1862.76248242681</v>
+      </c>
       <c r="D12" t="n">
         <v>2.27112e-07</v>
       </c>
@@ -4798,6 +5017,9 @@
       <c r="B13" t="n">
         <v>1401.637</v>
       </c>
+      <c r="C13" t="n">
+        <v>1840.312185252643</v>
+      </c>
       <c r="D13" t="n">
         <v>2.27351e-07</v>
       </c>
@@ -4848,6 +5070,9 @@
       <c r="B14" t="n">
         <v>1386.363</v>
       </c>
+      <c r="C14" t="n">
+        <v>1823.249463554655</v>
+      </c>
       <c r="D14" t="n">
         <v>2.27644e-07</v>
       </c>
@@ -4898,6 +5123,9 @@
       <c r="B15" t="n">
         <v>1374.024</v>
       </c>
+      <c r="C15" t="n">
+        <v>1808.630171406865</v>
+      </c>
       <c r="D15" t="n">
         <v>2.27914e-07</v>
       </c>
@@ -4948,6 +5176,9 @@
       <c r="B16" t="n">
         <v>1348.227</v>
       </c>
+      <c r="C16" t="n">
+        <v>1786.957457563326</v>
+      </c>
       <c r="D16" t="n">
         <v>2.28279e-07</v>
       </c>
@@ -4998,6 +5229,9 @@
       <c r="B17" t="n">
         <v>1335.891</v>
       </c>
+      <c r="C17" t="n">
+        <v>1771.740622166712</v>
+      </c>
       <c r="D17" t="n">
         <v>2.28588e-07</v>
       </c>
@@ -5048,6 +5282,9 @@
       <c r="B18" t="n">
         <v>1319.195</v>
       </c>
+      <c r="C18" t="n">
+        <v>1756.637773915822</v>
+      </c>
       <c r="D18" t="n">
         <v>2.28858e-07</v>
       </c>
@@ -5098,6 +5335,9 @@
       <c r="B19" t="n">
         <v>1309.05</v>
       </c>
+      <c r="C19" t="n">
+        <v>1747.609385682665</v>
+      </c>
       <c r="D19" t="n">
         <v>2.28997e-07</v>
       </c>
@@ -5148,6 +5388,9 @@
       <c r="B20" t="n">
         <v>1295.642</v>
       </c>
+      <c r="C20" t="n">
+        <v>1732.264578201273</v>
+      </c>
       <c r="D20" t="n">
         <v>2.29365e-07</v>
       </c>
@@ -5198,6 +5441,9 @@
       <c r="B21" t="n">
         <v>1274.321</v>
       </c>
+      <c r="C21" t="n">
+        <v>1710.80856847468</v>
+      </c>
       <c r="D21" t="n">
         <v>2.29598e-07</v>
       </c>
@@ -5247,6 +5493,9 @@
       </c>
       <c r="B22" t="n">
         <v>1257.798</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1695.955660180961</v>
       </c>
       <c r="D22" t="n">
         <v>2.30063e-07</v>
@@ -5318,7 +5567,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -5444,6 +5693,9 @@
       <c r="B2" t="n">
         <v>2065.626</v>
       </c>
+      <c r="C2" t="n">
+        <v>2601.62047726172</v>
+      </c>
       <c r="D2" t="n">
         <v>2.17084e-07</v>
       </c>
@@ -5494,6 +5746,9 @@
       <c r="B3" t="n">
         <v>1734.047</v>
       </c>
+      <c r="C3" t="n">
+        <v>2167.776000059104</v>
+      </c>
       <c r="D3" t="n">
         <v>2.26824e-07</v>
       </c>
@@ -5544,6 +5799,9 @@
       <c r="B4" t="n">
         <v>1642.096</v>
       </c>
+      <c r="C4" t="n">
+        <v>2070.366256307197</v>
+      </c>
       <c r="D4" t="n">
         <v>2.27197e-07</v>
       </c>
@@ -5594,6 +5852,9 @@
       <c r="B5" t="n">
         <v>1605.516</v>
       </c>
+      <c r="C5" t="n">
+        <v>2030.904925363868</v>
+      </c>
       <c r="D5" t="n">
         <v>2.26753e-07</v>
       </c>
@@ -5644,6 +5905,9 @@
       <c r="B6" t="n">
         <v>1573.433</v>
       </c>
+      <c r="C6" t="n">
+        <v>2003.122225302584</v>
+      </c>
       <c r="D6" t="n">
         <v>2.26422e-07</v>
       </c>
@@ -5694,6 +5958,9 @@
       <c r="B7" t="n">
         <v>1551.094</v>
       </c>
+      <c r="C7" t="n">
+        <v>1983.435762356056</v>
+      </c>
       <c r="D7" t="n">
         <v>2.26397e-07</v>
       </c>
@@ -5744,6 +6011,9 @@
       <c r="B8" t="n">
         <v>1529.057</v>
       </c>
+      <c r="C8" t="n">
+        <v>1960.575132403359</v>
+      </c>
       <c r="D8" t="n">
         <v>2.26568e-07</v>
       </c>
@@ -5794,6 +6064,9 @@
       <c r="B9" t="n">
         <v>1500.209</v>
       </c>
+      <c r="C9" t="n">
+        <v>1933.432781903236</v>
+      </c>
       <c r="D9" t="n">
         <v>2.26951e-07</v>
       </c>
@@ -5844,6 +6117,9 @@
       <c r="B10" t="n">
         <v>1476.013</v>
       </c>
+      <c r="C10" t="n">
+        <v>1912.020554611371</v>
+      </c>
       <c r="D10" t="n">
         <v>2.27133e-07</v>
       </c>
@@ -5893,6 +6169,9 @@
       </c>
       <c r="B11" t="n">
         <v>1454.721</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1890.68821071824</v>
       </c>
       <c r="D11" t="n">
         <v>2.27413e-07</v>
@@ -5964,7 +6243,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -6090,6 +6369,9 @@
       <c r="B2" t="n">
         <v>1725.394</v>
       </c>
+      <c r="C2" t="n">
+        <v>2186.697247525924</v>
+      </c>
       <c r="D2" t="n">
         <v>2.26531e-07</v>
       </c>
@@ -6140,6 +6422,9 @@
       <c r="B3" t="n">
         <v>1623.539</v>
       </c>
+      <c r="C3" t="n">
+        <v>2053.854316412766</v>
+      </c>
       <c r="D3" t="n">
         <v>2.26623e-07</v>
       </c>
@@ -6190,6 +6475,9 @@
       <c r="B4" t="n">
         <v>1576.376</v>
       </c>
+      <c r="C4" t="n">
+        <v>2009.862671719732</v>
+      </c>
       <c r="D4" t="n">
         <v>2.26515e-07</v>
       </c>
@@ -6240,6 +6528,9 @@
       <c r="B5" t="n">
         <v>1559.103</v>
       </c>
+      <c r="C5" t="n">
+        <v>1990.385256924629</v>
+      </c>
       <c r="D5" t="n">
         <v>2.26581e-07</v>
       </c>
@@ -6290,6 +6581,9 @@
       <c r="B6" t="n">
         <v>1528.372</v>
       </c>
+      <c r="C6" t="n">
+        <v>1965.611563424251</v>
+      </c>
       <c r="D6" t="n">
         <v>2.26773e-07</v>
       </c>
@@ -6340,6 +6634,9 @@
       <c r="B7" t="n">
         <v>1522.61</v>
       </c>
+      <c r="C7" t="n">
+        <v>1956.544055695254</v>
+      </c>
       <c r="D7" t="n">
         <v>2.27016e-07</v>
       </c>
@@ -6390,6 +6687,9 @@
       <c r="B8" t="n">
         <v>1504.563</v>
       </c>
+      <c r="C8" t="n">
+        <v>1936.969298581042</v>
+      </c>
       <c r="D8" t="n">
         <v>2.27357e-07</v>
       </c>
@@ -6440,6 +6740,9 @@
       <c r="B9" t="n">
         <v>1479.745</v>
       </c>
+      <c r="C9" t="n">
+        <v>1916.160844936774</v>
+      </c>
       <c r="D9" t="n">
         <v>2.27833e-07</v>
       </c>
@@ -6490,6 +6793,9 @@
       <c r="B10" t="n">
         <v>1463.767</v>
       </c>
+      <c r="C10" t="n">
+        <v>1899.77606564336</v>
+      </c>
       <c r="D10" t="n">
         <v>2.28047e-07</v>
       </c>
@@ -6540,6 +6846,9 @@
       <c r="B11" t="n">
         <v>1448.391</v>
       </c>
+      <c r="C11" t="n">
+        <v>1883.386708212762</v>
+      </c>
       <c r="D11" t="n">
         <v>2.2845e-07</v>
       </c>
@@ -6590,6 +6899,9 @@
       <c r="B12" t="n">
         <v>1432.515</v>
       </c>
+      <c r="C12" t="n">
+        <v>1867.370401511714</v>
+      </c>
       <c r="D12" t="n">
         <v>2.28776e-07</v>
       </c>
@@ -6640,6 +6952,9 @@
       <c r="B13" t="n">
         <v>1412.245</v>
       </c>
+      <c r="C13" t="n">
+        <v>1848.2608030271</v>
+      </c>
       <c r="D13" t="n">
         <v>2.2912e-07</v>
       </c>
@@ -6690,6 +7005,9 @@
       <c r="B14" t="n">
         <v>1407.569</v>
       </c>
+      <c r="C14" t="n">
+        <v>1839.196920401653</v>
+      </c>
       <c r="D14" t="n">
         <v>2.29467e-07</v>
       </c>
@@ -6740,6 +7058,9 @@
       <c r="B15" t="n">
         <v>1390.912</v>
       </c>
+      <c r="C15" t="n">
+        <v>1821.097421454789</v>
+      </c>
       <c r="D15" t="n">
         <v>2.29705e-07</v>
       </c>
@@ -6790,6 +7111,9 @@
       <c r="B16" t="n">
         <v>1369.928</v>
       </c>
+      <c r="C16" t="n">
+        <v>1803.184365729607</v>
+      </c>
       <c r="D16" t="n">
         <v>2.30137e-07</v>
       </c>
@@ -6840,6 +7164,9 @@
       <c r="B17" t="n">
         <v>1362.544</v>
       </c>
+      <c r="C17" t="n">
+        <v>1790.865815305591</v>
+      </c>
       <c r="D17" t="n">
         <v>2.3027e-07</v>
       </c>
@@ -6890,6 +7217,9 @@
       <c r="B18" t="n">
         <v>1345.587</v>
       </c>
+      <c r="C18" t="n">
+        <v>1775.410441078668</v>
+      </c>
       <c r="D18" t="n">
         <v>2.30766e-07</v>
       </c>
@@ -6940,6 +7270,9 @@
       <c r="B19" t="n">
         <v>1331.909</v>
       </c>
+      <c r="C19" t="n">
+        <v>1758.826002218653</v>
+      </c>
       <c r="D19" t="n">
         <v>2.3117e-07</v>
       </c>
@@ -6990,6 +7323,9 @@
       <c r="B20" t="n">
         <v>1316.11</v>
       </c>
+      <c r="C20" t="n">
+        <v>1744.215557494516</v>
+      </c>
       <c r="D20" t="n">
         <v>2.3163e-07</v>
       </c>
@@ -7040,6 +7376,9 @@
       <c r="B21" t="n">
         <v>1301.998</v>
       </c>
+      <c r="C21" t="n">
+        <v>1730.664725814722</v>
+      </c>
       <c r="D21" t="n">
         <v>2.31836e-07</v>
       </c>
@@ -7089,6 +7428,9 @@
       </c>
       <c r="B22" t="n">
         <v>1289.785</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1715.744768352527</v>
       </c>
       <c r="D22" t="n">
         <v>2.3223e-07</v>
@@ -7160,7 +7502,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -7286,6 +7628,9 @@
       <c r="B2" t="n">
         <v>1976.583</v>
       </c>
+      <c r="C2" t="n">
+        <v>2474.701747177023</v>
+      </c>
       <c r="D2" t="n">
         <v>2.21568e-07</v>
       </c>
@@ -7336,6 +7681,9 @@
       <c r="B3" t="n">
         <v>1669.171</v>
       </c>
+      <c r="C3" t="n">
+        <v>2094.259383596715</v>
+      </c>
       <c r="D3" t="n">
         <v>2.28968e-07</v>
       </c>
@@ -7386,6 +7734,9 @@
       <c r="B4" t="n">
         <v>1600.702</v>
       </c>
+      <c r="C4" t="n">
+        <v>2015.878415590754</v>
+      </c>
       <c r="D4" t="n">
         <v>2.28597e-07</v>
       </c>
@@ -7436,6 +7787,9 @@
       <c r="B5" t="n">
         <v>1563.355</v>
       </c>
+      <c r="C5" t="n">
+        <v>1982.567581177731</v>
+      </c>
       <c r="D5" t="n">
         <v>2.282e-07</v>
       </c>
@@ -7486,6 +7840,9 @@
       <c r="B6" t="n">
         <v>1532.769</v>
       </c>
+      <c r="C6" t="n">
+        <v>1953.279142176621</v>
+      </c>
       <c r="D6" t="n">
         <v>2.28012e-07</v>
       </c>
@@ -7536,6 +7893,9 @@
       <c r="B7" t="n">
         <v>1512.521</v>
       </c>
+      <c r="C7" t="n">
+        <v>1931.152394698897</v>
+      </c>
       <c r="D7" t="n">
         <v>2.28215e-07</v>
       </c>
@@ -7586,6 +7946,9 @@
       <c r="B8" t="n">
         <v>1474.567</v>
       </c>
+      <c r="C8" t="n">
+        <v>1900.462581414804</v>
+      </c>
       <c r="D8" t="n">
         <v>2.28493e-07</v>
       </c>
@@ -7636,6 +7999,9 @@
       <c r="B9" t="n">
         <v>1464.828</v>
       </c>
+      <c r="C9" t="n">
+        <v>1886.412584017256</v>
+      </c>
       <c r="D9" t="n">
         <v>2.28725e-07</v>
       </c>
@@ -7686,6 +8052,9 @@
       <c r="B10" t="n">
         <v>1431.029</v>
       </c>
+      <c r="C10" t="n">
+        <v>1858.171648458056</v>
+      </c>
       <c r="D10" t="n">
         <v>2.29008e-07</v>
       </c>
@@ -7735,6 +8104,9 @@
       </c>
       <c r="B11" t="n">
         <v>1415.186</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1840.119092537433</v>
       </c>
       <c r="D11" t="n">
         <v>2.29427e-07</v>
@@ -7806,7 +8178,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -7932,6 +8304,9 @@
       <c r="B2" t="n">
         <v>1707.309</v>
       </c>
+      <c r="C2" t="n">
+        <v>2160.535059640006</v>
+      </c>
       <c r="D2" t="n">
         <v>2.27208e-07</v>
       </c>
@@ -7982,6 +8357,9 @@
       <c r="B3" t="n">
         <v>1602.314</v>
       </c>
+      <c r="C3" t="n">
+        <v>2021.519206193573</v>
+      </c>
       <c r="D3" t="n">
         <v>2.27506e-07</v>
       </c>
@@ -8032,6 +8410,9 @@
       <c r="B4" t="n">
         <v>1557.452</v>
       </c>
+      <c r="C4" t="n">
+        <v>1978.010149402718</v>
+      </c>
       <c r="D4" t="n">
         <v>2.27772e-07</v>
       </c>
@@ -8082,6 +8463,9 @@
       <c r="B5" t="n">
         <v>1531.421</v>
       </c>
+      <c r="C5" t="n">
+        <v>1953.943863010883</v>
+      </c>
       <c r="D5" t="n">
         <v>2.28344e-07</v>
       </c>
@@ -8132,6 +8516,9 @@
       <c r="B6" t="n">
         <v>1510.483</v>
       </c>
+      <c r="C6" t="n">
+        <v>1934.700657098063</v>
+      </c>
       <c r="D6" t="n">
         <v>2.28373e-07</v>
       </c>
@@ -8182,6 +8569,9 @@
       <c r="B7" t="n">
         <v>1491.157</v>
       </c>
+      <c r="C7" t="n">
+        <v>1914.625022775606</v>
+      </c>
       <c r="D7" t="n">
         <v>2.28826e-07</v>
       </c>
@@ -8232,6 +8622,9 @@
       <c r="B8" t="n">
         <v>1470.39</v>
       </c>
+      <c r="C8" t="n">
+        <v>1896.221490548368</v>
+      </c>
       <c r="D8" t="n">
         <v>2.29134e-07</v>
       </c>
@@ -8282,6 +8675,9 @@
       <c r="B9" t="n">
         <v>1454.956</v>
       </c>
+      <c r="C9" t="n">
+        <v>1880.277551095924</v>
+      </c>
       <c r="D9" t="n">
         <v>2.29688e-07</v>
       </c>
@@ -8332,6 +8728,9 @@
       <c r="B10" t="n">
         <v>1433.046</v>
       </c>
+      <c r="C10" t="n">
+        <v>1859.535378742356</v>
+      </c>
       <c r="D10" t="n">
         <v>2.299e-07</v>
       </c>
@@ -8382,6 +8781,9 @@
       <c r="B11" t="n">
         <v>1423.702</v>
       </c>
+      <c r="C11" t="n">
+        <v>1847.287171972801</v>
+      </c>
       <c r="D11" t="n">
         <v>2.306e-07</v>
       </c>
@@ -8432,6 +8834,9 @@
       <c r="B12" t="n">
         <v>1413.549</v>
       </c>
+      <c r="C12" t="n">
+        <v>1835.520879922447</v>
+      </c>
       <c r="D12" t="n">
         <v>2.30583e-07</v>
       </c>
@@ -8482,6 +8887,9 @@
       <c r="B13" t="n">
         <v>1393.484</v>
       </c>
+      <c r="C13" t="n">
+        <v>1817.660030969975</v>
+      </c>
       <c r="D13" t="n">
         <v>2.30816e-07</v>
       </c>
@@ -8532,6 +8940,9 @@
       <c r="B14" t="n">
         <v>1379.736</v>
       </c>
+      <c r="C14" t="n">
+        <v>1800.803966462967</v>
+      </c>
       <c r="D14" t="n">
         <v>2.31275e-07</v>
       </c>
@@ -8582,6 +8993,9 @@
       <c r="B15" t="n">
         <v>1360.813</v>
       </c>
+      <c r="C15" t="n">
+        <v>1783.669996084115</v>
+      </c>
       <c r="D15" t="n">
         <v>2.31459e-07</v>
       </c>
@@ -8632,6 +9046,9 @@
       <c r="B16" t="n">
         <v>1356.489</v>
       </c>
+      <c r="C16" t="n">
+        <v>1775.073729701581</v>
+      </c>
       <c r="D16" t="n">
         <v>2.31756e-07</v>
       </c>
@@ -8682,6 +9099,9 @@
       <c r="B17" t="n">
         <v>1339.859</v>
       </c>
+      <c r="C17" t="n">
+        <v>1762.398994085765</v>
+      </c>
       <c r="D17" t="n">
         <v>2.32158e-07</v>
       </c>
@@ -8732,6 +9152,9 @@
       <c r="B18" t="n">
         <v>1327.183</v>
       </c>
+      <c r="C18" t="n">
+        <v>1745.732944836149</v>
+      </c>
       <c r="D18" t="n">
         <v>2.32559e-07</v>
       </c>
@@ -8782,6 +9205,9 @@
       <c r="B19" t="n">
         <v>1317.642</v>
       </c>
+      <c r="C19" t="n">
+        <v>1737.785993921399</v>
+      </c>
       <c r="D19" t="n">
         <v>2.32865e-07</v>
       </c>
@@ -8832,6 +9258,9 @@
       <c r="B20" t="n">
         <v>1302.174</v>
       </c>
+      <c r="C20" t="n">
+        <v>1721.772102220119</v>
+      </c>
       <c r="D20" t="n">
         <v>2.3326e-07</v>
       </c>
@@ -8882,6 +9311,9 @@
       <c r="B21" t="n">
         <v>1282.304</v>
       </c>
+      <c r="C21" t="n">
+        <v>1707.079753278358</v>
+      </c>
       <c r="D21" t="n">
         <v>2.33434e-07</v>
       </c>
@@ -8931,6 +9363,9 @@
       </c>
       <c r="B22" t="n">
         <v>1271.53</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1694.622978116683</v>
       </c>
       <c r="D22" t="n">
         <v>2.33696e-07</v>
@@ -9002,7 +9437,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -9128,6 +9563,9 @@
       <c r="B2" t="n">
         <v>1363.689</v>
       </c>
+      <c r="C2" t="n">
+        <v>1919.873802401291</v>
+      </c>
       <c r="D2" t="n">
         <v>2.41289e-07</v>
       </c>
@@ -9178,6 +9616,9 @@
       <c r="B3" t="n">
         <v>1179.436</v>
       </c>
+      <c r="C3" t="n">
+        <v>1658.258493788332</v>
+      </c>
       <c r="D3" t="n">
         <v>2.40085e-07</v>
       </c>
@@ -9228,6 +9669,9 @@
       <c r="B4" t="n">
         <v>1137.492</v>
       </c>
+      <c r="C4" t="n">
+        <v>1611.050988994953</v>
+      </c>
       <c r="D4" t="n">
         <v>2.38173e-07</v>
       </c>
@@ -9278,6 +9722,9 @@
       <c r="B5" t="n">
         <v>1110.765</v>
       </c>
+      <c r="C5" t="n">
+        <v>1584.493693018979</v>
+      </c>
       <c r="D5" t="n">
         <v>2.3722e-07</v>
       </c>
@@ -9328,6 +9775,9 @@
       <c r="B6" t="n">
         <v>1088.304</v>
       </c>
+      <c r="C6" t="n">
+        <v>1566.565933476016</v>
+      </c>
       <c r="D6" t="n">
         <v>2.36688e-07</v>
       </c>
@@ -9378,6 +9828,9 @@
       <c r="B7" t="n">
         <v>1062.168</v>
       </c>
+      <c r="C7" t="n">
+        <v>1542.431241922039</v>
+      </c>
       <c r="D7" t="n">
         <v>2.36447e-07</v>
       </c>
@@ -9428,6 +9881,9 @@
       <c r="B8" t="n">
         <v>1035.495</v>
       </c>
+      <c r="C8" t="n">
+        <v>1520.448758163297</v>
+      </c>
       <c r="D8" t="n">
         <v>2.36518e-07</v>
       </c>
@@ -9478,6 +9934,9 @@
       <c r="B9" t="n">
         <v>1021.711</v>
       </c>
+      <c r="C9" t="n">
+        <v>1507.345026154338</v>
+      </c>
       <c r="D9" t="n">
         <v>2.36683e-07</v>
       </c>
@@ -9528,6 +9987,9 @@
       <c r="B10" t="n">
         <v>989.984</v>
       </c>
+      <c r="C10" t="n">
+        <v>1479.370598080739</v>
+      </c>
       <c r="D10" t="n">
         <v>2.36865e-07</v>
       </c>
@@ -9577,6 +10039,9 @@
       </c>
       <c r="B11" t="n">
         <v>982.1680000000001</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1471.893237738889</v>
       </c>
       <c r="D11" t="n">
         <v>2.37054e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 37.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 37.xlsx
@@ -565,7 +565,7 @@
         <v>1814.005</v>
       </c>
       <c r="C2" t="n">
-        <v>2238.888957344104</v>
+        <v>806.4106548644272</v>
       </c>
       <c r="D2" t="n">
         <v>2.24383e-07</v>
@@ -598,16 +598,13 @@
         <v>-33884.43280066451</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.893447249540654e-11</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2578.408537518617</v>
+        <v>544.2652618395693</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.000000000000053e-08</v>
+        <v>1.001878294697087e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8176282665165663</v>
+        <v>0.9948705927330705</v>
       </c>
     </row>
     <row r="3">
@@ -618,7 +615,7 @@
         <v>1751.481</v>
       </c>
       <c r="C3" t="n">
-        <v>2181.764380934869</v>
+        <v>774.7773876724368</v>
       </c>
       <c r="D3" t="n">
         <v>2.23962e-07</v>
@@ -651,16 +648,13 @@
         <v>-35829.66572203031</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.361102179100492e-09</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2497.589322194382</v>
+        <v>555.8034175945377</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.000000000000198e-08</v>
+        <v>1.228541466159568e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8178140973748232</v>
+        <v>0.989213187208339</v>
       </c>
     </row>
     <row r="4">
@@ -671,7 +665,7 @@
         <v>1693.408</v>
       </c>
       <c r="C4" t="n">
-        <v>2130.515606069677</v>
+        <v>756.1500385841069</v>
       </c>
       <c r="D4" t="n">
         <v>2.24379e-07</v>
@@ -704,16 +698,13 @@
         <v>-31582.83307428906</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.012713234428511e-09</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2438.852105202525</v>
+        <v>548.9282261294655</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.000000000000014e-08</v>
+        <v>1.050842815960286e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8180347104926591</v>
+        <v>0.9998791833249452</v>
       </c>
     </row>
     <row r="5">
@@ -724,7 +715,7 @@
         <v>1652.642</v>
       </c>
       <c r="C5" t="n">
-        <v>2090.770210489846</v>
+        <v>742.5774100005927</v>
       </c>
       <c r="D5" t="n">
         <v>2.24522e-07</v>
@@ -757,16 +748,13 @@
         <v>-29997.91033496923</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.92679535815329e-08</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2391.33213503281</v>
+        <v>554.9763588232281</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000000019e-08</v>
+        <v>1.464536800067056e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8182294985083717</v>
+        <v>0.9821593207560129</v>
       </c>
     </row>
     <row r="6">
@@ -777,7 +765,7 @@
         <v>1625.187</v>
       </c>
       <c r="C6" t="n">
-        <v>2062.718267637992</v>
+        <v>730.1333453678124</v>
       </c>
       <c r="D6" t="n">
         <v>2.24955e-07</v>
@@ -810,16 +798,13 @@
         <v>-30169.33452599037</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.027390056868385e-08</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2350.327227582303</v>
+        <v>552.5157579102184</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.000000000000624e-08</v>
+        <v>1.477256123944596e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8184496117607183</v>
+        <v>0.9775785688364715</v>
       </c>
     </row>
     <row r="7">
@@ -830,7 +815,7 @@
         <v>1587.675</v>
       </c>
       <c r="C7" t="n">
-        <v>2027.83291869917</v>
+        <v>719.2961868962032</v>
       </c>
       <c r="D7" t="n">
         <v>2.25363e-07</v>
@@ -863,16 +848,13 @@
         <v>-27115.04254575271</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.673578386447352e-08</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2314.549376081962</v>
+        <v>558.6770246636237</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000015006e-08</v>
+        <v>1.400686969206441e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8186431331679291</v>
+        <v>0.9843548276808907</v>
       </c>
     </row>
     <row r="8">
@@ -883,7 +865,7 @@
         <v>1555.746</v>
       </c>
       <c r="C8" t="n">
-        <v>2000.054977658849</v>
+        <v>710.4294735603621</v>
       </c>
       <c r="D8" t="n">
         <v>2.25547e-07</v>
@@ -916,16 +898,13 @@
         <v>-24374.26331696161</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.597009395349453e-08</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2282.704001911986</v>
+        <v>568.425414354408</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000000000718e-08</v>
+        <v>1.98307267764219e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8188787031310908</v>
+        <v>0.9639018040206353</v>
       </c>
     </row>
     <row r="9">
@@ -936,7 +915,7 @@
         <v>1536.202</v>
       </c>
       <c r="C9" t="n">
-        <v>1981.311910774808</v>
+        <v>702.4003971104147</v>
       </c>
       <c r="D9" t="n">
         <v>2.26042e-07</v>
@@ -969,16 +948,13 @@
         <v>-23530.52061652963</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.954969134266329e-09</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2254.143282146671</v>
+        <v>557.4657414290219</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.000000000000055e-08</v>
+        <v>1.401960322563189e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8190792212900569</v>
+        <v>0.992761377279772</v>
       </c>
     </row>
     <row r="10">
@@ -989,7 +965,7 @@
         <v>1515.169</v>
       </c>
       <c r="C10" t="n">
-        <v>1956.678038206551</v>
+        <v>695.754448448108</v>
       </c>
       <c r="D10" t="n">
         <v>2.26303e-07</v>
@@ -1022,16 +998,13 @@
         <v>-20787.56162940363</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.333546903233828e-08</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2227.503790509776</v>
+        <v>536.3471054254892</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000000005741e-08</v>
+        <v>1.070669862622911e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8193053057181314</v>
+        <v>0.9994962280978815</v>
       </c>
     </row>
     <row r="11">
@@ -1042,7 +1015,7 @@
         <v>1494.237</v>
       </c>
       <c r="C11" t="n">
-        <v>1939.611393330302</v>
+        <v>688.8407957947632</v>
       </c>
       <c r="D11" t="n">
         <v>2.26613e-07</v>
@@ -1075,16 +1048,13 @@
         <v>-19951.74725563313</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.680971884019061e-09</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2201.678702542886</v>
+        <v>553.687463508469</v>
       </c>
       <c r="AA11" t="n">
-        <v>1e-08</v>
+        <v>1.196361998567219e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8195905642347411</v>
+        <v>0.9950746433019552</v>
       </c>
     </row>
   </sheetData>
@@ -1241,7 +1211,7 @@
         <v>1734.173</v>
       </c>
       <c r="C2" t="n">
-        <v>2208.72236273694</v>
+        <v>760.592203077439</v>
       </c>
       <c r="D2" t="n">
         <v>2.1836e-07</v>
@@ -1274,16 +1244,13 @@
         <v>-27042.63991557862</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.82174430945274e-08</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2455.265262115215</v>
+        <v>553.4274146527723</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.000000000002501e-08</v>
+        <v>1.03749126791311e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8185226366895402</v>
+        <v>0.998395904046931</v>
       </c>
     </row>
     <row r="3">
@@ -1294,7 +1261,7 @@
         <v>1616.769</v>
       </c>
       <c r="C3" t="n">
-        <v>2055.701533927863</v>
+        <v>726.7061409433096</v>
       </c>
       <c r="D3" t="n">
         <v>2.2176e-07</v>
@@ -1327,16 +1294,13 @@
         <v>-26524.84820753023</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.421866676084226e-08</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2339.950276312656</v>
+        <v>552.6417330894601</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.000000000000162e-08</v>
+        <v>1.555464912991042e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8186999632410487</v>
+        <v>0.9781109912361348</v>
       </c>
     </row>
     <row r="4">
@@ -1347,7 +1311,7 @@
         <v>1574.053</v>
       </c>
       <c r="C4" t="n">
-        <v>2012.46008941781</v>
+        <v>715.9976234414833</v>
       </c>
       <c r="D4" t="n">
         <v>2.22401e-07</v>
@@ -1380,16 +1344,13 @@
         <v>-25166.40150012512</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.089600563549254e-09</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2300.817529950784</v>
+        <v>569.9442362310058</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.000000000000091e-08</v>
+        <v>1.939173722205905e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8187320914830568</v>
+        <v>0.9650837725035449</v>
       </c>
     </row>
     <row r="5">
@@ -1400,7 +1361,7 @@
         <v>1550.28</v>
       </c>
       <c r="C5" t="n">
-        <v>1988.530096823612</v>
+        <v>708.5101374793697</v>
       </c>
       <c r="D5" t="n">
         <v>2.22896e-07</v>
@@ -1433,16 +1394,13 @@
         <v>-21632.2498408126</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.547081525494212e-12</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2274.467984741103</v>
+        <v>549.3154894558662</v>
       </c>
       <c r="AA5" t="n">
-        <v>1e-08</v>
+        <v>1.14028204110367e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8187874920412548</v>
+        <v>0.9974886711513156</v>
       </c>
     </row>
     <row r="6">
@@ -1453,7 +1411,7 @@
         <v>1520.239</v>
       </c>
       <c r="C6" t="n">
-        <v>1963.616743166558</v>
+        <v>701.5557817009154</v>
       </c>
       <c r="D6" t="n">
         <v>2.23227e-07</v>
@@ -1486,16 +1444,13 @@
         <v>-20927.31508191576</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.519006579676908e-10</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2250.89898729645</v>
+        <v>550.2400458786218</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.000000000003463e-08</v>
+        <v>1.191551905194287e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8189090153561743</v>
+        <v>0.9959263088272959</v>
       </c>
     </row>
     <row r="7">
@@ -1506,7 +1461,7 @@
         <v>1506.123</v>
       </c>
       <c r="C7" t="n">
-        <v>1948.409939626798</v>
+        <v>696.1314940050472</v>
       </c>
       <c r="D7" t="n">
         <v>2.23436e-07</v>
@@ -1539,16 +1494,13 @@
         <v>-20154.1812093094</v>
       </c>
       <c r="Y7" t="n">
-        <v>7.422382637472134e-09</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2227.315017743516</v>
+        <v>552.8621413269325</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.00000000000006e-08</v>
+        <v>1.5463741084628e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8190829829546588</v>
+        <v>0.9823475689435466</v>
       </c>
     </row>
     <row r="8">
@@ -1559,7 +1511,7 @@
         <v>1493.475</v>
       </c>
       <c r="C8" t="n">
-        <v>1934.813295582696</v>
+        <v>689.8900393172561</v>
       </c>
       <c r="D8" t="n">
         <v>2.23665e-07</v>
@@ -1592,16 +1544,13 @@
         <v>-21251.371166875</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.054772902839284e-11</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2204.953974872117</v>
+        <v>558.6925400344608</v>
       </c>
       <c r="AA8" t="n">
-        <v>1e-08</v>
+        <v>1.223028843655847e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8192748780869882</v>
+        <v>0.995529454363576</v>
       </c>
     </row>
     <row r="9">
@@ -1612,7 +1561,7 @@
         <v>1469.502</v>
       </c>
       <c r="C9" t="n">
-        <v>1913.11392593876</v>
+        <v>684.3319716082103</v>
       </c>
       <c r="D9" t="n">
         <v>2.2409e-07</v>
@@ -1645,16 +1594,13 @@
         <v>-18808.39280830049</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.426184467443721e-10</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2182.927240455587</v>
+        <v>588.333811186557</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.000000000000414e-08</v>
+        <v>2.726301158945863e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8195096820379845</v>
+        <v>0.9447311542516355</v>
       </c>
     </row>
     <row r="10">
@@ -1665,7 +1611,7 @@
         <v>1457.948</v>
       </c>
       <c r="C10" t="n">
-        <v>1898.95463328362</v>
+        <v>576.9053674575183</v>
       </c>
       <c r="D10" t="n">
         <v>2.24155e-07</v>
@@ -1698,16 +1644,13 @@
         <v>-17977.21283307825</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.505208771916953e-08</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2161.994632413858</v>
+        <v>692.1958844650743</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000000000001e-08</v>
+        <v>3.407134385286217e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8197443557903424</v>
+        <v>0.9543956146265028</v>
       </c>
     </row>
     <row r="11">
@@ -1718,7 +1661,7 @@
         <v>1431.258</v>
       </c>
       <c r="C11" t="n">
-        <v>1875.748439083413</v>
+        <v>578.2123575497081</v>
       </c>
       <c r="D11" t="n">
         <v>2.24609e-07</v>
@@ -1751,16 +1694,13 @@
         <v>-16308.54884706572</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.609727969716513e-08</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2141.491163647627</v>
+        <v>650.8783658047699</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.000000000000093e-08</v>
+        <v>1.76959283888552e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8199968971700398</v>
+        <v>0.9985940770692279</v>
       </c>
     </row>
     <row r="12">
@@ -1771,7 +1711,7 @@
         <v>1422.243</v>
       </c>
       <c r="C12" t="n">
-        <v>1863.993734506017</v>
+        <v>577.5835391734638</v>
       </c>
       <c r="D12" t="n">
         <v>2.24895e-07</v>
@@ -1804,16 +1744,13 @@
         <v>-16752.71122741924</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.97940369360391e-10</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2122.427144644078</v>
+        <v>662.0636367788763</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.000000000018457e-08</v>
+        <v>2.308972256751613e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.8202403327258045</v>
+        <v>0.9798474437341497</v>
       </c>
     </row>
     <row r="13">
@@ -1824,7 +1761,7 @@
         <v>1406.964</v>
       </c>
       <c r="C13" t="n">
-        <v>1848.549032655684</v>
+        <v>578.7438027949647</v>
       </c>
       <c r="D13" t="n">
         <v>2.25169e-07</v>
@@ -1857,16 +1794,13 @@
         <v>-14960.87306688871</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.452407163255564e-10</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2103.396953553567</v>
+        <v>636.7032443008753</v>
       </c>
       <c r="AA13" t="n">
-        <v>1e-08</v>
+        <v>1.605533635291811e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.8205032402107246</v>
+        <v>0.998598305273534</v>
       </c>
     </row>
     <row r="14">
@@ -1877,7 +1811,7 @@
         <v>1387.754</v>
       </c>
       <c r="C14" t="n">
-        <v>1830.66822299377</v>
+        <v>578.6286469270668</v>
       </c>
       <c r="D14" t="n">
         <v>2.25313e-07</v>
@@ -1910,16 +1844,13 @@
         <v>-15087.39618723035</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.31530856367991e-08</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2084.708174013747</v>
+        <v>639.5834347752536</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.000000000003199e-08</v>
+        <v>2.542053051622683e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.8207675303493057</v>
+        <v>0.9672063119137314</v>
       </c>
     </row>
     <row r="15">
@@ -1930,7 +1861,7 @@
         <v>1377.823</v>
       </c>
       <c r="C15" t="n">
-        <v>1819.529757053389</v>
+        <v>578.2063143262933</v>
       </c>
       <c r="D15" t="n">
         <v>2.25514e-07</v>
@@ -1963,16 +1894,13 @@
         <v>-13762.45113829071</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.631295866833511e-08</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2066.81775251792</v>
+        <v>635.6323681848229</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.000000000000053e-08</v>
+        <v>2.21010370016212e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.8210534225163004</v>
+        <v>0.9810073858048167</v>
       </c>
     </row>
     <row r="16">
@@ -1983,7 +1911,7 @@
         <v>1363.499</v>
       </c>
       <c r="C16" t="n">
-        <v>1804.660160027916</v>
+        <v>578.6919454493354</v>
       </c>
       <c r="D16" t="n">
         <v>2.25865e-07</v>
@@ -2016,16 +1944,13 @@
         <v>-11265.9556534322</v>
       </c>
       <c r="Y16" t="n">
-        <v>7.345875151367063e-08</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2048.792832840928</v>
+        <v>626.9851613230049</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.000000000000946e-08</v>
+        <v>2.065053151278423e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.8213242656865217</v>
+        <v>0.9817902358726706</v>
       </c>
     </row>
     <row r="17">
@@ -2036,7 +1961,7 @@
         <v>1350.148</v>
       </c>
       <c r="C17" t="n">
-        <v>1790.298221364868</v>
+        <v>579.0484434495976</v>
       </c>
       <c r="D17" t="n">
         <v>2.25957e-07</v>
@@ -2069,16 +1994,13 @@
         <v>-10747.53572476451</v>
       </c>
       <c r="Y17" t="n">
-        <v>225.4520561701192</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2039.051996498125</v>
+        <v>640.4901995638671</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.510715789863713e-08</v>
+        <v>2.990196021773305e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.8103600764440296</v>
+        <v>0.9542892816571016</v>
       </c>
     </row>
     <row r="18">
@@ -2089,7 +2011,7 @@
         <v>1333.816</v>
       </c>
       <c r="C18" t="n">
-        <v>1773.998488042879</v>
+        <v>578.7744972456019</v>
       </c>
       <c r="D18" t="n">
         <v>2.26299e-07</v>
@@ -2122,16 +2044,13 @@
         <v>-11194.77942225678</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.014639549571414e-08</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2013.7784627959</v>
+        <v>590.498531756598</v>
       </c>
       <c r="AA18" t="n">
-        <v>1e-08</v>
+        <v>1.440892447430188e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.8218891946936643</v>
+        <v>0.9999070470111708</v>
       </c>
     </row>
     <row r="19">
@@ -2142,7 +2061,7 @@
         <v>1318.449</v>
       </c>
       <c r="C19" t="n">
-        <v>1758.454319681135</v>
+        <v>578.4947221001729</v>
       </c>
       <c r="D19" t="n">
         <v>2.26416e-07</v>
@@ -2175,16 +2094,13 @@
         <v>-9714.786155060667</v>
       </c>
       <c r="Y19" t="n">
-        <v>9.581678617117404e-09</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1996.461483575034</v>
+        <v>609.4874661922694</v>
       </c>
       <c r="AA19" t="n">
-        <v>1e-08</v>
+        <v>2.11218900183574e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.8221769445101934</v>
+        <v>0.9771545806188758</v>
       </c>
     </row>
     <row r="20">
@@ -2195,7 +2111,7 @@
         <v>1309.593</v>
       </c>
       <c r="C20" t="n">
-        <v>1745.13548672248</v>
+        <v>577.240064647464</v>
       </c>
       <c r="D20" t="n">
         <v>2.26689e-07</v>
@@ -2228,16 +2144,13 @@
         <v>-8955.315205019604</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.375682099186868e-08</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1978.463301056841</v>
+        <v>584.0296122787362</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.000000000000274e-08</v>
+        <v>1.534917712701644e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.8224584116270415</v>
+        <v>0.9999272902812606</v>
       </c>
     </row>
     <row r="21">
@@ -2248,7 +2161,7 @@
         <v>1300.287</v>
       </c>
       <c r="C21" t="n">
-        <v>1736.888908032435</v>
+        <v>579.0877418165344</v>
       </c>
       <c r="D21" t="n">
         <v>2.27011e-07</v>
@@ -2281,16 +2194,13 @@
         <v>-3596.283406158472</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.294079101179809e-09</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1960.980244700381</v>
+        <v>565.1087552946128</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.000000000000001e-08</v>
+        <v>1.394343054473728e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.8227435059190626</v>
+        <v>0.9999909606917564</v>
       </c>
     </row>
     <row r="22">
@@ -2301,7 +2211,7 @@
         <v>1279.247</v>
       </c>
       <c r="C22" t="n">
-        <v>1715.756573114495</v>
+        <v>580.0576058078868</v>
       </c>
       <c r="D22" t="n">
         <v>2.27231e-07</v>
@@ -2334,16 +2244,13 @@
         <v>-7184.517534263151</v>
       </c>
       <c r="Y22" t="n">
-        <v>3.962954813716136e-08</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1943.195022111756</v>
+        <v>566.8908924821396</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.000000000000001e-08</v>
+        <v>1.663410522729806e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.8230417856069404</v>
+        <v>0.9974923132831842</v>
       </c>
     </row>
   </sheetData>
@@ -2500,7 +2407,7 @@
         <v>1666.632</v>
       </c>
       <c r="C2" t="n">
-        <v>2100.773393507358</v>
+        <v>742.6627200944924</v>
       </c>
       <c r="D2" t="n">
         <v>2.27294e-07</v>
@@ -2533,16 +2440,13 @@
         <v>-32328.17147043583</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.759203652615179e-12</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2390.816269073804</v>
+        <v>550.9709177813916</v>
       </c>
       <c r="AA2" t="n">
-        <v>1e-08</v>
+        <v>1.110061220741693e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8191011171213556</v>
+        <v>0.9959384276994533</v>
       </c>
     </row>
     <row r="3">
@@ -2553,7 +2457,7 @@
         <v>1616.93</v>
       </c>
       <c r="C3" t="n">
-        <v>2047.956735210037</v>
+        <v>728.8343489852844</v>
       </c>
       <c r="D3" t="n">
         <v>2.26925e-07</v>
@@ -2586,16 +2490,13 @@
         <v>-28618.12641874233</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.420144283658278e-09</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2343.605233010768</v>
+        <v>550.7285181982006</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.00000000000424e-08</v>
+        <v>1.271791376979302e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.819158854778375</v>
+        <v>0.9895125528240023</v>
       </c>
     </row>
     <row r="4">
@@ -2606,7 +2507,7 @@
         <v>1592.246</v>
       </c>
       <c r="C4" t="n">
-        <v>2019.972257365567</v>
+        <v>720.4352719613184</v>
       </c>
       <c r="D4" t="n">
         <v>2.26783e-07</v>
@@ -2639,16 +2540,13 @@
         <v>-26459.30299960887</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.911585327235647e-10</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2314.315309352774</v>
+        <v>556.3497230768319</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.000000000001963e-08</v>
+        <v>1.815547644205793e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8192077658626172</v>
+        <v>0.9688586798814269</v>
       </c>
     </row>
     <row r="5">
@@ -2659,7 +2557,7 @@
         <v>1562.477</v>
       </c>
       <c r="C5" t="n">
-        <v>1997.248667989006</v>
+        <v>712.9900656841962</v>
       </c>
       <c r="D5" t="n">
         <v>2.2684e-07</v>
@@ -2692,16 +2590,13 @@
         <v>-24151.1958163995</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.081182921806102e-10</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2287.834550709267</v>
+        <v>546.6347146765266</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000001058e-08</v>
+        <v>1.318605418932572e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8193358946850418</v>
+        <v>0.9876686132388537</v>
       </c>
     </row>
     <row r="6">
@@ -2712,7 +2607,7 @@
         <v>1542.867</v>
       </c>
       <c r="C6" t="n">
-        <v>1977.839566544007</v>
+        <v>705.7521024324867</v>
       </c>
       <c r="D6" t="n">
         <v>2.26993e-07</v>
@@ -2745,16 +2640,13 @@
         <v>-22407.56782625177</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.83114843799154e-11</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2262.839999367438</v>
+        <v>556.6680867384566</v>
       </c>
       <c r="AA6" t="n">
-        <v>1e-08</v>
+        <v>1.779477555677147e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8195168089212844</v>
+        <v>0.9691329089457352</v>
       </c>
     </row>
     <row r="7">
@@ -2765,7 +2657,7 @@
         <v>1527.195</v>
       </c>
       <c r="C7" t="n">
-        <v>1961.56163853549</v>
+        <v>698.8150923087316</v>
       </c>
       <c r="D7" t="n">
         <v>2.27219e-07</v>
@@ -2798,16 +2690,13 @@
         <v>-18982.49840342342</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.495115508536951e-09</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2238.890647832516</v>
+        <v>569.7207986231349</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000000559e-08</v>
+        <v>2.352050845295633e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8197447445237518</v>
+        <v>0.9553759928808447</v>
       </c>
     </row>
     <row r="8">
@@ -2818,7 +2707,7 @@
         <v>1501.91</v>
       </c>
       <c r="C8" t="n">
-        <v>1938.764184336931</v>
+        <v>692.8994398516173</v>
       </c>
       <c r="D8" t="n">
         <v>2.27296e-07</v>
@@ -2851,16 +2740,13 @@
         <v>-19465.72351907413</v>
       </c>
       <c r="Y8" t="n">
-        <v>7.737159419216305e-10</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2215.767698232795</v>
+        <v>545.4032479817383</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000000000122e-08</v>
+        <v>1.544196954268296e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8200057803792258</v>
+        <v>0.9839622483769431</v>
       </c>
     </row>
     <row r="9">
@@ -2871,7 +2757,7 @@
         <v>1486.43</v>
       </c>
       <c r="C9" t="n">
-        <v>1922.57095567159</v>
+        <v>686.9603513183221</v>
       </c>
       <c r="D9" t="n">
         <v>2.27522e-07</v>
@@ -2904,16 +2790,13 @@
         <v>-19339.90430714014</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.828090437360283e-09</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2193.053516771275</v>
+        <v>535.0699844572093</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.000000000000009e-08</v>
+        <v>1.134765251267426e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8202771340231321</v>
+        <v>0.9988260882550201</v>
       </c>
     </row>
     <row r="10">
@@ -2924,7 +2807,7 @@
         <v>1469.84</v>
       </c>
       <c r="C10" t="n">
-        <v>1904.025576292133</v>
+        <v>681.7421644900257</v>
       </c>
       <c r="D10" t="n">
         <v>2.27726e-07</v>
@@ -2957,16 +2840,13 @@
         <v>-16594.34793244085</v>
       </c>
       <c r="Y10" t="n">
-        <v>3.230477346280985e-09</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2171.461490941084</v>
+        <v>532.4646932186339</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000000000039e-08</v>
+        <v>1.177945032091716e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8205441858580831</v>
+        <v>0.9974191257230464</v>
       </c>
     </row>
     <row r="11">
@@ -2977,7 +2857,7 @@
         <v>1447.476</v>
       </c>
       <c r="C11" t="n">
-        <v>1882.479883837841</v>
+        <v>676.4481969973325</v>
       </c>
       <c r="D11" t="n">
         <v>2.27978e-07</v>
@@ -3010,16 +2890,13 @@
         <v>-15596.07931553804</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.684517039775811e-10</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2151.274158037089</v>
+        <v>539.2298816117016</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.000000000000403e-08</v>
+        <v>1.450316038069867e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8208021342611612</v>
+        <v>0.9850220847430234</v>
       </c>
     </row>
     <row r="12">
@@ -3030,7 +2907,7 @@
         <v>1436.798</v>
       </c>
       <c r="C12" t="n">
-        <v>1868.952916125145</v>
+        <v>671.5165132343935</v>
       </c>
       <c r="D12" t="n">
         <v>2.28017e-07</v>
@@ -3063,16 +2940,13 @@
         <v>-14769.67481251643</v>
       </c>
       <c r="Y12" t="n">
-        <v>7.446918971046903e-09</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2131.326899902479</v>
+        <v>549.355445613556</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.000000000002036e-08</v>
+        <v>1.527498727675409e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.8210655469749927</v>
+        <v>0.9833003780658153</v>
       </c>
     </row>
     <row r="13">
@@ -3083,7 +2957,7 @@
         <v>1422.429</v>
       </c>
       <c r="C13" t="n">
-        <v>1854.336474445235</v>
+        <v>568.7869292195547</v>
       </c>
       <c r="D13" t="n">
         <v>2.28219e-07</v>
@@ -3116,16 +2990,13 @@
         <v>-15975.07404308421</v>
       </c>
       <c r="Y13" t="n">
-        <v>7.181384087052383e-08</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2111.343376094178</v>
+        <v>681.8463018258083</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.000000000000002e-08</v>
+        <v>3.773737581622692e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.821347552752409</v>
+        <v>0.949761807450322</v>
       </c>
     </row>
     <row r="14">
@@ -3136,7 +3007,7 @@
         <v>1403.969</v>
       </c>
       <c r="C14" t="n">
-        <v>1843.085086708337</v>
+        <v>569.5633664657329</v>
       </c>
       <c r="D14" t="n">
         <v>2.28395e-07</v>
@@ -3169,16 +3040,13 @@
         <v>-13355.78921682381</v>
       </c>
       <c r="Y14" t="n">
-        <v>6.494330681542102e-08</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2091.041853246386</v>
+        <v>641.6516483065923</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.000000000000028e-08</v>
+        <v>1.778450983147968e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.8216530084900049</v>
+        <v>0.9906310829398145</v>
       </c>
     </row>
     <row r="15">
@@ -3189,7 +3057,7 @@
         <v>1390.713</v>
       </c>
       <c r="C15" t="n">
-        <v>1829.234555355921</v>
+        <v>570.0178679304324</v>
       </c>
       <c r="D15" t="n">
         <v>2.28736e-07</v>
@@ -3222,16 +3090,13 @@
         <v>-11123.3390118636</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.078887734892475e-09</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2072.09304580414</v>
+        <v>619.5531250079049</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.000000000000002e-08</v>
+        <v>2.144262990477957e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.8219399487869644</v>
+        <v>0.9765041524295658</v>
       </c>
     </row>
     <row r="16">
@@ -3242,7 +3107,7 @@
         <v>1375.576</v>
       </c>
       <c r="C16" t="n">
-        <v>1810.60908098756</v>
+        <v>569.5739839873314</v>
       </c>
       <c r="D16" t="n">
         <v>2.28791e-07</v>
@@ -3275,16 +3140,13 @@
         <v>-11142.64404687529</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.597180696414356e-08</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2054.277041036133</v>
+        <v>620.4582933705556</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.000000000000017e-08</v>
+        <v>1.735713491670204e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.8221908137552887</v>
+        <v>0.9936822499102658</v>
       </c>
     </row>
     <row r="17">
@@ -3295,7 +3157,7 @@
         <v>1358.484</v>
       </c>
       <c r="C17" t="n">
-        <v>1792.496740505121</v>
+        <v>570.0414540166132</v>
       </c>
       <c r="D17" t="n">
         <v>2.28949e-07</v>
@@ -3328,16 +3190,13 @@
         <v>-12259.44871055042</v>
       </c>
       <c r="Y17" t="n">
-        <v>6.987006061311345e-10</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2035.878660396785</v>
+        <v>616.0486359727522</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.000000000000009e-08</v>
+        <v>1.922992830301281e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.8224715805486366</v>
+        <v>0.9869813795072137</v>
       </c>
     </row>
     <row r="18">
@@ -3348,7 +3207,7 @@
         <v>1344.776</v>
       </c>
       <c r="C18" t="n">
-        <v>1779.565125889865</v>
+        <v>569.8945956656713</v>
       </c>
       <c r="D18" t="n">
         <v>2.29168e-07</v>
@@ -3381,16 +3240,13 @@
         <v>-10070.58681058115</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.220542885308264e-08</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2018.006363133932</v>
+        <v>607.3521937160235</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.000000000000029e-08</v>
+        <v>1.70888638428743e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.8227723225802002</v>
+        <v>0.9980967289281077</v>
       </c>
     </row>
     <row r="19">
@@ -3401,7 +3257,7 @@
         <v>1331.007</v>
       </c>
       <c r="C19" t="n">
-        <v>1763.02073434414</v>
+        <v>569.8725331035097</v>
       </c>
       <c r="D19" t="n">
         <v>2.29517e-07</v>
@@ -3434,16 +3290,13 @@
         <v>-8737.157956490941</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.769899736642806e-08</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2000.627236910612</v>
+        <v>590.0615513241332</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.00000000000004e-08</v>
+        <v>1.712612727758385e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.8230382867241879</v>
+        <v>0.9913769818672573</v>
       </c>
     </row>
     <row r="20">
@@ -3454,7 +3307,7 @@
         <v>1325.802</v>
       </c>
       <c r="C20" t="n">
-        <v>1755.921174867555</v>
+        <v>570.9807229520283</v>
       </c>
       <c r="D20" t="n">
         <v>2.29603e-07</v>
@@ -3487,16 +3340,13 @@
         <v>-6563.055618966206</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.050267230992006e-07</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1983.373668669812</v>
+        <v>587.3883387030505</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.000000000008203e-08</v>
+        <v>1.927217420621686e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.8233282147880248</v>
+        <v>0.9880757236790459</v>
       </c>
     </row>
     <row r="21">
@@ -3507,7 +3357,7 @@
         <v>1319.285</v>
       </c>
       <c r="C21" t="n">
-        <v>1744.860761538582</v>
+        <v>572.8989194368288</v>
       </c>
       <c r="D21" t="n">
         <v>2.29874e-07</v>
@@ -3540,16 +3390,13 @@
         <v>-3177.935540046626</v>
       </c>
       <c r="Y21" t="n">
-        <v>4.423441237068347e-12</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1966.909809023754</v>
+        <v>566.1149391526379</v>
       </c>
       <c r="AA21" t="n">
-        <v>1e-08</v>
+        <v>1.422141481204204e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.8236014468632761</v>
+        <v>0.9996116621899088</v>
       </c>
     </row>
     <row r="22">
@@ -3560,7 +3407,7 @@
         <v>1295.816</v>
       </c>
       <c r="C22" t="n">
-        <v>1727.18301184386</v>
+        <v>572.0271081386171</v>
       </c>
       <c r="D22" t="n">
         <v>2.29975e-07</v>
@@ -3593,16 +3440,13 @@
         <v>-5931.216647222574</v>
       </c>
       <c r="Y22" t="n">
-        <v>8.14539827550597e-08</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1949.736583056744</v>
+        <v>565.2065747107888</v>
       </c>
       <c r="AA22" t="n">
-        <v>1e-08</v>
+        <v>1.492284673299389e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.8238986609882004</v>
+        <v>0.9997771434911965</v>
       </c>
     </row>
   </sheetData>
@@ -3759,7 +3603,7 @@
         <v>2114.352</v>
       </c>
       <c r="C2" t="n">
-        <v>2622.082681448851</v>
+        <v>1013.603465334131</v>
       </c>
       <c r="D2" t="n">
         <v>2.20003e-07</v>
@@ -3792,16 +3636,13 @@
         <v>-32878.98200338369</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.552265266815576e-11</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2810.028019172369</v>
+        <v>359.127532031978</v>
       </c>
       <c r="AA2" t="n">
-        <v>1e-08</v>
+        <v>7.137517563631159e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8185291862628377</v>
+        <v>0.9865941365737988</v>
       </c>
     </row>
     <row r="3">
@@ -3812,7 +3653,7 @@
         <v>1776.086</v>
       </c>
       <c r="C3" t="n">
-        <v>2204.325735835511</v>
+        <v>783.9711520924304</v>
       </c>
       <c r="D3" t="n">
         <v>2.29222e-07</v>
@@ -3845,16 +3686,13 @@
         <v>-34271.2444060718</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.019998634059318e-10</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2503.763417908455</v>
+        <v>527.9142736431071</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.000000000000003e-08</v>
+        <v>1.265232887757042e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8193886405504134</v>
+        <v>0.9847079132959343</v>
       </c>
     </row>
     <row r="4">
@@ -3865,7 +3703,7 @@
         <v>1707.509</v>
       </c>
       <c r="C4" t="n">
-        <v>2122.06145040809</v>
+        <v>754.1872683288207</v>
       </c>
       <c r="D4" t="n">
         <v>2.2907e-07</v>
@@ -3898,16 +3736,13 @@
         <v>-34902.95157167217</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.139725053026806e-08</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2425.264105437148</v>
+        <v>519.5059541335542</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.00000000000232e-08</v>
+        <v>9.823596477843535e-10</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8195412157595431</v>
+        <v>0.9992177461297714</v>
       </c>
     </row>
     <row r="5">
@@ -3918,7 +3753,7 @@
         <v>1651.816</v>
       </c>
       <c r="C5" t="n">
-        <v>2074.321638043706</v>
+        <v>741.3725015072374</v>
       </c>
       <c r="D5" t="n">
         <v>2.28409e-07</v>
@@ -3951,16 +3786,13 @@
         <v>-25986.6960195928</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.124254504031348e-09</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2384.578961884988</v>
+        <v>535.0983874958117</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000000727e-08</v>
+        <v>1.468180993442073e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.819626022323808</v>
+        <v>0.9803743023036293</v>
       </c>
     </row>
     <row r="6">
@@ -3971,7 +3803,7 @@
         <v>1622.346</v>
       </c>
       <c r="C6" t="n">
-        <v>2048.950869429521</v>
+        <v>730.9544279007763</v>
       </c>
       <c r="D6" t="n">
         <v>2.27914e-07</v>
@@ -4004,16 +3836,13 @@
         <v>-22901.43711584846</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.18119233942094e-10</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2352.222820883977</v>
+        <v>540.8254964770331</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.000000000000004e-08</v>
+        <v>1.093410810968078e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.81971850671945</v>
+        <v>0.9997538730093655</v>
       </c>
     </row>
     <row r="7">
@@ -4024,7 +3853,7 @@
         <v>1609.309</v>
       </c>
       <c r="C7" t="n">
-        <v>2031.244450190667</v>
+        <v>722.3818281709529</v>
       </c>
       <c r="D7" t="n">
         <v>2.27454e-07</v>
@@ -4057,16 +3886,13 @@
         <v>-23161.36054999249</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.845755677649939e-09</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2321.25284060976</v>
+        <v>539.1726406904033</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000004895e-08</v>
+        <v>1.195472252299352e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8198646601700366</v>
+        <v>0.9937496007944279</v>
       </c>
     </row>
     <row r="8">
@@ -4077,7 +3903,7 @@
         <v>1577.922</v>
       </c>
       <c r="C8" t="n">
-        <v>2002.463466557829</v>
+        <v>713.225205188034</v>
       </c>
       <c r="D8" t="n">
         <v>2.27441e-07</v>
@@ -4110,16 +3936,13 @@
         <v>-20177.81004093328</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.546946160616957e-08</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2292.428652930454</v>
+        <v>553.5462850681706</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000000006078e-08</v>
+        <v>1.874151300241511e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.820011424146474</v>
+        <v>0.9677907983722848</v>
       </c>
     </row>
     <row r="9">
@@ -4130,7 +3953,7 @@
         <v>1549.557</v>
       </c>
       <c r="C9" t="n">
-        <v>1974.576761178508</v>
+        <v>705.1733776589019</v>
       </c>
       <c r="D9" t="n">
         <v>2.27318e-07</v>
@@ -4163,16 +3986,13 @@
         <v>-18618.63192384122</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.181426989628064e-08</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2263.067685503016</v>
+        <v>531.6743934702208</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.000000000000695e-08</v>
+        <v>1.150882043298146e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8202095243714427</v>
+        <v>0.9939206449849789</v>
       </c>
     </row>
     <row r="10">
@@ -4183,7 +4003,7 @@
         <v>1529.537</v>
       </c>
       <c r="C10" t="n">
-        <v>1955.719537220519</v>
+        <v>697.1403250369297</v>
       </c>
       <c r="D10" t="n">
         <v>2.27401e-07</v>
@@ -4216,16 +4036,13 @@
         <v>-16138.77255993648</v>
       </c>
       <c r="Y10" t="n">
-        <v>3.118462694968798e-11</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2235.436961411101</v>
+        <v>552.7211302881001</v>
       </c>
       <c r="AA10" t="n">
-        <v>1e-08</v>
+        <v>1.906296682649127e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8204178339387</v>
+        <v>0.968010907999696</v>
       </c>
     </row>
     <row r="11">
@@ -4236,7 +4053,7 @@
         <v>1508.141</v>
       </c>
       <c r="C11" t="n">
-        <v>1935.486029281826</v>
+        <v>689.5990032769326</v>
       </c>
       <c r="D11" t="n">
         <v>2.27702e-07</v>
@@ -4269,16 +4086,13 @@
         <v>-13616.67804076343</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.693786795954945e-08</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2208.050817214159</v>
+        <v>538.9741258657365</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.000000000005911e-08</v>
+        <v>1.508855364291728e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8206528904194995</v>
+        <v>0.9870893998441941</v>
       </c>
     </row>
   </sheetData>
@@ -4435,7 +4249,7 @@
         <v>1752.188</v>
       </c>
       <c r="C2" t="n">
-        <v>2211.449038200349</v>
+        <v>797.2030657927804</v>
       </c>
       <c r="D2" t="n">
         <v>2.26992e-07</v>
@@ -4468,16 +4282,13 @@
         <v>-27994.55023666909</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.356916661256501e-10</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2452.906615047635</v>
+        <v>490.3051336707458</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.000000000000002e-08</v>
+        <v>9.598013508482592e-10</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8206739496801244</v>
+        <v>0.9936465798495522</v>
       </c>
     </row>
     <row r="3">
@@ -4488,7 +4299,7 @@
         <v>1641.5</v>
       </c>
       <c r="C3" t="n">
-        <v>2076.397425720556</v>
+        <v>742.481608809699</v>
       </c>
       <c r="D3" t="n">
         <v>2.25966e-07</v>
@@ -4521,16 +4332,13 @@
         <v>-29049.09257838171</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.253085997257166e-10</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2351.907718848481</v>
+        <v>522.9075078620228</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.000000000000007e-08</v>
+        <v>1.220042393478639e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8208200367631943</v>
+        <v>0.9897941961281688</v>
       </c>
     </row>
     <row r="4">
@@ -4541,7 +4349,7 @@
         <v>1613.235</v>
       </c>
       <c r="C4" t="n">
-        <v>2041.611685644711</v>
+        <v>726.1125194477945</v>
       </c>
       <c r="D4" t="n">
         <v>2.25437e-07</v>
@@ -4574,16 +4382,13 @@
         <v>-30116.33539777904</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.813337324920056e-08</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2315.725769299457</v>
+        <v>528.483645176168</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.000000000033246e-08</v>
+        <v>1.172671949181118e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8207715042735004</v>
+        <v>0.993585126858705</v>
       </c>
     </row>
     <row r="5">
@@ -4594,7 +4399,7 @@
         <v>1580.094</v>
       </c>
       <c r="C5" t="n">
-        <v>2015.357201216074</v>
+        <v>716.8266230638045</v>
       </c>
       <c r="D5" t="n">
         <v>2.24967e-07</v>
@@ -4627,16 +4432,13 @@
         <v>-27784.85662755503</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.638750338927884e-08</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2287.05661856295</v>
+        <v>529.7939083195193</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000000018e-08</v>
+        <v>1.547971161839255e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8208208106397976</v>
+        <v>0.9789725414701598</v>
       </c>
     </row>
     <row r="6">
@@ -4647,7 +4449,7 @@
         <v>1552.763</v>
       </c>
       <c r="C6" t="n">
-        <v>1988.528617118454</v>
+        <v>708.0576736337122</v>
       </c>
       <c r="D6" t="n">
         <v>2.24991e-07</v>
@@ -4680,16 +4482,13 @@
         <v>-25865.7963457353</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.514072843960937e-09</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2258.473193636406</v>
+        <v>536.2838119957079</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.000000000000945e-08</v>
+        <v>1.751679229853825e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8209682809751588</v>
+        <v>0.9713628542335913</v>
       </c>
     </row>
     <row r="7">
@@ -4700,7 +4499,7 @@
         <v>1523.405</v>
       </c>
       <c r="C7" t="n">
-        <v>1963.199561538411</v>
+        <v>699.4459762747031</v>
       </c>
       <c r="D7" t="n">
         <v>2.25294e-07</v>
@@ -4733,16 +4532,13 @@
         <v>-24467.6119776858</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.041207795952953e-08</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2229.732318649618</v>
+        <v>545.572532063792</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000000314e-08</v>
+        <v>1.394557456227785e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8211768908728423</v>
+        <v>0.9855376295040111</v>
       </c>
     </row>
     <row r="8">
@@ -4753,7 +4549,7 @@
         <v>1504.731</v>
       </c>
       <c r="C8" t="n">
-        <v>1943.363577596999</v>
+        <v>691.3884885744743</v>
       </c>
       <c r="D8" t="n">
         <v>2.25734e-07</v>
@@ -4786,16 +4582,13 @@
         <v>-24766.20096783365</v>
       </c>
       <c r="Y8" t="n">
-        <v>7.794897760382419e-08</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2201.885953625297</v>
+        <v>517.491196665042</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000000010577e-08</v>
+        <v>1.084814663668602e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8214197738283352</v>
+        <v>0.9982683798901508</v>
       </c>
     </row>
     <row r="9">
@@ -4806,7 +4599,7 @@
         <v>1481.167</v>
       </c>
       <c r="C9" t="n">
-        <v>1921.024791025693</v>
+        <v>683.4407579552351</v>
       </c>
       <c r="D9" t="n">
         <v>2.26031e-07</v>
@@ -4839,16 +4632,13 @@
         <v>-24464.5295775602</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.677412408832826e-10</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2174.902578029177</v>
+        <v>535.5119617044713</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.000000000000308e-08</v>
+        <v>1.23129461337265e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8216921411896099</v>
+        <v>0.9921936313821969</v>
       </c>
     </row>
     <row r="10">
@@ -4859,7 +4649,7 @@
         <v>1460.938</v>
       </c>
       <c r="C10" t="n">
-        <v>1900.966858515827</v>
+        <v>676.3590264810762</v>
       </c>
       <c r="D10" t="n">
         <v>2.26428e-07</v>
@@ -4892,16 +4682,13 @@
         <v>-23321.49282712353</v>
       </c>
       <c r="Y10" t="n">
-        <v>3.005876595717843e-12</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2148.837317518531</v>
+        <v>514.9189030483533</v>
       </c>
       <c r="AA10" t="n">
-        <v>1e-08</v>
+        <v>1.170688683259269e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8219811738025582</v>
+        <v>0.9999186242733274</v>
       </c>
     </row>
     <row r="11">
@@ -4912,7 +4699,7 @@
         <v>1449.985</v>
       </c>
       <c r="C11" t="n">
-        <v>1886.941042762658</v>
+        <v>669.3581025135023</v>
       </c>
       <c r="D11" t="n">
         <v>2.26693e-07</v>
@@ -4945,16 +4732,13 @@
         <v>-24113.26421218426</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.088261798567025e-10</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2123.711437636119</v>
+        <v>532.973631667156</v>
       </c>
       <c r="AA11" t="n">
-        <v>1e-08</v>
+        <v>1.920617627073462e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8222926092268291</v>
+        <v>0.9692127893935595</v>
       </c>
     </row>
     <row r="12">
@@ -4965,7 +4749,7 @@
         <v>1422.934</v>
       </c>
       <c r="C12" t="n">
-        <v>1862.76248242681</v>
+        <v>663.2715540156051</v>
       </c>
       <c r="D12" t="n">
         <v>2.27112e-07</v>
@@ -4998,16 +4782,13 @@
         <v>-22010.59773809439</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.782017767900564e-08</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2100.123766861156</v>
+        <v>548.7486322119493</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.000000000013372e-08</v>
+        <v>2.435722615212987e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.8226092188268457</v>
+        <v>0.9565812492710115</v>
       </c>
     </row>
     <row r="13">
@@ -5018,7 +4799,7 @@
         <v>1401.637</v>
       </c>
       <c r="C13" t="n">
-        <v>1840.312185252643</v>
+        <v>656.838011016205</v>
       </c>
       <c r="D13" t="n">
         <v>2.27351e-07</v>
@@ -5051,16 +4832,13 @@
         <v>-20890.69694865254</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.532804041585183e-08</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2077.061366627192</v>
+        <v>547.9862545376463</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.00000000000013e-08</v>
+        <v>2.631429651321531e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.8229320424686237</v>
+        <v>0.9516355685909511</v>
       </c>
     </row>
     <row r="14">
@@ -5071,7 +4849,7 @@
         <v>1386.363</v>
       </c>
       <c r="C14" t="n">
-        <v>1823.249463554655</v>
+        <v>657.7886381279291</v>
       </c>
       <c r="D14" t="n">
         <v>2.27644e-07</v>
@@ -5104,16 +4882,13 @@
         <v>-20325.47257140532</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.609562704242201e-08</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2053.947534549518</v>
+        <v>506.8014581404119</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.000000000000001e-08</v>
+        <v>1.182475321737482e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.8232660060759044</v>
+        <v>0.9992446762806679</v>
       </c>
     </row>
     <row r="15">
@@ -5124,7 +4899,7 @@
         <v>1374.024</v>
       </c>
       <c r="C15" t="n">
-        <v>1808.630171406865</v>
+        <v>650.4307653614292</v>
       </c>
       <c r="D15" t="n">
         <v>2.27914e-07</v>
@@ -5157,16 +4932,13 @@
         <v>-21060.04159968036</v>
       </c>
       <c r="Y15" t="n">
-        <v>7.348741095256063e-08</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2032.367258601469</v>
+        <v>512.8533487686155</v>
       </c>
       <c r="AA15" t="n">
-        <v>1e-08</v>
+        <v>1.611277255392167e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.8235950722342219</v>
+        <v>0.9843636997040239</v>
       </c>
     </row>
     <row r="16">
@@ -5177,7 +4949,7 @@
         <v>1348.227</v>
       </c>
       <c r="C16" t="n">
-        <v>1786.957457563326</v>
+        <v>645.9846853829972</v>
       </c>
       <c r="D16" t="n">
         <v>2.28279e-07</v>
@@ -5210,16 +4982,13 @@
         <v>-17601.01131604091</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.073449630468893e-09</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2010.869800452661</v>
+        <v>512.5464462160543</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.000000000002504e-08</v>
+        <v>1.639106504356023e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.8239336936761154</v>
+        <v>0.9805146417011528</v>
       </c>
     </row>
     <row r="17">
@@ -5230,7 +4999,7 @@
         <v>1335.891</v>
       </c>
       <c r="C17" t="n">
-        <v>1771.740622166712</v>
+        <v>557.2513294192565</v>
       </c>
       <c r="D17" t="n">
         <v>2.28588e-07</v>
@@ -5263,16 +5032,13 @@
         <v>-18658.89170008088</v>
       </c>
       <c r="Y17" t="n">
-        <v>194.9128416968672</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1997.956112222552</v>
+        <v>597.2296463013718</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.497888028501448e-08</v>
+        <v>1.680885331331743e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.8114528996329761</v>
+        <v>0.99687104925572</v>
       </c>
     </row>
     <row r="18">
@@ -5283,7 +5049,7 @@
         <v>1319.195</v>
       </c>
       <c r="C18" t="n">
-        <v>1756.637773915822</v>
+        <v>558.2255771894813</v>
       </c>
       <c r="D18" t="n">
         <v>2.28858e-07</v>
@@ -5316,16 +5082,13 @@
         <v>-18399.17593732727</v>
       </c>
       <c r="Y18" t="n">
-        <v>3.269855886123153e-08</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1968.709742936593</v>
+        <v>586.4576196753344</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.000000000000175e-08</v>
+        <v>1.604591170145163e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.8246302099443671</v>
+        <v>0.9999212263256673</v>
       </c>
     </row>
     <row r="19">
@@ -5336,7 +5099,7 @@
         <v>1309.05</v>
       </c>
       <c r="C19" t="n">
-        <v>1747.609385682665</v>
+        <v>559.3119479196773</v>
       </c>
       <c r="D19" t="n">
         <v>2.28997e-07</v>
@@ -5369,16 +5132,13 @@
         <v>-17983.91603330377</v>
       </c>
       <c r="Y19" t="n">
-        <v>3.499427388928672e-08</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1948.006773315955</v>
+        <v>557.1458986793904</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.000000000000046e-08</v>
+        <v>1.513973558989767e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.8249848233707414</v>
+        <v>0.9972823079219971</v>
       </c>
     </row>
     <row r="20">
@@ -5389,7 +5149,7 @@
         <v>1295.642</v>
       </c>
       <c r="C20" t="n">
-        <v>1732.264578201273</v>
+        <v>557.87961280396</v>
       </c>
       <c r="D20" t="n">
         <v>2.29365e-07</v>
@@ -5422,16 +5182,13 @@
         <v>-16398.23479152647</v>
       </c>
       <c r="Y20" t="n">
-        <v>4.17880658220823e-08</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1926.945451865624</v>
+        <v>564.1246120046161</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.000000000000007e-08</v>
+        <v>1.682627634782727e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.8253519265853584</v>
+        <v>0.9925139538999314</v>
       </c>
     </row>
     <row r="21">
@@ -5442,7 +5199,7 @@
         <v>1274.321</v>
       </c>
       <c r="C21" t="n">
-        <v>1710.80856847468</v>
+        <v>556.5046656493115</v>
       </c>
       <c r="D21" t="n">
         <v>2.29598e-07</v>
@@ -5475,16 +5232,13 @@
         <v>-16234.77503383726</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.937766268094148e-08</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1906.448848261884</v>
+        <v>570.7472862407675</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.000000000000126e-08</v>
+        <v>1.967826953739224e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.8257241235007452</v>
+        <v>0.9864151187839335</v>
       </c>
     </row>
     <row r="22">
@@ -5495,7 +5249,7 @@
         <v>1257.798</v>
       </c>
       <c r="C22" t="n">
-        <v>1695.955660180961</v>
+        <v>556.6241228399665</v>
       </c>
       <c r="D22" t="n">
         <v>2.30063e-07</v>
@@ -5528,16 +5282,13 @@
         <v>-15107.81057219486</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.752329891567776e-08</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1885.524683424949</v>
+        <v>556.5017348581861</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.000000000000001e-08</v>
+        <v>1.699678407507479e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.8260891804618763</v>
+        <v>0.9946618933757436</v>
       </c>
     </row>
   </sheetData>
@@ -5694,7 +5445,7 @@
         <v>2065.626</v>
       </c>
       <c r="C2" t="n">
-        <v>2601.62047726172</v>
+        <v>1006.945386565617</v>
       </c>
       <c r="D2" t="n">
         <v>2.17084e-07</v>
@@ -5727,16 +5478,13 @@
         <v>-26706.68584874164</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.883427900413313e-10</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2774.566121206715</v>
+        <v>432.4177505520906</v>
       </c>
       <c r="AA2" t="n">
-        <v>1e-08</v>
+        <v>2.200239286473423e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8184418196520336</v>
+        <v>0.9257898877796686</v>
       </c>
     </row>
     <row r="3">
@@ -5747,7 +5495,7 @@
         <v>1734.047</v>
       </c>
       <c r="C3" t="n">
-        <v>2167.776000059104</v>
+        <v>775.158222383351</v>
       </c>
       <c r="D3" t="n">
         <v>2.26824e-07</v>
@@ -5780,16 +5528,13 @@
         <v>-36140.69431407058</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.593093609899253e-10</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2449.195621436328</v>
+        <v>521.4914607279974</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.000000000056022e-08</v>
+        <v>1.187958397213766e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8193364042068423</v>
+        <v>0.994366241367779</v>
       </c>
     </row>
     <row r="4">
@@ -5800,7 +5545,7 @@
         <v>1642.096</v>
       </c>
       <c r="C4" t="n">
-        <v>2070.366256307197</v>
+        <v>740.3442751896192</v>
       </c>
       <c r="D4" t="n">
         <v>2.27197e-07</v>
@@ -5833,16 +5578,13 @@
         <v>-33815.25327228026</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.915161895167579e-09</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2369.31096873786</v>
+        <v>528.9232459761366</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.000000000000004e-08</v>
+        <v>1.060813320250439e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8194467387990272</v>
+        <v>0.9970464237950107</v>
       </c>
     </row>
     <row r="5">
@@ -5853,7 +5595,7 @@
         <v>1605.516</v>
       </c>
       <c r="C5" t="n">
-        <v>2030.904925363868</v>
+        <v>725.3423403544176</v>
       </c>
       <c r="D5" t="n">
         <v>2.26753e-07</v>
@@ -5886,16 +5628,13 @@
         <v>-33711.18331039534</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.923251920167434e-10</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2330.488411175554</v>
+        <v>517.0298907490974</v>
       </c>
       <c r="AA5" t="n">
-        <v>1e-08</v>
+        <v>1.038584852760606e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8194650980331833</v>
+        <v>0.9999089269947435</v>
       </c>
     </row>
     <row r="6">
@@ -5906,7 +5645,7 @@
         <v>1573.433</v>
       </c>
       <c r="C6" t="n">
-        <v>2003.122225302584</v>
+        <v>715.7243941701057</v>
       </c>
       <c r="D6" t="n">
         <v>2.26422e-07</v>
@@ -5939,16 +5678,13 @@
         <v>-31866.97935458959</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.687712108181191e-10</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2298.737464489892</v>
+        <v>539.6135264225372</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.000000000000001e-08</v>
+        <v>1.520212641915584e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8195465745926814</v>
+        <v>0.9800387900932437</v>
       </c>
     </row>
     <row r="7">
@@ -5959,7 +5695,7 @@
         <v>1551.094</v>
       </c>
       <c r="C7" t="n">
-        <v>1983.435762356056</v>
+        <v>707.0671007484876</v>
       </c>
       <c r="D7" t="n">
         <v>2.26397e-07</v>
@@ -5992,16 +5728,13 @@
         <v>-32424.3647979683</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.244383013434563e-09</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2268.743891509471</v>
+        <v>573.0969420815801</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000000671e-08</v>
+        <v>2.353465012313345e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8196794514236461</v>
+        <v>0.9534524636389834</v>
       </c>
     </row>
     <row r="8">
@@ -6012,7 +5745,7 @@
         <v>1529.057</v>
       </c>
       <c r="C8" t="n">
-        <v>1960.575132403359</v>
+        <v>699.4164979610658</v>
       </c>
       <c r="D8" t="n">
         <v>2.26568e-07</v>
@@ -6045,16 +5778,13 @@
         <v>-31643.77130862837</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.644520601076616e-09</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2239.643704997689</v>
+        <v>556.841091113562</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000000001247e-08</v>
+        <v>1.953092179051221e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8198512129396183</v>
+        <v>0.9656625613799659</v>
       </c>
     </row>
     <row r="9">
@@ -6065,7 +5795,7 @@
         <v>1500.209</v>
       </c>
       <c r="C9" t="n">
-        <v>1933.432781903236</v>
+        <v>691.9380974819147</v>
       </c>
       <c r="D9" t="n">
         <v>2.26951e-07</v>
@@ -6098,16 +5828,13 @@
         <v>-28471.88613184045</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.680290477220372e-10</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2211.694723348148</v>
+        <v>544.3577741893721</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.000000000000001e-08</v>
+        <v>1.356183329452209e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8200324788438826</v>
+        <v>0.987667625413099</v>
       </c>
     </row>
     <row r="10">
@@ -6118,7 +5845,7 @@
         <v>1476.013</v>
       </c>
       <c r="C10" t="n">
-        <v>1912.020554611371</v>
+        <v>684.3853500420038</v>
       </c>
       <c r="D10" t="n">
         <v>2.27133e-07</v>
@@ -6151,16 +5878,13 @@
         <v>-28195.27725672555</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.566576168441471e-09</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2184.9101920838</v>
+        <v>556.1255379174424</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000000000002e-08</v>
+        <v>1.456610057998383e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8202582125603227</v>
+        <v>0.9849039634664136</v>
       </c>
     </row>
     <row r="11">
@@ -6171,7 +5895,7 @@
         <v>1454.721</v>
       </c>
       <c r="C11" t="n">
-        <v>1890.68821071824</v>
+        <v>677.7193021916255</v>
       </c>
       <c r="D11" t="n">
         <v>2.27413e-07</v>
@@ -6204,16 +5928,13 @@
         <v>-27865.28103089625</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.576929854027643e-08</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2158.5683705583</v>
+        <v>534.0661067310066</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.000000000002358e-08</v>
+        <v>1.189643417142042e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8204968058166173</v>
+        <v>0.9972170112929186</v>
       </c>
     </row>
   </sheetData>
@@ -6370,7 +6091,7 @@
         <v>1725.394</v>
       </c>
       <c r="C2" t="n">
-        <v>2186.697247525924</v>
+        <v>777.4502996353405</v>
       </c>
       <c r="D2" t="n">
         <v>2.26531e-07</v>
@@ -6403,16 +6124,13 @@
         <v>-31510.78978625819</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.59263497276218e-08</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2448.172831186998</v>
+        <v>545.4075283655528</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.000000000001174e-08</v>
+        <v>1.918226270595558e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8190425443742186</v>
+        <v>0.9578585833068927</v>
       </c>
     </row>
     <row r="3">
@@ -6423,7 +6141,7 @@
         <v>1623.539</v>
       </c>
       <c r="C3" t="n">
-        <v>2053.854316412766</v>
+        <v>730.0882887767348</v>
       </c>
       <c r="D3" t="n">
         <v>2.26623e-07</v>
@@ -6456,16 +6174,13 @@
         <v>-35754.91170814761</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.882485990923643e-08</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2344.058287504316</v>
+        <v>551.5160340536916</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.000000000000328e-08</v>
+        <v>1.2649360372142e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8192389671136557</v>
+        <v>0.9881789628428206</v>
       </c>
     </row>
     <row r="4">
@@ -6476,7 +6191,7 @@
         <v>1576.376</v>
       </c>
       <c r="C4" t="n">
-        <v>2009.862671719732</v>
+        <v>718.5620291257641</v>
       </c>
       <c r="D4" t="n">
         <v>2.26515e-07</v>
@@ -6509,16 +6224,13 @@
         <v>-31305.69343450797</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.391710035901277e-09</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2307.414050921421</v>
+        <v>553.2633668159355</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.000000000033528e-08</v>
+        <v>1.77322854108713e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8192374788991174</v>
+        <v>0.9702963757152242</v>
       </c>
     </row>
     <row r="5">
@@ -6529,7 +6241,7 @@
         <v>1559.103</v>
       </c>
       <c r="C5" t="n">
-        <v>1990.385256924629</v>
+        <v>711.3369679528366</v>
       </c>
       <c r="D5" t="n">
         <v>2.26581e-07</v>
@@ -6562,16 +6274,13 @@
         <v>-31604.15765627037</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.907241226290765e-09</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2281.789598885403</v>
+        <v>544.6804960150548</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000001366e-08</v>
+        <v>1.273983566334087e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8192612212629248</v>
+        <v>0.9890096894200742</v>
       </c>
     </row>
     <row r="6">
@@ -6582,7 +6291,7 @@
         <v>1528.372</v>
       </c>
       <c r="C6" t="n">
-        <v>1965.611563424251</v>
+        <v>704.8676348638388</v>
       </c>
       <c r="D6" t="n">
         <v>2.26773e-07</v>
@@ -6615,16 +6324,13 @@
         <v>-27814.62822560456</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.138654619019943e-08</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2258.501092430848</v>
+        <v>551.5081953997769</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.000000000017002e-08</v>
+        <v>1.772874582161515e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8193622015874842</v>
+        <v>0.9708572306765775</v>
       </c>
     </row>
     <row r="7">
@@ -6635,7 +6341,7 @@
         <v>1522.61</v>
       </c>
       <c r="C7" t="n">
-        <v>1956.544055695254</v>
+        <v>699.1489600949344</v>
       </c>
       <c r="D7" t="n">
         <v>2.27016e-07</v>
@@ -6668,16 +6374,13 @@
         <v>-29923.52076585288</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.396713625197265e-10</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2236.416516125864</v>
+        <v>553.6024733738143</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000000053e-08</v>
+        <v>1.250621702821074e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8195187763847008</v>
+        <v>0.9954479469324951</v>
       </c>
     </row>
     <row r="8">
@@ -6688,7 +6391,7 @@
         <v>1504.563</v>
       </c>
       <c r="C8" t="n">
-        <v>1936.969298581042</v>
+        <v>692.8563259181377</v>
       </c>
       <c r="D8" t="n">
         <v>2.27357e-07</v>
@@ -6721,16 +6424,13 @@
         <v>-29072.23275389842</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.660286056378543e-09</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2214.540011872067</v>
+        <v>538.4440786594206</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000000000018e-08</v>
+        <v>1.131583454254427e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8197320493551178</v>
+        <v>0.9992447249963148</v>
       </c>
     </row>
     <row r="9">
@@ -6741,7 +6441,7 @@
         <v>1479.745</v>
       </c>
       <c r="C9" t="n">
-        <v>1916.160844936774</v>
+        <v>687.2992401135675</v>
       </c>
       <c r="D9" t="n">
         <v>2.27833e-07</v>
@@ -6774,16 +6474,13 @@
         <v>-25834.00251372231</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.33698953844215e-09</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2193.210525266819</v>
+        <v>534.9735765024694</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.000000000003773e-08</v>
+        <v>1.18144331890965e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8199704015880463</v>
+        <v>0.9979979637776603</v>
       </c>
     </row>
     <row r="10">
@@ -6794,7 +6491,7 @@
         <v>1463.767</v>
       </c>
       <c r="C10" t="n">
-        <v>1899.77606564336</v>
+        <v>681.8605635149104</v>
       </c>
       <c r="D10" t="n">
         <v>2.28047e-07</v>
@@ -6827,16 +6524,13 @@
         <v>-26722.42094626218</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.41124281947301e-08</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2172.325156704148</v>
+        <v>531.5415252407221</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000000000008e-08</v>
+        <v>1.233588214788719e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8202329282049027</v>
+        <v>0.9994210814221932</v>
       </c>
     </row>
     <row r="11">
@@ -6847,7 +6541,7 @@
         <v>1448.391</v>
       </c>
       <c r="C11" t="n">
-        <v>1883.386708212762</v>
+        <v>676.9155599374723</v>
       </c>
       <c r="D11" t="n">
         <v>2.2845e-07</v>
@@ -6880,16 +6574,13 @@
         <v>-23727.63986318794</v>
       </c>
       <c r="Y11" t="n">
-        <v>9.229985201283662e-08</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2151.965347585302</v>
+        <v>539.3567678147166</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.000000000004753e-08</v>
+        <v>1.571772207351236e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8205133468811094</v>
+        <v>0.9817643469467833</v>
       </c>
     </row>
     <row r="12">
@@ -6900,7 +6591,7 @@
         <v>1432.515</v>
       </c>
       <c r="C12" t="n">
-        <v>1867.370401511714</v>
+        <v>671.8909488113256</v>
       </c>
       <c r="D12" t="n">
         <v>2.28776e-07</v>
@@ -6933,16 +6624,13 @@
         <v>-23785.29957196176</v>
       </c>
       <c r="Y12" t="n">
-        <v>3.164702529728533e-08</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2132.172169751793</v>
+        <v>531.5279358782092</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.000000000003629e-08</v>
+        <v>1.164927976019353e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.8208002111185573</v>
+        <v>0.9995433503703017</v>
       </c>
     </row>
     <row r="13">
@@ -6953,7 +6641,7 @@
         <v>1412.245</v>
       </c>
       <c r="C13" t="n">
-        <v>1848.2608030271</v>
+        <v>570.9935860901658</v>
       </c>
       <c r="D13" t="n">
         <v>2.2912e-07</v>
@@ -6986,16 +6674,13 @@
         <v>-22260.50799699948</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.113454508951787e-08</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2112.461221515814</v>
+        <v>671.5387466434647</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.000000000000326e-08</v>
+        <v>3.447643106668514e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.8210845874163852</v>
+        <v>0.9540459598187967</v>
       </c>
     </row>
     <row r="14">
@@ -7006,7 +6691,7 @@
         <v>1407.569</v>
       </c>
       <c r="C14" t="n">
-        <v>1839.196920401653</v>
+        <v>571.3788395580959</v>
       </c>
       <c r="D14" t="n">
         <v>2.29467e-07</v>
@@ -7039,16 +6724,13 @@
         <v>-22421.76430748341</v>
       </c>
       <c r="Y14" t="n">
-        <v>6.866990322863331e-10</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2093.589109911672</v>
+        <v>626.6628846548982</v>
       </c>
       <c r="AA14" t="n">
-        <v>1e-08</v>
+        <v>1.868700767209052e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.8213822948186666</v>
+        <v>0.9916269404122878</v>
       </c>
     </row>
     <row r="15">
@@ -7059,7 +6741,7 @@
         <v>1390.912</v>
       </c>
       <c r="C15" t="n">
-        <v>1821.097421454789</v>
+        <v>570.8438975885348</v>
       </c>
       <c r="D15" t="n">
         <v>2.29705e-07</v>
@@ -7092,16 +6774,13 @@
         <v>-21513.07805774334</v>
       </c>
       <c r="Y15" t="n">
-        <v>9.524684903577736e-11</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2074.379845100409</v>
+        <v>655.7114428724319</v>
       </c>
       <c r="AA15" t="n">
-        <v>1e-08</v>
+        <v>3.417974729402216e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.8216872463320141</v>
+        <v>0.9526277227545635</v>
       </c>
     </row>
     <row r="16">
@@ -7112,7 +6791,7 @@
         <v>1369.928</v>
       </c>
       <c r="C16" t="n">
-        <v>1803.184365729607</v>
+        <v>571.3234357681347</v>
       </c>
       <c r="D16" t="n">
         <v>2.30137e-07</v>
@@ -7145,16 +6824,13 @@
         <v>-20537.69861342705</v>
       </c>
       <c r="Y16" t="n">
-        <v>4.791237062375483e-08</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2055.375363242407</v>
+        <v>634.0433705766857</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.000000000005102e-08</v>
+        <v>2.253595212310725e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.8219848548655849</v>
+        <v>0.9788532184460293</v>
       </c>
     </row>
     <row r="17">
@@ -7165,7 +6841,7 @@
         <v>1362.544</v>
       </c>
       <c r="C17" t="n">
-        <v>1790.865815305591</v>
+        <v>570.7091658096319</v>
       </c>
       <c r="D17" t="n">
         <v>2.3027e-07</v>
@@ -7198,16 +6874,13 @@
         <v>-20938.39357372569</v>
       </c>
       <c r="Y17" t="n">
-        <v>6.15130475819423e-09</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2036.978913403617</v>
+        <v>601.2805021905723</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.000000000000003e-08</v>
+        <v>1.574174347623807e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.8222921132524216</v>
+        <v>0.9959569423180327</v>
       </c>
     </row>
     <row r="18">
@@ -7218,7 +6891,7 @@
         <v>1345.587</v>
       </c>
       <c r="C18" t="n">
-        <v>1775.410441078668</v>
+        <v>570.0635487064516</v>
       </c>
       <c r="D18" t="n">
         <v>2.30766e-07</v>
@@ -7251,16 +6924,13 @@
         <v>-18212.15246948718</v>
       </c>
       <c r="Y18" t="n">
-        <v>215.439725150856</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1995.954777419473</v>
+        <v>654.9617639705306</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.421089080265279e-08</v>
+        <v>7.805474141577416e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.8148377086709585</v>
+        <v>0.8951760969550675</v>
       </c>
     </row>
     <row r="19">
@@ -7271,7 +6941,7 @@
         <v>1331.909</v>
       </c>
       <c r="C19" t="n">
-        <v>1758.826002218653</v>
+        <v>569.3807956770328</v>
       </c>
       <c r="D19" t="n">
         <v>2.3117e-07</v>
@@ -7304,16 +6974,13 @@
         <v>-17767.17453717029</v>
       </c>
       <c r="Y19" t="n">
-        <v>6.232654591143145e-09</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1999.304523283349</v>
+        <v>587.6638462860572</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.000000000000246e-08</v>
+        <v>1.606585535669432e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.8229108495188741</v>
+        <v>0.9934707230520006</v>
       </c>
     </row>
     <row r="20">
@@ -7324,7 +6991,7 @@
         <v>1316.11</v>
       </c>
       <c r="C20" t="n">
-        <v>1744.215557494516</v>
+        <v>571.7107580641057</v>
       </c>
       <c r="D20" t="n">
         <v>2.3163e-07</v>
@@ -7357,16 +7024,13 @@
         <v>-16398.47873422297</v>
       </c>
       <c r="Y20" t="n">
-        <v>7.571974585333299e-10</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1980.823354486376</v>
+        <v>584.8958499280994</v>
       </c>
       <c r="AA20" t="n">
-        <v>1e-08</v>
+        <v>1.5711762624931e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.8232226342904261</v>
+        <v>0.9980322206248653</v>
       </c>
     </row>
     <row r="21">
@@ -7377,7 +7041,7 @@
         <v>1301.998</v>
       </c>
       <c r="C21" t="n">
-        <v>1730.664725814722</v>
+        <v>574.2061277651851</v>
       </c>
       <c r="D21" t="n">
         <v>2.31836e-07</v>
@@ -7410,16 +7074,13 @@
         <v>-16013.67661334544</v>
       </c>
       <c r="Y21" t="n">
-        <v>3.945118807396416e-09</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1962.866129307823</v>
+        <v>606.8924664005814</v>
       </c>
       <c r="AA21" t="n">
-        <v>1e-08</v>
+        <v>5.181790330932803e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.8235257258343727</v>
+        <v>0.921014150532225</v>
       </c>
     </row>
     <row r="22">
@@ -7430,7 +7091,7 @@
         <v>1289.785</v>
       </c>
       <c r="C22" t="n">
-        <v>1715.744768352527</v>
+        <v>572.6091302194724</v>
       </c>
       <c r="D22" t="n">
         <v>2.3223e-07</v>
@@ -7463,16 +7124,13 @@
         <v>-14976.13898527562</v>
       </c>
       <c r="Y22" t="n">
-        <v>7.424481533400172e-08</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1944.151827818589</v>
+        <v>565.6990723229848</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.000000000000027e-08</v>
+        <v>1.596334188809029e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.823832716983225</v>
+        <v>0.9996306959727895</v>
       </c>
     </row>
   </sheetData>
@@ -7629,7 +7287,7 @@
         <v>1976.583</v>
       </c>
       <c r="C2" t="n">
-        <v>2474.701747177023</v>
+        <v>20912.30665160419</v>
       </c>
       <c r="D2" t="n">
         <v>2.21568e-07</v>
@@ -7662,10 +7320,7 @@
         <v>-25213.20964593093</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.178533343438866e-12</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2658.812629016438</v>
+        <v>-17895.96373124947</v>
       </c>
       <c r="AA2" t="n">
         <v>1e-08</v>
@@ -7682,7 +7337,7 @@
         <v>1669.171</v>
       </c>
       <c r="C3" t="n">
-        <v>2094.259383596715</v>
+        <v>757.0274655827966</v>
       </c>
       <c r="D3" t="n">
         <v>2.28968e-07</v>
@@ -7715,16 +7370,13 @@
         <v>-31277.19949447679</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.321018380837263e-08</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2379.381414814334</v>
+        <v>497.1173260402832</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.00000000001412e-08</v>
+        <v>1.145536041967605e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8210765106441527</v>
+        <v>0.9917608764516552</v>
       </c>
     </row>
     <row r="4">
@@ -7735,7 +7387,7 @@
         <v>1600.702</v>
       </c>
       <c r="C4" t="n">
-        <v>2015.878415590754</v>
+        <v>724.2368015280892</v>
       </c>
       <c r="D4" t="n">
         <v>2.28597e-07</v>
@@ -7768,16 +7420,13 @@
         <v>-33442.27658870722</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.426657910376211e-08</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2308.640491278848</v>
+        <v>524.046260636291</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.00000000000008e-08</v>
+        <v>1.166916197277876e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8211563763242047</v>
+        <v>0.9937164239817536</v>
       </c>
     </row>
     <row r="5">
@@ -7788,7 +7437,7 @@
         <v>1563.355</v>
       </c>
       <c r="C5" t="n">
-        <v>1982.567581177731</v>
+        <v>708.5590051063386</v>
       </c>
       <c r="D5" t="n">
         <v>2.282e-07</v>
@@ -7821,16 +7470,13 @@
         <v>-33669.09441678843</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.07323689996329e-09</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2271.301881635975</v>
+        <v>531.3307591732123</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000000654e-08</v>
+        <v>1.324376614220701e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8211863162311187</v>
+        <v>0.9952739672663901</v>
       </c>
     </row>
     <row r="6">
@@ -7841,7 +7487,7 @@
         <v>1532.769</v>
       </c>
       <c r="C6" t="n">
-        <v>1953.279142176621</v>
+        <v>699.0108420114086</v>
       </c>
       <c r="D6" t="n">
         <v>2.28012e-07</v>
@@ -7874,16 +7520,13 @@
         <v>-31612.38967299644</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.073228953434104e-12</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2239.342588407337</v>
+        <v>537.2591669365306</v>
       </c>
       <c r="AA6" t="n">
-        <v>1e-08</v>
+        <v>1.172760663243328e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8212713417327091</v>
+        <v>0.9982914470663958</v>
       </c>
     </row>
     <row r="7">
@@ -7894,7 +7537,7 @@
         <v>1512.521</v>
       </c>
       <c r="C7" t="n">
-        <v>1931.152394698897</v>
+        <v>690.8212923754468</v>
       </c>
       <c r="D7" t="n">
         <v>2.28215e-07</v>
@@ -7927,16 +7570,13 @@
         <v>-32029.38294373039</v>
       </c>
       <c r="Y7" t="n">
-        <v>6.116323499204814e-08</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2208.626226218052</v>
+        <v>547.8921105226279</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000004567e-08</v>
+        <v>2.027496451722919e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8213975431315231</v>
+        <v>0.9640612150987161</v>
       </c>
     </row>
     <row r="8">
@@ -7947,7 +7587,7 @@
         <v>1474.567</v>
       </c>
       <c r="C8" t="n">
-        <v>1900.462581414804</v>
+        <v>682.8504337304446</v>
       </c>
       <c r="D8" t="n">
         <v>2.28493e-07</v>
@@ -7980,16 +7620,13 @@
         <v>-27888.57401359933</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.751298632844075e-10</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2179.723996827127</v>
+        <v>530.5831234452415</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000000000048e-08</v>
+        <v>1.475486318409354e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8215651857466469</v>
+        <v>0.9888016907474487</v>
       </c>
     </row>
     <row r="9">
@@ -8000,7 +7637,7 @@
         <v>1464.828</v>
       </c>
       <c r="C9" t="n">
-        <v>1886.412584017256</v>
+        <v>675.4905590479414</v>
       </c>
       <c r="D9" t="n">
         <v>2.28725e-07</v>
@@ -8033,16 +7670,13 @@
         <v>-30042.78279684855</v>
       </c>
       <c r="Y9" t="n">
-        <v>7.808436692014853e-12</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2152.038528362595</v>
+        <v>544.304973194594</v>
       </c>
       <c r="AA9" t="n">
-        <v>1e-08</v>
+        <v>2.042855093206767e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8217690172635903</v>
+        <v>0.9649485829942931</v>
       </c>
     </row>
     <row r="10">
@@ -8053,7 +7687,7 @@
         <v>1431.029</v>
       </c>
       <c r="C10" t="n">
-        <v>1858.171648458056</v>
+        <v>669.0359197483524</v>
       </c>
       <c r="D10" t="n">
         <v>2.29008e-07</v>
@@ -8086,16 +7720,13 @@
         <v>-26793.56365285002</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.31055830514826e-10</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2124.659760987732</v>
+        <v>526.7840968567145</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000000000012e-08</v>
+        <v>1.195401304344684e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8220058724131702</v>
+        <v>0.9992884802188641</v>
       </c>
     </row>
     <row r="11">
@@ -8106,7 +7737,7 @@
         <v>1415.186</v>
       </c>
       <c r="C11" t="n">
-        <v>1840.119092537433</v>
+        <v>662.2758005784473</v>
       </c>
       <c r="D11" t="n">
         <v>2.29427e-07</v>
@@ -8139,16 +7770,13 @@
         <v>-25988.77844201832</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.568867439192769e-08</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2098.5094102756</v>
+        <v>526.818582030515</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.000000000003242e-08</v>
+        <v>1.256193950569335e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.822262789375012</v>
+        <v>0.9982410224491581</v>
       </c>
     </row>
   </sheetData>
@@ -8305,7 +7933,7 @@
         <v>1707.309</v>
       </c>
       <c r="C2" t="n">
-        <v>2160.535059640006</v>
+        <v>766.1340368087276</v>
       </c>
       <c r="D2" t="n">
         <v>2.27208e-07</v>
@@ -8338,16 +7966,13 @@
         <v>-31824.08555246776</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.799273845483685e-09</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2416.473483771344</v>
+        <v>513.8781089407778</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.000000000000672e-08</v>
+        <v>1.091648725321788e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8204761022178662</v>
+        <v>0.9983544674742383</v>
       </c>
     </row>
     <row r="3">
@@ -8358,7 +7983,7 @@
         <v>1602.314</v>
       </c>
       <c r="C3" t="n">
-        <v>2021.519206193573</v>
+        <v>719.4628048108686</v>
       </c>
       <c r="D3" t="n">
         <v>2.27506e-07</v>
@@ -8391,16 +8016,13 @@
         <v>-36113.65276631213</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.548953750599256e-08</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2306.410461792562</v>
+        <v>549.3657740432024</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.000000000000465e-08</v>
+        <v>1.923712674670702e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8206982435186609</v>
+        <v>0.9648942468334766</v>
       </c>
     </row>
     <row r="4">
@@ -8411,7 +8033,7 @@
         <v>1557.452</v>
       </c>
       <c r="C4" t="n">
-        <v>1978.010149402718</v>
+        <v>707.0836129768564</v>
       </c>
       <c r="D4" t="n">
         <v>2.27772e-07</v>
@@ -8444,16 +8066,13 @@
         <v>-32806.27562153985</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.348775983279524e-09</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2268.352087800372</v>
+        <v>535.3458810527129</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.000000000006328e-08</v>
+        <v>1.182083964721296e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8206928436905053</v>
+        <v>0.9998542029647809</v>
       </c>
     </row>
     <row r="5">
@@ -8464,7 +8083,7 @@
         <v>1531.421</v>
       </c>
       <c r="C5" t="n">
-        <v>1953.943863010883</v>
+        <v>700.3734180970621</v>
       </c>
       <c r="D5" t="n">
         <v>2.28344e-07</v>
@@ -8497,16 +8116,13 @@
         <v>-29618.19054009091</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.366292432417547e-08</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2241.71034169518</v>
+        <v>545.2985676329293</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000001511e-08</v>
+        <v>1.869313212281271e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8207304499822511</v>
+        <v>0.9684062951243697</v>
       </c>
     </row>
     <row r="6">
@@ -8517,7 +8133,7 @@
         <v>1510.483</v>
       </c>
       <c r="C6" t="n">
-        <v>1934.700657098063</v>
+        <v>693.5920369299503</v>
       </c>
       <c r="D6" t="n">
         <v>2.28373e-07</v>
@@ -8550,16 +8166,13 @@
         <v>-29391.40258984867</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.040892421831557e-12</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2217.495790347891</v>
+        <v>538.9384077920859</v>
       </c>
       <c r="AA6" t="n">
-        <v>1e-08</v>
+        <v>1.410259275151567e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8208330205522311</v>
+        <v>0.9854427032818346</v>
       </c>
     </row>
     <row r="7">
@@ -8570,7 +8183,7 @@
         <v>1491.157</v>
       </c>
       <c r="C7" t="n">
-        <v>1914.625022775606</v>
+        <v>687.2274286801464</v>
       </c>
       <c r="D7" t="n">
         <v>2.28826e-07</v>
@@ -8603,16 +8216,13 @@
         <v>-28051.95150293668</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.163827076607538e-08</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2194.09778788681</v>
+        <v>544.9622253358291</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.000000000043812e-08</v>
+        <v>1.918610614181891e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8209980295427457</v>
+        <v>0.9686856491713661</v>
       </c>
     </row>
     <row r="8">
@@ -8623,7 +8233,7 @@
         <v>1470.39</v>
       </c>
       <c r="C8" t="n">
-        <v>1896.221490548368</v>
+        <v>681.1364144707683</v>
       </c>
       <c r="D8" t="n">
         <v>2.29134e-07</v>
@@ -8656,16 +8266,13 @@
         <v>-27492.4371183081</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.421282168708254e-11</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2171.718961287622</v>
+        <v>560.0208501942416</v>
       </c>
       <c r="AA8" t="n">
-        <v>1e-08</v>
+        <v>2.473126484146643e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8211956966675322</v>
+        <v>0.9531817820633781</v>
       </c>
     </row>
     <row r="9">
@@ -8676,7 +8283,7 @@
         <v>1454.956</v>
       </c>
       <c r="C9" t="n">
-        <v>1880.277551095924</v>
+        <v>675.9904723623566</v>
       </c>
       <c r="D9" t="n">
         <v>2.29688e-07</v>
@@ -8709,16 +8316,13 @@
         <v>-25366.28310645062</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.800470212966129e-09</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2150.271644099466</v>
+        <v>525.141482008976</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.000000000005795e-08</v>
+        <v>1.196633442539321e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8214275415280712</v>
+        <v>0.9979416767763609</v>
       </c>
     </row>
     <row r="10">
@@ -8729,7 +8333,7 @@
         <v>1433.046</v>
       </c>
       <c r="C10" t="n">
-        <v>1859.535378742356</v>
+        <v>670.9437319421124</v>
       </c>
       <c r="D10" t="n">
         <v>2.299e-07</v>
@@ -8762,16 +8366,13 @@
         <v>-24737.56724248871</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.209818556764471e-08</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2129.886604784695</v>
+        <v>530.380782665721</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000000000114e-08</v>
+        <v>1.272383162161157e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8216658026258539</v>
+        <v>0.9945155275574328</v>
       </c>
     </row>
     <row r="11">
@@ -8782,7 +8383,7 @@
         <v>1423.702</v>
       </c>
       <c r="C11" t="n">
-        <v>1847.287171972801</v>
+        <v>665.7582457633805</v>
       </c>
       <c r="D11" t="n">
         <v>2.306e-07</v>
@@ -8815,16 +8416,13 @@
         <v>-23091.47112830595</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.282787595306996e-08</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2109.777906018549</v>
+        <v>532.4725744165858</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.000000000000349e-08</v>
+        <v>1.632180603353895e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8219279195950848</v>
+        <v>0.9821481873167149</v>
       </c>
     </row>
     <row r="12">
@@ -8835,7 +8433,7 @@
         <v>1413.549</v>
       </c>
       <c r="C12" t="n">
-        <v>1835.520879922447</v>
+        <v>661.3000552858904</v>
       </c>
       <c r="D12" t="n">
         <v>2.30583e-07</v>
@@ -8868,16 +8466,13 @@
         <v>-24835.84474048759</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.596273875510573e-10</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2091.004586416669</v>
+        <v>517.8959470646439</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.00000000000047e-08</v>
+        <v>1.190655531450696e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.8221969564938763</v>
+        <v>0.9978601306845347</v>
       </c>
     </row>
     <row r="13">
@@ -8888,7 +8483,7 @@
         <v>1393.484</v>
       </c>
       <c r="C13" t="n">
-        <v>1817.660030969975</v>
+        <v>564.0229146202997</v>
       </c>
       <c r="D13" t="n">
         <v>2.30816e-07</v>
@@ -8921,16 +8516,13 @@
         <v>-23470.11550650002</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.424799153077533e-08</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2072.679106968035</v>
+        <v>669.9593727727321</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.000000000005907e-08</v>
+        <v>3.681385688725523e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.8224741148930019</v>
+        <v>0.950116129244952</v>
       </c>
     </row>
     <row r="14">
@@ -8941,7 +8533,7 @@
         <v>1379.736</v>
       </c>
       <c r="C14" t="n">
-        <v>1800.803966462967</v>
+        <v>563.5830484756208</v>
       </c>
       <c r="D14" t="n">
         <v>2.31275e-07</v>
@@ -8974,16 +8566,13 @@
         <v>-22874.38725960436</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.63933232433278e-08</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2054.57121273991</v>
+        <v>634.7735442955686</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.000000000000386e-08</v>
+        <v>2.303235757921938e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.8227540448103694</v>
+        <v>0.9811826589480472</v>
       </c>
     </row>
     <row r="15">
@@ -8994,7 +8583,7 @@
         <v>1360.813</v>
       </c>
       <c r="C15" t="n">
-        <v>1783.669996084115</v>
+        <v>562.0178031022953</v>
       </c>
       <c r="D15" t="n">
         <v>2.31459e-07</v>
@@ -9027,16 +8616,13 @@
         <v>-20697.7849186613</v>
       </c>
       <c r="Y15" t="n">
-        <v>8.284350392887859e-08</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2036.907459823528</v>
+        <v>612.5583775344636</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.00000000000012e-08</v>
+        <v>1.814033686615497e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.8230354745270387</v>
+        <v>0.9984190794063736</v>
       </c>
     </row>
     <row r="16">
@@ -9047,7 +8633,7 @@
         <v>1356.489</v>
       </c>
       <c r="C16" t="n">
-        <v>1775.073729701581</v>
+        <v>563.7806029575479</v>
       </c>
       <c r="D16" t="n">
         <v>2.31756e-07</v>
@@ -9080,16 +8666,13 @@
         <v>-20792.96495376527</v>
       </c>
       <c r="Y16" t="n">
-        <v>3.120711221992213e-08</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2019.117536474495</v>
+        <v>586.6774705423518</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.000000000001246e-08</v>
+        <v>1.599985188379471e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.8233366675585391</v>
+        <v>0.9965809837612872</v>
       </c>
     </row>
     <row r="17">
@@ -9100,7 +8683,7 @@
         <v>1339.859</v>
       </c>
       <c r="C17" t="n">
-        <v>1762.398994085765</v>
+        <v>567.7670358541775</v>
       </c>
       <c r="D17" t="n">
         <v>2.32158e-07</v>
@@ -9133,16 +8716,13 @@
         <v>-19771.9837905243</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.16789655310853e-09</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2001.861790416041</v>
+        <v>602.872382805666</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.000000000000738e-08</v>
+        <v>2.025584337611527e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.8236274810406217</v>
+        <v>0.984136699445718</v>
       </c>
     </row>
     <row r="18">
@@ -9153,7 +8733,7 @@
         <v>1327.183</v>
       </c>
       <c r="C18" t="n">
-        <v>1745.732944836149</v>
+        <v>563.5406086005142</v>
       </c>
       <c r="D18" t="n">
         <v>2.32559e-07</v>
@@ -9186,16 +8766,13 @@
         <v>-19394.36958960264</v>
       </c>
       <c r="Y18" t="n">
-        <v>213.0517617979157</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1982.412671349128</v>
+        <v>599.3276808751469</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.464092348456783e-08</v>
+        <v>1.838707439170955e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.8143536509127001</v>
+        <v>0.9881654864586358</v>
       </c>
     </row>
     <row r="19">
@@ -9206,7 +8783,7 @@
         <v>1317.642</v>
       </c>
       <c r="C19" t="n">
-        <v>1737.785993921399</v>
+        <v>566.7399890220394</v>
       </c>
       <c r="D19" t="n">
         <v>2.32865e-07</v>
@@ -9239,16 +8816,13 @@
         <v>-17141.6828876498</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.566822510386609e-08</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1967.190607268022</v>
+        <v>567.8647141936563</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.000000000000009e-08</v>
+        <v>1.492096786840086e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.8242196422748366</v>
+        <v>0.998464362867022</v>
       </c>
     </row>
     <row r="20">
@@ -9259,7 +8833,7 @@
         <v>1302.174</v>
       </c>
       <c r="C20" t="n">
-        <v>1721.772102220119</v>
+        <v>564.0418750463484</v>
       </c>
       <c r="D20" t="n">
         <v>2.3326e-07</v>
@@ -9292,16 +8866,13 @@
         <v>-16025.17259570055</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.245367317068335e-07</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1949.403625562016</v>
+        <v>563.6181437720772</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.000000000001419e-08</v>
+        <v>1.495764398963259e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.8245234996489053</v>
+        <v>0.9983401765512648</v>
       </c>
     </row>
     <row r="21">
@@ -9312,7 +8883,7 @@
         <v>1282.304</v>
       </c>
       <c r="C21" t="n">
-        <v>1707.079753278358</v>
+        <v>566.3533188015703</v>
       </c>
       <c r="D21" t="n">
         <v>2.33434e-07</v>
@@ -9345,16 +8916,13 @@
         <v>-15454.23373669312</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.185533263051768e-09</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1932.263815453651</v>
+        <v>552.4955311371131</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.000000000000485e-08</v>
+        <v>1.453929314115367e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.8248405806765271</v>
+        <v>0.999711519248498</v>
       </c>
     </row>
     <row r="22">
@@ -9365,7 +8933,7 @@
         <v>1271.53</v>
       </c>
       <c r="C22" t="n">
-        <v>1694.622978116683</v>
+        <v>568.0005326963307</v>
       </c>
       <c r="D22" t="n">
         <v>2.33696e-07</v>
@@ -9398,16 +8966,13 @@
         <v>-15254.3744343405</v>
       </c>
       <c r="Y22" t="n">
-        <v>5.341544813221286e-08</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1915.068446222447</v>
+        <v>595.291273105415</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.000000000000105e-08</v>
+        <v>5.264672071197736e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.825137287977138</v>
+        <v>0.9197504801762313</v>
       </c>
     </row>
   </sheetData>
@@ -9564,7 +9129,7 @@
         <v>1363.689</v>
       </c>
       <c r="C2" t="n">
-        <v>1919.873802401291</v>
+        <v>633.4806108712447</v>
       </c>
       <c r="D2" t="n">
         <v>2.41289e-07</v>
@@ -9597,16 +9162,13 @@
         <v>-26607.76010804871</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.561212350355966e-08</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2002.081351190302</v>
+        <v>559.4404928000627</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.000000000025406e-08</v>
+        <v>2.70626807058657e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8208152587456541</v>
+        <v>0.9479098475447612</v>
       </c>
     </row>
     <row r="3">
@@ -9617,7 +9179,7 @@
         <v>1179.436</v>
       </c>
       <c r="C3" t="n">
-        <v>1658.258493788332</v>
+        <v>584.9141657411153</v>
       </c>
       <c r="D3" t="n">
         <v>2.40085e-07</v>
@@ -9650,16 +9212,13 @@
         <v>-28977.90291191796</v>
       </c>
       <c r="Y3" t="n">
-        <v>7.958536421594163e-08</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1845.078878028542</v>
+        <v>519.7013477362474</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.000000000000006e-08</v>
+        <v>1.403538965959263e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8213138079844127</v>
+        <v>0.9967450104767382</v>
       </c>
     </row>
     <row r="4">
@@ -9670,7 +9229,7 @@
         <v>1137.492</v>
       </c>
       <c r="C4" t="n">
-        <v>1611.050988994953</v>
+        <v>1003.500284313974</v>
       </c>
       <c r="D4" t="n">
         <v>2.38173e-07</v>
@@ -9703,16 +9262,13 @@
         <v>-30029.17494132651</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.629517581915167e-08</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1799.075986342032</v>
+        <v>121.926421424258</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.000000000000002e-08</v>
+        <v>1.737600884394978e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8214426527690188</v>
+        <v>0.9194164015133063</v>
       </c>
     </row>
     <row r="5">
@@ -9723,7 +9279,7 @@
         <v>1110.765</v>
       </c>
       <c r="C5" t="n">
-        <v>1584.493693018979</v>
+        <v>990.857696609815</v>
       </c>
       <c r="D5" t="n">
         <v>2.3722e-07</v>
@@ -9756,16 +9312,13 @@
         <v>-28940.05921438317</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.655467005359109e-08</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1769.28253467059</v>
+        <v>127.5211221662516</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.000000000139312e-08</v>
+        <v>1.821273652072874e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8215546323192502</v>
+        <v>0.9176691978968846</v>
       </c>
     </row>
     <row r="6">
@@ -9776,7 +9329,7 @@
         <v>1088.304</v>
       </c>
       <c r="C6" t="n">
-        <v>1566.565933476016</v>
+        <v>986.5051320827298</v>
       </c>
       <c r="D6" t="n">
         <v>2.36688e-07</v>
@@ -9809,16 +9362,13 @@
         <v>-27231.77261128127</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.037721765307055e-11</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1741.065750781662</v>
+        <v>121.1565579649292</v>
       </c>
       <c r="AA6" t="n">
-        <v>1e-08</v>
+        <v>1.802028297178659e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8217464343880716</v>
+        <v>0.9154850139492798</v>
       </c>
     </row>
     <row r="7">
@@ -9829,7 +9379,7 @@
         <v>1062.168</v>
       </c>
       <c r="C7" t="n">
-        <v>1542.431241922039</v>
+        <v>985.2600188550368</v>
       </c>
       <c r="D7" t="n">
         <v>2.36447e-07</v>
@@ -9862,16 +9412,13 @@
         <v>-25668.73843584974</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.544063932410871e-11</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1713.29247573609</v>
+        <v>115.4328128588589</v>
       </c>
       <c r="AA7" t="n">
-        <v>1e-08</v>
+        <v>1.94371675469023e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8219930186703909</v>
+        <v>0.9127312000657009</v>
       </c>
     </row>
     <row r="8">
@@ -9882,7 +9429,7 @@
         <v>1035.495</v>
       </c>
       <c r="C8" t="n">
-        <v>1520.448758163297</v>
+        <v>995.1543120936301</v>
       </c>
       <c r="D8" t="n">
         <v>2.36518e-07</v>
@@ -9915,16 +9462,13 @@
         <v>-22966.88120499742</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.502247663862155e-08</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1686.289858227703</v>
+        <v>96.78970991611379</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.000000000000003e-08</v>
+        <v>2.004337519627341e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8222803212474934</v>
+        <v>0.9081772016922594</v>
       </c>
     </row>
     <row r="9">
@@ -9935,7 +9479,7 @@
         <v>1021.711</v>
       </c>
       <c r="C9" t="n">
-        <v>1507.345026154338</v>
+        <v>979.0909250709622</v>
       </c>
       <c r="D9" t="n">
         <v>2.36683e-07</v>
@@ -9968,16 +9512,13 @@
         <v>-23053.0418001188</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.548853834689077e-08</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1659.747023603323</v>
+        <v>102.4360408039152</v>
       </c>
       <c r="AA9" t="n">
-        <v>1e-08</v>
+        <v>2.078145189406318e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8226145878480111</v>
+        <v>0.9048048524675953</v>
       </c>
     </row>
     <row r="10">
@@ -9988,7 +9529,7 @@
         <v>989.984</v>
       </c>
       <c r="C10" t="n">
-        <v>1479.370598080739</v>
+        <v>975.4115913300501</v>
       </c>
       <c r="D10" t="n">
         <v>2.36865e-07</v>
@@ -10021,16 +9562,13 @@
         <v>-19835.01773981188</v>
       </c>
       <c r="Y10" t="n">
-        <v>7.439743487959913e-08</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1634.862859063115</v>
+        <v>94.70158618483798</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000000025642e-08</v>
+        <v>2.029989236641931e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8229475306037469</v>
+        <v>0.9053398463255157</v>
       </c>
     </row>
     <row r="11">
@@ -10041,7 +9579,7 @@
         <v>982.1680000000001</v>
       </c>
       <c r="C11" t="n">
-        <v>1471.893237738889</v>
+        <v>952.7997677061559</v>
       </c>
       <c r="D11" t="n">
         <v>2.37054e-07</v>
@@ -10074,16 +9612,13 @@
         <v>-20223.12058336674</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.277321864779594e-09</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1611.30018337099</v>
+        <v>109.1669910865625</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.000000000005047e-08</v>
+        <v>2.132451123714692e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8232909354589683</v>
+        <v>0.9067428141746021</v>
       </c>
     </row>
   </sheetData>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 37.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 37.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1124,6 +1124,566 @@
         <v>1e-08</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.8195905642347411</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1814.005</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2253.107593179908</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.24383e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-68.199</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.1088709677419345</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.1169354838709749</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.9373467112596927</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.710906862745058</v>
+      </c>
+      <c r="L12" t="n">
+        <v>31.95090078484899</v>
+      </c>
+      <c r="M12" t="n">
+        <v>86.213808969772</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>15.11079491418703</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-33884.43280066451</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>23.07612674970665</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.000000000000053e-08</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.8176282665165663</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1751.481</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.9655326198108606</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2188.793676286034</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.9714554612977426</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.23962e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-69.407</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.08882803943045019</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.9273712737127594</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.439593908629462</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.762434782608725</v>
+      </c>
+      <c r="L13" t="n">
+        <v>40.37003936828826</v>
+      </c>
+      <c r="M13" t="n">
+        <v>86.51638124513785</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>16.42692960319695</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-35829.66572203031</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>18.05168116332061</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.000000000000198e-08</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8178140973748232</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1693.408</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.9335189263535657</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2143.958022470847</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.9515559882539771</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.24379e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-70.164</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.07149390243902387</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.3456483126110175</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.578769230769201</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.231582733812893</v>
+      </c>
+      <c r="L14" t="n">
+        <v>25.6634660535035</v>
+      </c>
+      <c r="M14" t="n">
+        <v>86.16211128698326</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>14.90664947099158</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-31582.83307428906</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>13.35498330014252</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.000000000000014e-08</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8180347104926591</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1652.642</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.9110460004244749</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2109.394669426909</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.9362156853103624</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.24522e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-70.727</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.2601889338731617</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.3443361753958819</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.664341085271118</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.992842251563519</v>
+      </c>
+      <c r="L15" t="n">
+        <v>18.72734141500719</v>
+      </c>
+      <c r="M15" t="n">
+        <v>86.04141363964973</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>14.45076058823592</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-29997.91033496923</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>9.864418233361221</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.000000000000019e-08</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8182294985083717</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1625.187</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.8959109815022559</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2077.095042642274</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.9218800952646827</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.24955e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-71.139</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.4259552042160158</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.543716814159225</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.797009674582347</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.920082449941083</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>86.12432079972868</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>14.76086174755428</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-30169.33452599037</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>7.557665192993227</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.000000000000624e-08</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.8184496117607183</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1587.675</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.8752318764281246</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1981.889809986311</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.8796250192336285</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.25363e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-71.512</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.2482710926694099</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.9458868894601636</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.786717752235247</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.007663782447485</v>
+      </c>
+      <c r="L17" t="n">
+        <v>4.51110953705539</v>
+      </c>
+      <c r="M17" t="n">
+        <v>85.77123499468352</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>13.52444643847756</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-27115.04254575271</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>38.76543404329288</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.000000000015006e-08</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.8186431331679291</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1555.746</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.8576304916469358</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1955.653379058821</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.867980466169715</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.25547e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-71.86</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.2365289256198387</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.6462519936204337</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.0199999999999</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1.985517241379309</v>
+      </c>
+      <c r="L18" t="n">
+        <v>6.489044029537423</v>
+      </c>
+      <c r="M18" t="n">
+        <v>85.37825944008871</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>12.37011350224619</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-24374.26331696161</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>37.59084261048099</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.000000000000718e-08</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.8188787031310908</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1536.202</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.846856541189247</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1930.20444815657</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.8566854303803524</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.26042e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-72.11799999999999</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.4756152125279234</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.8560157790926779</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.147137404580147</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.4176935229068</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>85.27434755980602</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>12.09691152370871</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-23530.52061652963</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>38.10685035466179</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.000000000000055e-08</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.8190792212900569</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1515.169</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.8352617550668271</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1904.161039150334</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.8451265465147669</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.26303e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-72.42</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.3281318681318835</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.3952885747938589</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.473522458628804</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.484276729559794</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>84.74055280911873</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>10.86326323359942</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-20787.56162940363</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>39.58319483086154</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.000000000005741e-08</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.8193053057181314</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1494.237</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.8237226468504772</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1889.738151566274</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.838725215469717</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.26613e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-72.63200000000001</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.5958997722096797</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.9006720430106904</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.382040229884739</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.840613382899512</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>84.58879417662122</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>10.5568572289101</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-19951.74725563313</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>35.574278622409</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.8195905642347411</v>
       </c>
     </row>
@@ -1138,7 +1698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2456,6 +3016,1182 @@
         <v>1.000000000000001e-08</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.8230417856069404</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1734.173</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2225.162280193221</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.1836e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-70.553</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.02930056710776019</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.6405990016638455</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.589749702026103</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1.824793388429707</v>
+      </c>
+      <c r="L23" t="n">
+        <v>9.432026888864842</v>
+      </c>
+      <c r="M23" t="n">
+        <v>85.45957009787902</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>12.59259461433588</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-27042.63991557862</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-12.73340785379969</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.000000000002501e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8185226366895402</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1616.769</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9322997186555205</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2074.53736281772</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9323083450064499</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.2176e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-71.649</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.480022701475612</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.048488372092987</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.747043701799433</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.381683168316887</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>85.63132537760877</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>13.08971427682943</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-26524.84820753023</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>5.756284279998908</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.000000000000162e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8186999632410487</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1574.053</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.9076678047691896</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2038.526512680002</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.916124873599326</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.22401e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-72</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.09793814432989037</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.7197236180904809</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.607972027971993</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.164204923486249</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>85.4876478688723</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>12.67127907417432</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-25166.40150012512</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>5.552002194201464</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.000000000000091e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8187320914830568</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1550.28</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.8939592532002285</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1942.232271927552</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.8728497194186212</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.22896e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-72.30200000000001</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.4296296296296545</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.187945670628036</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.814352941176516</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.303811659192842</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>84.84286460311084</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>11.07998180379455</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-21632.2498408126</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>40.83270614863659</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8187874920412548</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1520.239</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.87663629868531</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1924.74029740893</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.8649887311777532</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.23227e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-72.473</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.1950216702447615</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.7518172918802845</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.914725219686896</v>
+      </c>
+      <c r="K27" t="n">
+        <v>198.3639554685594</v>
+      </c>
+      <c r="L27" t="n">
+        <v>10.22460720698108</v>
+      </c>
+      <c r="M27" t="n">
+        <v>84.7323776488215</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>10.84630868447197</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-20927.31508191576</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>39.67275784165508</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.000000000003463e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8189090153561743</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1506.123</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.8684963956883195</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1903.423091488834</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.8554086631935679</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.23436e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-72.694</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.06501597444090429</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.9289377289377438</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.194461228600265</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>84.59105134495663</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>10.56128893297003</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-20154.1812093094</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>40.03574555882096</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.00000000000006e-08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8190829829546588</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1493.475</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.8612030056978167</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1884.554241618192</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.8469288997000918</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.23665e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-72.852</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.7691810344827577</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.4347941567064756</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.845958986731119</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.497112462006142</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>84.90403921391294</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>11.21370860709948</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-21251.371166875</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>39.93187026082614</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8192748780869882</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1469.502</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.8473791253813777</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1867.187165908857</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.839124041661681</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.2409e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-73.06100000000001</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.1756676557863458</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.9686885245901828</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2.019999999999881</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.240888382687974</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>84.33061355650793</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>10.07316464817905</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-18808.39280830049</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>39.38991293034599</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.000000000000414e-08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8195096820379845</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1457.948</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.8407165836395792</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1848.685238533062</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8308091751279066</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.24155e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-73.24299999999999</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.3970967741935599</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.8061988304093648</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.824253285543583</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.315241057542936</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>84.13571377470832</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>9.736149532744328</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-17977.21283307825</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>39.83806790685981</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.8197443557903424</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1431.258</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.8253259622886528</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1831.857705783647</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8232467906226502</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.24609e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-73.43300000000001</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.1106759985996982</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.8184413038333375</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.833500934192491</v>
+      </c>
+      <c r="K32" t="n">
+        <v>144.9482804417476</v>
+      </c>
+      <c r="L32" t="n">
+        <v>12.15869700766287</v>
+      </c>
+      <c r="M32" t="n">
+        <v>83.62693198340274</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>8.953190197812932</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-16308.54884706572</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>39.58507572473854</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.000000000000093e-08</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.8199968971700398</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1422.243</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.8201275189960863</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1819.458004701762</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.817674297689322</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.24895e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-73.559</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.3702647657840789</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.143052837573473</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.8790804597700728</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.021743486973854</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>83.83798892062528</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>9.262350478321244</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-16752.71122741924</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>37.89174368963643</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.000000000018457e-08</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.8202403327258045</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1406.964</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.8113169793325118</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1800.476200980507</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8091437721226172</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.25169e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-73.732</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.2877232142856614</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.405994550408705</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.50575539568316</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.936387434555119</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>83.20322023117525</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>8.390262785299676</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-14960.87306688871</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>39.18564839267754</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.8205032402107246</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1387.754</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.800239653137259</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1785.645705262406</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8024788668929577</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.25313e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-73.881</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.3714269366830515</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.8503673459096406</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2.043658230434645</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>12.98579330606225</v>
+      </c>
+      <c r="M35" t="n">
+        <v>83.31039133485693</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>8.525938583617762</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-15087.39618723035</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>38.7692261811211</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.000000000003199e-08</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.8207675303493057</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1377.823</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.7945130041812437</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1771.056625858577</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.7959224554645914</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.25514e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-74.036</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.6510152284263235</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.9631118881119339</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2.31041666666649</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.234974358974374</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>82.77205570185487</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>7.884886174652769</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-13762.45113829071</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>38.64649308239984</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.000000000000053e-08</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.8210534225163004</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1363.499</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.7862531592868762</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1753.00678804084</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.7878107604307487</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2.25865e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-74.211</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.5440170940171065</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.936247334754709</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.6707732634339</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.454852780806948</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>81.37261339886355</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>6.590883140842604</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-11265.9556534322</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>40.18540239608728</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.000000000000946e-08</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.8213242656865217</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1350.148</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.7785543887489887</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1741.682220099315</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.7827214381631875</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2.25957e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-74.35599999999999</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.5098619329389125</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.7420062695924973</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.044923504867866</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2.340714285714211</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>81.0653623008742</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>6.360706249932048</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-10747.53572476451</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>38.31810766546016</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.510715789863713e-08</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.8103600764440296</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1333.816</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.769136643229943</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1727.511068509587</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.7763528457616943</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.26299e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-74.477</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.4613285426200271</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.7398772601394012</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.99555212535027</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>13.81502638564219</v>
+      </c>
+      <c r="M39" t="n">
+        <v>81.44626384795927</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>6.648496026660166</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-11194.77942225678</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>38.2254067001644</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.8218891946936643</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1318.449</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.7602753589174783</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1713.968552469707</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.7702667655865868</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2.26416e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-74.639</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.2898748790101046</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.269621472933257</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2.244571369077356</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>14.74319502199522</v>
+      </c>
+      <c r="M40" t="n">
+        <v>80.34224241284748</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>5.876324005354421</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-9714.786155060667</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>38.0958993995946</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.8221769445101934</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1309.593</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.7551686019791567</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1698.357717570476</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.7632511716956661</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2.26689e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-74.783</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.3332374905675237</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1.107963636104315</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2.289249762274023</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>14.88771675382138</v>
+      </c>
+      <c r="M41" t="n">
+        <v>79.69222702606045</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>5.49840428730893</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-8955.315205019604</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>38.18990709224056</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.000000000000274e-08</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.8224584116270415</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1300.287</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.7498023553590097</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1687.986483143556</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7585902826813066</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2.27011e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-74.971</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.2976653696498407</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.6623397435897345</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.763428571428488</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1867.049700598666</v>
+      </c>
+      <c r="L42" t="n">
+        <v>8.292286702259029</v>
+      </c>
+      <c r="M42" t="n">
+        <v>68.33184752971762</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>2.516960505517481</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-3596.283406158472</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>35.72616597554759</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.8227435059190626</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1279.247</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.7376697711243342</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1674.989408875758</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7527493269975396</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2.27231e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-75.081</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.1556142395020361</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.9158969469020262</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.535521410276816</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>12.02037272647894</v>
+      </c>
+      <c r="M43" t="n">
+        <v>77.64371908125486</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>4.564866310470252</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-7184.517534263151</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>34.80544849813191</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.8230417856069404</v>
       </c>
     </row>
@@ -2470,7 +4206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3788,6 +5524,1182 @@
         <v>1e-08</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.8238986609882004</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1666.632</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2116.248140823616</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.27294e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-70.212</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.1377253814147054</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.5629430719656501</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2.065820312499969</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.631500572737585</v>
+      </c>
+      <c r="L23" t="n">
+        <v>26.52221769991947</v>
+      </c>
+      <c r="M23" t="n">
+        <v>86.30453737813669</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>15.4828538005469</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-32328.17147043583</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>7.904021476536627</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8191011171213556</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1616.93</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9701781797061377</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2062.729676087733</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9747106855271447</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.26925e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-70.964</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.1207894736842202</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.2109480812641009</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.727401129943493</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.058928571428568</v>
+      </c>
+      <c r="L24" t="n">
+        <v>14.96426361016274</v>
+      </c>
+      <c r="M24" t="n">
+        <v>85.93608381357207</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>14.07501086633753</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-28618.12641874233</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>12.24606896571527</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.00000000000424e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.819158854778375</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1592.246</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.9553674716434102</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2041.82331199822</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.964831709765174</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.26783e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-71.386</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.1295652173913009</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.457097791798051</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.9557506584723289</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.273717948717932</v>
+      </c>
+      <c r="L25" t="n">
+        <v>3.681735239928523</v>
+      </c>
+      <c r="M25" t="n">
+        <v>85.67170262351074</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>13.21229623021994</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-26459.30299960887</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>10.33867942847189</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.000000000001963e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8192077658626172</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1562.477</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.9375057001185624</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2023.131442267842</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9559991587189134</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.2684e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-71.68600000000001</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.1426403641881793</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.2949778434268754</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.002176165803086</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1.853786407767103</v>
+      </c>
+      <c r="L26" t="n">
+        <v>7.637224899724427</v>
+      </c>
+      <c r="M26" t="n">
+        <v>85.33004455851005</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>12.24183986044723</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-24151.1958163995</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>7.833730021501083</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.000000000001058e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8193358946850418</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1542.867</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.9257394553806718</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1933.975296748536</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9138698149054759</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.26993e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-71.97499999999999</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.283169934640523</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.1156387665198062</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.384948096885778</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.163495346432306</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.688692417291086</v>
+      </c>
+      <c r="M27" t="n">
+        <v>85.03478076531864</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>11.51052496840783</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-22407.56782625177</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>40.03533914105992</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8195168089212844</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1527.195</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.9163360597900437</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1916.766919725064</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.9057382651635</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.27219e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-72.274</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.01135225375626116</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.6962580645160908</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.831591173054323</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.493097781429663</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>84.2400002662892</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>9.913651483187909</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-18982.49840342342</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>38.83894225710549</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.000000000000559e-08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8197447445237518</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1501.91</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.9011647442266798</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1895.610445077036</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.8957411035642016</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.27296e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-72.444</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.07807486631016659</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.3324637681159458</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.307331378298916</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.695432692307555</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>84.43062595896234</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>10.25522982194955</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-19465.72351907413</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>39.60096510926655</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.000000000000122e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8200057803792258</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1486.43</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.8918765510322615</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1877.186460591567</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.8870351375056568</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.27522e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-72.636</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.1341750841750771</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.011721611721508</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.8588805166846648</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.063777372262793</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>84.45046240258837</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>10.29211795212646</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-19339.90430714014</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>38.95374858028856</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.000000000000009e-08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8202771340231321</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1469.84</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.8819223439847548</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1858.644230022394</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8782732961074374</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.27726e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-72.879</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.07529411764707157</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.8552980132449808</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.133294255568543</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1.676223776223773</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>83.6422461829779</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>8.974934835992356</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-16594.34793244085</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>39.26059461708883</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.000000000000039e-08</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.8205441858580831</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1447.476</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.8685036648762293</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1840.211096805982</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8695630069590022</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.27978e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-73.063</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.002571593300138852</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.6903123642057366</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.962285863326118</v>
+      </c>
+      <c r="K32" t="n">
+        <v>99.74616749257568</v>
+      </c>
+      <c r="L32" t="n">
+        <v>11.05691453182798</v>
+      </c>
+      <c r="M32" t="n">
+        <v>83.31773182951167</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>8.535389969490076</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-15596.07931553804</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>39.9381860075855</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.000000000000403e-08</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.8208021342611612</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1436.798</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.8620967316120175</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1823.440523018431</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.8616383342970224</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.28017e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-73.253</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.6487940630797658</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.5527454242927992</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.7203931203931289</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.232245681381968</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>83.03145397549866</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>8.18147515995436</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-14769.67481251643</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>40.03351978101398</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.000000000002036e-08</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.8210655469749927</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1422.429</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.8534751522831675</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1808.446960746973</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8545533606674071</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.28219e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-73.373</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.2305605786618494</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.6732049036777501</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.6869158878504688</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1.599117174959912</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>83.58078884250946</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>8.888296224222582</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-15975.07404308421</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>39.26341586851822</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.821347552752409</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1403.969</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.8423989218975755</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1795.517561904026</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8484437752206287</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.28395e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-73.58</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.1053719008264366</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.9346760070052187</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.660254083484704</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2.463922518159819</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>82.47404990565391</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>7.569261213164475</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-13355.78921682381</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>36.80539314172984</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.000000000000028e-08</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.8216530084900049</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1390.713</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.8344451564592543</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1782.563571984096</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8423225696445718</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.28736e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-73.764</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.6781186094069789</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.7646058732611916</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.249132321041141</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1.762386831275659</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>81.1654071925622</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>6.4339107332009</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-11123.3390118636</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>34.90685538839864</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.8219399487869644</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1375.576</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.8253627675455649</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1762.767682869111</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.8329683314845417</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2.28791e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-73.91200000000001</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.05174050632911318</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.7378446115288498</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.821863799283468</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.478697571743799</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>81.25011141979748</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>6.49718835944087</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-11142.64404687529</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>38.19886405628222</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.000000000000017e-08</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.8221908137552887</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1358.484</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.815107354232968</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1746.020641502253</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.8250547787003485</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2.28949e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-74.04000000000001</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.1077569267046579</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.8628880939403321</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.076976556772219</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>12.62484052896874</v>
+      </c>
+      <c r="M38" t="n">
+        <v>82.04382341130896</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>7.155074524292647</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-12259.44871055042</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>38.84108735264135</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.000000000000009e-08</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.8224715805486366</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1344.776</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.8068823831535694</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1734.22850255449</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.8194825876513472</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.29168e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-74.23099999999999</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.176780744818429</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.9103422243583772</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2.143715902524771</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>12.49799451256502</v>
+      </c>
+      <c r="M39" t="n">
+        <v>80.54836204260863</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>6.006907316357553</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-10070.58681058115</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>37.15980544366062</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.000000000000029e-08</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.8227723225802002</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1331.007</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.7986208113128753</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1721.973496936591</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.8136916761880398</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2.29517e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-74.402</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.1010356071492755</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.6008663326674747</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.382839315726722</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>10.18982465148447</v>
+      </c>
+      <c r="M40" t="n">
+        <v>79.32418504194004</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>5.304622809673369</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-8737.157956490941</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>35.66457373031835</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.00000000000004e-08</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.8230382867241879</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1325.802</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.7954977463531242</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1704.675047261767</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.8055175640217358</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2.29603e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-74.532</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.4139037433154948</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.5054739652870959</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.297139451728147</v>
+      </c>
+      <c r="K41" t="n">
+        <v>597.5635477582638</v>
+      </c>
+      <c r="L41" t="n">
+        <v>7.925446018006033</v>
+      </c>
+      <c r="M41" t="n">
+        <v>76.44555650575067</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>4.147932263933119</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-6563.055618966206</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>36.68062096731262</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.000000000008203e-08</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.8233282147880248</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1319.285</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.7915874650192722</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1693.321351295788</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.8001525523546444</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2.29874e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-74.678</v>
+      </c>
+      <c r="H42" t="n">
+        <v>2.079816513760966</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.162073669850004</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.324105621805775</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>9.00388309997849</v>
+      </c>
+      <c r="M42" t="n">
+        <v>66.39545723699418</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>2.288414978859699</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-3177.935540046626</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>35.50956525343429</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.8236014468632761</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1295.816</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.7775057721200601</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1683.529363597727</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7955255015333502</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2.29975e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-74.821</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.2988756647136587</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1.387271293560417</v>
+      </c>
+      <c r="J43" t="n">
+        <v>420.3744437853853</v>
+      </c>
+      <c r="K43" t="n">
+        <v>3.12848237024448</v>
+      </c>
+      <c r="L43" t="n">
+        <v>14.88860810910578</v>
+      </c>
+      <c r="M43" t="n">
+        <v>75.40248657078702</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>3.839742268476164</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-5931.216647222574</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>32.75829128386522</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.8238986609882004</v>
       </c>
     </row>
@@ -3802,7 +6714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4504,6 +7416,566 @@
         <v>1.000000000005911e-08</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.8206528904194995</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2114.352</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2567.145723441704</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.20003e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-63.839</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.431894484412487</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.8811166875783988</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.08922184630251</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.365713647531854</v>
+      </c>
+      <c r="L12" t="n">
+        <v>38.2566300129368</v>
+      </c>
+      <c r="M12" t="n">
+        <v>85.58749317576543</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>12.95917804770604</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-32878.98200338369</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-13.61616937576628</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.8185291862628377</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1776.086</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.8400143400909594</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2213.131404977121</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.862098082227305</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.29222e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-68.29300000000001</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.339083557951492</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.6986625514402766</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.613246753246833</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.484845005740534</v>
+      </c>
+      <c r="L13" t="n">
+        <v>40.84944473000199</v>
+      </c>
+      <c r="M13" t="n">
+        <v>86.33254120178223</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>15.60140437099001</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-34271.2444060718</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>11.39834774076394</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.000000000000003e-08</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8193886405504134</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1707.509</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.8075802893747116</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2127.966175955553</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.8289230161436435</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.2907e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-69.758</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.8489827856024568</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.134729981378031</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.030195258019581</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.372504302926083</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>86.52383344429219</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>16.46223246911723</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-34902.95157167217</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>17.11261511828729</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.00000000000232e-08</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8195412157595431</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1651.816</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.7812398313998806</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2034.067205457312</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.7923458286311428</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.28409e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-70.52500000000001</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.477319587628826</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.2870216306156402</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.4399999999999719</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.570635559131069</v>
+      </c>
+      <c r="L15" t="n">
+        <v>14.57725431040487</v>
+      </c>
+      <c r="M15" t="n">
+        <v>85.47269265229681</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>12.62924771528568</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-25986.6960195928</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>43.75459186235082</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.000000000000727e-08</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.819626022323808</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1622.346</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.7673017548639016</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2071.416127487723</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.8068946412245854</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.27914e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-71.063</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.2379770992366461</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.2167682926829192</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.8632281553398714</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.256623931624028</v>
+      </c>
+      <c r="L16" t="n">
+        <v>4.71765885319662</v>
+      </c>
+      <c r="M16" t="n">
+        <v>84.95719505833407</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>11.33253390931329</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-22901.43711584846</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>13.1120294214054</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.000000000000004e-08</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.81971850671945</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1609.309</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.7611357995262853</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1986.056412815307</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.773643815650891</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.27454e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-71.434</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.3137404580153053</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.7694181326116535</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.798919891989181</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.65327210103329</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>85.06989948091764</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>11.59292868412084</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-23161.36054999249</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>40.30682971393446</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.000000000004895e-08</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.8198646601700366</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1577.922</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.7462910622261573</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1959.973065355459</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.76348336888635</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.27441e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-71.786</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.1881212121211997</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.5490413723511688</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.054942233632748</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.331086773378218</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>84.44551878995303</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>10.28290016869336</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-20177.81004093328</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>41.30681775402047</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.000000000006078e-08</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.820011424146474</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1549.557</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.7328756044405095</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1934.352038922309</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.753503013583886</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.27318e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-72.102</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.05238938053096634</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.301152737752157</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.8725058004639754</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.831724137930979</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>84.07635978635334</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>9.637906645515752</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-18618.63192384122</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>41.74044572566095</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.000000000000695e-08</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.8202095243714427</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1529.537</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.7234069823756878</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1910.349746518935</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.7441532161866447</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.27401e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-72.398</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.532818532818521</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.265392781316305</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.261915367483245</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.32924382716062</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>83.30282229920091</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>8.516214533260847</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-16138.77255993648</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>41.93311670202138</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.8204178339387</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1508.141</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.713287569903214</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1890.114224284662</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.7362707177178222</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.27702e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-72.669</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.08376511226253135</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.8553914327916869</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.568986568986848</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.368965517241506</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>82.24184420943112</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>7.340041498655531</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-13616.67804076343</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>40.38726788392125</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.000000000005911e-08</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.8206528904194995</v>
       </c>
     </row>
@@ -4518,7 +7990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5836,6 +9308,1182 @@
         <v>1.000000000000001e-08</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.8260891804618763</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1752.188</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2148.676907444279</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.26992e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-67.372</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.4869999999999874</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.6737344794651208</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.575963718820805</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1.951912811387893</v>
+      </c>
+      <c r="L23" t="n">
+        <v>26.20274229909328</v>
+      </c>
+      <c r="M23" t="n">
+        <v>85.54930609885143</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>12.8475451673552</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-27994.55023666909</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>19.86687273630901</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8206739496801244</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1641.5</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9368286964640781</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2093.868547835544</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9744920423266773</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.25966e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-69.82299999999999</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.1497304582210163</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.3503177966101514</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.9553706505295381</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1.72708453133978</v>
+      </c>
+      <c r="L24" t="n">
+        <v>31.23666636032365</v>
+      </c>
+      <c r="M24" t="n">
+        <v>85.93282605545672</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>14.06369903347455</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-29049.09257838171</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.536063768465965</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.000000000000007e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8208200367631943</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1613.235</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.9206974365764405</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2055.693576898199</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9567253083867889</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.25437e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-70.57599999999999</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.6931880108992096</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.970169851380163</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.738701923076884</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.363570391872275</v>
+      </c>
+      <c r="L25" t="n">
+        <v>40.65357220003479</v>
+      </c>
+      <c r="M25" t="n">
+        <v>86.13302842758512</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>14.79420167824835</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-30116.33539777904</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>3.722678010726668</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.000000000033246e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8207715042735004</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1580.094</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.9017833702776187</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2036.134900012137</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9476226476664639</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.24967e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-71.001</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.3458024691357947</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.9166007905138214</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.182299421009067</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1.658766066838045</v>
+      </c>
+      <c r="L26" t="n">
+        <v>29.38923148774891</v>
+      </c>
+      <c r="M26" t="n">
+        <v>85.87537354245515</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>13.86713946698253</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-27784.85662755503</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0.9162753307722369</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.000000000000018e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8208208106397976</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1552.763</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.8861851582136163</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2016.853317988344</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9386489476387911</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.24991e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-71.354</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.2321518987341711</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.1113342898134799</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.8645858343336816</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1.8121238177128</v>
+      </c>
+      <c r="L27" t="n">
+        <v>24.71394861051551</v>
+      </c>
+      <c r="M27" t="n">
+        <v>85.63761957366458</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>13.10867392331554</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-25865.7963457353</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-1.619143864552257</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.000000000000945e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8209682809751588</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1523.405</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.8694301068150222</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1997.888137884348</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.9298225019138476</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.25294e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-71.629</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.05934227885786165</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.6005761402328612</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.532840450276582</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.954573601903386</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>85.45919496875602</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>12.59154993513136</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-24467.6119776858</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-4.518262092147552</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.000000000000314e-08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8211768908728423</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1504.731</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.8587725746324026</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1973.099644998167</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.9182858707896899</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.25734e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-71.94199999999999</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.4915335463258502</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.4865558912386746</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.185519801980111</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1.924806201550274</v>
+      </c>
+      <c r="L29" t="n">
+        <v>21.18783918556908</v>
+      </c>
+      <c r="M29" t="n">
+        <v>85.56021029924068</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>12.8792260947461</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-24766.20096783365</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-3.950702632946559</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.000000000010577e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8214197738283352</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1481.167</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.8453242460283942</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1954.505593786764</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.9096321494475085</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.26031e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-72.199</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.231912442396321</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.6570913461537948</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.081048867699593</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1.711094674556141</v>
+      </c>
+      <c r="L30" t="n">
+        <v>20.32712017379618</v>
+      </c>
+      <c r="M30" t="n">
+        <v>85.55940687519681</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>12.87688653762767</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-24464.5295775602</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-5.978150254025309</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.000000000000308e-08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8216921411896099</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1460.938</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.8337792519980733</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1938.317501370514</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.9020981677864384</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.26428e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-72.48699999999999</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.2057101024890352</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.271705822267619</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.8030549898166958</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1.396064139941646</v>
+      </c>
+      <c r="L31" t="n">
+        <v>16.92010723924846</v>
+      </c>
+      <c r="M31" t="n">
+        <v>85.40422513712912</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>12.44030672333366</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-23321.49282712353</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-9.095778135515502</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.8219811738025582</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1449.985</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.8275282104431717</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1917.909852213438</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8926003930924524</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.26693e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-72.73</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.7619289340101655</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.5406703910614478</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.105078124999963</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1.987357052096633</v>
+      </c>
+      <c r="L32" t="n">
+        <v>8.762145353953002</v>
+      </c>
+      <c r="M32" t="n">
+        <v>85.59276080069311</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>12.97472850640924</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-24113.26421218426</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-9.861865699923214</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.8222926092268291</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1422.934</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.8120897985832571</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1901.808770835966</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.8851069066023763</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.27112e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-72.97499999999999</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.4365217391304382</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.5882830626450249</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.7748936170212753</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1.905228136882119</v>
+      </c>
+      <c r="L33" t="n">
+        <v>10.9254735318043</v>
+      </c>
+      <c r="M33" t="n">
+        <v>85.24697785761123</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>12.02693509018668</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-22010.59773809439</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-11.52942593963985</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.000000000013372e-08</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.8226092188268457</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1401.637</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.7999352809173446</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1886.05487543026</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8777750013954438</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.27351e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-73.182</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.0712492986465626</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.9195057918310804</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.733921613928859</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3.02995129294358</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>85.05790523896528</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>11.56465363896059</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-20890.69694865254</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-13.58788772333742</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.00000000000013e-08</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.8229320424686237</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1386.363</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.791218179784361</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1869.65739697233</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8701435709085619</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.27644e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-73.383</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.1312300785086742</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.8418000460879128</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.613647221346541</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3.285827468284071</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>84.97882892517599</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>11.38161299652891</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-20325.47257140532</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>-15.56500370655453</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.8232660060759044</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1374.024</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.7841761272192255</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1858.20571139413</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8648139257029356</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.27914e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-73.56100000000001</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.3695086705202783</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.8465543644716442</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.138181818181774</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1.667074164629117</v>
+      </c>
+      <c r="L36" t="n">
+        <v>6.151229337767465</v>
+      </c>
+      <c r="M36" t="n">
+        <v>85.18898742923123</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>11.88129490106161</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-21060.04159968036</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-18.69792495978288</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.8235950722342219</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1348.227</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.7694533919876179</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1735.922825074733</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.8079031421897248</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2.28279e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-73.82899999999999</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.09827574830586402</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.8198447735687885</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.534216757741388</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.599138654126015</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>84.35561416766511</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>10.11807351576503</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-17601.01131604091</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>32.16363495932444</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.000000000002504e-08</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.8239336936761154</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1335.891</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.7624130515675259</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1715.296562903905</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.7983036244123582</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2.28588e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-73.968</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.230741238383157</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.6820397306422959</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.955199415995926</v>
+      </c>
+      <c r="K38" t="n">
+        <v>169.2793659631687</v>
+      </c>
+      <c r="L38" t="n">
+        <v>11.09197632594297</v>
+      </c>
+      <c r="M38" t="n">
+        <v>84.71072808275181</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>10.80166188820601</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-18658.89170008088</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>33.34646345482554</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.497888028501448e-08</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.8114528996329761</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1319.195</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.7528843936837828</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1702.110020109997</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.7921665720020018</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.28858e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-74.142</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.2812007158236932</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.9821551153021205</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.651257533095767</v>
+      </c>
+      <c r="K39" t="n">
+        <v>204.796077482548</v>
+      </c>
+      <c r="L39" t="n">
+        <v>11.76774026077038</v>
+      </c>
+      <c r="M39" t="n">
+        <v>84.69030337307916</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>10.75987387345335</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-18399.17593732727</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>31.10769376057067</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.000000000000175e-08</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.8246302099443671</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1309.05</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.7470944898606771</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1689.394997729227</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.7862489664575307</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2.28997e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-74.34099999999999</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.1469578783151231</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.088868613138731</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.590184049079822</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2.314400805639467</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>84.62588928958161</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>10.63016017542289</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-17983.91603330377</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>28.20671186003062</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.000000000000046e-08</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.8249848233707414</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1295.642</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.739442342944935</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1669.938458625182</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.7771938409351052</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2.29365e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-74.547</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1.295652173913164</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.522453703703692</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.168284789644061</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2.098214285714322</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>84.1942210862541</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>9.834950007408469</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-16398.23479152647</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>28.92109616336063</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.000000000000007e-08</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.8253519265853584</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1274.321</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.7272741281186722</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1656.588767736055</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7709808589633271</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2.29598e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-74.712</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.3445262079741157</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.8480375779889433</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.836434238680506</v>
+      </c>
+      <c r="K42" t="n">
+        <v>240.1895114834599</v>
+      </c>
+      <c r="L42" t="n">
+        <v>12.94118715152236</v>
+      </c>
+      <c r="M42" t="n">
+        <v>84.19667320161133</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>9.839134206106463</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-16234.77503383726</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>26.95685416207743</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.000000000000126e-08</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.8257241235007452</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1257.798</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.7178442039324547</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1641.779802435399</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.764088726763577</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2.30063e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-74.887</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.1578404731347258</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1.027030476449264</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.948484209243774</v>
+      </c>
+      <c r="K43" t="n">
+        <v>152.3408541231487</v>
+      </c>
+      <c r="L43" t="n">
+        <v>13.92238537179344</v>
+      </c>
+      <c r="M43" t="n">
+        <v>83.85151603775746</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>9.282886142075425</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-15107.81057219486</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>25.1763925903831</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.8260891804618763</v>
       </c>
     </row>
@@ -5850,7 +10498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6552,6 +11200,566 @@
         <v>1.000000000002358e-08</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.8204968058166173</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2065.626</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2549.782662427734</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.17084e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-63.712</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.008526011560703359</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.2356905158069797</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.223657289002546</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.937210319195471</v>
+      </c>
+      <c r="L12" t="n">
+        <v>18.31781065589669</v>
+      </c>
+      <c r="M12" t="n">
+        <v>84.65983800603161</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>10.69813543401735</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-26706.68584874164</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-18.87454873676347</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.8184418196520336</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1734.047</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.8394777176507268</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2115.272356579714</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.8295892774506874</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.26824e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-68.53400000000001</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.4063169164882285</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.209662716499547</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.865051903114133</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.524650349650324</v>
+      </c>
+      <c r="L13" t="n">
+        <v>48.98266741622771</v>
+      </c>
+      <c r="M13" t="n">
+        <v>86.5720619659517</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>16.69440914035216</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-36140.69431407058</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>34.40842148861202</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.000000000056022e-08</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8193364042068423</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1642.096</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.7949628829226587</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2089.9847702229</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.8196717316420039</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.27197e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-69.932</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.1388724035608282</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.5539375928677206</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.224352331606205</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.011111111111056</v>
+      </c>
+      <c r="L14" t="n">
+        <v>35.24388342079883</v>
+      </c>
+      <c r="M14" t="n">
+        <v>86.49428931529927</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>16.32315568605788</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-33815.25327228026</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>11.06866020706934</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.000000000000004e-08</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8194467387990272</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1605.516</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.7772539656259168</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2051.986090607948</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.8047690184912401</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.26753e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-70.63800000000001</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.3527233115468388</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.135159010600653</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.750452781371344</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.545211038961076</v>
+      </c>
+      <c r="L15" t="n">
+        <v>35.66630946901088</v>
+      </c>
+      <c r="M15" t="n">
+        <v>86.54633220578661</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>16.56973769831434</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-33711.18331039534</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>13.05552009663529</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8194650980331833</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1573.433</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.7617221123281755</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2030.620458869357</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.796389625198853</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.26422e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-71.063</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.568979591837334</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.5918367346938418</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.246266829865426</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.630878438331771</v>
+      </c>
+      <c r="L16" t="n">
+        <v>30.54955838724893</v>
+      </c>
+      <c r="M16" t="n">
+        <v>86.40523466484903</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>15.91775132115982</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-31866.97935458959</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>9.974758075612044</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.8195465745926814</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1551.094</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.7509074730856408</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2009.584799480844</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.7881396438579005</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.26397e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-71.49299999999999</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.5385826771653189</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.7513513513512898</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.773292682926698</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.62443181818189</v>
+      </c>
+      <c r="L17" t="n">
+        <v>31.14868334330851</v>
+      </c>
+      <c r="M17" t="n">
+        <v>86.50628571425651</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>16.37934454992757</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-32424.3647979683</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>7.6153371576994</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.000000000000671e-08</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.8196794514236461</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1529.057</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.740239036495474</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1987.758198385347</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.779579462860076</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.26568e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-71.81</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.1458715596330224</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.7686084142394567</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.9082830025884414</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.406709265175569</v>
+      </c>
+      <c r="L18" t="n">
+        <v>26.86433710735612</v>
+      </c>
+      <c r="M18" t="n">
+        <v>86.46587755173864</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>16.19160001210235</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-31643.77130862837</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>5.672999842023387</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.000000000001247e-08</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.8198512129396183</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1500.209</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.7262732943911434</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1965.776120305347</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.7709583052987211</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.26951e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-72.119</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.5334164588528282</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.3569690265486528</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.486222910216602</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.998251028806719</v>
+      </c>
+      <c r="L19" t="n">
+        <v>21.72706834716728</v>
+      </c>
+      <c r="M19" t="n">
+        <v>86.13663104753107</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>14.80803934345315</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-28471.88613184045</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>5.022504323832095</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.8200324788438826</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1476.013</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.7145596540709692</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1947.680694262493</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.7638614549241778</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.27133e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-72.371</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.08562231759656634</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.6327305605786776</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.179915433403778</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.367962308598139</v>
+      </c>
+      <c r="L20" t="n">
+        <v>20.68473178421213</v>
+      </c>
+      <c r="M20" t="n">
+        <v>86.14507632132964</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>14.84057887122033</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-28195.27725672555</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.547791185078495</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.8202582125603227</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1454.721</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.7042518829642926</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1845.323151992882</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.7237178208106126</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.27413e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-72.613</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.5690839694655903</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.789198036006593</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.06653491436098</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.093353783231048</v>
+      </c>
+      <c r="L21" t="n">
+        <v>18.90079930798803</v>
+      </c>
+      <c r="M21" t="n">
+        <v>86.14517076772654</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>14.84094357687393</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-27865.28103089625</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>40.963089103112</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.000000000002358e-08</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.8204968058166173</v>
       </c>
     </row>
@@ -6566,7 +11774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7884,6 +13092,1182 @@
         <v>1.000000000000027e-08</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.823832716983225</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1725.394</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2138.57308772435</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.26531e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-68.236</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.09621212121211134</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.579910213243531</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.198611111111068</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1.84922663080031</v>
+      </c>
+      <c r="L23" t="n">
+        <v>27.28134498970658</v>
+      </c>
+      <c r="M23" t="n">
+        <v>86.07779278082386</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>14.58521938025298</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-31510.78978625819</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>23.94144562074575</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.000000000001174e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8190425443742186</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1623.539</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9409671066434681</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2072.384770942926</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9690502432854171</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.26623e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-70.407</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.127974276527387</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.592886456908658</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.572594303310357</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.902889150943452</v>
+      </c>
+      <c r="L24" t="n">
+        <v>45.80276428893944</v>
+      </c>
+      <c r="M24" t="n">
+        <v>86.71101429127195</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>17.40136246034252</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-35754.91170814761</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>8.691875009620389</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.000000000000328e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8192389671136557</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1576.376</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.9136324804653314</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2036.776653932738</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9523998340875351</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.26515e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-71.047</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.1330097087378676</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.6944256756757132</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.8076222980659673</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1.705754276827385</v>
+      </c>
+      <c r="L25" t="n">
+        <v>28.99724198031014</v>
+      </c>
+      <c r="M25" t="n">
+        <v>86.33261709878029</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>15.60172812781192</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-31305.69343450797</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>9.663589194667452</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.000000000033528e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8192374788991174</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1559.103</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.9036214337131112</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2016.470382015516</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9429045907246673</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.26581e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-71.413</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.2635772357723764</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.639449541284046</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.681267605633818</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.196181556195921</v>
+      </c>
+      <c r="L26" t="n">
+        <v>28.72366326198399</v>
+      </c>
+      <c r="M26" t="n">
+        <v>86.40287891827006</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>15.90729940551821</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-31604.15765627037</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>8.791970512144189</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.000000000001366e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8192612212629248</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1528.372</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.8858104293859836</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1999.774793652565</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.935097708435357</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.26773e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-71.712</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.01210788447567915</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.5447299884820154</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.856184190534649</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.58000024195704</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>85.9769002109458</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>14.21828667036405</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-27814.62822560456</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>6.904414995707725</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.000000000017002e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8193622015874842</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1522.61</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.8824709022982578</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1913.751825213129</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.8948732387021421</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.27016e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-71.94</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.7445880452343256</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.140589569160918</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.937861635220054</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.553503709810368</v>
+      </c>
+      <c r="L28" t="n">
+        <v>17.43443059815125</v>
+      </c>
+      <c r="M28" t="n">
+        <v>86.27982389567983</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>15.37971297586586</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-29923.52076585288</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>39.13516541032675</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.000000000000053e-08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8195187763847008</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1504.563</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.872011262355149</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1891.449318258831</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.884444552826351</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.27357e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-72.148</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.6744597249507919</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.7736263736263697</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.406268958543911</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.199042709867385</v>
+      </c>
+      <c r="L29" t="n">
+        <v>13.06027197575831</v>
+      </c>
+      <c r="M29" t="n">
+        <v>86.20941217304882</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>15.09321636962727</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-29072.23275389842</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>40.98533036275228</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.000000000000018e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8197320493551178</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1479.745</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.8576273013584143</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1876.204318067162</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.8773159677528845</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.27833e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-72.38200000000001</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.2073002754820919</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.3582966226137943</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.345641025641084</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1.738850771869655</v>
+      </c>
+      <c r="L30" t="n">
+        <v>12.15643809338188</v>
+      </c>
+      <c r="M30" t="n">
+        <v>85.79513385908204</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>13.6015933304339</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-25834.00251372231</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>39.88777310287787</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.000000000003773e-08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8199704015880463</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1463.767</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.8483668078131719</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1856.874515544182</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8682773229509206</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.28047e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-72.521</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.2298837209302214</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.9225694444444078</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.323400936037491</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.832970027247847</v>
+      </c>
+      <c r="L31" t="n">
+        <v>14.5048227156996</v>
+      </c>
+      <c r="M31" t="n">
+        <v>85.96567808557072</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>14.17860570379382</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-26722.42094626218</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>40.47616992883206</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.000000000000008e-08</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.8202329282049027</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1448.391</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.8394552200830652</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1841.603902449623</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8611367612454475</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.2845e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-72.786</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.02760055478501769</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.9089694656488944</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.319334186939821</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.337323177366693</v>
+      </c>
+      <c r="L32" t="n">
+        <v>4.717625830787687</v>
+      </c>
+      <c r="M32" t="n">
+        <v>85.5172088672479</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>12.75518302956416</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-23727.63986318794</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>39.77230233348018</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.000000000004753e-08</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.8205133468811094</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1432.515</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.8302538434699552</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1825.7493111597</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.8537231304553988</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.28776e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-72.90900000000001</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.3793418647166591</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.425649350649342</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.9542828685259375</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.321040723981803</v>
+      </c>
+      <c r="L33" t="n">
+        <v>5.567578232998313</v>
+      </c>
+      <c r="M33" t="n">
+        <v>85.56542189687642</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>12.89442272168864</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-23785.29957196176</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>39.32903134096705</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.000000000003629e-08</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.8208002111185573</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1412.245</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.8185058021530154</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1807.745761651649</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8453046435627163</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.2912e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-73.08199999999999</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.08666779644603255</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.080168917990076</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.01014971772294</v>
+      </c>
+      <c r="K34" t="n">
+        <v>170.0653319377327</v>
+      </c>
+      <c r="L34" t="n">
+        <v>10.83969555292598</v>
+      </c>
+      <c r="M34" t="n">
+        <v>85.31747505331563</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>12.20883237135663</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-22260.50799699948</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>40.01013744742227</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.000000000000326e-08</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.8210845874163852</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1407.569</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.8157956965191718</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1794.452730024516</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8390888019328759</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.29467e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-73.259</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.3842712842713084</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.290158730158643</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.528615071282966</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2.242210682492571</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>85.38524211641437</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>12.38891233107171</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-22421.76430748341</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>39.01528645035341</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.8213822948186666</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1390.912</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.8061416696708115</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1777.07029992611</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8309607514125629</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.29705e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-73.426</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.027234042553295</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.465553602811938</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.289686684072999</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.77490542244616</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>85.24034746041217</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>12.0101038958284</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-21513.07805774334</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>39.54041482867422</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.8216872463320141</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1369.928</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.7939798098289433</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1761.077708490638</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.8234825915464018</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2.30137e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-73.56999999999999</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.21411040280697</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.9528213977307621</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.161891702725772</v>
+      </c>
+      <c r="K37" t="n">
+        <v>234.9250182913892</v>
+      </c>
+      <c r="L37" t="n">
+        <v>11.46800660480105</v>
+      </c>
+      <c r="M37" t="n">
+        <v>85.06827953940441</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>11.58910184507283</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-20537.69861342705</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>39.42275902157348</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.000000000005102e-08</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.8219848548655849</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1362.544</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.7897002076047558</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1745.001728498767</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.8159654390655495</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2.3027e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-73.717</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.05991820040898529</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.007889908256965</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.046840148698868</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1.801273344651929</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>85.19625531608348</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>11.89935556707356</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-20938.39357372569</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>40.00496390614296</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.000000000000003e-08</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.8222921132524216</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1345.587</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.7798723074265935</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1728.952427016954</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.8084607614962217</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.30766e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-73.904</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.06120996441281047</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.350961538461419</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.141958041958062</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2.245559400230678</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>84.56143802201298</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>10.50343798962148</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-18212.15246948718</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>40.21215069318691</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.421089080265279e-08</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.8148377086709585</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1331.909</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.7719448427431647</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1717.525155257987</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.8031173519936141</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2.3117e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-74.04000000000001</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.2368739386270691</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.8097902213669905</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2.287953337953273</v>
+      </c>
+      <c r="K40" t="n">
+        <v>281.5521706328904</v>
+      </c>
+      <c r="L40" t="n">
+        <v>12.28759359951612</v>
+      </c>
+      <c r="M40" t="n">
+        <v>84.47851608554285</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>10.34473803912889</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-17767.17453717029</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>37.61966330527116</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.000000000000246e-08</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.8229108495188741</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1316.11</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.7627880936180375</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1702.271224002862</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.7959845907414108</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2.3163e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-74.197</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.2904118554497644</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.8952887230360997</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2.303426508968609</v>
+      </c>
+      <c r="K41" t="n">
+        <v>142.7397743217941</v>
+      </c>
+      <c r="L41" t="n">
+        <v>12.79435262426438</v>
+      </c>
+      <c r="M41" t="n">
+        <v>84.09420207595871</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>9.667232401881646</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-16398.47873422297</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>37.42406297715081</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.8232226342904261</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1301.998</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.7546090921841621</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1690.322879212088</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7903975267035442</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2.31836e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-74.351</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.4227656391380519</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.191995461282282</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2.003856027382683</v>
+      </c>
+      <c r="K42" t="n">
+        <v>88.54771123134913</v>
+      </c>
+      <c r="L42" t="n">
+        <v>13.13137324208033</v>
+      </c>
+      <c r="M42" t="n">
+        <v>84.01084049015429</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>9.531712064456077</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-16013.67661334544</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>35.72913342963284</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.8235257258343727</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1289.785</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.7475307089279317</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1676.638676626878</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7839987729439657</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2.3223e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-74.499</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.1574391531351618</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1.136325712258059</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2.154501364622637</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>13.3394274310729</v>
+      </c>
+      <c r="M43" t="n">
+        <v>83.67584587017204</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>9.023010523109644</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-14976.13898527562</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>34.48419028497779</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.000000000000027e-08</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.823832716983225</v>
       </c>
     </row>
@@ -7898,7 +14282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8600,6 +14984,566 @@
         <v>1.000000000003242e-08</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.822262789375012</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1976.583</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2417.224710682251</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.21568e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-63.826</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.03717826501429401</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.9036512667661331</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.304858934169242</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.398347880299212</v>
+      </c>
+      <c r="L12" t="n">
+        <v>17.52773798041081</v>
+      </c>
+      <c r="M12" t="n">
+        <v>84.5764744127804</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>10.53273353379627</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-25213.20964593093</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-5.137212538410722</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.8203803972618613</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1669.171</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.844473012264094</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2052.429786017192</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.8490852244506066</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.28968e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-68.801</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.00114942528747</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.6365644171779661</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.211347517730546</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.979069767441867</v>
+      </c>
+      <c r="L13" t="n">
+        <v>27.86887657473744</v>
+      </c>
+      <c r="M13" t="n">
+        <v>86.17563969181897</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>14.95953847465796</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-31277.19949447679</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>36.81668602327727</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.00000000001412e-08</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8210765106441527</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1600.702</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.8098329288474099</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2035.482156771276</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.842074031336859</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.28597e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-70.30200000000001</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.5792358803986944</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.198348623853214</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.345126353790681</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.879833546735038</v>
+      </c>
+      <c r="L14" t="n">
+        <v>35.09740516751448</v>
+      </c>
+      <c r="M14" t="n">
+        <v>86.54124499778651</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>16.54530740975163</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-33442.27658870722</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>14.20875003525032</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.00000000000008e-08</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8211563763242047</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1563.355</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.7909381999136894</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2003.101468174898</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.8286782190016301</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.282e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-70.964</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.3695299837924907</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.7317617866004271</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.520353982300912</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.36239316239313</v>
+      </c>
+      <c r="L15" t="n">
+        <v>35.85785008889203</v>
+      </c>
+      <c r="M15" t="n">
+        <v>86.6233617917888</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>16.94864190427047</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-33669.09441678843</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>13.65524331835275</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.000000000000654e-08</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8211863162311187</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1532.769</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.775464020483835</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1980.814424952181</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.8194581232760545</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.28012e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-71.467</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.6836193447738098</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.718024263431579</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.299609374999871</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.596841230257761</v>
+      </c>
+      <c r="L16" t="n">
+        <v>29.36174383510147</v>
+      </c>
+      <c r="M16" t="n">
+        <v>86.46440893826606</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>16.18485725363871</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-31612.38967299644</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>11.1224823879985</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.8212713417327091</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1512.521</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.765220079298466</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1957.309173502929</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.8097340577618402</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.28215e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-71.85899999999999</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.7341463414634198</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.9037707390648045</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.778440366972658</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.20272058823532</v>
+      </c>
+      <c r="L17" t="n">
+        <v>30.23905992524642</v>
+      </c>
+      <c r="M17" t="n">
+        <v>86.55211011509773</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>16.59757227241609</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-32029.38294373039</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>9.665213583791797</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.000000000004567e-08</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.8213975431315231</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1474.567</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.7460182547355714</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1864.449496123376</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.771318234454563</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.28493e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-72.2</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.04825505694218435</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.7287996416597156</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.006861744505672</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.725666318463911</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>86.11491787455944</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>14.72502721987783</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-27888.57401359933</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>42.2155595922701</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.000000000000048e-08</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.8215651857466469</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1464.828</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.7410910647314076</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1913.863047136863</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.7917605006597354</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.28725e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-72.48699999999999</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.6702495201535517</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.5075872534143083</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.728731762065069</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.178120617110777</v>
+      </c>
+      <c r="L19" t="n">
+        <v>19.4337680401639</v>
+      </c>
+      <c r="M19" t="n">
+        <v>86.42202768193623</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>15.99265637160989</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-30042.78279684855</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>6.915292386621445</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.8217690172635903</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1431.029</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.7239913527537168</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1895.343817673055</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.7840991403476522</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.29008e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-72.72199999999999</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.1961976532433493</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.7466548932889133</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.104446850700857</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.662353940939166</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>86.05687071797711</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>14.50758793014598</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-26793.56365285002</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>4.199046951273431</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.000000000000012e-08</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.8220058724131702</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1415.186</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.7159760050551887</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1877.357275337488</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.7766581514085266</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.29427e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-73.03100000000001</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.1088129496402817</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.6109788359787877</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.662652439024532</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.515861214374207</v>
+      </c>
+      <c r="L21" t="n">
+        <v>13.48776047587132</v>
+      </c>
+      <c r="M21" t="n">
+        <v>85.98428394516897</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>14.24451601456959</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-25988.77844201832</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.227991598565382</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.000000000003242e-08</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.822262789375012</v>
       </c>
     </row>
@@ -8614,7 +15558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9932,6 +16876,1182 @@
         <v>1.000000000000105e-08</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.825137287977138</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1707.309</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2117.543731024332</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.27208e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-68.58199999999999</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.3268547544409184</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.3639620653319273</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.135317460317502</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1.999566294919434</v>
+      </c>
+      <c r="L23" t="n">
+        <v>28.58171116857689</v>
+      </c>
+      <c r="M23" t="n">
+        <v>86.16137949357943</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>14.90379915294437</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-31824.08555246776</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>23.59062019027147</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.000000000000672e-08</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8204761022178662</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1602.314</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.9385026377767587</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2038.025631278527</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9624479539285172</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.27506e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-70.69199999999999</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.010450819672298</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.36998556998567</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.023262548262392</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.37401614530768</v>
+      </c>
+      <c r="L24" t="n">
+        <v>45.61712262839713</v>
+      </c>
+      <c r="M24" t="n">
+        <v>86.79263340993062</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>17.8451439499894</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-36113.65276631213</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>11.91301762886599</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.000000000000465e-08</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8206982435186609</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1557.452</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.9122261992410279</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2002.624507050117</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9457299406427726</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.27772e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-71.28700000000001</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.3337711069418418</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.8616384915474086</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.456127703398524</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.735040431266991</v>
+      </c>
+      <c r="L25" t="n">
+        <v>32.91758066093285</v>
+      </c>
+      <c r="M25" t="n">
+        <v>86.54811692382954</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>16.57832548785629</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-32806.27562153985</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>12.21108025750596</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.000000000006328e-08</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8206928436905053</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1531.421</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.8969793985740133</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1982.409852563968</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9361836657819599</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.28344e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-71.64</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.5822335025379765</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.3393034825870915</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.083526011560681</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1.682924693520053</v>
+      </c>
+      <c r="L26" t="n">
+        <v>24.54508164125475</v>
+      </c>
+      <c r="M26" t="n">
+        <v>86.23674973217966</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>15.20317817144176</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-29618.19054009091</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>10.46711242255412</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.000000000001511e-08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8207304499822511</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1510.483</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.8847156548697395</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1965.008713500955</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9279660602571874</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.28373e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-71.904</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.3136904761904776</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.8953033268100781</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.26761658031052</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.034717314487501</v>
+      </c>
+      <c r="L27" t="n">
+        <v>23.60173868367039</v>
+      </c>
+      <c r="M27" t="n">
+        <v>86.24736211313162</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>15.24629616551704</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-29391.40258984867</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>8.683463124071181</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8208330205522311</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1491.157</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.8733960870586402</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1945.995458373217</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.9189871405545276</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.28826e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-72.15600000000001</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.04291044776119547</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.2950581395348822</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.8731196054253997</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1.806311111111066</v>
+      </c>
+      <c r="L28" t="n">
+        <v>19.59912046677297</v>
+      </c>
+      <c r="M28" t="n">
+        <v>86.11350596708473</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>14.71966139354527</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-28051.95150293668</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>8.152636404853297</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.000000000043812e-08</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8209980295427457</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1470.39</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.8612325009708259</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1929.568269150623</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.9112294782300533</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.29134e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-72.348</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.3281818181817898</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.816512059369262</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.297667185069858</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.330802603036872</v>
+      </c>
+      <c r="L29" t="n">
+        <v>18.64732543072838</v>
+      </c>
+      <c r="M29" t="n">
+        <v>86.07504764752811</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>14.57498644759217</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-27492.4371183081</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>6.782613958993466</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8211956966675322</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1454.956</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.8521925439390291</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1913.957562836629</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.9038573960929622</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.29688e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-72.587</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.178793774319074</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.6773684210526116</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2.001771653543291</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.098723792160551</v>
+      </c>
+      <c r="L30" t="n">
+        <v>11.7583777222668</v>
+      </c>
+      <c r="M30" t="n">
+        <v>85.79693583129814</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>13.60744570377883</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-25366.28310645062</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>5.350019541613847</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.000000000005795e-08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.8214275415280712</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1433.046</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.8393594832569852</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1898.124327260887</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8963802255657292</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.299e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-72.749</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.03059747805387442</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.8862654114972607</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.168101995779776</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.881818023094851</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>85.73588205690906</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>13.41190804852343</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-24737.56724248871</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>4.680114738742986</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.000000000000114e-08</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.8216658026258539</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1423.702</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.8338865430920823</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1883.045241374129</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8892591986580753</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.306e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-72.967</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.151244813278019</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.8328335832083608</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.831975867269925</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.216684961580693</v>
+      </c>
+      <c r="L32" t="n">
+        <v>3.923065558429141</v>
+      </c>
+      <c r="M32" t="n">
+        <v>85.48070060833098</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>12.65171940152116</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-23091.47112830595</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>3.490526713461122</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.000000000000349e-08</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.8219279195950848</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1413.549</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.8279397578294263</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1867.881231647006</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.8820980668689399</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.30583e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-73.09099999999999</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1.684496124031096</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.8995283018868317</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.265756097560942</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.158956276445599</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>85.81920739517349</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>13.68019415199602</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-24835.84474048759</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>3.11127427055817</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.00000000000047e-08</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.8221969564938763</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1393.484</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.8161873451144461</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1774.685693306221</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8380869151862764</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.30816e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-73.26600000000001</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.1842735042735007</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.152362204724511</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.9858313817329802</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.084994640943294</v>
+      </c>
+      <c r="L34" t="n">
+        <v>4.612823787080787</v>
+      </c>
+      <c r="M34" t="n">
+        <v>85.62399170057979</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>13.0676921238932</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-23470.11550650002</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>40.80646111768738</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.000000000005907e-08</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.8224741148930019</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1379.736</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.8081349070379177</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1839.960771103148</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8689127615858457</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.31275e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-73.401</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.2252941176470674</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.097491638796096</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.846596858638824</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1.909555984556186</v>
+      </c>
+      <c r="L35" t="n">
+        <v>2.754370899840299</v>
+      </c>
+      <c r="M35" t="n">
+        <v>85.55071496161554</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>12.85162974153452</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-22874.38725960436</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.710259781083892</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.000000000000386e-08</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.8227540448103694</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1360.813</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.7970513832001119</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1747.85368440823</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8254156260389153</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.31459e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-73.57599999999999</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.303173811325937</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.7327051583199683</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.53760208464232</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.833069515023729</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>85.14591459323887</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>11.77536653826197</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-20697.7849186613</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>39.25859359460605</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.00000000000012e-08</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.8230354745270387</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1356.489</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.7945187426529117</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1733.447727334346</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.8186124810257471</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2.31756e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-73.727</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.1888888888888683</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.8676007005253411</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.319271948608185</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.096476964769652</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>85.20306171179796</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>11.91631893868786</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-20792.96495376527</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>38.8470885505817</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.000000000001246e-08</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.8233366675585391</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1339.859</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.7847782680229531</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1721.683318361871</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.8130567945952314</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2.32158e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-73.876</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1.086604361370562</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.6737421383647707</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.201222222222253</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2.373281596452195</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>85.0082594806691</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>11.44906108399377</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-19771.9837905243</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>37.35352832265767</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.000000000000738e-08</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.8236274810406217</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1327.183</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.7773537186297267</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1705.886001705738</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.8055965866077013</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.32559e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-73.995</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.422398723147652</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2.239309165363264</v>
+      </c>
+      <c r="K39" t="n">
+        <v>220.5790203217626</v>
+      </c>
+      <c r="L39" t="n">
+        <v>11.88215658211635</v>
+      </c>
+      <c r="M39" t="n">
+        <v>84.95622239657972</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>11.33033717120812</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-19394.36958960264</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>37.654607665404</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.464092348456783e-08</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.8143536509127001</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1317.642</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.771765392204926</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1696.220314937365</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.8010320118002202</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2.32865e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-74.193</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.7847533632288599</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.6963358778626619</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.605189340813335</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2.53189655172417</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>84.37381452768477</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>10.15101724148481</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-17141.6828876498</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>35.16089394839446</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.000000000000009e-08</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.8242196422748366</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1302.174</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.7627055207932483</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1681.598587320977</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.7941269701700693</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2.3326e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-74.32899999999999</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.2832935560859366</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.7404326123127918</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.631699846860639</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2.36012658227846</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>84.05341940455079</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>9.600459284815479</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-16025.17259570055</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>34.89157736232596</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.000000000001419e-08</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.8245234996489053</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1282.304</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.7510673229040554</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1670.886161154721</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7890680776384502</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2.33434e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-74.482</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.365206615101939</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.7872225741210328</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2.225948247459714</v>
+      </c>
+      <c r="K42" t="n">
+        <v>101.6304037336233</v>
+      </c>
+      <c r="L42" t="n">
+        <v>12.64917044087986</v>
+      </c>
+      <c r="M42" t="n">
+        <v>83.89363160979561</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>9.347402608555718</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-15454.23373669312</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>32.68594342794518</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.000000000000485e-08</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.8248405806765271</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1271.53</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.7447568073500462</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1659.499381632835</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7836907249278271</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2.33696e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-74.619</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.1865732385879416</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.9332594066054982</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2.111439809826614</v>
+      </c>
+      <c r="K43" t="n">
+        <v>36.49932329440752</v>
+      </c>
+      <c r="L43" t="n">
+        <v>12.64331534003451</v>
+      </c>
+      <c r="M43" t="n">
+        <v>83.86981723841019</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>9.310813091120549</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-15254.3744343405</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>31.1503220451666</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.000000000000105e-08</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.825137287977138</v>
       </c>
     </row>
@@ -9946,7 +18066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10651,6 +18771,566 @@
         <v>0.8232909354589683</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1363.689</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1837.4807557511</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.41289e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-69.84699999999999</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.652969502407674</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.9714918759231738</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.823969631236549</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.324081920903947</v>
+      </c>
+      <c r="L12" t="n">
+        <v>22.82423733684878</v>
+      </c>
+      <c r="M12" t="n">
+        <v>86.06649056588259</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>14.54318003780779</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-26607.76010804871</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-13.0456815097225</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.000000000025406e-08</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.8208152587456541</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1179.436</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.8648863487202728</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1730.793201590899</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.9419381379498635</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.40085e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-73.486</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.06595552634264876</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.6095211640488656</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.38003883746137</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.621239424175997</v>
+      </c>
+      <c r="L13" t="n">
+        <v>50.85254216498522</v>
+      </c>
+      <c r="M13" t="n">
+        <v>86.76546241648256</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>17.69492494451351</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-28977.90291191796</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-40.58806300857623</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.000000000000006e-08</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8213138079844127</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1137.492</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.8341286026359381</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1690.415924204038</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.9199638793022642</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.38173e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-74.542</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.5132828438434337</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.8908917102314814</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.187218099859213</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.203137382955591</v>
+      </c>
+      <c r="L14" t="n">
+        <v>85.39575238121419</v>
+      </c>
+      <c r="M14" t="n">
+        <v>86.96343756573788</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>18.85096281736867</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-30029.17494132651</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-43.11276151562515</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8214426527690188</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1110.765</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.8145295591590164</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1655.30591035736</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.9008561886574571</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.3722e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-75.048</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.6363350520922247</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.8934421014780461</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.023616360547382</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.470953803303345</v>
+      </c>
+      <c r="L15" t="n">
+        <v>53.99923398529888</v>
+      </c>
+      <c r="M15" t="n">
+        <v>86.90504759300956</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>18.49464364817777</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-28940.05921438317</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-38.39258863794089</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.000000000139312e-08</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8215546323192502</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1088.304</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.7980587949305157</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1647.383187181073</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.8965444574181013</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.36688e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-75.452</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.5206253863312862</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.090066845998116</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.098067154008203</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.38313973714139</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>86.7663765867857</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>17.69993807928302</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-27231.77261128127</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-48.88472453674751</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.8217464343880716</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1062.168</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.7788931347249994</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1633.877810122782</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.8891945153759759</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.36447e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-75.76900000000001</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.3189518553430451</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.133811248587095</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.10164667200612</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.65644972942968</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>86.62685619091015</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>16.96624050265522</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-25668.73843584974</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-55.41715929879774</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.8219930186703909</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1035.495</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.7593336897195767</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1554.53867447796</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.8460163022727915</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.36518e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-76.04900000000001</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.2281633311814284</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.7282481621591466</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.153065842138447</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.769971558902065</v>
+      </c>
+      <c r="L18" t="n">
+        <v>11.11147487416984</v>
+      </c>
+      <c r="M18" t="n">
+        <v>86.30373212081655</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>15.47947138083346</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-22966.88120499742</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-24.46183875037775</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.000000000000003e-08</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.8222803212474934</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1021.711</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.7492258132169431</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1468.775614362724</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.7993420392380319</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.36683e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-76.327</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.5797690245411441</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.362247955967011</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.576389246777412</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.870754713704029</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>86.36723549598375</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>15.75080959971839</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-23053.0418001188</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>11.44807609923487</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.8226145878480111</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>989.984</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.725960244601225</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1557.592829759313</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.8476784450036984</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.36865e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-76.54000000000001</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.1421666842083509</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.8353907198479037</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.646223373422676</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.379534458877418</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>85.86676725399651</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>13.83816496641358</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-19835.01773981188</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-53.60153549473785</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.000000000025642e-08</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.8229475306037469</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>982.1680000000001</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.7202287325042587</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1490.17972035264</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.8109906542904199</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.37054e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-76.782</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.199133148405159</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.511615056773624</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.428066822575181</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.70935048165387</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>85.99200204422762</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>14.27203626382984</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-20223.12058336674</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-26.7019262059315</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.000000000005047e-08</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.8232909354589683</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
